--- a/PIT4/Schema Publication Changelog.xlsx
+++ b/PIT4/Schema Publication Changelog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ctrowell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D0422A-8779-4DA4-801D-853D61E5D42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5ECF376-AEBE-4C24-AA26-A05E95CBCE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19110" windowHeight="10430" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="v0.10" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="O'Brien, Ciaran - Personal View" guid="{3ECA9ADB-6C26-4D30-9FA0-625C82AEEE29}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1276" windowHeight="751" activeSheetId="2"/>
+    <customWorkbookView name="Arnold, Eve - Personal View" guid="{057DBB0B-BBF6-4A94-8406-46C99A7DC1D6}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1276" windowHeight="758" activeSheetId="2"/>
     <customWorkbookView name="Walsh, David P - Personal View" guid="{99CEABDF-88F7-4121-AD5F-66FD045725EC}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1436" windowHeight="675" activeSheetId="2"/>
-    <customWorkbookView name="Arnold, Eve - Personal View" guid="{057DBB0B-BBF6-4A94-8406-46C99A7DC1D6}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1276" windowHeight="758" activeSheetId="2"/>
-    <customWorkbookView name="O'Brien, Ciaran - Personal View" guid="{3ECA9ADB-6C26-4D30-9FA0-625C82AEEE29}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1276" windowHeight="751" activeSheetId="2"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="726">
   <si>
     <t>Document</t>
   </si>
@@ -4066,6 +4066,15 @@
   </si>
   <si>
     <t>PAYE Modernisation - RPN Data Items</t>
+  </si>
+  <si>
+    <t>Payroll Employer Submission - Employee Level Validation</t>
+  </si>
+  <si>
+    <t>PRSI Class and Subclass</t>
+  </si>
+  <si>
+    <t>Warning added on PRSI Class and Subclass</t>
   </si>
 </sst>
 </file>
@@ -4695,7 +4704,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5068,6 +5077,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -5110,38 +5125,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5164,6 +5149,66 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5185,36 +5230,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5233,15 +5248,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5250,33 +5256,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5299,8 +5278,44 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5640,15 +5655,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="48.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5662,15 +5677,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="140" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="142"/>
-    </row>
-    <row r="3" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="144"/>
+    </row>
+    <row r="3" spans="1:4" ht="26" x14ac:dyDescent="0.35">
       <c r="A3" s="29" t="s">
         <v>5</v>
       </c>
@@ -5684,15 +5699,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="140" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="142" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="142"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="144"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="27" t="s">
         <v>9</v>
       </c>
@@ -5706,7 +5721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
         <v>12</v>
       </c>
@@ -5720,11 +5735,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="143" t="s">
+    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A7" s="145" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="146">
+      <c r="B7" s="148">
         <v>0.1</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -5734,9 +5749,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="144"/>
-      <c r="B8" s="147"/>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="146"/>
+      <c r="B8" s="149"/>
       <c r="C8" s="10" t="s">
         <v>16</v>
       </c>
@@ -5744,9 +5759,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
-      <c r="B9" s="147"/>
+    <row r="9" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A9" s="146"/>
+      <c r="B9" s="149"/>
       <c r="C9" s="10" t="s">
         <v>18</v>
       </c>
@@ -5754,9 +5769,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="144"/>
-      <c r="B10" s="147"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="146"/>
+      <c r="B10" s="149"/>
       <c r="C10" s="10" t="s">
         <v>20</v>
       </c>
@@ -5764,9 +5779,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="144"/>
-      <c r="B11" s="147"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="146"/>
+      <c r="B11" s="149"/>
       <c r="C11" s="10" t="s">
         <v>22</v>
       </c>
@@ -5774,9 +5789,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="145"/>
-      <c r="B12" s="148"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="147"/>
+      <c r="B12" s="150"/>
       <c r="C12" s="10" t="s">
         <v>24</v>
       </c>
@@ -5784,11 +5799,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="151" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="153" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="146">
+      <c r="B13" s="148">
         <v>0.1</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -5798,9 +5813,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="152"/>
-      <c r="B14" s="148"/>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="154"/>
+      <c r="B14" s="150"/>
       <c r="C14" s="10" t="s">
         <v>29</v>
       </c>
@@ -5808,7 +5823,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
         <v>31</v>
       </c>
@@ -5822,7 +5837,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="33" t="s">
         <v>33</v>
       </c>
@@ -5836,15 +5851,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="140" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="142" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="141"/>
-      <c r="C17" s="141"/>
-      <c r="D17" s="142"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="143"/>
+      <c r="C17" s="143"/>
+      <c r="D17" s="144"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>35</v>
       </c>
@@ -5858,7 +5873,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>36</v>
       </c>
@@ -5872,19 +5887,19 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="140" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="142" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="141"/>
-      <c r="C20" s="141"/>
-      <c r="D20" s="142"/>
-    </row>
-    <row r="21" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="153" t="s">
+      <c r="B20" s="143"/>
+      <c r="C20" s="143"/>
+      <c r="D20" s="144"/>
+    </row>
+    <row r="21" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A21" s="155" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="150">
+      <c r="B21" s="152">
         <v>0.1</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -5894,9 +5909,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="152"/>
-      <c r="B22" s="148"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="154"/>
+      <c r="B22" s="150"/>
       <c r="C22" s="26" t="s">
         <v>41</v>
       </c>
@@ -5904,7 +5919,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>43</v>
       </c>
@@ -5918,19 +5933,19 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="140" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="142" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="141"/>
-      <c r="C24" s="141"/>
-      <c r="D24" s="142"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="149" t="s">
+      <c r="B24" s="143"/>
+      <c r="C24" s="143"/>
+      <c r="D24" s="144"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="151" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="150">
+      <c r="B25" s="152">
         <v>0.1</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -5940,9 +5955,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="144"/>
-      <c r="B26" s="147"/>
+    <row r="26" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A26" s="146"/>
+      <c r="B26" s="149"/>
       <c r="C26" s="10" t="s">
         <v>48</v>
       </c>
@@ -5950,9 +5965,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="144"/>
-      <c r="B27" s="147"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="146"/>
+      <c r="B27" s="149"/>
       <c r="C27" s="10" t="s">
         <v>50</v>
       </c>
@@ -5960,9 +5975,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="144"/>
-      <c r="B28" s="147"/>
+    <row r="28" spans="1:4" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="146"/>
+      <c r="B28" s="149"/>
       <c r="C28" s="20" t="s">
         <v>52</v>
       </c>
@@ -5970,9 +5985,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="144"/>
-      <c r="B29" s="147"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="146"/>
+      <c r="B29" s="149"/>
       <c r="C29" s="10" t="s">
         <v>54</v>
       </c>
@@ -5980,9 +5995,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="144"/>
-      <c r="B30" s="147"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="146"/>
+      <c r="B30" s="149"/>
       <c r="C30" s="10" t="s">
         <v>56</v>
       </c>
@@ -5990,9 +6005,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="144"/>
-      <c r="B31" s="147"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="146"/>
+      <c r="B31" s="149"/>
       <c r="C31" s="10" t="s">
         <v>58</v>
       </c>
@@ -6000,9 +6015,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="145"/>
-      <c r="B32" s="148"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="147"/>
+      <c r="B32" s="150"/>
       <c r="C32" s="10" t="s">
         <v>60</v>
       </c>
@@ -6010,7 +6025,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>62</v>
       </c>
@@ -6024,7 +6039,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
         <v>64</v>
       </c>
@@ -6038,7 +6053,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>65</v>
       </c>
@@ -6052,7 +6067,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>66</v>
       </c>
@@ -6066,7 +6081,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>67</v>
       </c>
@@ -6080,7 +6095,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>68</v>
       </c>
@@ -6094,7 +6109,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="22" t="s">
         <v>69</v>
       </c>
@@ -6108,7 +6123,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="24" t="s">
         <v>71</v>
       </c>
@@ -6122,15 +6137,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="140" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="142" t="s">
         <v>72</v>
       </c>
-      <c r="B41" s="141"/>
-      <c r="C41" s="141"/>
-      <c r="D41" s="142"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="143"/>
+      <c r="C41" s="143"/>
+      <c r="D41" s="144"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>73</v>
       </c>
@@ -6144,7 +6159,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
         <v>74</v>
       </c>
@@ -6158,7 +6173,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>75</v>
       </c>
@@ -6172,7 +6187,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="12" t="s">
         <v>76</v>
       </c>
@@ -6188,7 +6203,7 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{99CEABDF-88F7-4121-AD5F-66FD045725EC}" topLeftCell="B1">
+    <customSheetView guid="{3ECA9ADB-6C26-4D30-9FA0-625C82AEEE29}" topLeftCell="B1">
       <selection activeCell="C15" sqref="C15:D15"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6198,7 +6213,7 @@
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
     </customSheetView>
-    <customSheetView guid="{3ECA9ADB-6C26-4D30-9FA0-625C82AEEE29}" topLeftCell="B1">
+    <customSheetView guid="{99CEABDF-88F7-4121-AD5F-66FD045725EC}" topLeftCell="B1">
       <selection activeCell="C15" sqref="C15:D15"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
@@ -6228,15 +6243,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:XFC79"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="51.28515625" style="38" customWidth="1"/>
+    <col min="1" max="1" width="31.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" customWidth="1"/>
+    <col min="4" max="4" width="51.26953125" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -6250,7 +6265,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
         <v>77</v>
       </c>
@@ -6258,7 +6273,7 @@
       <c r="C2" s="35"/>
       <c r="D2" s="40"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="44" t="s">
         <v>78</v>
       </c>
@@ -6270,7 +6285,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="44" t="s">
         <v>79</v>
       </c>
@@ -6282,7 +6297,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="44" t="s">
         <v>80</v>
       </c>
@@ -6294,7 +6309,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>8</v>
       </c>
@@ -6302,11 +6317,11 @@
       <c r="C6" s="35"/>
       <c r="D6" s="40"/>
     </row>
-    <row r="7" spans="1:4" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154" t="s">
+    <row r="7" spans="1:4" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="171" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="170" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="39" t="s">
@@ -6316,9 +6331,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="154"/>
-      <c r="B8" s="155"/>
+    <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A8" s="171"/>
+      <c r="B8" s="170"/>
       <c r="C8" s="34" t="s">
         <v>84</v>
       </c>
@@ -6326,9 +6341,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="154"/>
-      <c r="B9" s="155"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="171"/>
+      <c r="B9" s="170"/>
       <c r="C9" s="34" t="s">
         <v>86</v>
       </c>
@@ -6336,9 +6351,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="154"/>
-      <c r="B10" s="155"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="171"/>
+      <c r="B10" s="170"/>
       <c r="C10" s="34" t="s">
         <v>18</v>
       </c>
@@ -6346,9 +6361,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="154"/>
-      <c r="B11" s="155"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="171"/>
+      <c r="B11" s="170"/>
       <c r="C11" s="34" t="s">
         <v>89</v>
       </c>
@@ -6356,9 +6371,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="154"/>
-      <c r="B12" s="155"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="171"/>
+      <c r="B12" s="170"/>
       <c r="C12" s="34" t="s">
         <v>91</v>
       </c>
@@ -6366,11 +6381,11 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="157" t="s">
+    <row r="13" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="173" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="155" t="s">
+      <c r="B13" s="170" t="s">
         <v>81</v>
       </c>
       <c r="C13" s="34" t="s">
@@ -6380,9 +6395,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="157"/>
-      <c r="B14" s="155"/>
+    <row r="14" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="173"/>
+      <c r="B14" s="170"/>
       <c r="C14" s="34" t="s">
         <v>96</v>
       </c>
@@ -6390,9 +6405,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="157"/>
-      <c r="B15" s="155"/>
+    <row r="15" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="173"/>
+      <c r="B15" s="170"/>
       <c r="C15" s="39" t="s">
         <v>98</v>
       </c>
@@ -6400,11 +6415,11 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="158" t="s">
+    <row r="16" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="159" t="s">
+      <c r="B16" s="165" t="s">
         <v>81</v>
       </c>
       <c r="C16" s="54" t="s">
@@ -6414,9 +6429,9 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="158"/>
-      <c r="B17" s="159"/>
+    <row r="17" spans="1:4" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="156"/>
+      <c r="B17" s="165"/>
       <c r="C17" s="53" t="s">
         <v>102</v>
       </c>
@@ -6424,9 +6439,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="158"/>
-      <c r="B18" s="159"/>
+    <row r="18" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="156"/>
+      <c r="B18" s="165"/>
       <c r="C18" s="53" t="s">
         <v>89</v>
       </c>
@@ -6434,9 +6449,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="158"/>
-      <c r="B19" s="159"/>
+    <row r="19" spans="1:4" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="156"/>
+      <c r="B19" s="165"/>
       <c r="C19" s="53" t="s">
         <v>105</v>
       </c>
@@ -6444,9 +6459,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="158"/>
-      <c r="B20" s="159"/>
+    <row r="20" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="156"/>
+      <c r="B20" s="165"/>
       <c r="C20" s="53" t="s">
         <v>107</v>
       </c>
@@ -6454,9 +6469,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="158"/>
-      <c r="B21" s="159"/>
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="156"/>
+      <c r="B21" s="165"/>
       <c r="C21" s="53" t="s">
         <v>109</v>
       </c>
@@ -6464,9 +6479,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="158"/>
-      <c r="B22" s="159"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="156"/>
+      <c r="B22" s="165"/>
       <c r="C22" s="53" t="s">
         <v>111</v>
       </c>
@@ -6474,9 +6489,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="158"/>
-      <c r="B23" s="159"/>
+    <row r="23" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="156"/>
+      <c r="B23" s="165"/>
       <c r="C23" s="61" t="s">
         <v>113</v>
       </c>
@@ -6484,27 +6499,27 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="158"/>
-      <c r="B24" s="159"/>
-      <c r="C24" s="158" t="s">
+    <row r="24" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="156"/>
+      <c r="B24" s="165"/>
+      <c r="C24" s="156" t="s">
         <v>115</v>
       </c>
-      <c r="D24" s="165" t="s">
+      <c r="D24" s="157" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="158"/>
-      <c r="B25" s="159"/>
-      <c r="C25" s="158"/>
-      <c r="D25" s="165"/>
-    </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="154" t="s">
+    <row r="25" spans="1:4" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="156"/>
+      <c r="B25" s="165"/>
+      <c r="C25" s="156"/>
+      <c r="D25" s="157"/>
+    </row>
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="171" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="155" t="s">
+      <c r="B26" s="170" t="s">
         <v>81</v>
       </c>
       <c r="C26" s="34" t="s">
@@ -6514,15 +6529,15 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="154"/>
-      <c r="B27" s="155"/>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="171"/>
+      <c r="B27" s="170"/>
       <c r="C27" s="34"/>
       <c r="D27" s="37" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="44" t="s">
         <v>121</v>
       </c>
@@ -6534,7 +6549,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="26" x14ac:dyDescent="0.35">
       <c r="A29" s="35" t="s">
         <v>34</v>
       </c>
@@ -6542,29 +6557,29 @@
       <c r="C29" s="35"/>
       <c r="D29" s="35"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="156" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="172" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="155" t="s">
+      <c r="B30" s="170" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="158" t="s">
+      <c r="C30" s="156" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="168" t="s">
+      <c r="D30" s="160" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="156"/>
-      <c r="B31" s="155"/>
-      <c r="C31" s="158"/>
-      <c r="D31" s="168"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="156"/>
-      <c r="B32" s="155"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="172"/>
+      <c r="B31" s="170"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="160"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="172"/>
+      <c r="B32" s="170"/>
       <c r="C32" s="53" t="s">
         <v>125</v>
       </c>
@@ -6572,9 +6587,9 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="156"/>
-      <c r="B33" s="155"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="172"/>
+      <c r="B33" s="170"/>
       <c r="C33" s="53" t="s">
         <v>127</v>
       </c>
@@ -6582,9 +6597,9 @@
         <v>128</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="156"/>
-      <c r="B34" s="155"/>
+    <row r="34" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="172"/>
+      <c r="B34" s="170"/>
       <c r="C34" s="62" t="s">
         <v>129</v>
       </c>
@@ -6592,9 +6607,9 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="156"/>
-      <c r="B35" s="155"/>
+    <row r="35" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="172"/>
+      <c r="B35" s="170"/>
       <c r="C35" s="53" t="s">
         <v>111</v>
       </c>
@@ -6602,9 +6617,9 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="156"/>
-      <c r="B36" s="155"/>
+    <row r="36" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="172"/>
+      <c r="B36" s="170"/>
       <c r="C36" s="62" t="s">
         <v>113</v>
       </c>
@@ -6612,27 +6627,27 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="156"/>
-      <c r="B37" s="155"/>
-      <c r="C37" s="169" t="s">
+    <row r="37" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="172"/>
+      <c r="B37" s="170"/>
+      <c r="C37" s="161" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="171" t="s">
+      <c r="D37" s="163" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="156"/>
-      <c r="B38" s="155"/>
-      <c r="C38" s="170"/>
-      <c r="D38" s="171"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="154" t="s">
+    <row r="38" spans="1:4" ht="6.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="172"/>
+      <c r="B38" s="170"/>
+      <c r="C38" s="162"/>
+      <c r="D38" s="163"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="171" t="s">
         <v>134</v>
       </c>
-      <c r="B39" s="155" t="s">
+      <c r="B39" s="170" t="s">
         <v>81</v>
       </c>
       <c r="C39" s="34" t="s">
@@ -6642,15 +6657,15 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="154"/>
-      <c r="B40" s="155"/>
+    <row r="40" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="171"/>
+      <c r="B40" s="170"/>
       <c r="C40" s="34"/>
       <c r="D40" s="45" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="44" t="s">
         <v>36</v>
       </c>
@@ -6662,7 +6677,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="35" t="s">
         <v>37</v>
       </c>
@@ -6670,11 +6685,11 @@
       <c r="C42" s="35"/>
       <c r="D42" s="40"/>
     </row>
-    <row r="43" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="156" t="s">
+    <row r="43" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="172" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="155" t="s">
+      <c r="B43" s="170" t="s">
         <v>81</v>
       </c>
       <c r="C43" s="34"/>
@@ -6682,9 +6697,9 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="156"/>
-      <c r="B44" s="155"/>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="172"/>
+      <c r="B44" s="170"/>
       <c r="C44" s="34" t="s">
         <v>118</v>
       </c>
@@ -6692,11 +6707,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="162" t="s">
+    <row r="45" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="167" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="155" t="s">
+      <c r="B45" s="170" t="s">
         <v>81</v>
       </c>
       <c r="C45" s="34"/>
@@ -6704,9 +6719,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="163"/>
-      <c r="B46" s="155"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="168"/>
+      <c r="B46" s="170"/>
       <c r="C46" s="34" t="s">
         <v>141</v>
       </c>
@@ -6714,9 +6729,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="163"/>
-      <c r="B47" s="155"/>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="168"/>
+      <c r="B47" s="170"/>
       <c r="C47" s="34" t="s">
         <v>143</v>
       </c>
@@ -6724,9 +6739,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="164"/>
-      <c r="B48" s="155"/>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="169"/>
+      <c r="B48" s="170"/>
       <c r="C48" s="34" t="s">
         <v>118</v>
       </c>
@@ -6734,11 +6749,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A49" s="159" t="s">
+    <row r="49" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A49" s="165" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="159" t="s">
+      <c r="B49" s="165" t="s">
         <v>81</v>
       </c>
       <c r="C49" s="53"/>
@@ -10841,9 +10856,9 @@
       <c r="XEY49" s="38"/>
       <c r="XFC49" s="38"/>
     </row>
-    <row r="50" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="159"/>
-      <c r="B50" s="159"/>
+    <row r="50" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="165"/>
+      <c r="B50" s="165"/>
       <c r="C50" s="54" t="s">
         <v>146</v>
       </c>
@@ -14946,9 +14961,9 @@
       <c r="XEY50" s="38"/>
       <c r="XFC50" s="38"/>
     </row>
-    <row r="51" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A51" s="159"/>
-      <c r="B51" s="159"/>
+    <row r="51" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A51" s="165"/>
+      <c r="B51" s="165"/>
       <c r="C51" s="34" t="s">
         <v>148</v>
       </c>
@@ -19051,9 +19066,9 @@
       <c r="XEY51" s="38"/>
       <c r="XFC51" s="38"/>
     </row>
-    <row r="52" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A52" s="159"/>
-      <c r="B52" s="159"/>
+    <row r="52" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A52" s="165"/>
+      <c r="B52" s="165"/>
       <c r="C52" s="53" t="s">
         <v>150</v>
       </c>
@@ -23156,13 +23171,13 @@
       <c r="XEY52" s="38"/>
       <c r="XFC52" s="38"/>
     </row>
-    <row r="53" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A53" s="159"/>
-      <c r="B53" s="159"/>
-      <c r="C53" s="167" t="s">
+    <row r="53" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A53" s="165"/>
+      <c r="B53" s="165"/>
+      <c r="C53" s="159" t="s">
         <v>152</v>
       </c>
-      <c r="D53" s="168" t="s">
+      <c r="D53" s="160" t="s">
         <v>153</v>
       </c>
       <c r="G53" s="38"/>
@@ -27261,11 +27276,11 @@
       <c r="XEY53" s="38"/>
       <c r="XFC53" s="38"/>
     </row>
-    <row r="54" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="159"/>
-      <c r="B54" s="159"/>
-      <c r="C54" s="167"/>
-      <c r="D54" s="168"/>
+    <row r="54" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="13.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="165"/>
+      <c r="B54" s="165"/>
+      <c r="C54" s="159"/>
+      <c r="D54" s="160"/>
       <c r="G54" s="38"/>
       <c r="K54" s="38"/>
       <c r="O54" s="38"/>
@@ -31362,7 +31377,7 @@
       <c r="XEY54" s="38"/>
       <c r="XFC54" s="38"/>
     </row>
-    <row r="55" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
       <c r="A55" s="35" t="s">
         <v>44</v>
       </c>
@@ -31370,7 +31385,7 @@
       <c r="C55" s="35"/>
       <c r="D55" s="40"/>
     </row>
-    <row r="56" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="26" x14ac:dyDescent="0.35">
       <c r="A56" s="44" t="s">
         <v>154</v>
       </c>
@@ -31382,11 +31397,11 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A57" s="160" t="s">
+    <row r="57" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A57" s="164" t="s">
         <v>156</v>
       </c>
-      <c r="B57" s="159" t="s">
+      <c r="B57" s="165" t="s">
         <v>81</v>
       </c>
       <c r="C57" s="53" t="s">
@@ -31396,9 +31411,9 @@
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="160"/>
-      <c r="B58" s="159"/>
+    <row r="58" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="164"/>
+      <c r="B58" s="165"/>
       <c r="C58" s="56" t="s">
         <v>159</v>
       </c>
@@ -31406,9 +31421,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="59" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A59" s="160"/>
-      <c r="B59" s="159"/>
+    <row r="59" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A59" s="164"/>
+      <c r="B59" s="165"/>
       <c r="C59" s="53" t="s">
         <v>161</v>
       </c>
@@ -31416,9 +31431,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="60" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="160"/>
-      <c r="B60" s="159"/>
+    <row r="60" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="29" x14ac:dyDescent="0.35">
+      <c r="A60" s="164"/>
+      <c r="B60" s="165"/>
       <c r="C60" s="53" t="s">
         <v>163</v>
       </c>
@@ -31426,9 +31441,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A61" s="160"/>
-      <c r="B61" s="159"/>
+    <row r="61" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A61" s="164"/>
+      <c r="B61" s="165"/>
       <c r="C61" s="34" t="s">
         <v>118</v>
       </c>
@@ -31436,9 +31451,9 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A62" s="160"/>
-      <c r="B62" s="159"/>
+    <row r="62" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A62" s="164"/>
+      <c r="B62" s="165"/>
       <c r="C62" s="53" t="s">
         <v>166</v>
       </c>
@@ -31446,9 +31461,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A63" s="160"/>
-      <c r="B63" s="159"/>
+    <row r="63" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A63" s="164"/>
+      <c r="B63" s="165"/>
       <c r="C63" s="53" t="s">
         <v>166</v>
       </c>
@@ -31456,17 +31471,17 @@
         <v>168</v>
       </c>
     </row>
-    <row r="64" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A64" s="160"/>
-      <c r="B64" s="159"/>
+    <row r="64" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A64" s="164"/>
+      <c r="B64" s="165"/>
       <c r="C64" s="53"/>
       <c r="D64" s="43" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="160"/>
-      <c r="B65" s="159"/>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="164"/>
+      <c r="B65" s="165"/>
       <c r="C65" s="53" t="s">
         <v>169</v>
       </c>
@@ -31474,17 +31489,17 @@
         <v>170</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="160"/>
-      <c r="B66" s="159"/>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="164"/>
+      <c r="B66" s="165"/>
       <c r="C66" s="53"/>
       <c r="D66" s="42" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="160"/>
-      <c r="B67" s="159"/>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="164"/>
+      <c r="B67" s="165"/>
       <c r="C67" s="53" t="s">
         <v>172</v>
       </c>
@@ -31492,9 +31507,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="160"/>
-      <c r="B68" s="159"/>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="164"/>
+      <c r="B68" s="165"/>
       <c r="C68" s="53" t="s">
         <v>174</v>
       </c>
@@ -31502,9 +31517,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="160"/>
-      <c r="B69" s="159"/>
+    <row r="69" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A69" s="164"/>
+      <c r="B69" s="165"/>
       <c r="C69" s="56" t="s">
         <v>176</v>
       </c>
@@ -31512,9 +31527,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="160"/>
-      <c r="B70" s="159"/>
+    <row r="70" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A70" s="164"/>
+      <c r="B70" s="165"/>
       <c r="C70" s="56" t="s">
         <v>178</v>
       </c>
@@ -31522,9 +31537,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="160"/>
-      <c r="B71" s="159"/>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="164"/>
+      <c r="B71" s="165"/>
       <c r="C71" s="53" t="s">
         <v>179</v>
       </c>
@@ -31532,9 +31547,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="160"/>
-      <c r="B72" s="159"/>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="164"/>
+      <c r="B72" s="165"/>
       <c r="C72" s="53" t="s">
         <v>181</v>
       </c>
@@ -31542,17 +31557,17 @@
         <v>173</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="160"/>
-      <c r="B73" s="159"/>
+    <row r="73" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="164"/>
+      <c r="B73" s="165"/>
       <c r="C73" s="53"/>
       <c r="D73" s="45" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="160"/>
-      <c r="B74" s="159"/>
+    <row r="74" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="164"/>
+      <c r="B74" s="165"/>
       <c r="C74" s="53" t="s">
         <v>182</v>
       </c>
@@ -31560,21 +31575,21 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="160"/>
-      <c r="B75" s="159"/>
-      <c r="C75" s="166"/>
-      <c r="D75" s="161" t="s">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="164"/>
+      <c r="B75" s="165"/>
+      <c r="C75" s="158"/>
+      <c r="D75" s="166" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="160"/>
-      <c r="B76" s="159"/>
-      <c r="C76" s="166"/>
-      <c r="D76" s="161"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="164"/>
+      <c r="B76" s="165"/>
+      <c r="C76" s="158"/>
+      <c r="D76" s="166"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="35" t="s">
         <v>72</v>
       </c>
@@ -31582,13 +31597,13 @@
       <c r="C77" s="35"/>
       <c r="D77" s="40"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="44"/>
       <c r="B78" s="36"/>
       <c r="C78" s="34"/>
       <c r="D78" s="46"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="44"/>
       <c r="B79" s="36"/>
       <c r="C79" s="34"/>
@@ -31596,8 +31611,8 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{99CEABDF-88F7-4121-AD5F-66FD045725EC}">
-      <selection activeCell="A7" sqref="A7"/>
+    <customSheetView guid="{3ECA9ADB-6C26-4D30-9FA0-625C82AEEE29}" topLeftCell="A13">
+      <selection activeCell="D20" sqref="D20"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
     </customSheetView>
@@ -31606,29 +31621,13 @@
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
     </customSheetView>
-    <customSheetView guid="{3ECA9ADB-6C26-4D30-9FA0-625C82AEEE29}" topLeftCell="A13">
-      <selection activeCell="D20" sqref="D20"/>
+    <customSheetView guid="{99CEABDF-88F7-4121-AD5F-66FD045725EC}">
+      <selection activeCell="A7" sqref="A7"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="30">
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="A57:A76"/>
-    <mergeCell ref="B57:B76"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="A49:A54"/>
-    <mergeCell ref="B49:B54"/>
     <mergeCell ref="A7:A12"/>
     <mergeCell ref="B7:B12"/>
     <mergeCell ref="A43:A44"/>
@@ -31643,6 +31642,22 @@
     <mergeCell ref="B16:B25"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="B39:B40"/>
+    <mergeCell ref="A57:A76"/>
+    <mergeCell ref="B57:B76"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="A49:A54"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
@@ -31652,15 +31667,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" customWidth="1"/>
-    <col min="2" max="2" width="45.7109375" customWidth="1"/>
-    <col min="3" max="3" width="49.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.85546875" customWidth="1"/>
+    <col min="1" max="1" width="30.26953125" customWidth="1"/>
+    <col min="2" max="2" width="45.7265625" customWidth="1"/>
+    <col min="3" max="3" width="49.26953125" customWidth="1"/>
+    <col min="4" max="4" width="80.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="44.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="44.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -31674,7 +31689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
         <v>77</v>
       </c>
@@ -31682,7 +31697,7 @@
       <c r="C2" s="35"/>
       <c r="D2" s="40"/>
     </row>
-    <row r="3" spans="1:4" ht="45.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="45.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="35" t="s">
         <v>8</v>
       </c>
@@ -31690,11 +31705,11 @@
       <c r="C3" s="35"/>
       <c r="D3" s="40"/>
     </row>
-    <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="154" t="s">
+    <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="171" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="155" t="s">
+      <c r="B4" s="170" t="s">
         <v>185</v>
       </c>
       <c r="C4" s="67" t="s">
@@ -31704,9 +31719,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="154"/>
-      <c r="B5" s="155"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="171"/>
+      <c r="B5" s="170"/>
       <c r="C5" s="181" t="s">
         <v>188</v>
       </c>
@@ -31714,59 +31729,59 @@
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="154"/>
-      <c r="B6" s="155"/>
+    <row r="6" spans="1:4" ht="7.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="171"/>
+      <c r="B6" s="170"/>
       <c r="C6" s="181"/>
       <c r="D6" s="180"/>
     </row>
-    <row r="7" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154"/>
-      <c r="B7" s="155"/>
+    <row r="7" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="171"/>
+      <c r="B7" s="170"/>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
     </row>
-    <row r="8" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="154"/>
-      <c r="B8" s="155"/>
+    <row r="8" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="171"/>
+      <c r="B8" s="170"/>
       <c r="C8" s="53"/>
       <c r="D8" s="53"/>
     </row>
-    <row r="9" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="154"/>
-      <c r="B9" s="155"/>
+    <row r="9" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="171"/>
+      <c r="B9" s="170"/>
       <c r="C9" s="66"/>
       <c r="D9" s="45"/>
     </row>
-    <row r="10" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="157" t="s">
+    <row r="10" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="173" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="155" t="s">
+      <c r="B10" s="170" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="179"/>
+      <c r="C10" s="183"/>
       <c r="D10" s="180" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="157"/>
-      <c r="B11" s="155"/>
-      <c r="C11" s="179"/>
+    <row r="11" spans="1:4" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="173"/>
+      <c r="B11" s="170"/>
+      <c r="C11" s="183"/>
       <c r="D11" s="180"/>
     </row>
-    <row r="12" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="157"/>
-      <c r="B12" s="155"/>
-      <c r="C12" s="179"/>
+    <row r="12" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="173"/>
+      <c r="B12" s="170"/>
+      <c r="C12" s="183"/>
       <c r="D12" s="180"/>
     </row>
-    <row r="13" spans="1:4" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="158" t="s">
+    <row r="13" spans="1:4" ht="31.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="159" t="s">
+      <c r="B13" s="165" t="s">
         <v>185</v>
       </c>
       <c r="C13" s="182"/>
@@ -31774,69 +31789,69 @@
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="158"/>
-      <c r="B14" s="159"/>
+    <row r="14" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="156"/>
+      <c r="B14" s="165"/>
       <c r="C14" s="182"/>
       <c r="D14" s="180"/>
     </row>
-    <row r="15" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="158"/>
-      <c r="B15" s="159"/>
+    <row r="15" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="156"/>
+      <c r="B15" s="165"/>
       <c r="C15" s="182"/>
       <c r="D15" s="45"/>
     </row>
-    <row r="16" spans="1:4" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="158"/>
-      <c r="B16" s="159"/>
+    <row r="16" spans="1:4" ht="27.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="156"/>
+      <c r="B16" s="165"/>
       <c r="C16" s="182"/>
       <c r="D16" s="45"/>
     </row>
-    <row r="17" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="158"/>
-      <c r="B17" s="159"/>
+    <row r="17" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="156"/>
+      <c r="B17" s="165"/>
       <c r="C17" s="182"/>
       <c r="D17" s="45"/>
     </row>
-    <row r="18" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="158"/>
-      <c r="B18" s="159"/>
+    <row r="18" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="156"/>
+      <c r="B18" s="165"/>
       <c r="C18" s="182"/>
       <c r="D18" s="45"/>
     </row>
-    <row r="19" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="158"/>
-      <c r="B19" s="159"/>
+    <row r="19" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="156"/>
+      <c r="B19" s="165"/>
       <c r="C19" s="182"/>
       <c r="D19" s="45"/>
     </row>
-    <row r="20" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="158"/>
-      <c r="B20" s="159"/>
+    <row r="20" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="156"/>
+      <c r="B20" s="165"/>
       <c r="C20" s="182"/>
       <c r="D20" s="45"/>
     </row>
-    <row r="21" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="158"/>
-      <c r="B21" s="159"/>
+    <row r="21" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="156"/>
+      <c r="B21" s="165"/>
       <c r="C21" s="182"/>
       <c r="D21" s="45"/>
     </row>
-    <row r="22" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="158"/>
-      <c r="B22" s="159"/>
+    <row r="22" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="156"/>
+      <c r="B22" s="165"/>
       <c r="C22" s="182"/>
       <c r="D22" s="45"/>
     </row>
-    <row r="23" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="158"/>
-      <c r="B23" s="159"/>
+    <row r="23" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="156"/>
+      <c r="B23" s="165"/>
       <c r="C23" s="182"/>
       <c r="D23" s="53" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="26" x14ac:dyDescent="0.35">
       <c r="A24" s="68" t="s">
         <v>193</v>
       </c>
@@ -31850,7 +31865,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="68" t="s">
         <v>195</v>
       </c>
@@ -31864,7 +31879,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="44" t="s">
         <v>121</v>
       </c>
@@ -31876,7 +31891,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="35" t="s">
         <v>34</v>
       </c>
@@ -31884,7 +31899,7 @@
       <c r="C27" s="35"/>
       <c r="D27" s="35"/>
     </row>
-    <row r="28" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="75" t="s">
         <v>35</v>
       </c>
@@ -31898,7 +31913,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="75"/>
       <c r="B29" s="47"/>
       <c r="C29" s="65" t="s">
@@ -31908,7 +31923,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="75"/>
       <c r="B30" s="47"/>
       <c r="C30" s="65" t="s">
@@ -31918,7 +31933,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="75"/>
       <c r="B31" s="47"/>
       <c r="C31" s="77" t="s">
@@ -31928,11 +31943,11 @@
         <v>204</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="183" t="s">
+    <row r="32" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="174" t="s">
         <v>205</v>
       </c>
-      <c r="B32" s="186" t="s">
+      <c r="B32" s="177" t="s">
         <v>185</v>
       </c>
       <c r="C32" s="79" t="s">
@@ -31942,27 +31957,27 @@
         <v>207</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="184"/>
-      <c r="B33" s="187"/>
+    <row r="33" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="175"/>
+      <c r="B33" s="178"/>
       <c r="C33" s="65"/>
       <c r="D33" s="69"/>
     </row>
-    <row r="34" spans="1:4" ht="9.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="184"/>
-      <c r="B34" s="187"/>
+    <row r="34" spans="1:4" ht="9.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="175"/>
+      <c r="B34" s="178"/>
       <c r="C34" s="65"/>
       <c r="D34" s="69"/>
     </row>
-    <row r="35" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="184"/>
-      <c r="B35" s="187"/>
+    <row r="35" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="175"/>
+      <c r="B35" s="178"/>
       <c r="C35" s="65"/>
       <c r="D35" s="69"/>
     </row>
-    <row r="36" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="185"/>
-      <c r="B36" s="188"/>
+    <row r="36" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="176"/>
+      <c r="B36" s="179"/>
       <c r="C36" s="65" t="s">
         <v>208</v>
       </c>
@@ -31970,7 +31985,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="44" t="s">
         <v>36</v>
       </c>
@@ -31982,7 +31997,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="35" t="s">
         <v>37</v>
       </c>
@@ -31990,11 +32005,11 @@
       <c r="C38" s="35"/>
       <c r="D38" s="40"/>
     </row>
-    <row r="39" spans="1:4" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="156" t="s">
+    <row r="39" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="172" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="155" t="s">
+      <c r="B39" s="170" t="s">
         <v>185</v>
       </c>
       <c r="C39" s="70" t="s">
@@ -32004,9 +32019,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="156"/>
-      <c r="B40" s="155"/>
+    <row r="40" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="172"/>
+      <c r="B40" s="170"/>
       <c r="C40" s="64" t="s">
         <v>188</v>
       </c>
@@ -32014,87 +32029,87 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="154" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="171" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="155" t="s">
+      <c r="B41" s="170" t="s">
         <v>185</v>
       </c>
-      <c r="C41" s="179" t="s">
+      <c r="C41" s="183" t="s">
         <v>212</v>
       </c>
-      <c r="D41" s="158" t="s">
+      <c r="D41" s="156" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="154"/>
-      <c r="B42" s="155"/>
-      <c r="C42" s="179"/>
-      <c r="D42" s="158"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="154"/>
-      <c r="B43" s="155"/>
-      <c r="C43" s="179" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="171"/>
+      <c r="B42" s="170"/>
+      <c r="C42" s="183"/>
+      <c r="D42" s="156"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="171"/>
+      <c r="B43" s="170"/>
+      <c r="C43" s="183" t="s">
         <v>188</v>
       </c>
-      <c r="D43" s="161" t="s">
+      <c r="D43" s="166" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="154"/>
-      <c r="B44" s="155"/>
-      <c r="C44" s="179"/>
-      <c r="D44" s="161"/>
-    </row>
-    <row r="45" spans="1:4" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="160" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="171"/>
+      <c r="B44" s="170"/>
+      <c r="C44" s="183"/>
+      <c r="D44" s="166"/>
+    </row>
+    <row r="45" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="164" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="159" t="s">
+      <c r="B45" s="165" t="s">
         <v>185</v>
       </c>
-      <c r="C45" s="175"/>
+      <c r="C45" s="187"/>
       <c r="D45" s="78" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="160"/>
-      <c r="B46" s="159"/>
-      <c r="C46" s="176"/>
-      <c r="D46" s="172" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="164"/>
+      <c r="B46" s="165"/>
+      <c r="C46" s="188"/>
+      <c r="D46" s="184" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="160"/>
-      <c r="B47" s="159"/>
-      <c r="C47" s="176"/>
-      <c r="D47" s="173"/>
-    </row>
-    <row r="48" spans="1:4" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="160"/>
-      <c r="B48" s="159"/>
-      <c r="C48" s="177"/>
-      <c r="D48" s="173"/>
-    </row>
-    <row r="49" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="160"/>
-      <c r="B49" s="159"/>
-      <c r="C49" s="167"/>
-      <c r="D49" s="173"/>
-    </row>
-    <row r="50" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="160"/>
-      <c r="B50" s="159"/>
-      <c r="C50" s="167"/>
-      <c r="D50" s="174"/>
-    </row>
-    <row r="51" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="164"/>
+      <c r="B47" s="165"/>
+      <c r="C47" s="188"/>
+      <c r="D47" s="185"/>
+    </row>
+    <row r="48" spans="1:4" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="164"/>
+      <c r="B48" s="165"/>
+      <c r="C48" s="189"/>
+      <c r="D48" s="185"/>
+    </row>
+    <row r="49" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="164"/>
+      <c r="B49" s="165"/>
+      <c r="C49" s="159"/>
+      <c r="D49" s="185"/>
+    </row>
+    <row r="50" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="164"/>
+      <c r="B50" s="165"/>
+      <c r="C50" s="159"/>
+      <c r="D50" s="186"/>
+    </row>
+    <row r="51" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="35" t="s">
         <v>44</v>
       </c>
@@ -32102,7 +32117,7 @@
       <c r="C51" s="35"/>
       <c r="D51" s="40"/>
     </row>
-    <row r="52" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="26" x14ac:dyDescent="0.35">
       <c r="A52" s="44" t="s">
         <v>154</v>
       </c>
@@ -32114,11 +32129,11 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="159" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="165" t="s">
         <v>156</v>
       </c>
-      <c r="B53" s="159" t="s">
+      <c r="B53" s="165" t="s">
         <v>185</v>
       </c>
       <c r="C53" s="65" t="s">
@@ -32128,9 +32143,9 @@
         <v>217</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="159"/>
-      <c r="B54" s="159"/>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="165"/>
+      <c r="B54" s="165"/>
       <c r="C54" s="65" t="s">
         <v>188</v>
       </c>
@@ -32138,9 +32153,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="159"/>
-      <c r="B55" s="159"/>
+    <row r="55" spans="1:4" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="165"/>
+      <c r="B55" s="165"/>
       <c r="C55" s="65" t="s">
         <v>218</v>
       </c>
@@ -32148,27 +32163,27 @@
         <v>219</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="159"/>
-      <c r="B56" s="159"/>
-      <c r="C56" s="178" t="s">
+    <row r="56" spans="1:4" ht="34.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="165"/>
+      <c r="B56" s="165"/>
+      <c r="C56" s="190" t="s">
         <v>220</v>
       </c>
       <c r="D56" s="71" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="159"/>
-      <c r="B57" s="159"/>
-      <c r="C57" s="178"/>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="165"/>
+      <c r="B57" s="165"/>
+      <c r="C57" s="190"/>
       <c r="D57" s="43" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="159"/>
-      <c r="B58" s="159"/>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="165"/>
+      <c r="B58" s="165"/>
       <c r="C58" s="65" t="s">
         <v>223</v>
       </c>
@@ -32176,9 +32191,9 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="159"/>
-      <c r="B59" s="159"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="165"/>
+      <c r="B59" s="165"/>
       <c r="C59" s="65" t="s">
         <v>225</v>
       </c>
@@ -32186,109 +32201,92 @@
         <v>226</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="159"/>
-      <c r="B60" s="159"/>
-      <c r="C60" s="178" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="165"/>
+      <c r="B60" s="165"/>
+      <c r="C60" s="190" t="s">
         <v>227</v>
       </c>
       <c r="D60" s="42" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="159"/>
-      <c r="B61" s="159"/>
-      <c r="C61" s="178"/>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="165"/>
+      <c r="B61" s="165"/>
+      <c r="C61" s="190"/>
       <c r="D61" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="159"/>
-      <c r="B62" s="159"/>
-      <c r="C62" s="178"/>
+    <row r="62" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="165"/>
+      <c r="B62" s="165"/>
+      <c r="C62" s="190"/>
       <c r="D62" s="71" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="159"/>
-      <c r="B63" s="159"/>
-      <c r="C63" s="179" t="s">
+    <row r="63" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="165"/>
+      <c r="B63" s="165"/>
+      <c r="C63" s="183" t="s">
         <v>231</v>
       </c>
       <c r="D63" s="41" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="159"/>
-      <c r="B64" s="159"/>
-      <c r="C64" s="179"/>
-      <c r="D64" s="161" t="s">
+    <row r="64" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="165"/>
+      <c r="B64" s="165"/>
+      <c r="C64" s="183"/>
+      <c r="D64" s="166" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="12.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="159"/>
-      <c r="B65" s="159"/>
-      <c r="C65" s="179"/>
-      <c r="D65" s="161"/>
-    </row>
-    <row r="66" spans="1:4" ht="13.15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="159"/>
-      <c r="B66" s="159"/>
-      <c r="C66" s="179"/>
-      <c r="D66" s="161"/>
-    </row>
-    <row r="67" spans="1:4" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="159"/>
-      <c r="B67" s="159"/>
-      <c r="C67" s="179"/>
-      <c r="D67" s="161"/>
-    </row>
-    <row r="68" spans="1:4" ht="11.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="12.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="165"/>
+      <c r="B65" s="165"/>
+      <c r="C65" s="183"/>
+      <c r="D65" s="166"/>
+    </row>
+    <row r="66" spans="1:4" ht="13.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="165"/>
+      <c r="B66" s="165"/>
+      <c r="C66" s="183"/>
+      <c r="D66" s="166"/>
+    </row>
+    <row r="67" spans="1:4" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="165"/>
+      <c r="B67" s="165"/>
+      <c r="C67" s="183"/>
+      <c r="D67" s="166"/>
+    </row>
+    <row r="68" spans="1:4" ht="11.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="35"/>
       <c r="D68" s="40"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="73"/>
       <c r="B69" s="74"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="73"/>
       <c r="B70" s="74"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="73"/>
       <c r="B71" s="74"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="73"/>
       <c r="B72" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B13:B23"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C13:C23"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C43:C44"/>
     <mergeCell ref="D64:D67"/>
     <mergeCell ref="D41:D42"/>
     <mergeCell ref="D46:D50"/>
@@ -32305,6 +32303,23 @@
     <mergeCell ref="B45:B50"/>
     <mergeCell ref="C49:C50"/>
     <mergeCell ref="C63:C67"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C13:C23"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B13:B23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -32313,16 +32328,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D277"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D278"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="46.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="46.54296875" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" customWidth="1"/>
     <col min="4" max="4" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -32336,7 +32351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="87" t="s">
         <v>235</v>
       </c>
@@ -32344,11 +32359,11 @@
       <c r="C2" s="87"/>
       <c r="D2" s="88"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="189" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="191" t="s">
         <v>236</v>
       </c>
-      <c r="B3" s="189" t="s">
+      <c r="B3" s="191" t="s">
         <v>237</v>
       </c>
       <c r="C3" s="85" t="s">
@@ -32358,9 +32373,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="190"/>
-      <c r="B4" s="190"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="192"/>
+      <c r="B4" s="192"/>
       <c r="C4" s="84" t="s">
         <v>240</v>
       </c>
@@ -32368,9 +32383,9 @@
         <v>241</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="191"/>
-      <c r="B5" s="191"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="193"/>
+      <c r="B5" s="193"/>
       <c r="C5" s="84" t="s">
         <v>240</v>
       </c>
@@ -32378,11 +32393,11 @@
         <v>242</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="198" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="197" t="s">
         <v>243</v>
       </c>
-      <c r="B6" s="192" t="s">
+      <c r="B6" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C6" s="84"/>
@@ -32390,33 +32405,33 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="199"/>
-      <c r="B7" s="193"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="198"/>
+      <c r="B7" s="195"/>
       <c r="C7" s="84"/>
       <c r="D7" s="53" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="199"/>
-      <c r="B8" s="193"/>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="198"/>
+      <c r="B8" s="195"/>
       <c r="C8" s="84"/>
       <c r="D8" s="104" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="199"/>
-      <c r="B9" s="193"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="198"/>
+      <c r="B9" s="195"/>
       <c r="C9" s="84"/>
       <c r="D9" s="104" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="200"/>
-      <c r="B10" s="194"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="199"/>
+      <c r="B10" s="196"/>
       <c r="C10" s="84" t="s">
         <v>248</v>
       </c>
@@ -32424,11 +32439,11 @@
         <v>249</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="189" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="191" t="s">
         <v>250</v>
       </c>
-      <c r="B11" s="192" t="s">
+      <c r="B11" s="194" t="s">
         <v>237</v>
       </c>
       <c r="C11" s="84" t="s">
@@ -32438,9 +32453,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="190"/>
-      <c r="B12" s="193"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="192"/>
+      <c r="B12" s="195"/>
       <c r="C12" s="84" t="s">
         <v>251</v>
       </c>
@@ -32448,9 +32463,9 @@
         <v>252</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="191"/>
-      <c r="B13" s="194"/>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="193"/>
+      <c r="B13" s="196"/>
       <c r="C13" s="84" t="s">
         <v>253</v>
       </c>
@@ -32458,7 +32473,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="87" t="s">
         <v>255</v>
       </c>
@@ -32466,11 +32481,11 @@
       <c r="C14" s="87"/>
       <c r="D14" s="88"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="169" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="161" t="s">
         <v>256</v>
       </c>
-      <c r="B15" s="192" t="s">
+      <c r="B15" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C15" s="99" t="s">
@@ -32480,9 +32495,9 @@
         <v>258</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="170"/>
-      <c r="B16" s="194"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="162"/>
+      <c r="B16" s="196"/>
       <c r="C16" s="99" t="s">
         <v>259</v>
       </c>
@@ -32490,7 +32505,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="102" t="s">
         <v>261</v>
       </c>
@@ -32504,7 +32519,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="100" t="s">
         <v>264</v>
       </c>
@@ -32516,11 +32531,11 @@
         <v>265</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="189" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="191" t="s">
         <v>266</v>
       </c>
-      <c r="B19" s="192" t="s">
+      <c r="B19" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C19" s="80" t="s">
@@ -32530,9 +32545,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="190"/>
-      <c r="B20" s="193"/>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="192"/>
+      <c r="B20" s="195"/>
       <c r="C20" s="53" t="s">
         <v>268</v>
       </c>
@@ -32540,9 +32555,9 @@
         <v>269</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="190"/>
-      <c r="B21" s="193"/>
+    <row r="21" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="192"/>
+      <c r="B21" s="195"/>
       <c r="C21" s="99" t="s">
         <v>270</v>
       </c>
@@ -32550,9 +32565,9 @@
         <v>271</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="190"/>
-      <c r="B22" s="193"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="192"/>
+      <c r="B22" s="195"/>
       <c r="C22" s="99" t="s">
         <v>5</v>
       </c>
@@ -32560,9 +32575,9 @@
         <v>272</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="190"/>
-      <c r="B23" s="193"/>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="192"/>
+      <c r="B23" s="195"/>
       <c r="C23" s="84" t="s">
         <v>238</v>
       </c>
@@ -32570,9 +32585,9 @@
         <v>273</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="190"/>
-      <c r="B24" s="193"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="192"/>
+      <c r="B24" s="195"/>
       <c r="C24" s="84" t="s">
         <v>274</v>
       </c>
@@ -32580,9 +32595,9 @@
         <v>275</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="190"/>
-      <c r="B25" s="193"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="192"/>
+      <c r="B25" s="195"/>
       <c r="C25" s="84" t="s">
         <v>276</v>
       </c>
@@ -32590,9 +32605,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="190"/>
-      <c r="B26" s="193"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="192"/>
+      <c r="B26" s="195"/>
       <c r="C26" s="84" t="s">
         <v>238</v>
       </c>
@@ -32600,9 +32615,9 @@
         <v>278</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="190"/>
-      <c r="B27" s="193"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="192"/>
+      <c r="B27" s="195"/>
       <c r="C27" s="99" t="s">
         <v>279</v>
       </c>
@@ -32610,9 +32625,9 @@
         <v>280</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="191"/>
-      <c r="B28" s="194"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="193"/>
+      <c r="B28" s="196"/>
       <c r="C28" s="99">
         <v>1.1000000000000001</v>
       </c>
@@ -32620,11 +32635,11 @@
         <v>242</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="198" t="s">
+    <row r="29" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="197" t="s">
         <v>281</v>
       </c>
-      <c r="B29" s="192" t="s">
+      <c r="B29" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C29" s="84" t="s">
@@ -32634,9 +32649,9 @@
         <v>282</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="199"/>
-      <c r="B30" s="193"/>
+    <row r="30" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="198"/>
+      <c r="B30" s="195"/>
       <c r="C30" s="84" t="s">
         <v>279</v>
       </c>
@@ -32644,9 +32659,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="199"/>
-      <c r="B31" s="193"/>
+    <row r="31" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="198"/>
+      <c r="B31" s="195"/>
       <c r="C31" s="84">
         <v>3.3</v>
       </c>
@@ -32654,9 +32669,9 @@
         <v>284</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="199"/>
-      <c r="B32" s="193"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="198"/>
+      <c r="B32" s="195"/>
       <c r="C32" s="90">
         <v>3</v>
       </c>
@@ -32664,9 +32679,9 @@
         <v>285</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="200"/>
-      <c r="B33" s="194"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="199"/>
+      <c r="B33" s="196"/>
       <c r="C33" s="90">
         <v>3.5</v>
       </c>
@@ -32674,11 +32689,11 @@
         <v>286</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="198" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="197" t="s">
         <v>287</v>
       </c>
-      <c r="B34" s="192" t="s">
+      <c r="B34" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C34" s="90"/>
@@ -32686,28 +32701,28 @@
         <v>288</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="200"/>
-      <c r="B35" s="194"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="199"/>
+      <c r="B35" s="196"/>
       <c r="C35" s="84"/>
       <c r="D35" s="62" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="201" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="214" t="s">
         <v>290</v>
       </c>
-      <c r="B36" s="192" t="s">
+      <c r="B36" s="194" t="s">
         <v>244</v>
       </c>
       <c r="D36" s="62" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="201"/>
-      <c r="B37" s="193"/>
+    <row r="37" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="214"/>
+      <c r="B37" s="195"/>
       <c r="C37" s="106" t="s">
         <v>292</v>
       </c>
@@ -32715,9 +32730,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="201"/>
-      <c r="B38" s="193"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="214"/>
+      <c r="B38" s="195"/>
       <c r="C38" s="53" t="s">
         <v>294</v>
       </c>
@@ -32725,9 +32740,9 @@
         <v>295</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A39" s="201"/>
-      <c r="B39" s="193"/>
+    <row r="39" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A39" s="214"/>
+      <c r="B39" s="195"/>
       <c r="C39" s="56" t="s">
         <v>296</v>
       </c>
@@ -32735,11 +32750,11 @@
         <v>293</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="108" t="s">
         <v>297</v>
       </c>
-      <c r="B40" s="192" t="s">
+      <c r="B40" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C40" s="84"/>
@@ -32747,9 +32762,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="109"/>
-      <c r="B41" s="193"/>
+      <c r="B41" s="195"/>
       <c r="C41" s="84" t="s">
         <v>298</v>
       </c>
@@ -32757,19 +32772,19 @@
         <v>299</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="100"/>
-      <c r="B42" s="194"/>
+      <c r="B42" s="196"/>
       <c r="C42" s="84"/>
       <c r="D42" s="107" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="108" t="s">
         <v>300</v>
       </c>
-      <c r="B43" s="192" t="s">
+      <c r="B43" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C43" s="84"/>
@@ -32777,35 +32792,35 @@
         <v>249</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="100"/>
-      <c r="B44" s="194"/>
+      <c r="B44" s="196"/>
       <c r="C44" s="84"/>
       <c r="D44" s="107" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="189" t="s">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="191" t="s">
         <v>301</v>
       </c>
-      <c r="B45" s="192" t="s">
+      <c r="B45" s="194" t="s">
         <v>244</v>
       </c>
-      <c r="C45" s="202"/>
+      <c r="C45" s="209"/>
       <c r="D45" s="107" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="191"/>
-      <c r="B46" s="194"/>
-      <c r="C46" s="203"/>
+    <row r="46" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="193"/>
+      <c r="B46" s="196"/>
+      <c r="C46" s="210"/>
       <c r="D46" s="107" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="100" t="s">
         <v>303</v>
       </c>
@@ -32817,7 +32832,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="100" t="s">
         <v>304</v>
       </c>
@@ -32829,7 +32844,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="100" t="s">
         <v>305</v>
       </c>
@@ -32841,7 +32856,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="87" t="s">
         <v>306</v>
       </c>
@@ -32849,11 +32864,11 @@
       <c r="C50" s="87"/>
       <c r="D50" s="88"/>
     </row>
-    <row r="51" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="201" t="s">
+    <row r="51" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A51" s="214" t="s">
         <v>307</v>
       </c>
-      <c r="B51" s="207" t="s">
+      <c r="B51" s="215" t="s">
         <v>244</v>
       </c>
       <c r="C51" s="84" t="s">
@@ -32863,9 +32878,9 @@
         <v>309</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="201"/>
-      <c r="B52" s="207"/>
+    <row r="52" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A52" s="214"/>
+      <c r="B52" s="215"/>
       <c r="C52" s="84" t="s">
         <v>310</v>
       </c>
@@ -32873,9 +32888,9 @@
         <v>311</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="201"/>
-      <c r="B53" s="207"/>
+    <row r="53" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A53" s="214"/>
+      <c r="B53" s="215"/>
       <c r="C53" s="84" t="s">
         <v>308</v>
       </c>
@@ -32883,7 +32898,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="45.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="45.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="87" t="s">
         <v>8</v>
       </c>
@@ -32891,11 +32906,11 @@
       <c r="C54" s="87"/>
       <c r="D54" s="88"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="158" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="156" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="178" t="s">
+      <c r="B55" s="190" t="s">
         <v>244</v>
       </c>
       <c r="C55" s="53"/>
@@ -32903,9 +32918,9 @@
         <v>313</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="158"/>
-      <c r="B56" s="178"/>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="156"/>
+      <c r="B56" s="190"/>
       <c r="C56" s="65" t="s">
         <v>314</v>
       </c>
@@ -32913,9 +32928,9 @@
         <v>315</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="158"/>
-      <c r="B57" s="178"/>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="156"/>
+      <c r="B57" s="190"/>
       <c r="C57" s="65" t="s">
         <v>316</v>
       </c>
@@ -32923,9 +32938,9 @@
         <v>317</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="158"/>
-      <c r="B58" s="178"/>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="156"/>
+      <c r="B58" s="190"/>
       <c r="C58" s="65" t="s">
         <v>316</v>
       </c>
@@ -32933,9 +32948,9 @@
         <v>318</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="158"/>
-      <c r="B59" s="178"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="156"/>
+      <c r="B59" s="190"/>
       <c r="C59" s="65" t="s">
         <v>248</v>
       </c>
@@ -32943,9 +32958,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="158"/>
-      <c r="B60" s="178"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="156"/>
+      <c r="B60" s="190"/>
       <c r="C60" s="70" t="s">
         <v>248</v>
       </c>
@@ -32953,11 +32968,11 @@
         <v>320</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="169" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="B61" s="192" t="s">
+      <c r="B61" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C61" s="65" t="s">
@@ -32967,9 +32982,9 @@
         <v>321</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="210"/>
-      <c r="B62" s="193"/>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="200"/>
+      <c r="B62" s="195"/>
       <c r="C62" s="65" t="s">
         <v>322</v>
       </c>
@@ -32977,9 +32992,9 @@
         <v>323</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="170"/>
-      <c r="B63" s="194"/>
+    <row r="63" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A63" s="162"/>
+      <c r="B63" s="196"/>
       <c r="C63" s="103" t="s">
         <v>324</v>
       </c>
@@ -32987,7 +33002,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="90" t="s">
         <v>326</v>
       </c>
@@ -33001,7 +33016,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="90" t="s">
         <v>327</v>
       </c>
@@ -33015,7 +33030,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="90" t="s">
         <v>328</v>
       </c>
@@ -33027,11 +33042,11 @@
         <v>329</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="158" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="156" t="s">
         <v>330</v>
       </c>
-      <c r="B67" s="178" t="s">
+      <c r="B67" s="190" t="s">
         <v>244</v>
       </c>
       <c r="C67" s="53" t="s">
@@ -33041,25 +33056,25 @@
         <v>332</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="158"/>
-      <c r="B68" s="178"/>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="156"/>
+      <c r="B68" s="190"/>
       <c r="C68" s="53"/>
       <c r="D68" s="71" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="158"/>
-      <c r="B69" s="178"/>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="156"/>
+      <c r="B69" s="190"/>
       <c r="C69" s="53"/>
       <c r="D69" s="53" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="158"/>
-      <c r="B70" s="178"/>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="156"/>
+      <c r="B70" s="190"/>
       <c r="C70" s="65" t="s">
         <v>335</v>
       </c>
@@ -33067,9 +33082,9 @@
         <v>336</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="158"/>
-      <c r="B71" s="178"/>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="156"/>
+      <c r="B71" s="190"/>
       <c r="C71" s="70" t="s">
         <v>337</v>
       </c>
@@ -33077,7 +33092,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="90" t="s">
         <v>339</v>
       </c>
@@ -33089,11 +33104,11 @@
       </c>
       <c r="D72" s="53"/>
     </row>
-    <row r="73" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A73" s="204" t="s">
+    <row r="73" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A73" s="211" t="s">
         <v>121</v>
       </c>
-      <c r="B73" s="192" t="s">
+      <c r="B73" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C73" s="53"/>
@@ -33101,9 +33116,9 @@
         <v>340</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="205"/>
-      <c r="B74" s="193"/>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="212"/>
+      <c r="B74" s="195"/>
       <c r="C74" s="70" t="s">
         <v>341</v>
       </c>
@@ -33111,9 +33126,9 @@
         <v>342</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="205"/>
-      <c r="B75" s="193"/>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="212"/>
+      <c r="B75" s="195"/>
       <c r="C75" s="70" t="s">
         <v>343</v>
       </c>
@@ -33121,9 +33136,9 @@
         <v>344</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="205"/>
-      <c r="B76" s="193"/>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="212"/>
+      <c r="B76" s="195"/>
       <c r="C76" s="91" t="s">
         <v>345</v>
       </c>
@@ -33131,9 +33146,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="205"/>
-      <c r="B77" s="193"/>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="212"/>
+      <c r="B77" s="195"/>
       <c r="C77" s="70" t="s">
         <v>343</v>
       </c>
@@ -33141,9 +33156,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="205"/>
-      <c r="B78" s="193"/>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="212"/>
+      <c r="B78" s="195"/>
       <c r="C78" s="70" t="s">
         <v>348</v>
       </c>
@@ -33151,9 +33166,9 @@
         <v>349</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="205"/>
-      <c r="B79" s="193"/>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="212"/>
+      <c r="B79" s="195"/>
       <c r="C79" s="70" t="s">
         <v>343</v>
       </c>
@@ -33161,9 +33176,9 @@
         <v>350</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="205"/>
-      <c r="B80" s="193"/>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="212"/>
+      <c r="B80" s="195"/>
       <c r="C80" s="70" t="s">
         <v>351</v>
       </c>
@@ -33171,9 +33186,9 @@
         <v>352</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="205"/>
-      <c r="B81" s="193"/>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="212"/>
+      <c r="B81" s="195"/>
       <c r="C81" s="70" t="s">
         <v>353</v>
       </c>
@@ -33181,9 +33196,9 @@
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="205"/>
-      <c r="B82" s="193"/>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="212"/>
+      <c r="B82" s="195"/>
       <c r="C82" s="70" t="s">
         <v>343</v>
       </c>
@@ -33191,9 +33206,9 @@
         <v>355</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="205"/>
-      <c r="B83" s="193"/>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="212"/>
+      <c r="B83" s="195"/>
       <c r="C83" s="70" t="s">
         <v>353</v>
       </c>
@@ -33201,9 +33216,9 @@
         <v>356</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="205"/>
-      <c r="B84" s="193"/>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="212"/>
+      <c r="B84" s="195"/>
       <c r="C84" s="70" t="s">
         <v>343</v>
       </c>
@@ -33211,9 +33226,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="205"/>
-      <c r="B85" s="193"/>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="212"/>
+      <c r="B85" s="195"/>
       <c r="C85" s="70" t="s">
         <v>248</v>
       </c>
@@ -33221,9 +33236,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="205"/>
-      <c r="B86" s="193"/>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="212"/>
+      <c r="B86" s="195"/>
       <c r="C86" s="70" t="s">
         <v>248</v>
       </c>
@@ -33231,9 +33246,9 @@
         <v>358</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="205"/>
-      <c r="B87" s="193"/>
+    <row r="87" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A87" s="212"/>
+      <c r="B87" s="195"/>
       <c r="C87" s="91" t="s">
         <v>359</v>
       </c>
@@ -33241,9 +33256,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="206"/>
-      <c r="B88" s="194"/>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="213"/>
+      <c r="B88" s="196"/>
       <c r="C88" s="70" t="s">
         <v>248</v>
       </c>
@@ -33251,7 +33266,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="90" t="s">
         <v>361</v>
       </c>
@@ -33265,7 +33280,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="90" t="s">
         <v>364</v>
       </c>
@@ -33279,7 +33294,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="90" t="s">
         <v>367</v>
       </c>
@@ -33291,11 +33306,11 @@
       </c>
       <c r="D91" s="53"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="169" t="s">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" s="161" t="s">
         <v>368</v>
       </c>
-      <c r="B92" s="192" t="s">
+      <c r="B92" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C92" s="70" t="s">
@@ -33303,9 +33318,9 @@
       </c>
       <c r="D92" s="53"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="170"/>
-      <c r="B93" s="194"/>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" s="162"/>
+      <c r="B93" s="196"/>
       <c r="C93" s="70" t="s">
         <v>337</v>
       </c>
@@ -33313,7 +33328,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="87" t="s">
         <v>34</v>
       </c>
@@ -33321,11 +33336,11 @@
       <c r="C94" s="87"/>
       <c r="D94" s="87"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="169" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="161" t="s">
         <v>369</v>
       </c>
-      <c r="B95" s="192" t="s">
+      <c r="B95" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C95" s="53"/>
@@ -33333,25 +33348,25 @@
         <v>370</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="210"/>
-      <c r="B96" s="193"/>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="200"/>
+      <c r="B96" s="195"/>
       <c r="C96" s="53"/>
       <c r="D96" s="53" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="210"/>
-      <c r="B97" s="193"/>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="200"/>
+      <c r="B97" s="195"/>
       <c r="C97" s="53"/>
       <c r="D97" s="53" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="210"/>
-      <c r="B98" s="193"/>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="200"/>
+      <c r="B98" s="195"/>
       <c r="C98" s="53" t="s">
         <v>373</v>
       </c>
@@ -33359,9 +33374,9 @@
         <v>374</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="210"/>
-      <c r="B99" s="193"/>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" s="200"/>
+      <c r="B99" s="195"/>
       <c r="C99" s="53" t="s">
         <v>375</v>
       </c>
@@ -33369,9 +33384,9 @@
         <v>376</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="210"/>
-      <c r="B100" s="193"/>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" s="200"/>
+      <c r="B100" s="195"/>
       <c r="C100" s="53" t="s">
         <v>377</v>
       </c>
@@ -33379,9 +33394,9 @@
         <v>378</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101" s="210"/>
-      <c r="B101" s="193"/>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" s="200"/>
+      <c r="B101" s="195"/>
       <c r="C101" s="56" t="s">
         <v>379</v>
       </c>
@@ -33389,9 +33404,9 @@
         <v>349</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="210"/>
-      <c r="B102" s="193"/>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" s="200"/>
+      <c r="B102" s="195"/>
       <c r="C102" s="53" t="s">
         <v>41</v>
       </c>
@@ -33399,9 +33414,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="210"/>
-      <c r="B103" s="193"/>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" s="200"/>
+      <c r="B103" s="195"/>
       <c r="C103" s="90" t="s">
         <v>343</v>
       </c>
@@ -33409,9 +33424,9 @@
         <v>355</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="210"/>
-      <c r="B104" s="193"/>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" s="200"/>
+      <c r="B104" s="195"/>
       <c r="C104" s="90" t="s">
         <v>353</v>
       </c>
@@ -33419,9 +33434,9 @@
         <v>381</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="210"/>
-      <c r="B105" s="193"/>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" s="200"/>
+      <c r="B105" s="195"/>
       <c r="C105" s="90" t="s">
         <v>377</v>
       </c>
@@ -33429,9 +33444,9 @@
         <v>382</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="210"/>
-      <c r="B106" s="193"/>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" s="200"/>
+      <c r="B106" s="195"/>
       <c r="C106" s="90" t="s">
         <v>343</v>
       </c>
@@ -33439,9 +33454,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="210"/>
-      <c r="B107" s="193"/>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" s="200"/>
+      <c r="B107" s="195"/>
       <c r="C107" s="90" t="s">
         <v>248</v>
       </c>
@@ -33449,9 +33464,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="210"/>
-      <c r="B108" s="193"/>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" s="200"/>
+      <c r="B108" s="195"/>
       <c r="C108" s="90" t="s">
         <v>248</v>
       </c>
@@ -33459,9 +33474,9 @@
         <v>358</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A109" s="210"/>
-      <c r="B109" s="193"/>
+    <row r="109" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A109" s="200"/>
+      <c r="B109" s="195"/>
       <c r="C109" s="91" t="s">
         <v>359</v>
       </c>
@@ -33469,9 +33484,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="170"/>
-      <c r="B110" s="194"/>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" s="162"/>
+      <c r="B110" s="196"/>
       <c r="C110" s="90" t="s">
         <v>248</v>
       </c>
@@ -33479,11 +33494,11 @@
         <v>320</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="211" t="s">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" s="201" t="s">
         <v>36</v>
       </c>
-      <c r="B111" s="192" t="s">
+      <c r="B111" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C111" s="113" t="s">
@@ -33493,9 +33508,9 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="212"/>
-      <c r="B112" s="193"/>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" s="202"/>
+      <c r="B112" s="195"/>
       <c r="C112" s="53" t="s">
         <v>383</v>
       </c>
@@ -33503,17 +33518,17 @@
         <v>384</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="212"/>
-      <c r="B113" s="193"/>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" s="202"/>
+      <c r="B113" s="195"/>
       <c r="C113" s="53"/>
       <c r="D113" s="53" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A114" s="212"/>
-      <c r="B114" s="193"/>
+    <row r="114" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A114" s="202"/>
+      <c r="B114" s="195"/>
       <c r="C114" s="56" t="s">
         <v>386</v>
       </c>
@@ -33521,9 +33536,9 @@
         <v>387</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="212"/>
-      <c r="B115" s="193"/>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" s="202"/>
+      <c r="B115" s="195"/>
       <c r="C115" s="56" t="s">
         <v>343</v>
       </c>
@@ -33531,9 +33546,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="212"/>
-      <c r="B116" s="193"/>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" s="202"/>
+      <c r="B116" s="195"/>
       <c r="C116" s="56" t="s">
         <v>345</v>
       </c>
@@ -33541,9 +33556,9 @@
         <v>388</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="212"/>
-      <c r="B117" s="193"/>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" s="202"/>
+      <c r="B117" s="195"/>
       <c r="C117" s="56" t="s">
         <v>348</v>
       </c>
@@ -33551,9 +33566,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="212"/>
-      <c r="B118" s="193"/>
+    <row r="118" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A118" s="202"/>
+      <c r="B118" s="195"/>
       <c r="C118" s="56" t="s">
         <v>389</v>
       </c>
@@ -33561,9 +33576,9 @@
         <v>390</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="212"/>
-      <c r="B119" s="193"/>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" s="202"/>
+      <c r="B119" s="195"/>
       <c r="C119" s="90" t="s">
         <v>343</v>
       </c>
@@ -33571,9 +33586,9 @@
         <v>391</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="212"/>
-      <c r="B120" s="193"/>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" s="202"/>
+      <c r="B120" s="195"/>
       <c r="C120" s="90" t="s">
         <v>351</v>
       </c>
@@ -33581,9 +33596,9 @@
         <v>352</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="212"/>
-      <c r="B121" s="193"/>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" s="202"/>
+      <c r="B121" s="195"/>
       <c r="C121" s="90" t="s">
         <v>353</v>
       </c>
@@ -33591,9 +33606,9 @@
         <v>354</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="212"/>
-      <c r="B122" s="193"/>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" s="202"/>
+      <c r="B122" s="195"/>
       <c r="C122" s="90" t="s">
         <v>343</v>
       </c>
@@ -33601,9 +33616,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="212"/>
-      <c r="B123" s="193"/>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" s="202"/>
+      <c r="B123" s="195"/>
       <c r="C123" s="90" t="s">
         <v>353</v>
       </c>
@@ -33611,9 +33626,9 @@
         <v>381</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="212"/>
-      <c r="B124" s="193"/>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" s="202"/>
+      <c r="B124" s="195"/>
       <c r="C124" s="90" t="s">
         <v>377</v>
       </c>
@@ -33621,9 +33636,9 @@
         <v>382</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="212"/>
-      <c r="B125" s="193"/>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" s="202"/>
+      <c r="B125" s="195"/>
       <c r="C125" s="90" t="s">
         <v>343</v>
       </c>
@@ -33631,9 +33646,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="212"/>
-      <c r="B126" s="193"/>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" s="202"/>
+      <c r="B126" s="195"/>
       <c r="C126" s="90" t="s">
         <v>248</v>
       </c>
@@ -33641,9 +33656,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="212"/>
-      <c r="B127" s="193"/>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" s="202"/>
+      <c r="B127" s="195"/>
       <c r="C127" s="90" t="s">
         <v>248</v>
       </c>
@@ -33651,9 +33666,9 @@
         <v>358</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="212"/>
-      <c r="B128" s="193"/>
+    <row r="128" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A128" s="202"/>
+      <c r="B128" s="195"/>
       <c r="C128" s="91" t="s">
         <v>359</v>
       </c>
@@ -33661,9 +33676,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="213"/>
-      <c r="B129" s="194"/>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" s="203"/>
+      <c r="B129" s="196"/>
       <c r="C129" s="90" t="s">
         <v>248</v>
       </c>
@@ -33671,49 +33686,49 @@
         <v>320</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="169" t="s">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" s="161" t="s">
         <v>205</v>
       </c>
-      <c r="B130" s="192" t="s">
+      <c r="B130" s="194" t="s">
         <v>244</v>
       </c>
-      <c r="C130" s="214" t="s">
+      <c r="C130" s="204" t="s">
         <v>392</v>
       </c>
       <c r="D130" s="80" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="210"/>
-      <c r="B131" s="193"/>
-      <c r="C131" s="215"/>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" s="200"/>
+      <c r="B131" s="195"/>
+      <c r="C131" s="205"/>
       <c r="D131" s="53" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="210"/>
-      <c r="B132" s="193"/>
-      <c r="C132" s="216" t="s">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" s="200"/>
+      <c r="B132" s="195"/>
+      <c r="C132" s="206" t="s">
         <v>395</v>
       </c>
       <c r="D132" s="53" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A133" s="210"/>
-      <c r="B133" s="193"/>
-      <c r="C133" s="216"/>
+    <row r="133" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A133" s="200"/>
+      <c r="B133" s="195"/>
+      <c r="C133" s="206"/>
       <c r="D133" s="56" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="210"/>
-      <c r="B134" s="193"/>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" s="200"/>
+      <c r="B134" s="195"/>
       <c r="C134" s="70" t="s">
         <v>398</v>
       </c>
@@ -33721,9 +33736,9 @@
         <v>399</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="210"/>
-      <c r="B135" s="193"/>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" s="200"/>
+      <c r="B135" s="195"/>
       <c r="C135" s="70">
         <v>2.1</v>
       </c>
@@ -33731,9 +33746,9 @@
         <v>400</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="210"/>
-      <c r="B136" s="193"/>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" s="200"/>
+      <c r="B136" s="195"/>
       <c r="C136" s="70" t="s">
         <v>392</v>
       </c>
@@ -33741,9 +33756,9 @@
         <v>401</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="210"/>
-      <c r="B137" s="193"/>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137" s="200"/>
+      <c r="B137" s="195"/>
       <c r="C137" s="70" t="s">
         <v>392</v>
       </c>
@@ -33751,9 +33766,9 @@
         <v>402</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="210"/>
-      <c r="B138" s="193"/>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" s="200"/>
+      <c r="B138" s="195"/>
       <c r="C138" s="70" t="s">
         <v>392</v>
       </c>
@@ -33761,9 +33776,9 @@
         <v>403</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="210"/>
-      <c r="B139" s="193"/>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" s="200"/>
+      <c r="B139" s="195"/>
       <c r="C139" s="93" t="s">
         <v>404</v>
       </c>
@@ -33771,9 +33786,9 @@
         <v>405</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="210"/>
-      <c r="B140" s="193"/>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" s="200"/>
+      <c r="B140" s="195"/>
       <c r="C140" s="70">
         <v>2.1</v>
       </c>
@@ -33781,9 +33796,9 @@
         <v>406</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="210"/>
-      <c r="B141" s="193"/>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" s="200"/>
+      <c r="B141" s="195"/>
       <c r="C141" s="70" t="s">
         <v>392</v>
       </c>
@@ -33791,9 +33806,9 @@
         <v>338</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="210"/>
-      <c r="B142" s="193"/>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" s="200"/>
+      <c r="B142" s="195"/>
       <c r="C142" s="70" t="s">
         <v>392</v>
       </c>
@@ -33801,9 +33816,9 @@
         <v>407</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="210"/>
-      <c r="B143" s="193"/>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" s="200"/>
+      <c r="B143" s="195"/>
       <c r="C143" s="70">
         <v>2.1</v>
       </c>
@@ -33811,11 +33826,11 @@
         <v>408</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="211" t="s">
+    <row r="144" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="201" t="s">
         <v>409</v>
       </c>
-      <c r="B144" s="192" t="s">
+      <c r="B144" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C144" s="53" t="s">
@@ -33825,9 +33840,9 @@
         <v>411</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A145" s="212"/>
-      <c r="B145" s="193"/>
+    <row r="145" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A145" s="202"/>
+      <c r="B145" s="195"/>
       <c r="C145" s="56" t="s">
         <v>412</v>
       </c>
@@ -33835,9 +33850,9 @@
         <v>413</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="213"/>
-      <c r="B146" s="194"/>
+    <row r="146" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="203"/>
+      <c r="B146" s="196"/>
       <c r="C146" s="53" t="s">
         <v>414</v>
       </c>
@@ -33845,11 +33860,11 @@
         <v>415</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="169" t="s">
+    <row r="147" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="161" t="s">
         <v>416</v>
       </c>
-      <c r="B147" s="192" t="s">
+      <c r="B147" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C147" s="70" t="s">
@@ -33857,9 +33872,9 @@
       </c>
       <c r="D147" s="53"/>
     </row>
-    <row r="148" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="210"/>
-      <c r="B148" s="193"/>
+    <row r="148" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="200"/>
+      <c r="B148" s="195"/>
       <c r="C148" s="70" t="s">
         <v>404</v>
       </c>
@@ -33867,9 +33882,9 @@
         <v>405</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="210"/>
-      <c r="B149" s="193"/>
+    <row r="149" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="200"/>
+      <c r="B149" s="195"/>
       <c r="C149" s="70">
         <v>2.1</v>
       </c>
@@ -33877,9 +33892,9 @@
         <v>406</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="210"/>
-      <c r="B150" s="193"/>
+    <row r="150" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="200"/>
+      <c r="B150" s="195"/>
       <c r="C150" s="70" t="s">
         <v>395</v>
       </c>
@@ -33887,9 +33902,9 @@
         <v>417</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="210"/>
-      <c r="B151" s="193"/>
+    <row r="151" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="200"/>
+      <c r="B151" s="195"/>
       <c r="C151" s="70" t="s">
         <v>392</v>
       </c>
@@ -33897,7 +33912,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" s="87" t="s">
         <v>37</v>
       </c>
@@ -33905,7 +33920,7 @@
       <c r="C152" s="87"/>
       <c r="D152" s="88"/>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" s="90" t="s">
         <v>418</v>
       </c>
@@ -33917,11 +33932,11 @@
       </c>
       <c r="D153" s="53"/>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" s="169" t="s">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A154" s="161" t="s">
         <v>420</v>
       </c>
-      <c r="B154" s="192" t="s">
+      <c r="B154" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C154" s="53"/>
@@ -33929,25 +33944,25 @@
         <v>333</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" s="210"/>
-      <c r="B155" s="193"/>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A155" s="200"/>
+      <c r="B155" s="195"/>
       <c r="C155" s="53"/>
       <c r="D155" s="53" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="210"/>
-      <c r="B156" s="193"/>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156" s="200"/>
+      <c r="B156" s="195"/>
       <c r="C156" s="53"/>
       <c r="D156" s="53" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" s="210"/>
-      <c r="B157" s="193"/>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157" s="200"/>
+      <c r="B157" s="195"/>
       <c r="C157" s="53" t="s">
         <v>422</v>
       </c>
@@ -33955,9 +33970,9 @@
         <v>318</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" s="210"/>
-      <c r="B158" s="193"/>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A158" s="200"/>
+      <c r="B158" s="195"/>
       <c r="C158" s="53" t="s">
         <v>423</v>
       </c>
@@ -33965,9 +33980,9 @@
         <v>424</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" s="210"/>
-      <c r="B159" s="193"/>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A159" s="200"/>
+      <c r="B159" s="195"/>
       <c r="C159" s="53" t="s">
         <v>316</v>
       </c>
@@ -33975,9 +33990,9 @@
         <v>349</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" s="210"/>
-      <c r="B160" s="193"/>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A160" s="200"/>
+      <c r="B160" s="195"/>
       <c r="C160" s="53" t="s">
         <v>248</v>
       </c>
@@ -33985,11 +34000,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="158" t="s">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A161" s="156" t="s">
         <v>426</v>
       </c>
-      <c r="B161" s="178" t="s">
+      <c r="B161" s="190" t="s">
         <v>244</v>
       </c>
       <c r="C161" s="71" t="s">
@@ -33999,9 +34014,9 @@
         <v>428</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="158"/>
-      <c r="B162" s="178"/>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A162" s="156"/>
+      <c r="B162" s="190"/>
       <c r="C162" s="53" t="s">
         <v>429</v>
       </c>
@@ -34009,43 +34024,43 @@
         <v>430</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A163" s="158"/>
-      <c r="B163" s="178"/>
+    <row r="163" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A163" s="156"/>
+      <c r="B163" s="190"/>
       <c r="C163" s="94" t="s">
         <v>431</v>
       </c>
-      <c r="D163" s="192" t="s">
+      <c r="D163" s="194" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A164" s="158"/>
-      <c r="B164" s="178"/>
+    <row r="164" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A164" s="156"/>
+      <c r="B164" s="190"/>
       <c r="C164" s="94" t="s">
         <v>433</v>
       </c>
-      <c r="D164" s="193"/>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="158"/>
-      <c r="B165" s="178"/>
+      <c r="D164" s="195"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A165" s="156"/>
+      <c r="B165" s="190"/>
       <c r="C165" s="94" t="s">
         <v>434</v>
       </c>
-      <c r="D165" s="193"/>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="158"/>
-      <c r="B166" s="178"/>
+      <c r="D165" s="195"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A166" s="156"/>
+      <c r="B166" s="190"/>
       <c r="C166" s="94" t="s">
         <v>435</v>
       </c>
-      <c r="D166" s="193"/>
-    </row>
-    <row r="167" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A167" s="158"/>
-      <c r="B167" s="178"/>
+      <c r="D166" s="195"/>
+    </row>
+    <row r="167" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A167" s="156"/>
+      <c r="B167" s="190"/>
       <c r="C167" s="94" t="s">
         <v>436</v>
       </c>
@@ -34053,7 +34068,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="90" t="s">
         <v>437</v>
       </c>
@@ -34067,11 +34082,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="195" t="s">
+    <row r="169" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="216" t="s">
         <v>43</v>
       </c>
-      <c r="B169" s="192" t="s">
+      <c r="B169" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C169" s="53" t="s">
@@ -34081,9 +34096,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="196"/>
-      <c r="B170" s="193"/>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A170" s="217"/>
+      <c r="B170" s="195"/>
       <c r="C170" s="53" t="s">
         <v>439</v>
       </c>
@@ -34091,9 +34106,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="196"/>
-      <c r="B171" s="193"/>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A171" s="217"/>
+      <c r="B171" s="195"/>
       <c r="C171" s="53" t="s">
         <v>440</v>
       </c>
@@ -34101,9 +34116,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="196"/>
-      <c r="B172" s="193"/>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A172" s="217"/>
+      <c r="B172" s="195"/>
       <c r="C172" s="53" t="s">
         <v>441</v>
       </c>
@@ -34111,9 +34126,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="196"/>
-      <c r="B173" s="193"/>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A173" s="217"/>
+      <c r="B173" s="195"/>
       <c r="C173" s="53" t="s">
         <v>442</v>
       </c>
@@ -34121,9 +34136,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="196"/>
-      <c r="B174" s="193"/>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A174" s="217"/>
+      <c r="B174" s="195"/>
       <c r="C174" s="53" t="s">
         <v>443</v>
       </c>
@@ -34131,9 +34146,9 @@
         <v>444</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="196"/>
-      <c r="B175" s="193"/>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A175" s="217"/>
+      <c r="B175" s="195"/>
       <c r="C175" s="53" t="s">
         <v>445</v>
       </c>
@@ -34141,9 +34156,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="196"/>
-      <c r="B176" s="193"/>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A176" s="217"/>
+      <c r="B176" s="195"/>
       <c r="C176" s="53" t="s">
         <v>446</v>
       </c>
@@ -34151,9 +34166,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="196"/>
-      <c r="B177" s="193"/>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A177" s="217"/>
+      <c r="B177" s="195"/>
       <c r="C177" s="53" t="s">
         <v>447</v>
       </c>
@@ -34161,9 +34176,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A178" s="196"/>
-      <c r="B178" s="193"/>
+    <row r="178" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A178" s="217"/>
+      <c r="B178" s="195"/>
       <c r="C178" s="95" t="s">
         <v>448</v>
       </c>
@@ -34171,9 +34186,9 @@
         <v>449</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A179" s="196"/>
-      <c r="B179" s="193"/>
+    <row r="179" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A179" s="217"/>
+      <c r="B179" s="195"/>
       <c r="C179" s="56" t="s">
         <v>450</v>
       </c>
@@ -34181,9 +34196,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="196"/>
-      <c r="B180" s="193"/>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A180" s="217"/>
+      <c r="B180" s="195"/>
       <c r="C180" s="53" t="s">
         <v>451</v>
       </c>
@@ -34191,9 +34206,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="196"/>
-      <c r="B181" s="193"/>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A181" s="217"/>
+      <c r="B181" s="195"/>
       <c r="C181" s="53" t="s">
         <v>452</v>
       </c>
@@ -34201,9 +34216,9 @@
         <v>453</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" s="196"/>
-      <c r="B182" s="193"/>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A182" s="217"/>
+      <c r="B182" s="195"/>
       <c r="C182" s="53" t="s">
         <v>454</v>
       </c>
@@ -34211,9 +34226,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="196"/>
-      <c r="B183" s="193"/>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A183" s="217"/>
+      <c r="B183" s="195"/>
       <c r="C183" s="53" t="s">
         <v>438</v>
       </c>
@@ -34221,9 +34236,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="196"/>
-      <c r="B184" s="193"/>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A184" s="217"/>
+      <c r="B184" s="195"/>
       <c r="C184" s="53" t="s">
         <v>455</v>
       </c>
@@ -34231,9 +34246,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="196"/>
-      <c r="B185" s="193"/>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A185" s="217"/>
+      <c r="B185" s="195"/>
       <c r="C185" s="53" t="s">
         <v>443</v>
       </c>
@@ -34241,9 +34256,9 @@
         <v>456</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="196"/>
-      <c r="B186" s="193"/>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A186" s="217"/>
+      <c r="B186" s="195"/>
       <c r="C186" s="53" t="s">
         <v>457</v>
       </c>
@@ -34251,17 +34266,17 @@
         <v>249</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A187" s="196"/>
-      <c r="B187" s="193"/>
+    <row r="187" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A187" s="217"/>
+      <c r="B187" s="195"/>
       <c r="C187" s="53"/>
       <c r="D187" s="81" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="196"/>
-      <c r="B188" s="193"/>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A188" s="217"/>
+      <c r="B188" s="195"/>
       <c r="C188" s="53" t="s">
         <v>459</v>
       </c>
@@ -34269,9 +34284,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="196"/>
-      <c r="B189" s="193"/>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A189" s="217"/>
+      <c r="B189" s="195"/>
       <c r="C189" s="53" t="s">
         <v>438</v>
       </c>
@@ -34279,9 +34294,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="196"/>
-      <c r="B190" s="193"/>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A190" s="217"/>
+      <c r="B190" s="195"/>
       <c r="C190" s="53" t="s">
         <v>460</v>
       </c>
@@ -34289,9 +34304,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="196"/>
-      <c r="B191" s="193"/>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A191" s="217"/>
+      <c r="B191" s="195"/>
       <c r="C191" s="53" t="s">
         <v>461</v>
       </c>
@@ -34299,9 +34314,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="196"/>
-      <c r="B192" s="193"/>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A192" s="217"/>
+      <c r="B192" s="195"/>
       <c r="C192" s="53" t="s">
         <v>462</v>
       </c>
@@ -34309,9 +34324,9 @@
         <v>463</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A193" s="196"/>
-      <c r="B193" s="193"/>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A193" s="217"/>
+      <c r="B193" s="195"/>
       <c r="C193" s="53" t="s">
         <v>464</v>
       </c>
@@ -34319,9 +34334,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A194" s="196"/>
-      <c r="B194" s="193"/>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A194" s="217"/>
+      <c r="B194" s="195"/>
       <c r="C194" s="53" t="s">
         <v>465</v>
       </c>
@@ -34329,9 +34344,9 @@
         <v>466</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="196"/>
-      <c r="B195" s="193"/>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A195" s="217"/>
+      <c r="B195" s="195"/>
       <c r="C195" s="53" t="s">
         <v>467</v>
       </c>
@@ -34339,9 +34354,9 @@
         <v>468</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A196" s="196"/>
-      <c r="B196" s="193"/>
+    <row r="196" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A196" s="217"/>
+      <c r="B196" s="195"/>
       <c r="C196" s="85" t="s">
         <v>469</v>
       </c>
@@ -34349,9 +34364,9 @@
         <v>470</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="196"/>
-      <c r="B197" s="193"/>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A197" s="217"/>
+      <c r="B197" s="195"/>
       <c r="C197" s="53" t="s">
         <v>471</v>
       </c>
@@ -34359,9 +34374,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" s="196"/>
-      <c r="B198" s="193"/>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A198" s="217"/>
+      <c r="B198" s="195"/>
       <c r="C198" s="53" t="s">
         <v>472</v>
       </c>
@@ -34369,9 +34384,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" s="196"/>
-      <c r="B199" s="193"/>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A199" s="217"/>
+      <c r="B199" s="195"/>
       <c r="C199" s="53" t="s">
         <v>473</v>
       </c>
@@ -34379,9 +34394,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A200" s="196"/>
-      <c r="B200" s="193"/>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A200" s="217"/>
+      <c r="B200" s="195"/>
       <c r="C200" s="53" t="s">
         <v>474</v>
       </c>
@@ -34389,9 +34404,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" s="196"/>
-      <c r="B201" s="193"/>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A201" s="217"/>
+      <c r="B201" s="195"/>
       <c r="C201" s="53" t="s">
         <v>475</v>
       </c>
@@ -34399,9 +34414,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A202" s="196"/>
-      <c r="B202" s="193"/>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A202" s="217"/>
+      <c r="B202" s="195"/>
       <c r="C202" s="53" t="s">
         <v>473</v>
       </c>
@@ -34409,9 +34424,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A203" s="196"/>
-      <c r="B203" s="193"/>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A203" s="217"/>
+      <c r="B203" s="195"/>
       <c r="C203" s="92" t="s">
         <v>476</v>
       </c>
@@ -34419,9 +34434,9 @@
         <v>477</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A204" s="196"/>
-      <c r="B204" s="193"/>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A204" s="217"/>
+      <c r="B204" s="195"/>
       <c r="C204" s="53" t="s">
         <v>478</v>
       </c>
@@ -34429,9 +34444,9 @@
         <v>479</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A205" s="196"/>
-      <c r="B205" s="193"/>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A205" s="217"/>
+      <c r="B205" s="195"/>
       <c r="C205" s="53" t="s">
         <v>480</v>
       </c>
@@ -34439,9 +34454,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A206" s="196"/>
-      <c r="B206" s="193"/>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A206" s="217"/>
+      <c r="B206" s="195"/>
       <c r="C206" s="53" t="s">
         <v>482</v>
       </c>
@@ -34449,9 +34464,9 @@
         <v>483</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A207" s="196"/>
-      <c r="B207" s="193"/>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A207" s="217"/>
+      <c r="B207" s="195"/>
       <c r="C207" s="53" t="s">
         <v>484</v>
       </c>
@@ -34459,9 +34474,9 @@
         <v>483</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A208" s="196"/>
-      <c r="B208" s="193"/>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A208" s="217"/>
+      <c r="B208" s="195"/>
       <c r="C208" s="53" t="s">
         <v>485</v>
       </c>
@@ -34469,9 +34484,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A209" s="196"/>
-      <c r="B209" s="193"/>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A209" s="217"/>
+      <c r="B209" s="195"/>
       <c r="C209" s="53" t="s">
         <v>486</v>
       </c>
@@ -34479,9 +34494,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A210" s="196"/>
-      <c r="B210" s="193"/>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A210" s="217"/>
+      <c r="B210" s="195"/>
       <c r="C210" s="53" t="s">
         <v>487</v>
       </c>
@@ -34489,9 +34504,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A211" s="196"/>
-      <c r="B211" s="193"/>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A211" s="217"/>
+      <c r="B211" s="195"/>
       <c r="C211" s="53" t="s">
         <v>488</v>
       </c>
@@ -34499,9 +34514,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A212" s="196"/>
-      <c r="B212" s="193"/>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A212" s="217"/>
+      <c r="B212" s="195"/>
       <c r="C212" s="53" t="s">
         <v>489</v>
       </c>
@@ -34509,9 +34524,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A213" s="196"/>
-      <c r="B213" s="193"/>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A213" s="217"/>
+      <c r="B213" s="195"/>
       <c r="C213" s="53" t="s">
         <v>490</v>
       </c>
@@ -34519,9 +34534,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A214" s="196"/>
-      <c r="B214" s="193"/>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A214" s="217"/>
+      <c r="B214" s="195"/>
       <c r="C214" s="53" t="s">
         <v>491</v>
       </c>
@@ -34529,9 +34544,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A215" s="196"/>
-      <c r="B215" s="193"/>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A215" s="217"/>
+      <c r="B215" s="195"/>
       <c r="C215" s="53" t="s">
         <v>492</v>
       </c>
@@ -34539,9 +34554,9 @@
         <v>493</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A216" s="196"/>
-      <c r="B216" s="193"/>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A216" s="217"/>
+      <c r="B216" s="195"/>
       <c r="C216" s="53" t="s">
         <v>494</v>
       </c>
@@ -34549,9 +34564,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A217" s="196"/>
-      <c r="B217" s="193"/>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A217" s="217"/>
+      <c r="B217" s="195"/>
       <c r="C217" s="53" t="s">
         <v>490</v>
       </c>
@@ -34559,9 +34574,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A218" s="196"/>
-      <c r="B218" s="193"/>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A218" s="217"/>
+      <c r="B218" s="195"/>
       <c r="C218" s="53" t="s">
         <v>495</v>
       </c>
@@ -34569,9 +34584,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A219" s="196"/>
-      <c r="B219" s="193"/>
+    <row r="219" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A219" s="217"/>
+      <c r="B219" s="195"/>
       <c r="C219" s="56" t="s">
         <v>496</v>
       </c>
@@ -34579,9 +34594,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A220" s="197"/>
-      <c r="B220" s="194"/>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A220" s="218"/>
+      <c r="B220" s="196"/>
       <c r="C220" s="56" t="s">
         <v>465</v>
       </c>
@@ -34589,11 +34604,11 @@
         <v>466</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A221" s="195" t="s">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A221" s="216" t="s">
         <v>497</v>
       </c>
-      <c r="B221" s="192" t="s">
+      <c r="B221" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C221" s="53" t="s">
@@ -34603,9 +34618,9 @@
         <v>498</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A222" s="196"/>
-      <c r="B222" s="193"/>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A222" s="217"/>
+      <c r="B222" s="195"/>
       <c r="C222" s="92" t="s">
         <v>499</v>
       </c>
@@ -34613,9 +34628,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A223" s="197"/>
-      <c r="B223" s="194"/>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A223" s="218"/>
+      <c r="B223" s="196"/>
       <c r="C223" s="53" t="s">
         <v>500</v>
       </c>
@@ -34623,7 +34638,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" s="90" t="s">
         <v>501</v>
       </c>
@@ -34637,7 +34652,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="90" t="s">
         <v>502</v>
       </c>
@@ -34651,7 +34666,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" s="87" t="s">
         <v>44</v>
       </c>
@@ -34659,11 +34674,11 @@
       <c r="C226" s="87"/>
       <c r="D226" s="88"/>
     </row>
-    <row r="227" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="169" t="s">
+    <row r="227" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A227" s="161" t="s">
         <v>156</v>
       </c>
-      <c r="B227" s="192" t="s">
+      <c r="B227" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C227" s="53"/>
@@ -34671,9 +34686,9 @@
         <v>333</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A228" s="210"/>
-      <c r="B228" s="193"/>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A228" s="200"/>
+      <c r="B228" s="195"/>
       <c r="C228" s="65" t="s">
         <v>503</v>
       </c>
@@ -34681,9 +34696,9 @@
         <v>504</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A229" s="210"/>
-      <c r="B229" s="193"/>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A229" s="200"/>
+      <c r="B229" s="195"/>
       <c r="C229" s="65">
         <v>10.1</v>
       </c>
@@ -34691,9 +34706,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A230" s="210"/>
-      <c r="B230" s="193"/>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A230" s="200"/>
+      <c r="B230" s="195"/>
       <c r="C230" s="65">
         <v>10.199999999999999</v>
       </c>
@@ -34701,9 +34716,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A231" s="210"/>
-      <c r="B231" s="193"/>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A231" s="200"/>
+      <c r="B231" s="195"/>
       <c r="C231" s="82" t="s">
         <v>506</v>
       </c>
@@ -34711,9 +34726,9 @@
         <v>507</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A232" s="210"/>
-      <c r="B232" s="193"/>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A232" s="200"/>
+      <c r="B232" s="195"/>
       <c r="C232" s="82" t="s">
         <v>508</v>
       </c>
@@ -34721,9 +34736,9 @@
         <v>509</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A233" s="210"/>
-      <c r="B233" s="193"/>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A233" s="200"/>
+      <c r="B233" s="195"/>
       <c r="C233" s="82" t="s">
         <v>166</v>
       </c>
@@ -34731,9 +34746,9 @@
         <v>510</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A234" s="210"/>
-      <c r="B234" s="193"/>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A234" s="200"/>
+      <c r="B234" s="195"/>
       <c r="C234" s="82" t="s">
         <v>511</v>
       </c>
@@ -34741,9 +34756,9 @@
         <v>512</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A235" s="210"/>
-      <c r="B235" s="193"/>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A235" s="200"/>
+      <c r="B235" s="195"/>
       <c r="C235" s="82" t="s">
         <v>60</v>
       </c>
@@ -34751,9 +34766,9 @@
         <v>513</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A236" s="210"/>
-      <c r="B236" s="193"/>
+    <row r="236" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A236" s="200"/>
+      <c r="B236" s="195"/>
       <c r="C236" s="82" t="s">
         <v>514</v>
       </c>
@@ -34761,9 +34776,9 @@
         <v>515</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A237" s="170"/>
-      <c r="B237" s="194"/>
+    <row r="237" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A237" s="162"/>
+      <c r="B237" s="196"/>
       <c r="C237" s="82" t="s">
         <v>514</v>
       </c>
@@ -34771,11 +34786,11 @@
         <v>516</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A238" s="169" t="s">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A238" s="161" t="s">
         <v>517</v>
       </c>
-      <c r="B238" s="192" t="s">
+      <c r="B238" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C238" s="82"/>
@@ -34783,9 +34798,9 @@
         <v>333</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A239" s="210"/>
-      <c r="B239" s="193"/>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A239" s="200"/>
+      <c r="B239" s="195"/>
       <c r="C239" s="62" t="s">
         <v>518</v>
       </c>
@@ -34793,7 +34808,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="61" t="s">
         <v>520</v>
       </c>
@@ -34807,7 +34822,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" s="98" t="s">
         <v>72</v>
       </c>
@@ -34815,11 +34830,11 @@
       <c r="C241" s="98"/>
       <c r="D241" s="98"/>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A242" s="169" t="s">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A242" s="161" t="s">
         <v>74</v>
       </c>
-      <c r="B242" s="192" t="s">
+      <c r="B242" s="194" t="s">
         <v>522</v>
       </c>
       <c r="C242" s="99" t="s">
@@ -34829,9 +34844,9 @@
         <v>523</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A243" s="210"/>
-      <c r="B243" s="193"/>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A243" s="200"/>
+      <c r="B243" s="195"/>
       <c r="C243" s="99" t="s">
         <v>257</v>
       </c>
@@ -34839,19 +34854,19 @@
         <v>524</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="170"/>
-      <c r="B244" s="194"/>
+    <row r="244" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A244" s="162"/>
+      <c r="B244" s="196"/>
       <c r="C244" s="53"/>
       <c r="D244" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A245" s="208" t="s">
+    <row r="245" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A245" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="B245" s="192" t="s">
+      <c r="B245" s="194" t="s">
         <v>522</v>
       </c>
       <c r="C245" s="56" t="s">
@@ -34861,19 +34876,19 @@
         <v>144</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A246" s="209"/>
-      <c r="B246" s="194"/>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A246" s="208"/>
+      <c r="B246" s="196"/>
       <c r="C246" s="56"/>
       <c r="D246" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A247" s="208" t="s">
+    <row r="247" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A247" s="207" t="s">
         <v>527</v>
       </c>
-      <c r="B247" s="192" t="s">
+      <c r="B247" s="194" t="s">
         <v>522</v>
       </c>
       <c r="C247" s="56"/>
@@ -34881,19 +34896,19 @@
         <v>528</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A248" s="209"/>
-      <c r="B248" s="194"/>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A248" s="208"/>
+      <c r="B248" s="196"/>
       <c r="C248" s="53"/>
       <c r="D248" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A249" s="208" t="s">
+    <row r="249" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A249" s="207" t="s">
         <v>76</v>
       </c>
-      <c r="B249" s="192" t="s">
+      <c r="B249" s="194" t="s">
         <v>522</v>
       </c>
       <c r="C249" s="56" t="s">
@@ -34903,15 +34918,15 @@
         <v>529</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A250" s="209"/>
-      <c r="B250" s="194"/>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A250" s="208"/>
+      <c r="B250" s="196"/>
       <c r="C250" s="53"/>
       <c r="D250" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" s="98" t="s">
         <v>530</v>
       </c>
@@ -34919,7 +34934,7 @@
       <c r="C251" s="98"/>
       <c r="D251" s="98"/>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" s="53"/>
       <c r="B252" s="65" t="s">
         <v>244</v>
@@ -34931,7 +34946,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" s="98" t="s">
         <v>531</v>
       </c>
@@ -34939,7 +34954,7 @@
       <c r="C253" s="98"/>
       <c r="D253" s="98"/>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" s="53"/>
       <c r="B254" s="65" t="s">
         <v>244</v>
@@ -34951,7 +34966,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" s="53"/>
       <c r="B255" s="65"/>
       <c r="C255" s="53" t="s">
@@ -34961,13 +34976,13 @@
         <v>533</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B256" s="115"/>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B257" s="115"/>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" s="62" t="s">
         <v>13</v>
       </c>
@@ -34979,7 +34994,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" s="62" t="s">
         <v>369</v>
       </c>
@@ -34991,7 +35006,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" s="62" t="s">
         <v>36</v>
       </c>
@@ -35003,7 +35018,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" s="62" t="s">
         <v>535</v>
       </c>
@@ -35015,7 +35030,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" s="62" t="s">
         <v>536</v>
       </c>
@@ -35027,7 +35042,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" s="62" t="s">
         <v>537</v>
       </c>
@@ -35039,7 +35054,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" s="62" t="s">
         <v>538</v>
       </c>
@@ -35053,7 +35068,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" s="62" t="s">
         <v>369</v>
       </c>
@@ -35067,7 +35082,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" s="62" t="s">
         <v>36</v>
       </c>
@@ -35081,7 +35096,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" s="62" t="s">
         <v>542</v>
       </c>
@@ -35095,7 +35110,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" s="53" t="s">
         <v>36</v>
       </c>
@@ -35109,7 +35124,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" s="90" t="s">
         <v>535</v>
       </c>
@@ -35123,7 +35138,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" s="90" t="s">
         <v>703</v>
       </c>
@@ -35137,7 +35152,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" s="90" t="s">
         <v>705</v>
       </c>
@@ -35152,7 +35167,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" s="90" t="s">
         <v>707</v>
       </c>
@@ -35167,7 +35182,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" s="90" t="s">
         <v>287</v>
       </c>
@@ -35182,7 +35197,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" s="90" t="s">
         <v>714</v>
       </c>
@@ -35197,7 +35212,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" s="90" t="s">
         <v>715</v>
       </c>
@@ -35212,12 +35227,12 @@
         <v>713</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A276" s="56" t="s">
         <v>721</v>
       </c>
       <c r="B276" s="138" t="str">
-        <f t="shared" ref="B276:B277" si="0">$B$270</f>
+        <f t="shared" ref="B276:B278" si="0">$B$270</f>
         <v>PIT Next Version</v>
       </c>
       <c r="C276" s="90" t="s">
@@ -35227,7 +35242,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" s="53" t="s">
         <v>722</v>
       </c>
@@ -35242,8 +35257,73 @@
         <v>719</v>
       </c>
     </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A278" s="219" t="s">
+        <v>723</v>
+      </c>
+      <c r="B278" s="140" t="str">
+        <f t="shared" si="0"/>
+        <v>PIT Next Version</v>
+      </c>
+      <c r="C278" t="s">
+        <v>724</v>
+      </c>
+      <c r="D278" s="219" t="s">
+        <v>725</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B221:B223"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="B169:B220"/>
+    <mergeCell ref="A169:A220"/>
+    <mergeCell ref="A19:A28"/>
+    <mergeCell ref="B19:B28"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="B67:B71"/>
+    <mergeCell ref="A73:A88"/>
+    <mergeCell ref="B73:B88"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="B55:B60"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A55:A60"/>
+    <mergeCell ref="A249:A250"/>
+    <mergeCell ref="B249:B250"/>
+    <mergeCell ref="A245:A246"/>
+    <mergeCell ref="B245:B246"/>
+    <mergeCell ref="A247:A248"/>
+    <mergeCell ref="B247:B248"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="B242:B244"/>
+    <mergeCell ref="A238:A239"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="B161:B167"/>
+    <mergeCell ref="A147:A151"/>
+    <mergeCell ref="B147:B151"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="A161:A167"/>
+    <mergeCell ref="A227:A237"/>
+    <mergeCell ref="B227:B237"/>
+    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="B130:B143"/>
+    <mergeCell ref="A154:A160"/>
+    <mergeCell ref="B154:B160"/>
+    <mergeCell ref="A130:A143"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="D163:D166"/>
@@ -35260,56 +35340,6 @@
     <mergeCell ref="A144:A146"/>
     <mergeCell ref="B144:B146"/>
     <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A147:A151"/>
-    <mergeCell ref="B147:B151"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="A161:A167"/>
-    <mergeCell ref="A227:A237"/>
-    <mergeCell ref="B227:B237"/>
-    <mergeCell ref="A67:A71"/>
-    <mergeCell ref="B130:B143"/>
-    <mergeCell ref="A154:A160"/>
-    <mergeCell ref="B154:B160"/>
-    <mergeCell ref="A130:A143"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="B242:B244"/>
-    <mergeCell ref="A238:A239"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="B161:B167"/>
-    <mergeCell ref="A249:A250"/>
-    <mergeCell ref="B249:B250"/>
-    <mergeCell ref="A245:A246"/>
-    <mergeCell ref="B245:B246"/>
-    <mergeCell ref="A247:A248"/>
-    <mergeCell ref="B247:B248"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="B67:B71"/>
-    <mergeCell ref="A73:A88"/>
-    <mergeCell ref="B73:B88"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="B55:B60"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A55:A60"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="B221:B223"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="B169:B220"/>
-    <mergeCell ref="A169:A220"/>
-    <mergeCell ref="A19:A28"/>
-    <mergeCell ref="B19:B28"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A15:A16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -35319,15 +35349,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DBC65A-63D2-46B3-B8B5-A94A70B9EDFE}">
   <dimension ref="A1:D155"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="52.7109375" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="3" width="85.42578125" customWidth="1"/>
-    <col min="4" max="4" width="128.42578125" customWidth="1"/>
+    <col min="1" max="1" width="52.7265625" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" customWidth="1"/>
+    <col min="3" max="3" width="85.453125" customWidth="1"/>
+    <col min="4" max="4" width="128.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -35341,11 +35371,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="192" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="194" t="s">
         <v>369</v>
       </c>
-      <c r="B2" s="192" t="s">
+      <c r="B2" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C2" s="53" t="s">
@@ -35355,9 +35385,9 @@
         <v>546</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="193"/>
-      <c r="B3" s="193"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="195"/>
+      <c r="B3" s="195"/>
       <c r="C3" s="53" t="s">
         <v>547</v>
       </c>
@@ -35365,9 +35395,9 @@
         <v>548</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="193"/>
-      <c r="B4" s="193"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="195"/>
+      <c r="B4" s="195"/>
       <c r="C4" s="53" t="s">
         <v>549</v>
       </c>
@@ -35375,9 +35405,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="193"/>
-      <c r="B5" s="193"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="195"/>
+      <c r="B5" s="195"/>
       <c r="C5" s="53" t="s">
         <v>551</v>
       </c>
@@ -35385,9 +35415,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="193"/>
-      <c r="B6" s="193"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="195"/>
+      <c r="B6" s="195"/>
       <c r="C6" s="53" t="s">
         <v>552</v>
       </c>
@@ -35395,9 +35425,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="193"/>
-      <c r="B7" s="193"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="195"/>
+      <c r="B7" s="195"/>
       <c r="C7" s="53" t="s">
         <v>553</v>
       </c>
@@ -35405,9 +35435,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="193"/>
-      <c r="B8" s="193"/>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="195"/>
+      <c r="B8" s="195"/>
       <c r="C8" s="53" t="s">
         <v>554</v>
       </c>
@@ -35415,9 +35445,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="193"/>
-      <c r="B9" s="193"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="195"/>
+      <c r="B9" s="195"/>
       <c r="C9" s="53" t="s">
         <v>555</v>
       </c>
@@ -35425,9 +35455,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="193"/>
-      <c r="B10" s="193"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="195"/>
+      <c r="B10" s="195"/>
       <c r="C10" s="53" t="s">
         <v>556</v>
       </c>
@@ -35435,9 +35465,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="193"/>
-      <c r="B11" s="193"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="195"/>
+      <c r="B11" s="195"/>
       <c r="C11" s="53" t="s">
         <v>557</v>
       </c>
@@ -35445,9 +35475,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="193"/>
-      <c r="B12" s="193"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="195"/>
+      <c r="B12" s="195"/>
       <c r="C12" s="53" t="s">
         <v>558</v>
       </c>
@@ -35455,9 +35485,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="193"/>
-      <c r="B13" s="193"/>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="195"/>
+      <c r="B13" s="195"/>
       <c r="C13" s="53" t="s">
         <v>559</v>
       </c>
@@ -35465,9 +35495,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="193"/>
-      <c r="B14" s="193"/>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="195"/>
+      <c r="B14" s="195"/>
       <c r="C14" s="53" t="s">
         <v>560</v>
       </c>
@@ -35475,9 +35505,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="193"/>
-      <c r="B15" s="193"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="195"/>
+      <c r="B15" s="195"/>
       <c r="C15" s="53" t="s">
         <v>561</v>
       </c>
@@ -35485,9 +35515,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="193"/>
-      <c r="B16" s="193"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="195"/>
+      <c r="B16" s="195"/>
       <c r="C16" s="53" t="s">
         <v>562</v>
       </c>
@@ -35495,9 +35525,9 @@
         <v>563</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="193"/>
-      <c r="B17" s="193"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="195"/>
+      <c r="B17" s="195"/>
       <c r="C17" s="53" t="s">
         <v>564</v>
       </c>
@@ -35505,9 +35535,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="193"/>
-      <c r="B18" s="193"/>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="195"/>
+      <c r="B18" s="195"/>
       <c r="C18" s="56" t="s">
         <v>565</v>
       </c>
@@ -35515,9 +35545,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="193"/>
-      <c r="B19" s="193"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="195"/>
+      <c r="B19" s="195"/>
       <c r="C19" s="53" t="s">
         <v>566</v>
       </c>
@@ -35525,9 +35555,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="194"/>
-      <c r="B20" s="194"/>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="196"/>
+      <c r="B20" s="196"/>
       <c r="C20" s="56" t="s">
         <v>567</v>
       </c>
@@ -35535,11 +35565,11 @@
         <v>550</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="159" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="165" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="178" t="s">
+      <c r="B21" s="190" t="s">
         <v>244</v>
       </c>
       <c r="C21" s="53" t="s">
@@ -35549,9 +35579,9 @@
         <v>546</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="159"/>
-      <c r="B22" s="178"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="165"/>
+      <c r="B22" s="190"/>
       <c r="C22" s="53" t="s">
         <v>547</v>
       </c>
@@ -35559,9 +35589,9 @@
         <v>548</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="159"/>
-      <c r="B23" s="178"/>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="165"/>
+      <c r="B23" s="190"/>
       <c r="C23" s="53" t="s">
         <v>549</v>
       </c>
@@ -35569,9 +35599,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="159"/>
-      <c r="B24" s="178"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="165"/>
+      <c r="B24" s="190"/>
       <c r="C24" s="53" t="s">
         <v>551</v>
       </c>
@@ -35579,9 +35609,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="159"/>
-      <c r="B25" s="178"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="165"/>
+      <c r="B25" s="190"/>
       <c r="C25" s="53" t="s">
         <v>552</v>
       </c>
@@ -35589,9 +35619,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="159"/>
-      <c r="B26" s="178"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="165"/>
+      <c r="B26" s="190"/>
       <c r="C26" s="53" t="s">
         <v>553</v>
       </c>
@@ -35599,9 +35629,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="159"/>
-      <c r="B27" s="178"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="165"/>
+      <c r="B27" s="190"/>
       <c r="C27" s="53" t="s">
         <v>554</v>
       </c>
@@ -35609,9 +35639,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="159"/>
-      <c r="B28" s="178"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="165"/>
+      <c r="B28" s="190"/>
       <c r="C28" s="53" t="s">
         <v>555</v>
       </c>
@@ -35619,9 +35649,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="159"/>
-      <c r="B29" s="178"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="165"/>
+      <c r="B29" s="190"/>
       <c r="C29" s="53" t="s">
         <v>556</v>
       </c>
@@ -35629,9 +35659,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="159"/>
-      <c r="B30" s="178"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="165"/>
+      <c r="B30" s="190"/>
       <c r="C30" s="53" t="s">
         <v>557</v>
       </c>
@@ -35639,9 +35669,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="159"/>
-      <c r="B31" s="178"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="165"/>
+      <c r="B31" s="190"/>
       <c r="C31" s="53" t="s">
         <v>558</v>
       </c>
@@ -35649,9 +35679,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="159"/>
-      <c r="B32" s="178"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="165"/>
+      <c r="B32" s="190"/>
       <c r="C32" s="53" t="s">
         <v>559</v>
       </c>
@@ -35659,9 +35689,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="159"/>
-      <c r="B33" s="178"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="165"/>
+      <c r="B33" s="190"/>
       <c r="C33" s="53" t="s">
         <v>560</v>
       </c>
@@ -35669,9 +35699,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="159"/>
-      <c r="B34" s="178"/>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="165"/>
+      <c r="B34" s="190"/>
       <c r="C34" s="53" t="s">
         <v>561</v>
       </c>
@@ -35679,9 +35709,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="159"/>
-      <c r="B35" s="178"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="165"/>
+      <c r="B35" s="190"/>
       <c r="C35" s="53" t="s">
         <v>562</v>
       </c>
@@ -35689,9 +35719,9 @@
         <v>563</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="159"/>
-      <c r="B36" s="178"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="165"/>
+      <c r="B36" s="190"/>
       <c r="C36" s="53" t="s">
         <v>564</v>
       </c>
@@ -35699,9 +35729,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="159"/>
-      <c r="B37" s="178"/>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="165"/>
+      <c r="B37" s="190"/>
       <c r="C37" s="56" t="s">
         <v>565</v>
       </c>
@@ -35709,9 +35739,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="159"/>
-      <c r="B38" s="178"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="165"/>
+      <c r="B38" s="190"/>
       <c r="C38" s="53" t="s">
         <v>566</v>
       </c>
@@ -35719,9 +35749,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="159"/>
-      <c r="B39" s="178"/>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="165"/>
+      <c r="B39" s="190"/>
       <c r="C39" s="56" t="s">
         <v>567</v>
       </c>
@@ -35729,11 +35759,11 @@
         <v>550</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="192" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="194" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="192" t="s">
+      <c r="B40" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C40" s="90" t="s">
@@ -35743,9 +35773,9 @@
         <v>569</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="193"/>
-      <c r="B41" s="193"/>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="195"/>
+      <c r="B41" s="195"/>
       <c r="C41" s="53" t="s">
         <v>570</v>
       </c>
@@ -35753,9 +35783,9 @@
         <v>571</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="193"/>
-      <c r="B42" s="193"/>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="195"/>
+      <c r="B42" s="195"/>
       <c r="C42" s="53" t="s">
         <v>572</v>
       </c>
@@ -35763,7 +35793,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="90" t="s">
         <v>574</v>
       </c>
@@ -35775,11 +35805,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="192" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="194" t="s">
         <v>330</v>
       </c>
-      <c r="B44" s="192" t="s">
+      <c r="B44" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C44" s="90" t="s">
@@ -35789,9 +35819,9 @@
         <v>569</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="193"/>
-      <c r="B45" s="193"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="195"/>
+      <c r="B45" s="195"/>
       <c r="C45" s="90" t="s">
         <v>575</v>
       </c>
@@ -35799,9 +35829,9 @@
         <v>571</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="194"/>
-      <c r="B46" s="194"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="196"/>
+      <c r="B46" s="196"/>
       <c r="C46" s="90" t="s">
         <v>576</v>
       </c>
@@ -35809,7 +35839,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="62" t="s">
         <v>577</v>
       </c>
@@ -35821,7 +35851,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="62" t="s">
         <v>579</v>
       </c>
@@ -35833,7 +35863,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="62" t="s">
         <v>328</v>
       </c>
@@ -35845,7 +35875,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="62" t="s">
         <v>581</v>
       </c>
@@ -35857,7 +35887,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="62" t="s">
         <v>582</v>
       </c>
@@ -35869,7 +35899,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="62" t="s">
         <v>583</v>
       </c>
@@ -35881,7 +35911,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="62" t="s">
         <v>535</v>
       </c>
@@ -35893,7 +35923,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="62" t="s">
         <v>583</v>
       </c>
@@ -35907,7 +35937,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="62" t="s">
         <v>583</v>
       </c>
@@ -35921,7 +35951,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="62" t="s">
         <v>589</v>
       </c>
@@ -35933,7 +35963,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="62" t="s">
         <v>369</v>
       </c>
@@ -35947,7 +35977,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="62" t="s">
         <v>36</v>
       </c>
@@ -35961,7 +35991,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="62" t="s">
         <v>593</v>
       </c>
@@ -35973,7 +36003,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="62" t="s">
         <v>583</v>
       </c>
@@ -35985,7 +36015,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="90" t="s">
         <v>574</v>
       </c>
@@ -35997,7 +36027,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="62" t="s">
         <v>596</v>
       </c>
@@ -36009,7 +36039,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="62" t="s">
         <v>205</v>
       </c>
@@ -36021,7 +36051,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="62" t="s">
         <v>330</v>
       </c>
@@ -36033,7 +36063,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="62" t="s">
         <v>577</v>
       </c>
@@ -36045,11 +36075,11 @@
         <v>598</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="178" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="190" t="s">
         <v>579</v>
       </c>
-      <c r="B66" s="178" t="s">
+      <c r="B66" s="190" t="s">
         <v>244</v>
       </c>
       <c r="C66" s="53" t="s">
@@ -36059,9 +36089,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="178"/>
-      <c r="B67" s="178"/>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="190"/>
+      <c r="B67" s="190"/>
       <c r="C67" s="53" t="s">
         <v>601</v>
       </c>
@@ -36069,9 +36099,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="178"/>
-      <c r="B68" s="178"/>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="190"/>
+      <c r="B68" s="190"/>
       <c r="C68" s="53" t="s">
         <v>602</v>
       </c>
@@ -36079,9 +36109,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="178"/>
-      <c r="B69" s="178"/>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="190"/>
+      <c r="B69" s="190"/>
       <c r="C69" s="53" t="s">
         <v>603</v>
       </c>
@@ -36089,9 +36119,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="178"/>
-      <c r="B70" s="178"/>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="190"/>
+      <c r="B70" s="190"/>
       <c r="C70" s="53" t="s">
         <v>604</v>
       </c>
@@ -36099,7 +36129,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="62" t="s">
         <v>328</v>
       </c>
@@ -36111,7 +36141,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="62" t="s">
         <v>582</v>
       </c>
@@ -36123,11 +36153,11 @@
         <v>606</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="178" t="s">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="190" t="s">
         <v>369</v>
       </c>
-      <c r="B73" s="178" t="s">
+      <c r="B73" s="190" t="s">
         <v>244</v>
       </c>
       <c r="C73" s="53"/>
@@ -36135,9 +36165,9 @@
         <v>597</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="178"/>
-      <c r="B74" s="178"/>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="190"/>
+      <c r="B74" s="190"/>
       <c r="C74" s="53" t="s">
         <v>599</v>
       </c>
@@ -36145,9 +36175,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="178"/>
-      <c r="B75" s="178"/>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="190"/>
+      <c r="B75" s="190"/>
       <c r="C75" s="53" t="s">
         <v>601</v>
       </c>
@@ -36155,9 +36185,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="178"/>
-      <c r="B76" s="178"/>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="190"/>
+      <c r="B76" s="190"/>
       <c r="C76" s="53" t="s">
         <v>602</v>
       </c>
@@ -36165,9 +36195,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="178"/>
-      <c r="B77" s="178"/>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="190"/>
+      <c r="B77" s="190"/>
       <c r="C77" s="53" t="s">
         <v>603</v>
       </c>
@@ -36175,9 +36205,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="178"/>
-      <c r="B78" s="178"/>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="190"/>
+      <c r="B78" s="190"/>
       <c r="C78" s="53" t="s">
         <v>604</v>
       </c>
@@ -36185,9 +36215,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="178"/>
-      <c r="B79" s="178"/>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="190"/>
+      <c r="B79" s="190"/>
       <c r="C79" s="53" t="s">
         <v>607</v>
       </c>
@@ -36195,11 +36225,11 @@
         <v>550</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="178" t="s">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="190" t="s">
         <v>36</v>
       </c>
-      <c r="B80" s="178" t="s">
+      <c r="B80" s="190" t="s">
         <v>244</v>
       </c>
       <c r="C80" s="53"/>
@@ -36207,9 +36237,9 @@
         <v>597</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="178"/>
-      <c r="B81" s="178"/>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="190"/>
+      <c r="B81" s="190"/>
       <c r="C81" s="53" t="s">
         <v>599</v>
       </c>
@@ -36217,9 +36247,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="178"/>
-      <c r="B82" s="178"/>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="190"/>
+      <c r="B82" s="190"/>
       <c r="C82" s="53" t="s">
         <v>601</v>
       </c>
@@ -36227,9 +36257,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="178"/>
-      <c r="B83" s="178"/>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="190"/>
+      <c r="B83" s="190"/>
       <c r="C83" s="53" t="s">
         <v>602</v>
       </c>
@@ -36237,9 +36267,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="178"/>
-      <c r="B84" s="178"/>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="190"/>
+      <c r="B84" s="190"/>
       <c r="C84" s="53" t="s">
         <v>603</v>
       </c>
@@ -36247,9 +36277,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="178"/>
-      <c r="B85" s="178"/>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="190"/>
+      <c r="B85" s="190"/>
       <c r="C85" s="53" t="s">
         <v>604</v>
       </c>
@@ -36257,9 +36287,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="178"/>
-      <c r="B86" s="178"/>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="190"/>
+      <c r="B86" s="190"/>
       <c r="C86" s="53" t="s">
         <v>607</v>
       </c>
@@ -36267,7 +36297,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="62" t="s">
         <v>535</v>
       </c>
@@ -36279,7 +36309,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="62" t="s">
         <v>583</v>
       </c>
@@ -36293,7 +36323,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="62" t="s">
         <v>610</v>
       </c>
@@ -36305,7 +36335,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="62" t="s">
         <v>611</v>
       </c>
@@ -36317,7 +36347,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="62" t="s">
         <v>613</v>
       </c>
@@ -36329,7 +36359,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="62" t="s">
         <v>615</v>
       </c>
@@ -36341,7 +36371,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="62" t="s">
         <v>617</v>
       </c>
@@ -36353,7 +36383,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="62" t="s">
         <v>619</v>
       </c>
@@ -36365,11 +36395,11 @@
         <v>620</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="192" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="194" t="s">
         <v>610</v>
       </c>
-      <c r="B95" s="192" t="s">
+      <c r="B95" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C95" s="53" t="s">
@@ -36379,9 +36409,9 @@
         <v>622</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="193"/>
-      <c r="B96" s="193"/>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="195"/>
+      <c r="B96" s="195"/>
       <c r="C96" s="53" t="s">
         <v>623</v>
       </c>
@@ -36389,9 +36419,9 @@
         <v>624</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="193"/>
-      <c r="B97" s="193"/>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="195"/>
+      <c r="B97" s="195"/>
       <c r="C97" s="53" t="s">
         <v>625</v>
       </c>
@@ -36399,9 +36429,9 @@
         <v>626</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="194"/>
-      <c r="B98" s="194"/>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="196"/>
+      <c r="B98" s="196"/>
       <c r="C98" s="53" t="s">
         <v>627</v>
       </c>
@@ -36409,7 +36439,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A99" s="65" t="s">
         <v>369</v>
       </c>
@@ -36423,7 +36453,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A100" s="65" t="s">
         <v>36</v>
       </c>
@@ -36437,7 +36467,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" s="53" t="s">
         <v>631</v>
       </c>
@@ -36451,11 +36481,11 @@
         <v>633</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="192" t="s">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" s="194" t="s">
         <v>369</v>
       </c>
-      <c r="B102" s="192" t="s">
+      <c r="B102" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C102" s="53" t="s">
@@ -36465,9 +36495,9 @@
         <v>635</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="193"/>
-      <c r="B103" s="193"/>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" s="195"/>
+      <c r="B103" s="195"/>
       <c r="C103" s="116" t="s">
         <v>557</v>
       </c>
@@ -36475,9 +36505,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="193"/>
-      <c r="B104" s="193"/>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" s="195"/>
+      <c r="B104" s="195"/>
       <c r="C104" s="53" t="s">
         <v>565</v>
       </c>
@@ -36485,9 +36515,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="194"/>
-      <c r="B105" s="194"/>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" s="196"/>
+      <c r="B105" s="196"/>
       <c r="C105" s="53" t="s">
         <v>564</v>
       </c>
@@ -36495,11 +36525,11 @@
         <v>637</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="192" t="s">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" s="194" t="s">
         <v>36</v>
       </c>
-      <c r="B106" s="192" t="s">
+      <c r="B106" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C106" s="53" t="s">
@@ -36509,9 +36539,9 @@
         <v>635</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="193"/>
-      <c r="B107" s="193"/>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" s="195"/>
+      <c r="B107" s="195"/>
       <c r="C107" s="116" t="s">
         <v>557</v>
       </c>
@@ -36519,9 +36549,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="193"/>
-      <c r="B108" s="193"/>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" s="195"/>
+      <c r="B108" s="195"/>
       <c r="C108" s="53" t="s">
         <v>565</v>
       </c>
@@ -36529,9 +36559,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="194"/>
-      <c r="B109" s="194"/>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" s="196"/>
+      <c r="B109" s="196"/>
       <c r="C109" s="53" t="s">
         <v>564</v>
       </c>
@@ -36539,7 +36569,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="53" t="s">
         <v>535</v>
       </c>
@@ -36551,7 +36581,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="53" t="s">
         <v>328</v>
       </c>
@@ -36563,7 +36593,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" s="53" t="s">
         <v>579</v>
       </c>
@@ -36575,7 +36605,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" s="53" t="s">
         <v>535</v>
       </c>
@@ -36589,7 +36619,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="53" t="s">
         <v>579</v>
       </c>
@@ -36603,7 +36633,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" s="62" t="s">
         <v>639</v>
       </c>
@@ -36617,7 +36647,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" s="62" t="s">
         <v>369</v>
       </c>
@@ -36629,7 +36659,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" s="53" t="s">
         <v>36</v>
       </c>
@@ -36641,7 +36671,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" s="53" t="s">
         <v>643</v>
       </c>
@@ -36653,7 +36683,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" s="53" t="s">
         <v>619</v>
       </c>
@@ -36665,7 +36695,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" s="53" t="s">
         <v>646</v>
       </c>
@@ -36677,7 +36707,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="53" t="s">
         <v>535</v>
       </c>
@@ -36691,7 +36721,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" s="53" t="s">
         <v>582</v>
       </c>
@@ -36705,7 +36735,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="53" t="s">
         <v>579</v>
       </c>
@@ -36719,7 +36749,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="53" t="s">
         <v>36</v>
       </c>
@@ -36733,11 +36763,11 @@
         <v>512</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="178" t="s">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" s="190" t="s">
         <v>583</v>
       </c>
-      <c r="B125" s="178" t="s">
+      <c r="B125" s="190" t="s">
         <v>244</v>
       </c>
       <c r="C125" s="89" t="s">
@@ -36747,9 +36777,9 @@
         <v>652</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="178"/>
-      <c r="B126" s="178"/>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" s="190"/>
+      <c r="B126" s="190"/>
       <c r="C126" s="53" t="s">
         <v>653</v>
       </c>
@@ -36757,9 +36787,9 @@
         <v>654</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="178"/>
-      <c r="B127" s="178"/>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" s="190"/>
+      <c r="B127" s="190"/>
       <c r="C127" s="53" t="s">
         <v>655</v>
       </c>
@@ -36767,9 +36797,9 @@
         <v>656</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="178"/>
-      <c r="B128" s="178"/>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" s="190"/>
+      <c r="B128" s="190"/>
       <c r="C128" s="53" t="s">
         <v>657</v>
       </c>
@@ -36777,9 +36807,9 @@
         <v>658</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="178"/>
-      <c r="B129" s="178"/>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" s="190"/>
+      <c r="B129" s="190"/>
       <c r="C129" s="53" t="s">
         <v>659</v>
       </c>
@@ -36787,7 +36817,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" s="53" t="s">
         <v>631</v>
       </c>
@@ -36801,7 +36831,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" s="121" t="s">
         <v>667</v>
       </c>
@@ -36815,8 +36845,8 @@
         <v>669</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="169" t="s">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" s="161" t="s">
         <v>663</v>
       </c>
       <c r="B132" s="117" t="s">
@@ -36829,8 +36859,8 @@
         <v>664</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="170"/>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" s="162"/>
       <c r="B133" s="118" t="s">
         <v>244</v>
       </c>
@@ -36841,7 +36871,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" s="53" t="s">
         <v>583</v>
       </c>
@@ -36855,7 +36885,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" s="121" t="s">
         <v>631</v>
       </c>
@@ -36869,7 +36899,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="136" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A136" s="53" t="s">
         <v>674</v>
       </c>
@@ -36883,7 +36913,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="137" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A137" s="53" t="s">
         <v>674</v>
       </c>
@@ -36897,11 +36927,11 @@
         <v>677</v>
       </c>
     </row>
-    <row r="138" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="178" t="s">
+    <row r="138" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="190" t="s">
         <v>574</v>
       </c>
-      <c r="B138" s="178" t="s">
+      <c r="B138" s="190" t="s">
         <v>244</v>
       </c>
       <c r="C138" s="53" t="s">
@@ -36911,9 +36941,9 @@
         <v>685</v>
       </c>
     </row>
-    <row r="139" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="178"/>
-      <c r="B139" s="178"/>
+    <row r="139" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="190"/>
+      <c r="B139" s="190"/>
       <c r="C139" s="53" t="s">
         <v>684</v>
       </c>
@@ -36921,7 +36951,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="140" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A140" s="62" t="s">
         <v>593</v>
       </c>
@@ -36935,11 +36965,11 @@
         <v>680</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="169" t="s">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" s="161" t="s">
         <v>681</v>
       </c>
-      <c r="B141" s="192" t="s">
+      <c r="B141" s="194" t="s">
         <v>244</v>
       </c>
       <c r="C141" s="53" t="s">
@@ -36949,9 +36979,9 @@
         <v>683</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="170"/>
-      <c r="B142" s="194"/>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" s="162"/>
+      <c r="B142" s="196"/>
       <c r="C142" s="53" t="s">
         <v>686</v>
       </c>
@@ -36959,7 +36989,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" s="53" t="s">
         <v>579</v>
       </c>
@@ -36973,7 +37003,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" s="53" t="s">
         <v>328</v>
       </c>
@@ -36987,7 +37017,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A145" s="53" t="s">
         <v>535</v>
       </c>
@@ -37001,7 +37031,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A146" s="53" t="s">
         <v>36</v>
       </c>
@@ -37015,7 +37045,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A147" s="53" t="s">
         <v>369</v>
       </c>
@@ -37029,7 +37059,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" s="62" t="s">
         <v>639</v>
       </c>
@@ -37043,7 +37073,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" s="53" t="s">
         <v>696</v>
       </c>
@@ -37057,7 +37087,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" s="90" t="s">
         <v>681</v>
       </c>
@@ -37071,7 +37101,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" s="90" t="s">
         <v>681</v>
       </c>
@@ -37085,7 +37115,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" s="90" t="s">
         <v>681</v>
       </c>
@@ -37099,7 +37129,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" s="90" t="s">
         <v>681</v>
       </c>
@@ -37113,8 +37143,8 @@
         <v>717</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A154" s="217" t="s">
+    <row r="154" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A154" s="141" t="s">
         <v>718</v>
       </c>
       <c r="B154" s="138" t="s">
@@ -37127,7 +37157,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" s="56" t="s">
         <v>720</v>
       </c>
@@ -37143,6 +37173,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="A2:A20"/>
+    <mergeCell ref="B2:B20"/>
+    <mergeCell ref="A21:A39"/>
+    <mergeCell ref="B21:B39"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="B40:B42"/>
     <mergeCell ref="A141:A142"/>
     <mergeCell ref="B141:B142"/>
     <mergeCell ref="A66:A70"/>
@@ -37159,17 +37200,6 @@
     <mergeCell ref="A125:A129"/>
     <mergeCell ref="B125:B129"/>
     <mergeCell ref="A102:A105"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="A2:A20"/>
-    <mergeCell ref="B2:B20"/>
-    <mergeCell ref="A21:A39"/>
-    <mergeCell ref="B21:B39"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="B40:B42"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -37178,15 +37208,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <nb82aa7489a64919aab5fd247ffa0d1e xmlns="184185d0-04c6-4ef5-ba23-3d0ec5a17fb8">
@@ -37229,6 +37250,15 @@
     </l29cd52af9b640b690e3347aa75f97a9>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -37452,19 +37482,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E83ECEA-8E14-42A0-80EE-042ED267BA0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F5A24BE-BB8C-4A62-B10D-ABDF1081592A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="184185d0-04c6-4ef5-ba23-3d0ec5a17fb8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F5A24BE-BB8C-4A62-B10D-ABDF1081592A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E83ECEA-8E14-42A0-80EE-042ED267BA0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="184185d0-04c6-4ef5-ba23-3d0ec5a17fb8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/PIT4/Schema Publication Changelog.xlsx
+++ b/PIT4/Schema Publication Changelog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ctrowell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ctrowell\Desktop\GitHub Docs\PIT4 Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5ECF376-AEBE-4C24-AA26-A05E95CBCE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E820892C-0EBA-4338-8BD8-4246D7E18553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19110" windowHeight="10430" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="0" windowWidth="16260" windowHeight="10210" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="v0.10" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Walsh, David P - Personal View" guid="{99CEABDF-88F7-4121-AD5F-66FD045725EC}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1436" windowHeight="675" activeSheetId="2"/>
+    <customWorkbookView name="Arnold, Eve - Personal View" guid="{057DBB0B-BBF6-4A94-8406-46C99A7DC1D6}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1276" windowHeight="758" activeSheetId="2"/>
     <customWorkbookView name="O'Brien, Ciaran - Personal View" guid="{3ECA9ADB-6C26-4D30-9FA0-625C82AEEE29}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1276" windowHeight="751" activeSheetId="2"/>
-    <customWorkbookView name="Arnold, Eve - Personal View" guid="{057DBB0B-BBF6-4A94-8406-46C99A7DC1D6}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1276" windowHeight="758" activeSheetId="2"/>
-    <customWorkbookView name="Walsh, David P - Personal View" guid="{99CEABDF-88F7-4121-AD5F-66FD045725EC}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1436" windowHeight="675" activeSheetId="2"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="731">
   <si>
     <t>Document</t>
   </si>
@@ -4075,6 +4075,21 @@
   </si>
   <si>
     <t>Warning added on PRSI Class and Subclass</t>
+  </si>
+  <si>
+    <t>Added SPS fields</t>
+  </si>
+  <si>
+    <t>Single Pension Scheme</t>
+  </si>
+  <si>
+    <t>Single Pension scheme fields added</t>
+  </si>
+  <si>
+    <t>payrollSubmission</t>
+  </si>
+  <si>
+    <t>Added SPS fields to example 1.3 REST and SOAP</t>
   </si>
 </sst>
 </file>
@@ -4704,7 +4719,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5078,10 +5093,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5125,8 +5149,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5149,66 +5203,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5230,6 +5224,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5248,6 +5272,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5256,6 +5289,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5278,43 +5338,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -5678,12 +5702,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="144"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="147"/>
     </row>
     <row r="3" spans="1:4" ht="26" x14ac:dyDescent="0.35">
       <c r="A3" s="29" t="s">
@@ -5700,12 +5724,12 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="142" t="s">
+      <c r="A4" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="143"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="144"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="147"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="27" t="s">
@@ -5736,10 +5760,10 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A7" s="145" t="s">
+      <c r="A7" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="148">
+      <c r="B7" s="151">
         <v>0.1</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -5750,8 +5774,8 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="146"/>
-      <c r="B8" s="149"/>
+      <c r="A8" s="149"/>
+      <c r="B8" s="152"/>
       <c r="C8" s="10" t="s">
         <v>16</v>
       </c>
@@ -5760,8 +5784,8 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A9" s="146"/>
-      <c r="B9" s="149"/>
+      <c r="A9" s="149"/>
+      <c r="B9" s="152"/>
       <c r="C9" s="10" t="s">
         <v>18</v>
       </c>
@@ -5770,8 +5794,8 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="146"/>
-      <c r="B10" s="149"/>
+      <c r="A10" s="149"/>
+      <c r="B10" s="152"/>
       <c r="C10" s="10" t="s">
         <v>20</v>
       </c>
@@ -5780,8 +5804,8 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="146"/>
-      <c r="B11" s="149"/>
+      <c r="A11" s="149"/>
+      <c r="B11" s="152"/>
       <c r="C11" s="10" t="s">
         <v>22</v>
       </c>
@@ -5790,8 +5814,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="147"/>
-      <c r="B12" s="150"/>
+      <c r="A12" s="150"/>
+      <c r="B12" s="153"/>
       <c r="C12" s="10" t="s">
         <v>24</v>
       </c>
@@ -5800,10 +5824,10 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="153" t="s">
+      <c r="A13" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="148">
+      <c r="B13" s="151">
         <v>0.1</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -5814,8 +5838,8 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="154"/>
-      <c r="B14" s="150"/>
+      <c r="A14" s="157"/>
+      <c r="B14" s="153"/>
       <c r="C14" s="10" t="s">
         <v>29</v>
       </c>
@@ -5852,12 +5876,12 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="142" t="s">
+      <c r="A17" s="145" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="143"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="144"/>
+      <c r="B17" s="146"/>
+      <c r="C17" s="146"/>
+      <c r="D17" s="147"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
@@ -5888,18 +5912,18 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="142" t="s">
+      <c r="A20" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="143"/>
-      <c r="C20" s="143"/>
-      <c r="D20" s="144"/>
+      <c r="B20" s="146"/>
+      <c r="C20" s="146"/>
+      <c r="D20" s="147"/>
     </row>
     <row r="21" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A21" s="155" t="s">
+      <c r="A21" s="158" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="152">
+      <c r="B21" s="155">
         <v>0.1</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -5910,8 +5934,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="154"/>
-      <c r="B22" s="150"/>
+      <c r="A22" s="157"/>
+      <c r="B22" s="153"/>
       <c r="C22" s="26" t="s">
         <v>41</v>
       </c>
@@ -5934,18 +5958,18 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="142" t="s">
+      <c r="A24" s="145" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="143"/>
-      <c r="C24" s="143"/>
-      <c r="D24" s="144"/>
+      <c r="B24" s="146"/>
+      <c r="C24" s="146"/>
+      <c r="D24" s="147"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="151" t="s">
+      <c r="A25" s="154" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="152">
+      <c r="B25" s="155">
         <v>0.1</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -5956,8 +5980,8 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A26" s="146"/>
-      <c r="B26" s="149"/>
+      <c r="A26" s="149"/>
+      <c r="B26" s="152"/>
       <c r="C26" s="10" t="s">
         <v>48</v>
       </c>
@@ -5966,8 +5990,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="146"/>
-      <c r="B27" s="149"/>
+      <c r="A27" s="149"/>
+      <c r="B27" s="152"/>
       <c r="C27" s="10" t="s">
         <v>50</v>
       </c>
@@ -5976,8 +6000,8 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="146"/>
-      <c r="B28" s="149"/>
+      <c r="A28" s="149"/>
+      <c r="B28" s="152"/>
       <c r="C28" s="20" t="s">
         <v>52</v>
       </c>
@@ -5986,8 +6010,8 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="146"/>
-      <c r="B29" s="149"/>
+      <c r="A29" s="149"/>
+      <c r="B29" s="152"/>
       <c r="C29" s="10" t="s">
         <v>54</v>
       </c>
@@ -5996,8 +6020,8 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="146"/>
-      <c r="B30" s="149"/>
+      <c r="A30" s="149"/>
+      <c r="B30" s="152"/>
       <c r="C30" s="10" t="s">
         <v>56</v>
       </c>
@@ -6006,8 +6030,8 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="146"/>
-      <c r="B31" s="149"/>
+      <c r="A31" s="149"/>
+      <c r="B31" s="152"/>
       <c r="C31" s="10" t="s">
         <v>58</v>
       </c>
@@ -6016,8 +6040,8 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="147"/>
-      <c r="B32" s="150"/>
+      <c r="A32" s="150"/>
+      <c r="B32" s="153"/>
       <c r="C32" s="10" t="s">
         <v>60</v>
       </c>
@@ -6138,12 +6162,12 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="142" t="s">
+      <c r="A41" s="145" t="s">
         <v>72</v>
       </c>
-      <c r="B41" s="143"/>
-      <c r="C41" s="143"/>
-      <c r="D41" s="144"/>
+      <c r="B41" s="146"/>
+      <c r="C41" s="146"/>
+      <c r="D41" s="147"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
@@ -6203,7 +6227,7 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{3ECA9ADB-6C26-4D30-9FA0-625C82AEEE29}" topLeftCell="B1">
+    <customSheetView guid="{99CEABDF-88F7-4121-AD5F-66FD045725EC}" topLeftCell="B1">
       <selection activeCell="C15" sqref="C15:D15"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6213,7 +6237,7 @@
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
     </customSheetView>
-    <customSheetView guid="{99CEABDF-88F7-4121-AD5F-66FD045725EC}" topLeftCell="B1">
+    <customSheetView guid="{3ECA9ADB-6C26-4D30-9FA0-625C82AEEE29}" topLeftCell="B1">
       <selection activeCell="C15" sqref="C15:D15"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
@@ -6318,10 +6342,10 @@
       <c r="D6" s="40"/>
     </row>
     <row r="7" spans="1:4" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="171" t="s">
+      <c r="A7" s="159" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="170" t="s">
+      <c r="B7" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="39" t="s">
@@ -6332,8 +6356,8 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A8" s="171"/>
-      <c r="B8" s="170"/>
+      <c r="A8" s="159"/>
+      <c r="B8" s="160"/>
       <c r="C8" s="34" t="s">
         <v>84</v>
       </c>
@@ -6342,8 +6366,8 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="171"/>
-      <c r="B9" s="170"/>
+      <c r="A9" s="159"/>
+      <c r="B9" s="160"/>
       <c r="C9" s="34" t="s">
         <v>86</v>
       </c>
@@ -6352,8 +6376,8 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="171"/>
-      <c r="B10" s="170"/>
+      <c r="A10" s="159"/>
+      <c r="B10" s="160"/>
       <c r="C10" s="34" t="s">
         <v>18</v>
       </c>
@@ -6362,8 +6386,8 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="171"/>
-      <c r="B11" s="170"/>
+      <c r="A11" s="159"/>
+      <c r="B11" s="160"/>
       <c r="C11" s="34" t="s">
         <v>89</v>
       </c>
@@ -6372,8 +6396,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="171"/>
-      <c r="B12" s="170"/>
+      <c r="A12" s="159"/>
+      <c r="B12" s="160"/>
       <c r="C12" s="34" t="s">
         <v>91</v>
       </c>
@@ -6382,10 +6406,10 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="173" t="s">
+      <c r="A13" s="162" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="170" t="s">
+      <c r="B13" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C13" s="34" t="s">
@@ -6396,8 +6420,8 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="173"/>
-      <c r="B14" s="170"/>
+      <c r="A14" s="162"/>
+      <c r="B14" s="160"/>
       <c r="C14" s="34" t="s">
         <v>96</v>
       </c>
@@ -6406,8 +6430,8 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="173"/>
-      <c r="B15" s="170"/>
+      <c r="A15" s="162"/>
+      <c r="B15" s="160"/>
       <c r="C15" s="39" t="s">
         <v>98</v>
       </c>
@@ -6416,10 +6440,10 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="156" t="s">
+      <c r="A16" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="165" t="s">
+      <c r="B16" s="164" t="s">
         <v>81</v>
       </c>
       <c r="C16" s="54" t="s">
@@ -6430,8 +6454,8 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="156"/>
-      <c r="B17" s="165"/>
+      <c r="A17" s="163"/>
+      <c r="B17" s="164"/>
       <c r="C17" s="53" t="s">
         <v>102</v>
       </c>
@@ -6440,8 +6464,8 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="156"/>
-      <c r="B18" s="165"/>
+      <c r="A18" s="163"/>
+      <c r="B18" s="164"/>
       <c r="C18" s="53" t="s">
         <v>89</v>
       </c>
@@ -6450,8 +6474,8 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="156"/>
-      <c r="B19" s="165"/>
+      <c r="A19" s="163"/>
+      <c r="B19" s="164"/>
       <c r="C19" s="53" t="s">
         <v>105</v>
       </c>
@@ -6460,8 +6484,8 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="156"/>
-      <c r="B20" s="165"/>
+      <c r="A20" s="163"/>
+      <c r="B20" s="164"/>
       <c r="C20" s="53" t="s">
         <v>107</v>
       </c>
@@ -6470,8 +6494,8 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="156"/>
-      <c r="B21" s="165"/>
+      <c r="A21" s="163"/>
+      <c r="B21" s="164"/>
       <c r="C21" s="53" t="s">
         <v>109</v>
       </c>
@@ -6480,8 +6504,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="156"/>
-      <c r="B22" s="165"/>
+      <c r="A22" s="163"/>
+      <c r="B22" s="164"/>
       <c r="C22" s="53" t="s">
         <v>111</v>
       </c>
@@ -6490,8 +6514,8 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="156"/>
-      <c r="B23" s="165"/>
+      <c r="A23" s="163"/>
+      <c r="B23" s="164"/>
       <c r="C23" s="61" t="s">
         <v>113</v>
       </c>
@@ -6500,26 +6524,26 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="156"/>
-      <c r="B24" s="165"/>
-      <c r="C24" s="156" t="s">
+      <c r="A24" s="163"/>
+      <c r="B24" s="164"/>
+      <c r="C24" s="163" t="s">
         <v>115</v>
       </c>
-      <c r="D24" s="157" t="s">
+      <c r="D24" s="170" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="156"/>
-      <c r="B25" s="165"/>
-      <c r="C25" s="156"/>
-      <c r="D25" s="157"/>
+      <c r="A25" s="163"/>
+      <c r="B25" s="164"/>
+      <c r="C25" s="163"/>
+      <c r="D25" s="170"/>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="171" t="s">
+      <c r="A26" s="159" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="170" t="s">
+      <c r="B26" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C26" s="34" t="s">
@@ -6530,8 +6554,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="171"/>
-      <c r="B27" s="170"/>
+      <c r="A27" s="159"/>
+      <c r="B27" s="160"/>
       <c r="C27" s="34"/>
       <c r="D27" s="37" t="s">
         <v>120</v>
@@ -6558,28 +6582,28 @@
       <c r="D29" s="35"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="172" t="s">
+      <c r="A30" s="161" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="170" t="s">
+      <c r="B30" s="160" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="156" t="s">
+      <c r="C30" s="163" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="160" t="s">
+      <c r="D30" s="173" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="172"/>
-      <c r="B31" s="170"/>
-      <c r="C31" s="156"/>
-      <c r="D31" s="160"/>
+      <c r="A31" s="161"/>
+      <c r="B31" s="160"/>
+      <c r="C31" s="163"/>
+      <c r="D31" s="173"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="172"/>
-      <c r="B32" s="170"/>
+      <c r="A32" s="161"/>
+      <c r="B32" s="160"/>
       <c r="C32" s="53" t="s">
         <v>125</v>
       </c>
@@ -6588,8 +6612,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="172"/>
-      <c r="B33" s="170"/>
+      <c r="A33" s="161"/>
+      <c r="B33" s="160"/>
       <c r="C33" s="53" t="s">
         <v>127</v>
       </c>
@@ -6598,8 +6622,8 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="172"/>
-      <c r="B34" s="170"/>
+      <c r="A34" s="161"/>
+      <c r="B34" s="160"/>
       <c r="C34" s="62" t="s">
         <v>129</v>
       </c>
@@ -6608,8 +6632,8 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="172"/>
-      <c r="B35" s="170"/>
+      <c r="A35" s="161"/>
+      <c r="B35" s="160"/>
       <c r="C35" s="53" t="s">
         <v>111</v>
       </c>
@@ -6618,8 +6642,8 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="172"/>
-      <c r="B36" s="170"/>
+      <c r="A36" s="161"/>
+      <c r="B36" s="160"/>
       <c r="C36" s="62" t="s">
         <v>113</v>
       </c>
@@ -6628,26 +6652,26 @@
       </c>
     </row>
     <row r="37" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="172"/>
-      <c r="B37" s="170"/>
-      <c r="C37" s="161" t="s">
+      <c r="A37" s="161"/>
+      <c r="B37" s="160"/>
+      <c r="C37" s="174" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="163" t="s">
+      <c r="D37" s="176" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="6.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="172"/>
-      <c r="B38" s="170"/>
-      <c r="C38" s="162"/>
-      <c r="D38" s="163"/>
+      <c r="A38" s="161"/>
+      <c r="B38" s="160"/>
+      <c r="C38" s="175"/>
+      <c r="D38" s="176"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="171" t="s">
+      <c r="A39" s="159" t="s">
         <v>134</v>
       </c>
-      <c r="B39" s="170" t="s">
+      <c r="B39" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C39" s="34" t="s">
@@ -6658,8 +6682,8 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="171"/>
-      <c r="B40" s="170"/>
+      <c r="A40" s="159"/>
+      <c r="B40" s="160"/>
       <c r="C40" s="34"/>
       <c r="D40" s="45" t="s">
         <v>136</v>
@@ -6686,10 +6710,10 @@
       <c r="D42" s="40"/>
     </row>
     <row r="43" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="170" t="s">
+      <c r="B43" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C43" s="34"/>
@@ -6698,8 +6722,8 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="172"/>
-      <c r="B44" s="170"/>
+      <c r="A44" s="161"/>
+      <c r="B44" s="160"/>
       <c r="C44" s="34" t="s">
         <v>118</v>
       </c>
@@ -6711,7 +6735,7 @@
       <c r="A45" s="167" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="170" t="s">
+      <c r="B45" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C45" s="34"/>
@@ -6721,7 +6745,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="168"/>
-      <c r="B46" s="170"/>
+      <c r="B46" s="160"/>
       <c r="C46" s="34" t="s">
         <v>141</v>
       </c>
@@ -6731,7 +6755,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="168"/>
-      <c r="B47" s="170"/>
+      <c r="B47" s="160"/>
       <c r="C47" s="34" t="s">
         <v>143</v>
       </c>
@@ -6741,7 +6765,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="169"/>
-      <c r="B48" s="170"/>
+      <c r="B48" s="160"/>
       <c r="C48" s="34" t="s">
         <v>118</v>
       </c>
@@ -6750,10 +6774,10 @@
       </c>
     </row>
     <row r="49" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A49" s="165" t="s">
+      <c r="A49" s="164" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="165" t="s">
+      <c r="B49" s="164" t="s">
         <v>81</v>
       </c>
       <c r="C49" s="53"/>
@@ -10857,8 +10881,8 @@
       <c r="XFC49" s="38"/>
     </row>
     <row r="50" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="165"/>
-      <c r="B50" s="165"/>
+      <c r="A50" s="164"/>
+      <c r="B50" s="164"/>
       <c r="C50" s="54" t="s">
         <v>146</v>
       </c>
@@ -14962,8 +14986,8 @@
       <c r="XFC50" s="38"/>
     </row>
     <row r="51" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A51" s="165"/>
-      <c r="B51" s="165"/>
+      <c r="A51" s="164"/>
+      <c r="B51" s="164"/>
       <c r="C51" s="34" t="s">
         <v>148</v>
       </c>
@@ -19067,8 +19091,8 @@
       <c r="XFC51" s="38"/>
     </row>
     <row r="52" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A52" s="165"/>
-      <c r="B52" s="165"/>
+      <c r="A52" s="164"/>
+      <c r="B52" s="164"/>
       <c r="C52" s="53" t="s">
         <v>150</v>
       </c>
@@ -23172,12 +23196,12 @@
       <c r="XFC52" s="38"/>
     </row>
     <row r="53" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A53" s="165"/>
-      <c r="B53" s="165"/>
-      <c r="C53" s="159" t="s">
+      <c r="A53" s="164"/>
+      <c r="B53" s="164"/>
+      <c r="C53" s="172" t="s">
         <v>152</v>
       </c>
-      <c r="D53" s="160" t="s">
+      <c r="D53" s="173" t="s">
         <v>153</v>
       </c>
       <c r="G53" s="38"/>
@@ -27277,10 +27301,10 @@
       <c r="XFC53" s="38"/>
     </row>
     <row r="54" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="13.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="165"/>
-      <c r="B54" s="165"/>
-      <c r="C54" s="159"/>
-      <c r="D54" s="160"/>
+      <c r="A54" s="164"/>
+      <c r="B54" s="164"/>
+      <c r="C54" s="172"/>
+      <c r="D54" s="173"/>
       <c r="G54" s="38"/>
       <c r="K54" s="38"/>
       <c r="O54" s="38"/>
@@ -31398,10 +31422,10 @@
       </c>
     </row>
     <row r="57" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A57" s="164" t="s">
+      <c r="A57" s="165" t="s">
         <v>156</v>
       </c>
-      <c r="B57" s="165" t="s">
+      <c r="B57" s="164" t="s">
         <v>81</v>
       </c>
       <c r="C57" s="53" t="s">
@@ -31412,8 +31436,8 @@
       </c>
     </row>
     <row r="58" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="29" x14ac:dyDescent="0.35">
-      <c r="A58" s="164"/>
-      <c r="B58" s="165"/>
+      <c r="A58" s="165"/>
+      <c r="B58" s="164"/>
       <c r="C58" s="56" t="s">
         <v>159</v>
       </c>
@@ -31422,8 +31446,8 @@
       </c>
     </row>
     <row r="59" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A59" s="164"/>
-      <c r="B59" s="165"/>
+      <c r="A59" s="165"/>
+      <c r="B59" s="164"/>
       <c r="C59" s="53" t="s">
         <v>161</v>
       </c>
@@ -31432,8 +31456,8 @@
       </c>
     </row>
     <row r="60" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="29" x14ac:dyDescent="0.35">
-      <c r="A60" s="164"/>
-      <c r="B60" s="165"/>
+      <c r="A60" s="165"/>
+      <c r="B60" s="164"/>
       <c r="C60" s="53" t="s">
         <v>163</v>
       </c>
@@ -31442,8 +31466,8 @@
       </c>
     </row>
     <row r="61" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A61" s="164"/>
-      <c r="B61" s="165"/>
+      <c r="A61" s="165"/>
+      <c r="B61" s="164"/>
       <c r="C61" s="34" t="s">
         <v>118</v>
       </c>
@@ -31452,8 +31476,8 @@
       </c>
     </row>
     <row r="62" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A62" s="164"/>
-      <c r="B62" s="165"/>
+      <c r="A62" s="165"/>
+      <c r="B62" s="164"/>
       <c r="C62" s="53" t="s">
         <v>166</v>
       </c>
@@ -31462,8 +31486,8 @@
       </c>
     </row>
     <row r="63" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A63" s="164"/>
-      <c r="B63" s="165"/>
+      <c r="A63" s="165"/>
+      <c r="B63" s="164"/>
       <c r="C63" s="53" t="s">
         <v>166</v>
       </c>
@@ -31472,16 +31496,16 @@
       </c>
     </row>
     <row r="64" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A64" s="164"/>
-      <c r="B64" s="165"/>
+      <c r="A64" s="165"/>
+      <c r="B64" s="164"/>
       <c r="C64" s="53"/>
       <c r="D64" s="43" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="164"/>
-      <c r="B65" s="165"/>
+      <c r="A65" s="165"/>
+      <c r="B65" s="164"/>
       <c r="C65" s="53" t="s">
         <v>169</v>
       </c>
@@ -31490,16 +31514,16 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="164"/>
-      <c r="B66" s="165"/>
+      <c r="A66" s="165"/>
+      <c r="B66" s="164"/>
       <c r="C66" s="53"/>
       <c r="D66" s="42" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="164"/>
-      <c r="B67" s="165"/>
+      <c r="A67" s="165"/>
+      <c r="B67" s="164"/>
       <c r="C67" s="53" t="s">
         <v>172</v>
       </c>
@@ -31508,8 +31532,8 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="164"/>
-      <c r="B68" s="165"/>
+      <c r="A68" s="165"/>
+      <c r="B68" s="164"/>
       <c r="C68" s="53" t="s">
         <v>174</v>
       </c>
@@ -31518,8 +31542,8 @@
       </c>
     </row>
     <row r="69" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A69" s="164"/>
-      <c r="B69" s="165"/>
+      <c r="A69" s="165"/>
+      <c r="B69" s="164"/>
       <c r="C69" s="56" t="s">
         <v>176</v>
       </c>
@@ -31528,8 +31552,8 @@
       </c>
     </row>
     <row r="70" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A70" s="164"/>
-      <c r="B70" s="165"/>
+      <c r="A70" s="165"/>
+      <c r="B70" s="164"/>
       <c r="C70" s="56" t="s">
         <v>178</v>
       </c>
@@ -31538,8 +31562,8 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="164"/>
-      <c r="B71" s="165"/>
+      <c r="A71" s="165"/>
+      <c r="B71" s="164"/>
       <c r="C71" s="53" t="s">
         <v>179</v>
       </c>
@@ -31548,8 +31572,8 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="164"/>
-      <c r="B72" s="165"/>
+      <c r="A72" s="165"/>
+      <c r="B72" s="164"/>
       <c r="C72" s="53" t="s">
         <v>181</v>
       </c>
@@ -31558,16 +31582,16 @@
       </c>
     </row>
     <row r="73" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="164"/>
-      <c r="B73" s="165"/>
+      <c r="A73" s="165"/>
+      <c r="B73" s="164"/>
       <c r="C73" s="53"/>
       <c r="D73" s="45" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="164"/>
-      <c r="B74" s="165"/>
+      <c r="A74" s="165"/>
+      <c r="B74" s="164"/>
       <c r="C74" s="53" t="s">
         <v>182</v>
       </c>
@@ -31576,17 +31600,17 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="164"/>
-      <c r="B75" s="165"/>
-      <c r="C75" s="158"/>
+      <c r="A75" s="165"/>
+      <c r="B75" s="164"/>
+      <c r="C75" s="171"/>
       <c r="D75" s="166" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="164"/>
-      <c r="B76" s="165"/>
-      <c r="C76" s="158"/>
+      <c r="A76" s="165"/>
+      <c r="B76" s="164"/>
+      <c r="C76" s="171"/>
       <c r="D76" s="166"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
@@ -31611,8 +31635,8 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{3ECA9ADB-6C26-4D30-9FA0-625C82AEEE29}" topLeftCell="A13">
-      <selection activeCell="D20" sqref="D20"/>
+    <customSheetView guid="{99CEABDF-88F7-4121-AD5F-66FD045725EC}">
+      <selection activeCell="A7" sqref="A7"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
     </customSheetView>
@@ -31621,13 +31645,29 @@
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
     </customSheetView>
-    <customSheetView guid="{99CEABDF-88F7-4121-AD5F-66FD045725EC}">
-      <selection activeCell="A7" sqref="A7"/>
+    <customSheetView guid="{3ECA9ADB-6C26-4D30-9FA0-625C82AEEE29}" topLeftCell="A13">
+      <selection activeCell="D20" sqref="D20"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="30">
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="A57:A76"/>
+    <mergeCell ref="B57:B76"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="A49:A54"/>
+    <mergeCell ref="B49:B54"/>
     <mergeCell ref="A7:A12"/>
     <mergeCell ref="B7:B12"/>
     <mergeCell ref="A43:A44"/>
@@ -31642,22 +31682,6 @@
     <mergeCell ref="B16:B25"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="B39:B40"/>
-    <mergeCell ref="A57:A76"/>
-    <mergeCell ref="B57:B76"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="A49:A54"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
@@ -31706,10 +31730,10 @@
       <c r="D3" s="40"/>
     </row>
     <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="159" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="170" t="s">
+      <c r="B4" s="160" t="s">
         <v>185</v>
       </c>
       <c r="C4" s="67" t="s">
@@ -31720,133 +31744,133 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="171"/>
-      <c r="B5" s="170"/>
-      <c r="C5" s="181" t="s">
+      <c r="A5" s="159"/>
+      <c r="B5" s="160"/>
+      <c r="C5" s="186" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="180" t="s">
+      <c r="D5" s="185" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="7.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="171"/>
-      <c r="B6" s="170"/>
-      <c r="C6" s="181"/>
-      <c r="D6" s="180"/>
+      <c r="A6" s="159"/>
+      <c r="B6" s="160"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="185"/>
     </row>
     <row r="7" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="171"/>
-      <c r="B7" s="170"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="160"/>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
     </row>
     <row r="8" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="171"/>
-      <c r="B8" s="170"/>
+      <c r="A8" s="159"/>
+      <c r="B8" s="160"/>
       <c r="C8" s="53"/>
       <c r="D8" s="53"/>
     </row>
     <row r="9" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="171"/>
-      <c r="B9" s="170"/>
+      <c r="A9" s="159"/>
+      <c r="B9" s="160"/>
       <c r="C9" s="66"/>
       <c r="D9" s="45"/>
     </row>
     <row r="10" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="173" t="s">
+      <c r="A10" s="162" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="170" t="s">
+      <c r="B10" s="160" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="183"/>
-      <c r="D10" s="180" t="s">
+      <c r="C10" s="184"/>
+      <c r="D10" s="185" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="173"/>
-      <c r="B11" s="170"/>
-      <c r="C11" s="183"/>
-      <c r="D11" s="180"/>
+      <c r="A11" s="162"/>
+      <c r="B11" s="160"/>
+      <c r="C11" s="184"/>
+      <c r="D11" s="185"/>
     </row>
     <row r="12" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="173"/>
-      <c r="B12" s="170"/>
-      <c r="C12" s="183"/>
-      <c r="D12" s="180"/>
+      <c r="A12" s="162"/>
+      <c r="B12" s="160"/>
+      <c r="C12" s="184"/>
+      <c r="D12" s="185"/>
     </row>
     <row r="13" spans="1:4" ht="31.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="156" t="s">
+      <c r="A13" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="165" t="s">
+      <c r="B13" s="164" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="182"/>
-      <c r="D13" s="180" t="s">
+      <c r="C13" s="187"/>
+      <c r="D13" s="185" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="156"/>
-      <c r="B14" s="165"/>
-      <c r="C14" s="182"/>
-      <c r="D14" s="180"/>
+      <c r="A14" s="163"/>
+      <c r="B14" s="164"/>
+      <c r="C14" s="187"/>
+      <c r="D14" s="185"/>
     </row>
     <row r="15" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="156"/>
-      <c r="B15" s="165"/>
-      <c r="C15" s="182"/>
+      <c r="A15" s="163"/>
+      <c r="B15" s="164"/>
+      <c r="C15" s="187"/>
       <c r="D15" s="45"/>
     </row>
     <row r="16" spans="1:4" ht="27.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="156"/>
-      <c r="B16" s="165"/>
-      <c r="C16" s="182"/>
+      <c r="A16" s="163"/>
+      <c r="B16" s="164"/>
+      <c r="C16" s="187"/>
       <c r="D16" s="45"/>
     </row>
     <row r="17" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="156"/>
-      <c r="B17" s="165"/>
-      <c r="C17" s="182"/>
+      <c r="A17" s="163"/>
+      <c r="B17" s="164"/>
+      <c r="C17" s="187"/>
       <c r="D17" s="45"/>
     </row>
     <row r="18" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="156"/>
-      <c r="B18" s="165"/>
-      <c r="C18" s="182"/>
+      <c r="A18" s="163"/>
+      <c r="B18" s="164"/>
+      <c r="C18" s="187"/>
       <c r="D18" s="45"/>
     </row>
     <row r="19" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="156"/>
-      <c r="B19" s="165"/>
-      <c r="C19" s="182"/>
+      <c r="A19" s="163"/>
+      <c r="B19" s="164"/>
+      <c r="C19" s="187"/>
       <c r="D19" s="45"/>
     </row>
     <row r="20" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="156"/>
-      <c r="B20" s="165"/>
-      <c r="C20" s="182"/>
+      <c r="A20" s="163"/>
+      <c r="B20" s="164"/>
+      <c r="C20" s="187"/>
       <c r="D20" s="45"/>
     </row>
     <row r="21" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="156"/>
-      <c r="B21" s="165"/>
-      <c r="C21" s="182"/>
+      <c r="A21" s="163"/>
+      <c r="B21" s="164"/>
+      <c r="C21" s="187"/>
       <c r="D21" s="45"/>
     </row>
     <row r="22" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="156"/>
-      <c r="B22" s="165"/>
-      <c r="C22" s="182"/>
+      <c r="A22" s="163"/>
+      <c r="B22" s="164"/>
+      <c r="C22" s="187"/>
       <c r="D22" s="45"/>
     </row>
     <row r="23" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="156"/>
-      <c r="B23" s="165"/>
-      <c r="C23" s="182"/>
+      <c r="A23" s="163"/>
+      <c r="B23" s="164"/>
+      <c r="C23" s="187"/>
       <c r="D23" s="53" t="s">
         <v>192</v>
       </c>
@@ -31944,10 +31968,10 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="174" t="s">
+      <c r="A32" s="188" t="s">
         <v>205</v>
       </c>
-      <c r="B32" s="177" t="s">
+      <c r="B32" s="191" t="s">
         <v>185</v>
       </c>
       <c r="C32" s="79" t="s">
@@ -31958,26 +31982,26 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="175"/>
-      <c r="B33" s="178"/>
+      <c r="A33" s="189"/>
+      <c r="B33" s="192"/>
       <c r="C33" s="65"/>
       <c r="D33" s="69"/>
     </row>
     <row r="34" spans="1:4" ht="9.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="175"/>
-      <c r="B34" s="178"/>
+      <c r="A34" s="189"/>
+      <c r="B34" s="192"/>
       <c r="C34" s="65"/>
       <c r="D34" s="69"/>
     </row>
     <row r="35" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="175"/>
-      <c r="B35" s="178"/>
+      <c r="A35" s="189"/>
+      <c r="B35" s="192"/>
       <c r="C35" s="65"/>
       <c r="D35" s="69"/>
     </row>
     <row r="36" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="176"/>
-      <c r="B36" s="179"/>
+      <c r="A36" s="190"/>
+      <c r="B36" s="193"/>
       <c r="C36" s="65" t="s">
         <v>208</v>
       </c>
@@ -32006,10 +32030,10 @@
       <c r="D38" s="40"/>
     </row>
     <row r="39" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="172" t="s">
+      <c r="A39" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="170" t="s">
+      <c r="B39" s="160" t="s">
         <v>185</v>
       </c>
       <c r="C39" s="70" t="s">
@@ -32020,8 +32044,8 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="172"/>
-      <c r="B40" s="170"/>
+      <c r="A40" s="161"/>
+      <c r="B40" s="160"/>
       <c r="C40" s="64" t="s">
         <v>188</v>
       </c>
@@ -32030,29 +32054,29 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="171" t="s">
+      <c r="A41" s="159" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="170" t="s">
+      <c r="B41" s="160" t="s">
         <v>185</v>
       </c>
-      <c r="C41" s="183" t="s">
+      <c r="C41" s="184" t="s">
         <v>212</v>
       </c>
-      <c r="D41" s="156" t="s">
+      <c r="D41" s="163" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="171"/>
-      <c r="B42" s="170"/>
-      <c r="C42" s="183"/>
-      <c r="D42" s="156"/>
+      <c r="A42" s="159"/>
+      <c r="B42" s="160"/>
+      <c r="C42" s="184"/>
+      <c r="D42" s="163"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="171"/>
-      <c r="B43" s="170"/>
-      <c r="C43" s="183" t="s">
+      <c r="A43" s="159"/>
+      <c r="B43" s="160"/>
+      <c r="C43" s="184" t="s">
         <v>188</v>
       </c>
       <c r="D43" s="166" t="s">
@@ -32060,54 +32084,54 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="171"/>
-      <c r="B44" s="170"/>
-      <c r="C44" s="183"/>
+      <c r="A44" s="159"/>
+      <c r="B44" s="160"/>
+      <c r="C44" s="184"/>
       <c r="D44" s="166"/>
     </row>
     <row r="45" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="164" t="s">
+      <c r="A45" s="165" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="165" t="s">
+      <c r="B45" s="164" t="s">
         <v>185</v>
       </c>
-      <c r="C45" s="187"/>
+      <c r="C45" s="180"/>
       <c r="D45" s="78" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="164"/>
-      <c r="B46" s="165"/>
-      <c r="C46" s="188"/>
-      <c r="D46" s="184" t="s">
+      <c r="A46" s="165"/>
+      <c r="B46" s="164"/>
+      <c r="C46" s="181"/>
+      <c r="D46" s="177" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="164"/>
-      <c r="B47" s="165"/>
-      <c r="C47" s="188"/>
-      <c r="D47" s="185"/>
+      <c r="A47" s="165"/>
+      <c r="B47" s="164"/>
+      <c r="C47" s="181"/>
+      <c r="D47" s="178"/>
     </row>
     <row r="48" spans="1:4" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="164"/>
-      <c r="B48" s="165"/>
-      <c r="C48" s="189"/>
-      <c r="D48" s="185"/>
+      <c r="A48" s="165"/>
+      <c r="B48" s="164"/>
+      <c r="C48" s="182"/>
+      <c r="D48" s="178"/>
     </row>
     <row r="49" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="164"/>
-      <c r="B49" s="165"/>
-      <c r="C49" s="159"/>
-      <c r="D49" s="185"/>
+      <c r="A49" s="165"/>
+      <c r="B49" s="164"/>
+      <c r="C49" s="172"/>
+      <c r="D49" s="178"/>
     </row>
     <row r="50" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="164"/>
-      <c r="B50" s="165"/>
-      <c r="C50" s="159"/>
-      <c r="D50" s="186"/>
+      <c r="A50" s="165"/>
+      <c r="B50" s="164"/>
+      <c r="C50" s="172"/>
+      <c r="D50" s="179"/>
     </row>
     <row r="51" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="35" t="s">
@@ -32130,10 +32154,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="165" t="s">
+      <c r="A53" s="164" t="s">
         <v>156</v>
       </c>
-      <c r="B53" s="165" t="s">
+      <c r="B53" s="164" t="s">
         <v>185</v>
       </c>
       <c r="C53" s="65" t="s">
@@ -32144,8 +32168,8 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="165"/>
-      <c r="B54" s="165"/>
+      <c r="A54" s="164"/>
+      <c r="B54" s="164"/>
       <c r="C54" s="65" t="s">
         <v>188</v>
       </c>
@@ -32154,8 +32178,8 @@
       </c>
     </row>
     <row r="55" spans="1:4" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="165"/>
-      <c r="B55" s="165"/>
+      <c r="A55" s="164"/>
+      <c r="B55" s="164"/>
       <c r="C55" s="65" t="s">
         <v>218</v>
       </c>
@@ -32164,9 +32188,9 @@
       </c>
     </row>
     <row r="56" spans="1:4" ht="34.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="165"/>
-      <c r="B56" s="165"/>
-      <c r="C56" s="190" t="s">
+      <c r="A56" s="164"/>
+      <c r="B56" s="164"/>
+      <c r="C56" s="183" t="s">
         <v>220</v>
       </c>
       <c r="D56" s="71" t="s">
@@ -32174,16 +32198,16 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="165"/>
-      <c r="B57" s="165"/>
-      <c r="C57" s="190"/>
+      <c r="A57" s="164"/>
+      <c r="B57" s="164"/>
+      <c r="C57" s="183"/>
       <c r="D57" s="43" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="165"/>
-      <c r="B58" s="165"/>
+      <c r="A58" s="164"/>
+      <c r="B58" s="164"/>
       <c r="C58" s="65" t="s">
         <v>223</v>
       </c>
@@ -32192,8 +32216,8 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="165"/>
-      <c r="B59" s="165"/>
+      <c r="A59" s="164"/>
+      <c r="B59" s="164"/>
       <c r="C59" s="65" t="s">
         <v>225</v>
       </c>
@@ -32202,9 +32226,9 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="165"/>
-      <c r="B60" s="165"/>
-      <c r="C60" s="190" t="s">
+      <c r="A60" s="164"/>
+      <c r="B60" s="164"/>
+      <c r="C60" s="183" t="s">
         <v>227</v>
       </c>
       <c r="D60" s="42" t="s">
@@ -32212,25 +32236,25 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="165"/>
-      <c r="B61" s="165"/>
-      <c r="C61" s="190"/>
+      <c r="A61" s="164"/>
+      <c r="B61" s="164"/>
+      <c r="C61" s="183"/>
       <c r="D61" s="42" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="165"/>
-      <c r="B62" s="165"/>
-      <c r="C62" s="190"/>
+      <c r="A62" s="164"/>
+      <c r="B62" s="164"/>
+      <c r="C62" s="183"/>
       <c r="D62" s="71" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="165"/>
-      <c r="B63" s="165"/>
-      <c r="C63" s="183" t="s">
+      <c r="A63" s="164"/>
+      <c r="B63" s="164"/>
+      <c r="C63" s="184" t="s">
         <v>231</v>
       </c>
       <c r="D63" s="41" t="s">
@@ -32238,29 +32262,29 @@
       </c>
     </row>
     <row r="64" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="165"/>
-      <c r="B64" s="165"/>
-      <c r="C64" s="183"/>
+      <c r="A64" s="164"/>
+      <c r="B64" s="164"/>
+      <c r="C64" s="184"/>
       <c r="D64" s="166" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="12.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="165"/>
-      <c r="B65" s="165"/>
-      <c r="C65" s="183"/>
+      <c r="A65" s="164"/>
+      <c r="B65" s="164"/>
+      <c r="C65" s="184"/>
       <c r="D65" s="166"/>
     </row>
     <row r="66" spans="1:4" ht="13.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="165"/>
-      <c r="B66" s="165"/>
-      <c r="C66" s="183"/>
+      <c r="A66" s="164"/>
+      <c r="B66" s="164"/>
+      <c r="C66" s="184"/>
       <c r="D66" s="166"/>
     </row>
     <row r="67" spans="1:4" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="165"/>
-      <c r="B67" s="165"/>
-      <c r="C67" s="183"/>
+      <c r="A67" s="164"/>
+      <c r="B67" s="164"/>
+      <c r="C67" s="184"/>
       <c r="D67" s="166"/>
     </row>
     <row r="68" spans="1:4" ht="11.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -32287,6 +32311,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="C13:C23"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C43:C44"/>
     <mergeCell ref="D64:D67"/>
     <mergeCell ref="D41:D42"/>
     <mergeCell ref="D46:D50"/>
@@ -32303,23 +32344,6 @@
     <mergeCell ref="B45:B50"/>
     <mergeCell ref="C49:C50"/>
     <mergeCell ref="C63:C67"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C13:C23"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B13:B23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -32328,7 +32352,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D278"/>
+  <dimension ref="A1:D282"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -32360,10 +32384,10 @@
       <c r="D2" s="88"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="191" t="s">
+      <c r="A3" s="194" t="s">
         <v>236</v>
       </c>
-      <c r="B3" s="191" t="s">
+      <c r="B3" s="194" t="s">
         <v>237</v>
       </c>
       <c r="C3" s="85" t="s">
@@ -32374,8 +32398,8 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="192"/>
-      <c r="B4" s="192"/>
+      <c r="A4" s="195"/>
+      <c r="B4" s="195"/>
       <c r="C4" s="84" t="s">
         <v>240</v>
       </c>
@@ -32384,8 +32408,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="193"/>
-      <c r="B5" s="193"/>
+      <c r="A5" s="196"/>
+      <c r="B5" s="196"/>
       <c r="C5" s="84" t="s">
         <v>240</v>
       </c>
@@ -32394,10 +32418,10 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="197" t="s">
+      <c r="A6" s="203" t="s">
         <v>243</v>
       </c>
-      <c r="B6" s="194" t="s">
+      <c r="B6" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C6" s="84"/>
@@ -32406,32 +32430,32 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="195"/>
+      <c r="A7" s="204"/>
+      <c r="B7" s="198"/>
       <c r="C7" s="84"/>
       <c r="D7" s="53" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="198"/>
-      <c r="B8" s="195"/>
+      <c r="A8" s="204"/>
+      <c r="B8" s="198"/>
       <c r="C8" s="84"/>
       <c r="D8" s="104" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="198"/>
-      <c r="B9" s="195"/>
+      <c r="A9" s="204"/>
+      <c r="B9" s="198"/>
       <c r="C9" s="84"/>
       <c r="D9" s="104" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="199"/>
-      <c r="B10" s="196"/>
+      <c r="A10" s="205"/>
+      <c r="B10" s="199"/>
       <c r="C10" s="84" t="s">
         <v>248</v>
       </c>
@@ -32440,10 +32464,10 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="191" t="s">
+      <c r="A11" s="194" t="s">
         <v>250</v>
       </c>
-      <c r="B11" s="194" t="s">
+      <c r="B11" s="197" t="s">
         <v>237</v>
       </c>
       <c r="C11" s="84" t="s">
@@ -32454,8 +32478,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="192"/>
-      <c r="B12" s="195"/>
+      <c r="A12" s="195"/>
+      <c r="B12" s="198"/>
       <c r="C12" s="84" t="s">
         <v>251</v>
       </c>
@@ -32464,8 +32488,8 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="193"/>
-      <c r="B13" s="196"/>
+      <c r="A13" s="196"/>
+      <c r="B13" s="199"/>
       <c r="C13" s="84" t="s">
         <v>253</v>
       </c>
@@ -32482,10 +32506,10 @@
       <c r="D14" s="88"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="161" t="s">
+      <c r="A15" s="174" t="s">
         <v>256</v>
       </c>
-      <c r="B15" s="194" t="s">
+      <c r="B15" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C15" s="99" t="s">
@@ -32496,8 +32520,8 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="162"/>
-      <c r="B16" s="196"/>
+      <c r="A16" s="175"/>
+      <c r="B16" s="199"/>
       <c r="C16" s="99" t="s">
         <v>259</v>
       </c>
@@ -32532,10 +32556,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="191" t="s">
+      <c r="A19" s="194" t="s">
         <v>266</v>
       </c>
-      <c r="B19" s="194" t="s">
+      <c r="B19" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C19" s="80" t="s">
@@ -32546,8 +32570,8 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="192"/>
-      <c r="B20" s="195"/>
+      <c r="A20" s="195"/>
+      <c r="B20" s="198"/>
       <c r="C20" s="53" t="s">
         <v>268</v>
       </c>
@@ -32556,8 +32580,8 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="192"/>
-      <c r="B21" s="195"/>
+      <c r="A21" s="195"/>
+      <c r="B21" s="198"/>
       <c r="C21" s="99" t="s">
         <v>270</v>
       </c>
@@ -32566,8 +32590,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="192"/>
-      <c r="B22" s="195"/>
+      <c r="A22" s="195"/>
+      <c r="B22" s="198"/>
       <c r="C22" s="99" t="s">
         <v>5</v>
       </c>
@@ -32576,8 +32600,8 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="192"/>
-      <c r="B23" s="195"/>
+      <c r="A23" s="195"/>
+      <c r="B23" s="198"/>
       <c r="C23" s="84" t="s">
         <v>238</v>
       </c>
@@ -32586,8 +32610,8 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="192"/>
-      <c r="B24" s="195"/>
+      <c r="A24" s="195"/>
+      <c r="B24" s="198"/>
       <c r="C24" s="84" t="s">
         <v>274</v>
       </c>
@@ -32596,8 +32620,8 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="192"/>
-      <c r="B25" s="195"/>
+      <c r="A25" s="195"/>
+      <c r="B25" s="198"/>
       <c r="C25" s="84" t="s">
         <v>276</v>
       </c>
@@ -32606,8 +32630,8 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="192"/>
-      <c r="B26" s="195"/>
+      <c r="A26" s="195"/>
+      <c r="B26" s="198"/>
       <c r="C26" s="84" t="s">
         <v>238</v>
       </c>
@@ -32616,8 +32640,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="192"/>
-      <c r="B27" s="195"/>
+      <c r="A27" s="195"/>
+      <c r="B27" s="198"/>
       <c r="C27" s="99" t="s">
         <v>279</v>
       </c>
@@ -32626,8 +32650,8 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="193"/>
-      <c r="B28" s="196"/>
+      <c r="A28" s="196"/>
+      <c r="B28" s="199"/>
       <c r="C28" s="99">
         <v>1.1000000000000001</v>
       </c>
@@ -32636,10 +32660,10 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="197" t="s">
+      <c r="A29" s="203" t="s">
         <v>281</v>
       </c>
-      <c r="B29" s="194" t="s">
+      <c r="B29" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C29" s="84" t="s">
@@ -32650,8 +32674,8 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="198"/>
-      <c r="B30" s="195"/>
+      <c r="A30" s="204"/>
+      <c r="B30" s="198"/>
       <c r="C30" s="84" t="s">
         <v>279</v>
       </c>
@@ -32660,8 +32684,8 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="198"/>
-      <c r="B31" s="195"/>
+      <c r="A31" s="204"/>
+      <c r="B31" s="198"/>
       <c r="C31" s="84">
         <v>3.3</v>
       </c>
@@ -32670,8 +32694,8 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="198"/>
-      <c r="B32" s="195"/>
+      <c r="A32" s="204"/>
+      <c r="B32" s="198"/>
       <c r="C32" s="90">
         <v>3</v>
       </c>
@@ -32680,8 +32704,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="199"/>
-      <c r="B33" s="196"/>
+      <c r="A33" s="205"/>
+      <c r="B33" s="199"/>
       <c r="C33" s="90">
         <v>3.5</v>
       </c>
@@ -32690,10 +32714,10 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="197" t="s">
+      <c r="A34" s="203" t="s">
         <v>287</v>
       </c>
-      <c r="B34" s="194" t="s">
+      <c r="B34" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C34" s="90"/>
@@ -32702,18 +32726,18 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="199"/>
-      <c r="B35" s="196"/>
+      <c r="A35" s="205"/>
+      <c r="B35" s="199"/>
       <c r="C35" s="84"/>
       <c r="D35" s="62" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="214" t="s">
+      <c r="A36" s="206" t="s">
         <v>290</v>
       </c>
-      <c r="B36" s="194" t="s">
+      <c r="B36" s="197" t="s">
         <v>244</v>
       </c>
       <c r="D36" s="62" t="s">
@@ -32721,8 +32745,8 @@
       </c>
     </row>
     <row r="37" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="214"/>
-      <c r="B37" s="195"/>
+      <c r="A37" s="206"/>
+      <c r="B37" s="198"/>
       <c r="C37" s="106" t="s">
         <v>292</v>
       </c>
@@ -32731,8 +32755,8 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="214"/>
-      <c r="B38" s="195"/>
+      <c r="A38" s="206"/>
+      <c r="B38" s="198"/>
       <c r="C38" s="53" t="s">
         <v>294</v>
       </c>
@@ -32741,8 +32765,8 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A39" s="214"/>
-      <c r="B39" s="195"/>
+      <c r="A39" s="206"/>
+      <c r="B39" s="198"/>
       <c r="C39" s="56" t="s">
         <v>296</v>
       </c>
@@ -32754,7 +32778,7 @@
       <c r="A40" s="108" t="s">
         <v>297</v>
       </c>
-      <c r="B40" s="194" t="s">
+      <c r="B40" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C40" s="84"/>
@@ -32764,7 +32788,7 @@
     </row>
     <row r="41" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="109"/>
-      <c r="B41" s="195"/>
+      <c r="B41" s="198"/>
       <c r="C41" s="84" t="s">
         <v>298</v>
       </c>
@@ -32774,7 +32798,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="100"/>
-      <c r="B42" s="196"/>
+      <c r="B42" s="199"/>
       <c r="C42" s="84"/>
       <c r="D42" s="107" t="s">
         <v>289</v>
@@ -32784,7 +32808,7 @@
       <c r="A43" s="108" t="s">
         <v>300</v>
       </c>
-      <c r="B43" s="194" t="s">
+      <c r="B43" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C43" s="84"/>
@@ -32794,28 +32818,28 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="100"/>
-      <c r="B44" s="196"/>
+      <c r="B44" s="199"/>
       <c r="C44" s="84"/>
       <c r="D44" s="107" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="191" t="s">
+      <c r="A45" s="194" t="s">
         <v>301</v>
       </c>
-      <c r="B45" s="194" t="s">
+      <c r="B45" s="197" t="s">
         <v>244</v>
       </c>
-      <c r="C45" s="209"/>
+      <c r="C45" s="207"/>
       <c r="D45" s="107" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="193"/>
-      <c r="B46" s="196"/>
-      <c r="C46" s="210"/>
+      <c r="A46" s="196"/>
+      <c r="B46" s="199"/>
+      <c r="C46" s="208"/>
       <c r="D46" s="107" t="s">
         <v>302</v>
       </c>
@@ -32865,10 +32889,10 @@
       <c r="D50" s="88"/>
     </row>
     <row r="51" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A51" s="214" t="s">
+      <c r="A51" s="206" t="s">
         <v>307</v>
       </c>
-      <c r="B51" s="215" t="s">
+      <c r="B51" s="212" t="s">
         <v>244</v>
       </c>
       <c r="C51" s="84" t="s">
@@ -32879,8 +32903,8 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A52" s="214"/>
-      <c r="B52" s="215"/>
+      <c r="A52" s="206"/>
+      <c r="B52" s="212"/>
       <c r="C52" s="84" t="s">
         <v>310</v>
       </c>
@@ -32889,8 +32913,8 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A53" s="214"/>
-      <c r="B53" s="215"/>
+      <c r="A53" s="206"/>
+      <c r="B53" s="212"/>
       <c r="C53" s="84" t="s">
         <v>308</v>
       </c>
@@ -32907,10 +32931,10 @@
       <c r="D54" s="88"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="156" t="s">
+      <c r="A55" s="163" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="190" t="s">
+      <c r="B55" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C55" s="53"/>
@@ -32919,8 +32943,8 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="156"/>
-      <c r="B56" s="190"/>
+      <c r="A56" s="163"/>
+      <c r="B56" s="183"/>
       <c r="C56" s="65" t="s">
         <v>314</v>
       </c>
@@ -32929,8 +32953,8 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="156"/>
-      <c r="B57" s="190"/>
+      <c r="A57" s="163"/>
+      <c r="B57" s="183"/>
       <c r="C57" s="65" t="s">
         <v>316</v>
       </c>
@@ -32939,8 +32963,8 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="156"/>
-      <c r="B58" s="190"/>
+      <c r="A58" s="163"/>
+      <c r="B58" s="183"/>
       <c r="C58" s="65" t="s">
         <v>316</v>
       </c>
@@ -32949,8 +32973,8 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="156"/>
-      <c r="B59" s="190"/>
+      <c r="A59" s="163"/>
+      <c r="B59" s="183"/>
       <c r="C59" s="65" t="s">
         <v>248</v>
       </c>
@@ -32959,8 +32983,8 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="156"/>
-      <c r="B60" s="190"/>
+      <c r="A60" s="163"/>
+      <c r="B60" s="183"/>
       <c r="C60" s="70" t="s">
         <v>248</v>
       </c>
@@ -32969,10 +32993,10 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="161" t="s">
+      <c r="A61" s="174" t="s">
         <v>26</v>
       </c>
-      <c r="B61" s="194" t="s">
+      <c r="B61" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C61" s="65" t="s">
@@ -32983,8 +33007,8 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="200"/>
-      <c r="B62" s="195"/>
+      <c r="A62" s="215"/>
+      <c r="B62" s="198"/>
       <c r="C62" s="65" t="s">
         <v>322</v>
       </c>
@@ -32993,8 +33017,8 @@
       </c>
     </row>
     <row r="63" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A63" s="162"/>
-      <c r="B63" s="196"/>
+      <c r="A63" s="175"/>
+      <c r="B63" s="199"/>
       <c r="C63" s="103" t="s">
         <v>324</v>
       </c>
@@ -33043,10 +33067,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="156" t="s">
+      <c r="A67" s="163" t="s">
         <v>330</v>
       </c>
-      <c r="B67" s="190" t="s">
+      <c r="B67" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C67" s="53" t="s">
@@ -33057,24 +33081,24 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="156"/>
-      <c r="B68" s="190"/>
+      <c r="A68" s="163"/>
+      <c r="B68" s="183"/>
       <c r="C68" s="53"/>
       <c r="D68" s="71" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="156"/>
-      <c r="B69" s="190"/>
+      <c r="A69" s="163"/>
+      <c r="B69" s="183"/>
       <c r="C69" s="53"/>
       <c r="D69" s="53" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="156"/>
-      <c r="B70" s="190"/>
+      <c r="A70" s="163"/>
+      <c r="B70" s="183"/>
       <c r="C70" s="65" t="s">
         <v>335</v>
       </c>
@@ -33083,8 +33107,8 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="156"/>
-      <c r="B71" s="190"/>
+      <c r="A71" s="163"/>
+      <c r="B71" s="183"/>
       <c r="C71" s="70" t="s">
         <v>337</v>
       </c>
@@ -33105,10 +33129,10 @@
       <c r="D72" s="53"/>
     </row>
     <row r="73" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A73" s="211" t="s">
+      <c r="A73" s="209" t="s">
         <v>121</v>
       </c>
-      <c r="B73" s="194" t="s">
+      <c r="B73" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C73" s="53"/>
@@ -33117,8 +33141,8 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="212"/>
-      <c r="B74" s="195"/>
+      <c r="A74" s="210"/>
+      <c r="B74" s="198"/>
       <c r="C74" s="70" t="s">
         <v>341</v>
       </c>
@@ -33127,8 +33151,8 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="212"/>
-      <c r="B75" s="195"/>
+      <c r="A75" s="210"/>
+      <c r="B75" s="198"/>
       <c r="C75" s="70" t="s">
         <v>343</v>
       </c>
@@ -33137,8 +33161,8 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="212"/>
-      <c r="B76" s="195"/>
+      <c r="A76" s="210"/>
+      <c r="B76" s="198"/>
       <c r="C76" s="91" t="s">
         <v>345</v>
       </c>
@@ -33147,8 +33171,8 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="212"/>
-      <c r="B77" s="195"/>
+      <c r="A77" s="210"/>
+      <c r="B77" s="198"/>
       <c r="C77" s="70" t="s">
         <v>343</v>
       </c>
@@ -33157,8 +33181,8 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="212"/>
-      <c r="B78" s="195"/>
+      <c r="A78" s="210"/>
+      <c r="B78" s="198"/>
       <c r="C78" s="70" t="s">
         <v>348</v>
       </c>
@@ -33167,8 +33191,8 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="212"/>
-      <c r="B79" s="195"/>
+      <c r="A79" s="210"/>
+      <c r="B79" s="198"/>
       <c r="C79" s="70" t="s">
         <v>343</v>
       </c>
@@ -33177,8 +33201,8 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="212"/>
-      <c r="B80" s="195"/>
+      <c r="A80" s="210"/>
+      <c r="B80" s="198"/>
       <c r="C80" s="70" t="s">
         <v>351</v>
       </c>
@@ -33187,8 +33211,8 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="212"/>
-      <c r="B81" s="195"/>
+      <c r="A81" s="210"/>
+      <c r="B81" s="198"/>
       <c r="C81" s="70" t="s">
         <v>353</v>
       </c>
@@ -33197,8 +33221,8 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" s="212"/>
-      <c r="B82" s="195"/>
+      <c r="A82" s="210"/>
+      <c r="B82" s="198"/>
       <c r="C82" s="70" t="s">
         <v>343</v>
       </c>
@@ -33207,8 +33231,8 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="212"/>
-      <c r="B83" s="195"/>
+      <c r="A83" s="210"/>
+      <c r="B83" s="198"/>
       <c r="C83" s="70" t="s">
         <v>353</v>
       </c>
@@ -33217,8 +33241,8 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="212"/>
-      <c r="B84" s="195"/>
+      <c r="A84" s="210"/>
+      <c r="B84" s="198"/>
       <c r="C84" s="70" t="s">
         <v>343</v>
       </c>
@@ -33227,8 +33251,8 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="212"/>
-      <c r="B85" s="195"/>
+      <c r="A85" s="210"/>
+      <c r="B85" s="198"/>
       <c r="C85" s="70" t="s">
         <v>248</v>
       </c>
@@ -33237,8 +33261,8 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="212"/>
-      <c r="B86" s="195"/>
+      <c r="A86" s="210"/>
+      <c r="B86" s="198"/>
       <c r="C86" s="70" t="s">
         <v>248</v>
       </c>
@@ -33247,8 +33271,8 @@
       </c>
     </row>
     <row r="87" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A87" s="212"/>
-      <c r="B87" s="195"/>
+      <c r="A87" s="210"/>
+      <c r="B87" s="198"/>
       <c r="C87" s="91" t="s">
         <v>359</v>
       </c>
@@ -33257,8 +33281,8 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" s="213"/>
-      <c r="B88" s="196"/>
+      <c r="A88" s="211"/>
+      <c r="B88" s="199"/>
       <c r="C88" s="70" t="s">
         <v>248</v>
       </c>
@@ -33307,10 +33331,10 @@
       <c r="D91" s="53"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" s="161" t="s">
+      <c r="A92" s="174" t="s">
         <v>368</v>
       </c>
-      <c r="B92" s="194" t="s">
+      <c r="B92" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C92" s="70" t="s">
@@ -33319,8 +33343,8 @@
       <c r="D92" s="53"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" s="162"/>
-      <c r="B93" s="196"/>
+      <c r="A93" s="175"/>
+      <c r="B93" s="199"/>
       <c r="C93" s="70" t="s">
         <v>337</v>
       </c>
@@ -33337,10 +33361,10 @@
       <c r="D94" s="87"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" s="161" t="s">
+      <c r="A95" s="174" t="s">
         <v>369</v>
       </c>
-      <c r="B95" s="194" t="s">
+      <c r="B95" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C95" s="53"/>
@@ -33349,24 +33373,24 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" s="200"/>
-      <c r="B96" s="195"/>
+      <c r="A96" s="215"/>
+      <c r="B96" s="198"/>
       <c r="C96" s="53"/>
       <c r="D96" s="53" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" s="200"/>
-      <c r="B97" s="195"/>
+      <c r="A97" s="215"/>
+      <c r="B97" s="198"/>
       <c r="C97" s="53"/>
       <c r="D97" s="53" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" s="200"/>
-      <c r="B98" s="195"/>
+      <c r="A98" s="215"/>
+      <c r="B98" s="198"/>
       <c r="C98" s="53" t="s">
         <v>373</v>
       </c>
@@ -33375,8 +33399,8 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" s="200"/>
-      <c r="B99" s="195"/>
+      <c r="A99" s="215"/>
+      <c r="B99" s="198"/>
       <c r="C99" s="53" t="s">
         <v>375</v>
       </c>
@@ -33385,8 +33409,8 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" s="200"/>
-      <c r="B100" s="195"/>
+      <c r="A100" s="215"/>
+      <c r="B100" s="198"/>
       <c r="C100" s="53" t="s">
         <v>377</v>
       </c>
@@ -33395,8 +33419,8 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" s="200"/>
-      <c r="B101" s="195"/>
+      <c r="A101" s="215"/>
+      <c r="B101" s="198"/>
       <c r="C101" s="56" t="s">
         <v>379</v>
       </c>
@@ -33405,8 +33429,8 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" s="200"/>
-      <c r="B102" s="195"/>
+      <c r="A102" s="215"/>
+      <c r="B102" s="198"/>
       <c r="C102" s="53" t="s">
         <v>41</v>
       </c>
@@ -33415,8 +33439,8 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" s="200"/>
-      <c r="B103" s="195"/>
+      <c r="A103" s="215"/>
+      <c r="B103" s="198"/>
       <c r="C103" s="90" t="s">
         <v>343</v>
       </c>
@@ -33425,8 +33449,8 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" s="200"/>
-      <c r="B104" s="195"/>
+      <c r="A104" s="215"/>
+      <c r="B104" s="198"/>
       <c r="C104" s="90" t="s">
         <v>353</v>
       </c>
@@ -33435,8 +33459,8 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" s="200"/>
-      <c r="B105" s="195"/>
+      <c r="A105" s="215"/>
+      <c r="B105" s="198"/>
       <c r="C105" s="90" t="s">
         <v>377</v>
       </c>
@@ -33445,8 +33469,8 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" s="200"/>
-      <c r="B106" s="195"/>
+      <c r="A106" s="215"/>
+      <c r="B106" s="198"/>
       <c r="C106" s="90" t="s">
         <v>343</v>
       </c>
@@ -33455,8 +33479,8 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" s="200"/>
-      <c r="B107" s="195"/>
+      <c r="A107" s="215"/>
+      <c r="B107" s="198"/>
       <c r="C107" s="90" t="s">
         <v>248</v>
       </c>
@@ -33465,8 +33489,8 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" s="200"/>
-      <c r="B108" s="195"/>
+      <c r="A108" s="215"/>
+      <c r="B108" s="198"/>
       <c r="C108" s="90" t="s">
         <v>248</v>
       </c>
@@ -33475,8 +33499,8 @@
       </c>
     </row>
     <row r="109" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A109" s="200"/>
-      <c r="B109" s="195"/>
+      <c r="A109" s="215"/>
+      <c r="B109" s="198"/>
       <c r="C109" s="91" t="s">
         <v>359</v>
       </c>
@@ -33485,8 +33509,8 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" s="162"/>
-      <c r="B110" s="196"/>
+      <c r="A110" s="175"/>
+      <c r="B110" s="199"/>
       <c r="C110" s="90" t="s">
         <v>248</v>
       </c>
@@ -33495,10 +33519,10 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" s="201" t="s">
+      <c r="A111" s="216" t="s">
         <v>36</v>
       </c>
-      <c r="B111" s="194" t="s">
+      <c r="B111" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C111" s="113" t="s">
@@ -33509,8 +33533,8 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" s="202"/>
-      <c r="B112" s="195"/>
+      <c r="A112" s="217"/>
+      <c r="B112" s="198"/>
       <c r="C112" s="53" t="s">
         <v>383</v>
       </c>
@@ -33519,16 +33543,16 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" s="202"/>
-      <c r="B113" s="195"/>
+      <c r="A113" s="217"/>
+      <c r="B113" s="198"/>
       <c r="C113" s="53"/>
       <c r="D113" s="53" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A114" s="202"/>
-      <c r="B114" s="195"/>
+      <c r="A114" s="217"/>
+      <c r="B114" s="198"/>
       <c r="C114" s="56" t="s">
         <v>386</v>
       </c>
@@ -33537,8 +33561,8 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" s="202"/>
-      <c r="B115" s="195"/>
+      <c r="A115" s="217"/>
+      <c r="B115" s="198"/>
       <c r="C115" s="56" t="s">
         <v>343</v>
       </c>
@@ -33547,8 +33571,8 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" s="202"/>
-      <c r="B116" s="195"/>
+      <c r="A116" s="217"/>
+      <c r="B116" s="198"/>
       <c r="C116" s="56" t="s">
         <v>345</v>
       </c>
@@ -33557,8 +33581,8 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" s="202"/>
-      <c r="B117" s="195"/>
+      <c r="A117" s="217"/>
+      <c r="B117" s="198"/>
       <c r="C117" s="56" t="s">
         <v>348</v>
       </c>
@@ -33567,8 +33591,8 @@
       </c>
     </row>
     <row r="118" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A118" s="202"/>
-      <c r="B118" s="195"/>
+      <c r="A118" s="217"/>
+      <c r="B118" s="198"/>
       <c r="C118" s="56" t="s">
         <v>389</v>
       </c>
@@ -33577,8 +33601,8 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" s="202"/>
-      <c r="B119" s="195"/>
+      <c r="A119" s="217"/>
+      <c r="B119" s="198"/>
       <c r="C119" s="90" t="s">
         <v>343</v>
       </c>
@@ -33587,8 +33611,8 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" s="202"/>
-      <c r="B120" s="195"/>
+      <c r="A120" s="217"/>
+      <c r="B120" s="198"/>
       <c r="C120" s="90" t="s">
         <v>351</v>
       </c>
@@ -33597,8 +33621,8 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" s="202"/>
-      <c r="B121" s="195"/>
+      <c r="A121" s="217"/>
+      <c r="B121" s="198"/>
       <c r="C121" s="90" t="s">
         <v>353</v>
       </c>
@@ -33607,8 +33631,8 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" s="202"/>
-      <c r="B122" s="195"/>
+      <c r="A122" s="217"/>
+      <c r="B122" s="198"/>
       <c r="C122" s="90" t="s">
         <v>343</v>
       </c>
@@ -33617,8 +33641,8 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" s="202"/>
-      <c r="B123" s="195"/>
+      <c r="A123" s="217"/>
+      <c r="B123" s="198"/>
       <c r="C123" s="90" t="s">
         <v>353</v>
       </c>
@@ -33627,8 +33651,8 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" s="202"/>
-      <c r="B124" s="195"/>
+      <c r="A124" s="217"/>
+      <c r="B124" s="198"/>
       <c r="C124" s="90" t="s">
         <v>377</v>
       </c>
@@ -33637,8 +33661,8 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" s="202"/>
-      <c r="B125" s="195"/>
+      <c r="A125" s="217"/>
+      <c r="B125" s="198"/>
       <c r="C125" s="90" t="s">
         <v>343</v>
       </c>
@@ -33647,8 +33671,8 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" s="202"/>
-      <c r="B126" s="195"/>
+      <c r="A126" s="217"/>
+      <c r="B126" s="198"/>
       <c r="C126" s="90" t="s">
         <v>248</v>
       </c>
@@ -33657,8 +33681,8 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" s="202"/>
-      <c r="B127" s="195"/>
+      <c r="A127" s="217"/>
+      <c r="B127" s="198"/>
       <c r="C127" s="90" t="s">
         <v>248</v>
       </c>
@@ -33667,8 +33691,8 @@
       </c>
     </row>
     <row r="128" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A128" s="202"/>
-      <c r="B128" s="195"/>
+      <c r="A128" s="217"/>
+      <c r="B128" s="198"/>
       <c r="C128" s="91" t="s">
         <v>359</v>
       </c>
@@ -33677,8 +33701,8 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" s="203"/>
-      <c r="B129" s="196"/>
+      <c r="A129" s="218"/>
+      <c r="B129" s="199"/>
       <c r="C129" s="90" t="s">
         <v>248</v>
       </c>
@@ -33687,13 +33711,13 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" s="161" t="s">
+      <c r="A130" s="174" t="s">
         <v>205</v>
       </c>
-      <c r="B130" s="194" t="s">
+      <c r="B130" s="197" t="s">
         <v>244</v>
       </c>
-      <c r="C130" s="204" t="s">
+      <c r="C130" s="219" t="s">
         <v>392</v>
       </c>
       <c r="D130" s="80" t="s">
@@ -33701,17 +33725,17 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" s="200"/>
-      <c r="B131" s="195"/>
-      <c r="C131" s="205"/>
+      <c r="A131" s="215"/>
+      <c r="B131" s="198"/>
+      <c r="C131" s="220"/>
       <c r="D131" s="53" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" s="200"/>
-      <c r="B132" s="195"/>
-      <c r="C132" s="206" t="s">
+      <c r="A132" s="215"/>
+      <c r="B132" s="198"/>
+      <c r="C132" s="221" t="s">
         <v>395</v>
       </c>
       <c r="D132" s="53" t="s">
@@ -33719,16 +33743,16 @@
       </c>
     </row>
     <row r="133" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A133" s="200"/>
-      <c r="B133" s="195"/>
-      <c r="C133" s="206"/>
+      <c r="A133" s="215"/>
+      <c r="B133" s="198"/>
+      <c r="C133" s="221"/>
       <c r="D133" s="56" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" s="200"/>
-      <c r="B134" s="195"/>
+      <c r="A134" s="215"/>
+      <c r="B134" s="198"/>
       <c r="C134" s="70" t="s">
         <v>398</v>
       </c>
@@ -33737,8 +33761,8 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" s="200"/>
-      <c r="B135" s="195"/>
+      <c r="A135" s="215"/>
+      <c r="B135" s="198"/>
       <c r="C135" s="70">
         <v>2.1</v>
       </c>
@@ -33747,8 +33771,8 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" s="200"/>
-      <c r="B136" s="195"/>
+      <c r="A136" s="215"/>
+      <c r="B136" s="198"/>
       <c r="C136" s="70" t="s">
         <v>392</v>
       </c>
@@ -33757,8 +33781,8 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" s="200"/>
-      <c r="B137" s="195"/>
+      <c r="A137" s="215"/>
+      <c r="B137" s="198"/>
       <c r="C137" s="70" t="s">
         <v>392</v>
       </c>
@@ -33767,8 +33791,8 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" s="200"/>
-      <c r="B138" s="195"/>
+      <c r="A138" s="215"/>
+      <c r="B138" s="198"/>
       <c r="C138" s="70" t="s">
         <v>392</v>
       </c>
@@ -33777,8 +33801,8 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" s="200"/>
-      <c r="B139" s="195"/>
+      <c r="A139" s="215"/>
+      <c r="B139" s="198"/>
       <c r="C139" s="93" t="s">
         <v>404</v>
       </c>
@@ -33787,8 +33811,8 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" s="200"/>
-      <c r="B140" s="195"/>
+      <c r="A140" s="215"/>
+      <c r="B140" s="198"/>
       <c r="C140" s="70">
         <v>2.1</v>
       </c>
@@ -33797,8 +33821,8 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" s="200"/>
-      <c r="B141" s="195"/>
+      <c r="A141" s="215"/>
+      <c r="B141" s="198"/>
       <c r="C141" s="70" t="s">
         <v>392</v>
       </c>
@@ -33807,8 +33831,8 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" s="200"/>
-      <c r="B142" s="195"/>
+      <c r="A142" s="215"/>
+      <c r="B142" s="198"/>
       <c r="C142" s="70" t="s">
         <v>392</v>
       </c>
@@ -33817,8 +33841,8 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" s="200"/>
-      <c r="B143" s="195"/>
+      <c r="A143" s="215"/>
+      <c r="B143" s="198"/>
       <c r="C143" s="70">
         <v>2.1</v>
       </c>
@@ -33827,10 +33851,10 @@
       </c>
     </row>
     <row r="144" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="201" t="s">
+      <c r="A144" s="216" t="s">
         <v>409</v>
       </c>
-      <c r="B144" s="194" t="s">
+      <c r="B144" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C144" s="53" t="s">
@@ -33841,8 +33865,8 @@
       </c>
     </row>
     <row r="145" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A145" s="202"/>
-      <c r="B145" s="195"/>
+      <c r="A145" s="217"/>
+      <c r="B145" s="198"/>
       <c r="C145" s="56" t="s">
         <v>412</v>
       </c>
@@ -33851,8 +33875,8 @@
       </c>
     </row>
     <row r="146" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="203"/>
-      <c r="B146" s="196"/>
+      <c r="A146" s="218"/>
+      <c r="B146" s="199"/>
       <c r="C146" s="53" t="s">
         <v>414</v>
       </c>
@@ -33861,10 +33885,10 @@
       </c>
     </row>
     <row r="147" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="161" t="s">
+      <c r="A147" s="174" t="s">
         <v>416</v>
       </c>
-      <c r="B147" s="194" t="s">
+      <c r="B147" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C147" s="70" t="s">
@@ -33873,8 +33897,8 @@
       <c r="D147" s="53"/>
     </row>
     <row r="148" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="200"/>
-      <c r="B148" s="195"/>
+      <c r="A148" s="215"/>
+      <c r="B148" s="198"/>
       <c r="C148" s="70" t="s">
         <v>404</v>
       </c>
@@ -33883,8 +33907,8 @@
       </c>
     </row>
     <row r="149" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="200"/>
-      <c r="B149" s="195"/>
+      <c r="A149" s="215"/>
+      <c r="B149" s="198"/>
       <c r="C149" s="70">
         <v>2.1</v>
       </c>
@@ -33893,8 +33917,8 @@
       </c>
     </row>
     <row r="150" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="200"/>
-      <c r="B150" s="195"/>
+      <c r="A150" s="215"/>
+      <c r="B150" s="198"/>
       <c r="C150" s="70" t="s">
         <v>395</v>
       </c>
@@ -33903,8 +33927,8 @@
       </c>
     </row>
     <row r="151" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="200"/>
-      <c r="B151" s="195"/>
+      <c r="A151" s="215"/>
+      <c r="B151" s="198"/>
       <c r="C151" s="70" t="s">
         <v>392</v>
       </c>
@@ -33933,10 +33957,10 @@
       <c r="D153" s="53"/>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A154" s="161" t="s">
+      <c r="A154" s="174" t="s">
         <v>420</v>
       </c>
-      <c r="B154" s="194" t="s">
+      <c r="B154" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C154" s="53"/>
@@ -33945,24 +33969,24 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A155" s="200"/>
-      <c r="B155" s="195"/>
+      <c r="A155" s="215"/>
+      <c r="B155" s="198"/>
       <c r="C155" s="53"/>
       <c r="D155" s="53" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A156" s="200"/>
-      <c r="B156" s="195"/>
+      <c r="A156" s="215"/>
+      <c r="B156" s="198"/>
       <c r="C156" s="53"/>
       <c r="D156" s="53" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A157" s="200"/>
-      <c r="B157" s="195"/>
+      <c r="A157" s="215"/>
+      <c r="B157" s="198"/>
       <c r="C157" s="53" t="s">
         <v>422</v>
       </c>
@@ -33971,8 +33995,8 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A158" s="200"/>
-      <c r="B158" s="195"/>
+      <c r="A158" s="215"/>
+      <c r="B158" s="198"/>
       <c r="C158" s="53" t="s">
         <v>423</v>
       </c>
@@ -33981,8 +34005,8 @@
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A159" s="200"/>
-      <c r="B159" s="195"/>
+      <c r="A159" s="215"/>
+      <c r="B159" s="198"/>
       <c r="C159" s="53" t="s">
         <v>316</v>
       </c>
@@ -33991,8 +34015,8 @@
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A160" s="200"/>
-      <c r="B160" s="195"/>
+      <c r="A160" s="215"/>
+      <c r="B160" s="198"/>
       <c r="C160" s="53" t="s">
         <v>248</v>
       </c>
@@ -34001,10 +34025,10 @@
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A161" s="156" t="s">
+      <c r="A161" s="163" t="s">
         <v>426</v>
       </c>
-      <c r="B161" s="190" t="s">
+      <c r="B161" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C161" s="71" t="s">
@@ -34015,8 +34039,8 @@
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A162" s="156"/>
-      <c r="B162" s="190"/>
+      <c r="A162" s="163"/>
+      <c r="B162" s="183"/>
       <c r="C162" s="53" t="s">
         <v>429</v>
       </c>
@@ -34025,42 +34049,42 @@
       </c>
     </row>
     <row r="163" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A163" s="156"/>
-      <c r="B163" s="190"/>
+      <c r="A163" s="163"/>
+      <c r="B163" s="183"/>
       <c r="C163" s="94" t="s">
         <v>431</v>
       </c>
-      <c r="D163" s="194" t="s">
+      <c r="D163" s="197" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A164" s="156"/>
-      <c r="B164" s="190"/>
+      <c r="A164" s="163"/>
+      <c r="B164" s="183"/>
       <c r="C164" s="94" t="s">
         <v>433</v>
       </c>
-      <c r="D164" s="195"/>
+      <c r="D164" s="198"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A165" s="156"/>
-      <c r="B165" s="190"/>
+      <c r="A165" s="163"/>
+      <c r="B165" s="183"/>
       <c r="C165" s="94" t="s">
         <v>434</v>
       </c>
-      <c r="D165" s="195"/>
+      <c r="D165" s="198"/>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A166" s="156"/>
-      <c r="B166" s="190"/>
+      <c r="A166" s="163"/>
+      <c r="B166" s="183"/>
       <c r="C166" s="94" t="s">
         <v>435</v>
       </c>
-      <c r="D166" s="195"/>
+      <c r="D166" s="198"/>
     </row>
     <row r="167" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A167" s="156"/>
-      <c r="B167" s="190"/>
+      <c r="A167" s="163"/>
+      <c r="B167" s="183"/>
       <c r="C167" s="94" t="s">
         <v>436</v>
       </c>
@@ -34083,10 +34107,10 @@
       </c>
     </row>
     <row r="169" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="216" t="s">
+      <c r="A169" s="200" t="s">
         <v>43</v>
       </c>
-      <c r="B169" s="194" t="s">
+      <c r="B169" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C169" s="53" t="s">
@@ -34097,8 +34121,8 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A170" s="217"/>
-      <c r="B170" s="195"/>
+      <c r="A170" s="201"/>
+      <c r="B170" s="198"/>
       <c r="C170" s="53" t="s">
         <v>439</v>
       </c>
@@ -34107,8 +34131,8 @@
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A171" s="217"/>
-      <c r="B171" s="195"/>
+      <c r="A171" s="201"/>
+      <c r="B171" s="198"/>
       <c r="C171" s="53" t="s">
         <v>440</v>
       </c>
@@ -34117,8 +34141,8 @@
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A172" s="217"/>
-      <c r="B172" s="195"/>
+      <c r="A172" s="201"/>
+      <c r="B172" s="198"/>
       <c r="C172" s="53" t="s">
         <v>441</v>
       </c>
@@ -34127,8 +34151,8 @@
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A173" s="217"/>
-      <c r="B173" s="195"/>
+      <c r="A173" s="201"/>
+      <c r="B173" s="198"/>
       <c r="C173" s="53" t="s">
         <v>442</v>
       </c>
@@ -34137,8 +34161,8 @@
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A174" s="217"/>
-      <c r="B174" s="195"/>
+      <c r="A174" s="201"/>
+      <c r="B174" s="198"/>
       <c r="C174" s="53" t="s">
         <v>443</v>
       </c>
@@ -34147,8 +34171,8 @@
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A175" s="217"/>
-      <c r="B175" s="195"/>
+      <c r="A175" s="201"/>
+      <c r="B175" s="198"/>
       <c r="C175" s="53" t="s">
         <v>445</v>
       </c>
@@ -34157,8 +34181,8 @@
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A176" s="217"/>
-      <c r="B176" s="195"/>
+      <c r="A176" s="201"/>
+      <c r="B176" s="198"/>
       <c r="C176" s="53" t="s">
         <v>446</v>
       </c>
@@ -34167,8 +34191,8 @@
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A177" s="217"/>
-      <c r="B177" s="195"/>
+      <c r="A177" s="201"/>
+      <c r="B177" s="198"/>
       <c r="C177" s="53" t="s">
         <v>447</v>
       </c>
@@ -34177,8 +34201,8 @@
       </c>
     </row>
     <row r="178" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A178" s="217"/>
-      <c r="B178" s="195"/>
+      <c r="A178" s="201"/>
+      <c r="B178" s="198"/>
       <c r="C178" s="95" t="s">
         <v>448</v>
       </c>
@@ -34187,8 +34211,8 @@
       </c>
     </row>
     <row r="179" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A179" s="217"/>
-      <c r="B179" s="195"/>
+      <c r="A179" s="201"/>
+      <c r="B179" s="198"/>
       <c r="C179" s="56" t="s">
         <v>450</v>
       </c>
@@ -34197,8 +34221,8 @@
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A180" s="217"/>
-      <c r="B180" s="195"/>
+      <c r="A180" s="201"/>
+      <c r="B180" s="198"/>
       <c r="C180" s="53" t="s">
         <v>451</v>
       </c>
@@ -34207,8 +34231,8 @@
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A181" s="217"/>
-      <c r="B181" s="195"/>
+      <c r="A181" s="201"/>
+      <c r="B181" s="198"/>
       <c r="C181" s="53" t="s">
         <v>452</v>
       </c>
@@ -34217,8 +34241,8 @@
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A182" s="217"/>
-      <c r="B182" s="195"/>
+      <c r="A182" s="201"/>
+      <c r="B182" s="198"/>
       <c r="C182" s="53" t="s">
         <v>454</v>
       </c>
@@ -34227,8 +34251,8 @@
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A183" s="217"/>
-      <c r="B183" s="195"/>
+      <c r="A183" s="201"/>
+      <c r="B183" s="198"/>
       <c r="C183" s="53" t="s">
         <v>438</v>
       </c>
@@ -34237,8 +34261,8 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A184" s="217"/>
-      <c r="B184" s="195"/>
+      <c r="A184" s="201"/>
+      <c r="B184" s="198"/>
       <c r="C184" s="53" t="s">
         <v>455</v>
       </c>
@@ -34247,8 +34271,8 @@
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A185" s="217"/>
-      <c r="B185" s="195"/>
+      <c r="A185" s="201"/>
+      <c r="B185" s="198"/>
       <c r="C185" s="53" t="s">
         <v>443</v>
       </c>
@@ -34257,8 +34281,8 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A186" s="217"/>
-      <c r="B186" s="195"/>
+      <c r="A186" s="201"/>
+      <c r="B186" s="198"/>
       <c r="C186" s="53" t="s">
         <v>457</v>
       </c>
@@ -34267,16 +34291,16 @@
       </c>
     </row>
     <row r="187" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A187" s="217"/>
-      <c r="B187" s="195"/>
+      <c r="A187" s="201"/>
+      <c r="B187" s="198"/>
       <c r="C187" s="53"/>
       <c r="D187" s="81" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A188" s="217"/>
-      <c r="B188" s="195"/>
+      <c r="A188" s="201"/>
+      <c r="B188" s="198"/>
       <c r="C188" s="53" t="s">
         <v>459</v>
       </c>
@@ -34285,8 +34309,8 @@
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A189" s="217"/>
-      <c r="B189" s="195"/>
+      <c r="A189" s="201"/>
+      <c r="B189" s="198"/>
       <c r="C189" s="53" t="s">
         <v>438</v>
       </c>
@@ -34295,8 +34319,8 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A190" s="217"/>
-      <c r="B190" s="195"/>
+      <c r="A190" s="201"/>
+      <c r="B190" s="198"/>
       <c r="C190" s="53" t="s">
         <v>460</v>
       </c>
@@ -34305,8 +34329,8 @@
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A191" s="217"/>
-      <c r="B191" s="195"/>
+      <c r="A191" s="201"/>
+      <c r="B191" s="198"/>
       <c r="C191" s="53" t="s">
         <v>461</v>
       </c>
@@ -34315,8 +34339,8 @@
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A192" s="217"/>
-      <c r="B192" s="195"/>
+      <c r="A192" s="201"/>
+      <c r="B192" s="198"/>
       <c r="C192" s="53" t="s">
         <v>462</v>
       </c>
@@ -34325,8 +34349,8 @@
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A193" s="217"/>
-      <c r="B193" s="195"/>
+      <c r="A193" s="201"/>
+      <c r="B193" s="198"/>
       <c r="C193" s="53" t="s">
         <v>464</v>
       </c>
@@ -34335,8 +34359,8 @@
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A194" s="217"/>
-      <c r="B194" s="195"/>
+      <c r="A194" s="201"/>
+      <c r="B194" s="198"/>
       <c r="C194" s="53" t="s">
         <v>465</v>
       </c>
@@ -34345,8 +34369,8 @@
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A195" s="217"/>
-      <c r="B195" s="195"/>
+      <c r="A195" s="201"/>
+      <c r="B195" s="198"/>
       <c r="C195" s="53" t="s">
         <v>467</v>
       </c>
@@ -34355,8 +34379,8 @@
       </c>
     </row>
     <row r="196" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A196" s="217"/>
-      <c r="B196" s="195"/>
+      <c r="A196" s="201"/>
+      <c r="B196" s="198"/>
       <c r="C196" s="85" t="s">
         <v>469</v>
       </c>
@@ -34365,8 +34389,8 @@
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A197" s="217"/>
-      <c r="B197" s="195"/>
+      <c r="A197" s="201"/>
+      <c r="B197" s="198"/>
       <c r="C197" s="53" t="s">
         <v>471</v>
       </c>
@@ -34375,8 +34399,8 @@
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A198" s="217"/>
-      <c r="B198" s="195"/>
+      <c r="A198" s="201"/>
+      <c r="B198" s="198"/>
       <c r="C198" s="53" t="s">
         <v>472</v>
       </c>
@@ -34385,8 +34409,8 @@
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A199" s="217"/>
-      <c r="B199" s="195"/>
+      <c r="A199" s="201"/>
+      <c r="B199" s="198"/>
       <c r="C199" s="53" t="s">
         <v>473</v>
       </c>
@@ -34395,8 +34419,8 @@
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A200" s="217"/>
-      <c r="B200" s="195"/>
+      <c r="A200" s="201"/>
+      <c r="B200" s="198"/>
       <c r="C200" s="53" t="s">
         <v>474</v>
       </c>
@@ -34405,8 +34429,8 @@
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A201" s="217"/>
-      <c r="B201" s="195"/>
+      <c r="A201" s="201"/>
+      <c r="B201" s="198"/>
       <c r="C201" s="53" t="s">
         <v>475</v>
       </c>
@@ -34415,8 +34439,8 @@
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A202" s="217"/>
-      <c r="B202" s="195"/>
+      <c r="A202" s="201"/>
+      <c r="B202" s="198"/>
       <c r="C202" s="53" t="s">
         <v>473</v>
       </c>
@@ -34425,8 +34449,8 @@
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A203" s="217"/>
-      <c r="B203" s="195"/>
+      <c r="A203" s="201"/>
+      <c r="B203" s="198"/>
       <c r="C203" s="92" t="s">
         <v>476</v>
       </c>
@@ -34435,8 +34459,8 @@
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A204" s="217"/>
-      <c r="B204" s="195"/>
+      <c r="A204" s="201"/>
+      <c r="B204" s="198"/>
       <c r="C204" s="53" t="s">
         <v>478</v>
       </c>
@@ -34445,8 +34469,8 @@
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A205" s="217"/>
-      <c r="B205" s="195"/>
+      <c r="A205" s="201"/>
+      <c r="B205" s="198"/>
       <c r="C205" s="53" t="s">
         <v>480</v>
       </c>
@@ -34455,8 +34479,8 @@
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A206" s="217"/>
-      <c r="B206" s="195"/>
+      <c r="A206" s="201"/>
+      <c r="B206" s="198"/>
       <c r="C206" s="53" t="s">
         <v>482</v>
       </c>
@@ -34465,8 +34489,8 @@
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A207" s="217"/>
-      <c r="B207" s="195"/>
+      <c r="A207" s="201"/>
+      <c r="B207" s="198"/>
       <c r="C207" s="53" t="s">
         <v>484</v>
       </c>
@@ -34475,8 +34499,8 @@
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A208" s="217"/>
-      <c r="B208" s="195"/>
+      <c r="A208" s="201"/>
+      <c r="B208" s="198"/>
       <c r="C208" s="53" t="s">
         <v>485</v>
       </c>
@@ -34485,8 +34509,8 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A209" s="217"/>
-      <c r="B209" s="195"/>
+      <c r="A209" s="201"/>
+      <c r="B209" s="198"/>
       <c r="C209" s="53" t="s">
         <v>486</v>
       </c>
@@ -34495,8 +34519,8 @@
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A210" s="217"/>
-      <c r="B210" s="195"/>
+      <c r="A210" s="201"/>
+      <c r="B210" s="198"/>
       <c r="C210" s="53" t="s">
         <v>487</v>
       </c>
@@ -34505,8 +34529,8 @@
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A211" s="217"/>
-      <c r="B211" s="195"/>
+      <c r="A211" s="201"/>
+      <c r="B211" s="198"/>
       <c r="C211" s="53" t="s">
         <v>488</v>
       </c>
@@ -34515,8 +34539,8 @@
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A212" s="217"/>
-      <c r="B212" s="195"/>
+      <c r="A212" s="201"/>
+      <c r="B212" s="198"/>
       <c r="C212" s="53" t="s">
         <v>489</v>
       </c>
@@ -34525,8 +34549,8 @@
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A213" s="217"/>
-      <c r="B213" s="195"/>
+      <c r="A213" s="201"/>
+      <c r="B213" s="198"/>
       <c r="C213" s="53" t="s">
         <v>490</v>
       </c>
@@ -34535,8 +34559,8 @@
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A214" s="217"/>
-      <c r="B214" s="195"/>
+      <c r="A214" s="201"/>
+      <c r="B214" s="198"/>
       <c r="C214" s="53" t="s">
         <v>491</v>
       </c>
@@ -34545,8 +34569,8 @@
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A215" s="217"/>
-      <c r="B215" s="195"/>
+      <c r="A215" s="201"/>
+      <c r="B215" s="198"/>
       <c r="C215" s="53" t="s">
         <v>492</v>
       </c>
@@ -34555,8 +34579,8 @@
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A216" s="217"/>
-      <c r="B216" s="195"/>
+      <c r="A216" s="201"/>
+      <c r="B216" s="198"/>
       <c r="C216" s="53" t="s">
         <v>494</v>
       </c>
@@ -34565,8 +34589,8 @@
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A217" s="217"/>
-      <c r="B217" s="195"/>
+      <c r="A217" s="201"/>
+      <c r="B217" s="198"/>
       <c r="C217" s="53" t="s">
         <v>490</v>
       </c>
@@ -34575,8 +34599,8 @@
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A218" s="217"/>
-      <c r="B218" s="195"/>
+      <c r="A218" s="201"/>
+      <c r="B218" s="198"/>
       <c r="C218" s="53" t="s">
         <v>495</v>
       </c>
@@ -34585,8 +34609,8 @@
       </c>
     </row>
     <row r="219" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A219" s="217"/>
-      <c r="B219" s="195"/>
+      <c r="A219" s="201"/>
+      <c r="B219" s="198"/>
       <c r="C219" s="56" t="s">
         <v>496</v>
       </c>
@@ -34595,8 +34619,8 @@
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A220" s="218"/>
-      <c r="B220" s="196"/>
+      <c r="A220" s="202"/>
+      <c r="B220" s="199"/>
       <c r="C220" s="56" t="s">
         <v>465</v>
       </c>
@@ -34605,10 +34629,10 @@
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A221" s="216" t="s">
+      <c r="A221" s="200" t="s">
         <v>497</v>
       </c>
-      <c r="B221" s="194" t="s">
+      <c r="B221" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C221" s="53" t="s">
@@ -34619,8 +34643,8 @@
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A222" s="217"/>
-      <c r="B222" s="195"/>
+      <c r="A222" s="201"/>
+      <c r="B222" s="198"/>
       <c r="C222" s="92" t="s">
         <v>499</v>
       </c>
@@ -34629,8 +34653,8 @@
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A223" s="218"/>
-      <c r="B223" s="196"/>
+      <c r="A223" s="202"/>
+      <c r="B223" s="199"/>
       <c r="C223" s="53" t="s">
         <v>500</v>
       </c>
@@ -34675,10 +34699,10 @@
       <c r="D226" s="88"/>
     </row>
     <row r="227" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A227" s="161" t="s">
+      <c r="A227" s="174" t="s">
         <v>156</v>
       </c>
-      <c r="B227" s="194" t="s">
+      <c r="B227" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C227" s="53"/>
@@ -34687,8 +34711,8 @@
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A228" s="200"/>
-      <c r="B228" s="195"/>
+      <c r="A228" s="215"/>
+      <c r="B228" s="198"/>
       <c r="C228" s="65" t="s">
         <v>503</v>
       </c>
@@ -34697,8 +34721,8 @@
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A229" s="200"/>
-      <c r="B229" s="195"/>
+      <c r="A229" s="215"/>
+      <c r="B229" s="198"/>
       <c r="C229" s="65">
         <v>10.1</v>
       </c>
@@ -34707,8 +34731,8 @@
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A230" s="200"/>
-      <c r="B230" s="195"/>
+      <c r="A230" s="215"/>
+      <c r="B230" s="198"/>
       <c r="C230" s="65">
         <v>10.199999999999999</v>
       </c>
@@ -34717,8 +34741,8 @@
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A231" s="200"/>
-      <c r="B231" s="195"/>
+      <c r="A231" s="215"/>
+      <c r="B231" s="198"/>
       <c r="C231" s="82" t="s">
         <v>506</v>
       </c>
@@ -34727,8 +34751,8 @@
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A232" s="200"/>
-      <c r="B232" s="195"/>
+      <c r="A232" s="215"/>
+      <c r="B232" s="198"/>
       <c r="C232" s="82" t="s">
         <v>508</v>
       </c>
@@ -34737,8 +34761,8 @@
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A233" s="200"/>
-      <c r="B233" s="195"/>
+      <c r="A233" s="215"/>
+      <c r="B233" s="198"/>
       <c r="C233" s="82" t="s">
         <v>166</v>
       </c>
@@ -34747,8 +34771,8 @@
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A234" s="200"/>
-      <c r="B234" s="195"/>
+      <c r="A234" s="215"/>
+      <c r="B234" s="198"/>
       <c r="C234" s="82" t="s">
         <v>511</v>
       </c>
@@ -34757,8 +34781,8 @@
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A235" s="200"/>
-      <c r="B235" s="195"/>
+      <c r="A235" s="215"/>
+      <c r="B235" s="198"/>
       <c r="C235" s="82" t="s">
         <v>60</v>
       </c>
@@ -34767,8 +34791,8 @@
       </c>
     </row>
     <row r="236" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A236" s="200"/>
-      <c r="B236" s="195"/>
+      <c r="A236" s="215"/>
+      <c r="B236" s="198"/>
       <c r="C236" s="82" t="s">
         <v>514</v>
       </c>
@@ -34777,8 +34801,8 @@
       </c>
     </row>
     <row r="237" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A237" s="162"/>
-      <c r="B237" s="196"/>
+      <c r="A237" s="175"/>
+      <c r="B237" s="199"/>
       <c r="C237" s="82" t="s">
         <v>514</v>
       </c>
@@ -34787,10 +34811,10 @@
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A238" s="161" t="s">
+      <c r="A238" s="174" t="s">
         <v>517</v>
       </c>
-      <c r="B238" s="194" t="s">
+      <c r="B238" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C238" s="82"/>
@@ -34799,8 +34823,8 @@
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A239" s="200"/>
-      <c r="B239" s="195"/>
+      <c r="A239" s="215"/>
+      <c r="B239" s="198"/>
       <c r="C239" s="62" t="s">
         <v>518</v>
       </c>
@@ -34831,10 +34855,10 @@
       <c r="D241" s="98"/>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A242" s="161" t="s">
+      <c r="A242" s="174" t="s">
         <v>74</v>
       </c>
-      <c r="B242" s="194" t="s">
+      <c r="B242" s="197" t="s">
         <v>522</v>
       </c>
       <c r="C242" s="99" t="s">
@@ -34845,8 +34869,8 @@
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A243" s="200"/>
-      <c r="B243" s="195"/>
+      <c r="A243" s="215"/>
+      <c r="B243" s="198"/>
       <c r="C243" s="99" t="s">
         <v>257</v>
       </c>
@@ -34855,18 +34879,18 @@
       </c>
     </row>
     <row r="244" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="162"/>
-      <c r="B244" s="196"/>
+      <c r="A244" s="175"/>
+      <c r="B244" s="199"/>
       <c r="C244" s="53"/>
       <c r="D244" s="53" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A245" s="207" t="s">
+      <c r="A245" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="B245" s="194" t="s">
+      <c r="B245" s="197" t="s">
         <v>522</v>
       </c>
       <c r="C245" s="56" t="s">
@@ -34877,18 +34901,18 @@
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A246" s="208"/>
-      <c r="B246" s="196"/>
+      <c r="A246" s="214"/>
+      <c r="B246" s="199"/>
       <c r="C246" s="56"/>
       <c r="D246" s="53" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A247" s="207" t="s">
+      <c r="A247" s="213" t="s">
         <v>527</v>
       </c>
-      <c r="B247" s="194" t="s">
+      <c r="B247" s="197" t="s">
         <v>522</v>
       </c>
       <c r="C247" s="56"/>
@@ -34897,18 +34921,18 @@
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A248" s="208"/>
-      <c r="B248" s="196"/>
+      <c r="A248" s="214"/>
+      <c r="B248" s="199"/>
       <c r="C248" s="53"/>
       <c r="D248" s="53" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A249" s="207" t="s">
+      <c r="A249" s="213" t="s">
         <v>76</v>
       </c>
-      <c r="B249" s="194" t="s">
+      <c r="B249" s="197" t="s">
         <v>522</v>
       </c>
       <c r="C249" s="56" t="s">
@@ -34919,8 +34943,8 @@
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A250" s="208"/>
-      <c r="B250" s="196"/>
+      <c r="A250" s="214"/>
+      <c r="B250" s="199"/>
       <c r="C250" s="53"/>
       <c r="D250" s="53" t="s">
         <v>525</v>
@@ -35232,7 +35256,7 @@
         <v>721</v>
       </c>
       <c r="B276" s="138" t="str">
-        <f t="shared" ref="B276:B278" si="0">$B$270</f>
+        <f t="shared" ref="B276:B279" si="0">$B$270</f>
         <v>PIT Next Version</v>
       </c>
       <c r="C276" s="90" t="s">
@@ -35258,22 +35282,129 @@
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A278" s="219" t="s">
+      <c r="A278" s="144" t="s">
         <v>723</v>
       </c>
-      <c r="B278" s="140" t="str">
+      <c r="B278" s="142" t="str">
         <f t="shared" si="0"/>
         <v>PIT Next Version</v>
       </c>
       <c r="C278" t="s">
         <v>724</v>
       </c>
-      <c r="D278" s="219" t="s">
+      <c r="D278" s="144" t="s">
         <v>725</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A279" s="56" t="s">
+        <v>721</v>
+      </c>
+      <c r="B279" s="141" t="str">
+        <f t="shared" si="0"/>
+        <v>PIT Next Version</v>
+      </c>
+      <c r="C279" s="222" t="s">
+        <v>727</v>
+      </c>
+      <c r="D279" s="62" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A280" s="62" t="s">
+        <v>538</v>
+      </c>
+      <c r="B280" s="143" t="s">
+        <v>244</v>
+      </c>
+      <c r="C280" s="53" t="s">
+        <v>729</v>
+      </c>
+      <c r="D280" s="53" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A281" s="62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B281" s="143" t="s">
+        <v>244</v>
+      </c>
+      <c r="C281" s="222" t="s">
+        <v>727</v>
+      </c>
+      <c r="D281" s="53" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A282" s="90" t="s">
+        <v>535</v>
+      </c>
+      <c r="B282" s="141" t="s">
+        <v>244</v>
+      </c>
+      <c r="C282" s="222" t="s">
+        <v>727</v>
+      </c>
+      <c r="D282" s="62" t="s">
+        <v>728</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="D163:D166"/>
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="A95:A110"/>
+    <mergeCell ref="B95:B110"/>
+    <mergeCell ref="A111:A129"/>
+    <mergeCell ref="B111:B129"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="A144:A146"/>
+    <mergeCell ref="B144:B146"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="A147:A151"/>
+    <mergeCell ref="B147:B151"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="A161:A167"/>
+    <mergeCell ref="A227:A237"/>
+    <mergeCell ref="B227:B237"/>
+    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="B130:B143"/>
+    <mergeCell ref="A154:A160"/>
+    <mergeCell ref="B154:B160"/>
+    <mergeCell ref="A130:A143"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="B242:B244"/>
+    <mergeCell ref="A238:A239"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="B161:B167"/>
+    <mergeCell ref="A249:A250"/>
+    <mergeCell ref="B249:B250"/>
+    <mergeCell ref="A245:A246"/>
+    <mergeCell ref="B245:B246"/>
+    <mergeCell ref="A247:A248"/>
+    <mergeCell ref="B247:B248"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="B67:B71"/>
+    <mergeCell ref="A73:A88"/>
+    <mergeCell ref="B73:B88"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="B55:B60"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A55:A60"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="B221:B223"/>
@@ -35290,56 +35421,6 @@
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="B67:B71"/>
-    <mergeCell ref="A73:A88"/>
-    <mergeCell ref="B73:B88"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="B55:B60"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A55:A60"/>
-    <mergeCell ref="A249:A250"/>
-    <mergeCell ref="B249:B250"/>
-    <mergeCell ref="A245:A246"/>
-    <mergeCell ref="B245:B246"/>
-    <mergeCell ref="A247:A248"/>
-    <mergeCell ref="B247:B248"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="B242:B244"/>
-    <mergeCell ref="A238:A239"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="B161:B167"/>
-    <mergeCell ref="A147:A151"/>
-    <mergeCell ref="B147:B151"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="A161:A167"/>
-    <mergeCell ref="A227:A237"/>
-    <mergeCell ref="B227:B237"/>
-    <mergeCell ref="A67:A71"/>
-    <mergeCell ref="B130:B143"/>
-    <mergeCell ref="A154:A160"/>
-    <mergeCell ref="B154:B160"/>
-    <mergeCell ref="A130:A143"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="D163:D166"/>
-    <mergeCell ref="A29:A33"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="A95:A110"/>
-    <mergeCell ref="B95:B110"/>
-    <mergeCell ref="A111:A129"/>
-    <mergeCell ref="B111:B129"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="A144:A146"/>
-    <mergeCell ref="B144:B146"/>
-    <mergeCell ref="A61:A63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -35372,10 +35453,10 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="194" t="s">
+      <c r="A2" s="197" t="s">
         <v>369</v>
       </c>
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C2" s="53" t="s">
@@ -35386,8 +35467,8 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="195"/>
-      <c r="B3" s="195"/>
+      <c r="A3" s="198"/>
+      <c r="B3" s="198"/>
       <c r="C3" s="53" t="s">
         <v>547</v>
       </c>
@@ -35396,8 +35477,8 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="195"/>
-      <c r="B4" s="195"/>
+      <c r="A4" s="198"/>
+      <c r="B4" s="198"/>
       <c r="C4" s="53" t="s">
         <v>549</v>
       </c>
@@ -35406,8 +35487,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="195"/>
-      <c r="B5" s="195"/>
+      <c r="A5" s="198"/>
+      <c r="B5" s="198"/>
       <c r="C5" s="53" t="s">
         <v>551</v>
       </c>
@@ -35416,8 +35497,8 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="195"/>
-      <c r="B6" s="195"/>
+      <c r="A6" s="198"/>
+      <c r="B6" s="198"/>
       <c r="C6" s="53" t="s">
         <v>552</v>
       </c>
@@ -35426,8 +35507,8 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="195"/>
-      <c r="B7" s="195"/>
+      <c r="A7" s="198"/>
+      <c r="B7" s="198"/>
       <c r="C7" s="53" t="s">
         <v>553</v>
       </c>
@@ -35436,8 +35517,8 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="195"/>
-      <c r="B8" s="195"/>
+      <c r="A8" s="198"/>
+      <c r="B8" s="198"/>
       <c r="C8" s="53" t="s">
         <v>554</v>
       </c>
@@ -35446,8 +35527,8 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="195"/>
-      <c r="B9" s="195"/>
+      <c r="A9" s="198"/>
+      <c r="B9" s="198"/>
       <c r="C9" s="53" t="s">
         <v>555</v>
       </c>
@@ -35456,8 +35537,8 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="195"/>
-      <c r="B10" s="195"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="198"/>
       <c r="C10" s="53" t="s">
         <v>556</v>
       </c>
@@ -35466,8 +35547,8 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="195"/>
-      <c r="B11" s="195"/>
+      <c r="A11" s="198"/>
+      <c r="B11" s="198"/>
       <c r="C11" s="53" t="s">
         <v>557</v>
       </c>
@@ -35476,8 +35557,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="195"/>
-      <c r="B12" s="195"/>
+      <c r="A12" s="198"/>
+      <c r="B12" s="198"/>
       <c r="C12" s="53" t="s">
         <v>558</v>
       </c>
@@ -35486,8 +35567,8 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="195"/>
-      <c r="B13" s="195"/>
+      <c r="A13" s="198"/>
+      <c r="B13" s="198"/>
       <c r="C13" s="53" t="s">
         <v>559</v>
       </c>
@@ -35496,8 +35577,8 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="195"/>
-      <c r="B14" s="195"/>
+      <c r="A14" s="198"/>
+      <c r="B14" s="198"/>
       <c r="C14" s="53" t="s">
         <v>560</v>
       </c>
@@ -35506,8 +35587,8 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="195"/>
-      <c r="B15" s="195"/>
+      <c r="A15" s="198"/>
+      <c r="B15" s="198"/>
       <c r="C15" s="53" t="s">
         <v>561</v>
       </c>
@@ -35516,8 +35597,8 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="195"/>
-      <c r="B16" s="195"/>
+      <c r="A16" s="198"/>
+      <c r="B16" s="198"/>
       <c r="C16" s="53" t="s">
         <v>562</v>
       </c>
@@ -35526,8 +35607,8 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="195"/>
-      <c r="B17" s="195"/>
+      <c r="A17" s="198"/>
+      <c r="B17" s="198"/>
       <c r="C17" s="53" t="s">
         <v>564</v>
       </c>
@@ -35536,8 +35617,8 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="195"/>
-      <c r="B18" s="195"/>
+      <c r="A18" s="198"/>
+      <c r="B18" s="198"/>
       <c r="C18" s="56" t="s">
         <v>565</v>
       </c>
@@ -35546,8 +35627,8 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="195"/>
-      <c r="B19" s="195"/>
+      <c r="A19" s="198"/>
+      <c r="B19" s="198"/>
       <c r="C19" s="53" t="s">
         <v>566</v>
       </c>
@@ -35556,8 +35637,8 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="196"/>
-      <c r="B20" s="196"/>
+      <c r="A20" s="199"/>
+      <c r="B20" s="199"/>
       <c r="C20" s="56" t="s">
         <v>567</v>
       </c>
@@ -35566,10 +35647,10 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="165" t="s">
+      <c r="A21" s="164" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="190" t="s">
+      <c r="B21" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C21" s="53" t="s">
@@ -35580,8 +35661,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="165"/>
-      <c r="B22" s="190"/>
+      <c r="A22" s="164"/>
+      <c r="B22" s="183"/>
       <c r="C22" s="53" t="s">
         <v>547</v>
       </c>
@@ -35590,8 +35671,8 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="165"/>
-      <c r="B23" s="190"/>
+      <c r="A23" s="164"/>
+      <c r="B23" s="183"/>
       <c r="C23" s="53" t="s">
         <v>549</v>
       </c>
@@ -35600,8 +35681,8 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="165"/>
-      <c r="B24" s="190"/>
+      <c r="A24" s="164"/>
+      <c r="B24" s="183"/>
       <c r="C24" s="53" t="s">
         <v>551</v>
       </c>
@@ -35610,8 +35691,8 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="165"/>
-      <c r="B25" s="190"/>
+      <c r="A25" s="164"/>
+      <c r="B25" s="183"/>
       <c r="C25" s="53" t="s">
         <v>552</v>
       </c>
@@ -35620,8 +35701,8 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="165"/>
-      <c r="B26" s="190"/>
+      <c r="A26" s="164"/>
+      <c r="B26" s="183"/>
       <c r="C26" s="53" t="s">
         <v>553</v>
       </c>
@@ -35630,8 +35711,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="165"/>
-      <c r="B27" s="190"/>
+      <c r="A27" s="164"/>
+      <c r="B27" s="183"/>
       <c r="C27" s="53" t="s">
         <v>554</v>
       </c>
@@ -35640,8 +35721,8 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="165"/>
-      <c r="B28" s="190"/>
+      <c r="A28" s="164"/>
+      <c r="B28" s="183"/>
       <c r="C28" s="53" t="s">
         <v>555</v>
       </c>
@@ -35650,8 +35731,8 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="165"/>
-      <c r="B29" s="190"/>
+      <c r="A29" s="164"/>
+      <c r="B29" s="183"/>
       <c r="C29" s="53" t="s">
         <v>556</v>
       </c>
@@ -35660,8 +35741,8 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="165"/>
-      <c r="B30" s="190"/>
+      <c r="A30" s="164"/>
+      <c r="B30" s="183"/>
       <c r="C30" s="53" t="s">
         <v>557</v>
       </c>
@@ -35670,8 +35751,8 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="165"/>
-      <c r="B31" s="190"/>
+      <c r="A31" s="164"/>
+      <c r="B31" s="183"/>
       <c r="C31" s="53" t="s">
         <v>558</v>
       </c>
@@ -35680,8 +35761,8 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="165"/>
-      <c r="B32" s="190"/>
+      <c r="A32" s="164"/>
+      <c r="B32" s="183"/>
       <c r="C32" s="53" t="s">
         <v>559</v>
       </c>
@@ -35690,8 +35771,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="165"/>
-      <c r="B33" s="190"/>
+      <c r="A33" s="164"/>
+      <c r="B33" s="183"/>
       <c r="C33" s="53" t="s">
         <v>560</v>
       </c>
@@ -35700,8 +35781,8 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="165"/>
-      <c r="B34" s="190"/>
+      <c r="A34" s="164"/>
+      <c r="B34" s="183"/>
       <c r="C34" s="53" t="s">
         <v>561</v>
       </c>
@@ -35710,8 +35791,8 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="165"/>
-      <c r="B35" s="190"/>
+      <c r="A35" s="164"/>
+      <c r="B35" s="183"/>
       <c r="C35" s="53" t="s">
         <v>562</v>
       </c>
@@ -35720,8 +35801,8 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="165"/>
-      <c r="B36" s="190"/>
+      <c r="A36" s="164"/>
+      <c r="B36" s="183"/>
       <c r="C36" s="53" t="s">
         <v>564</v>
       </c>
@@ -35730,8 +35811,8 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="165"/>
-      <c r="B37" s="190"/>
+      <c r="A37" s="164"/>
+      <c r="B37" s="183"/>
       <c r="C37" s="56" t="s">
         <v>565</v>
       </c>
@@ -35740,8 +35821,8 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="165"/>
-      <c r="B38" s="190"/>
+      <c r="A38" s="164"/>
+      <c r="B38" s="183"/>
       <c r="C38" s="53" t="s">
         <v>566</v>
       </c>
@@ -35750,8 +35831,8 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="165"/>
-      <c r="B39" s="190"/>
+      <c r="A39" s="164"/>
+      <c r="B39" s="183"/>
       <c r="C39" s="56" t="s">
         <v>567</v>
       </c>
@@ -35760,10 +35841,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="194" t="s">
+      <c r="A40" s="197" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="194" t="s">
+      <c r="B40" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C40" s="90" t="s">
@@ -35774,8 +35855,8 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="195"/>
-      <c r="B41" s="195"/>
+      <c r="A41" s="198"/>
+      <c r="B41" s="198"/>
       <c r="C41" s="53" t="s">
         <v>570</v>
       </c>
@@ -35784,8 +35865,8 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="195"/>
-      <c r="B42" s="195"/>
+      <c r="A42" s="198"/>
+      <c r="B42" s="198"/>
       <c r="C42" s="53" t="s">
         <v>572</v>
       </c>
@@ -35806,10 +35887,10 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="194" t="s">
+      <c r="A44" s="197" t="s">
         <v>330</v>
       </c>
-      <c r="B44" s="194" t="s">
+      <c r="B44" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C44" s="90" t="s">
@@ -35820,8 +35901,8 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="195"/>
-      <c r="B45" s="195"/>
+      <c r="A45" s="198"/>
+      <c r="B45" s="198"/>
       <c r="C45" s="90" t="s">
         <v>575</v>
       </c>
@@ -35830,8 +35911,8 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="196"/>
-      <c r="B46" s="196"/>
+      <c r="A46" s="199"/>
+      <c r="B46" s="199"/>
       <c r="C46" s="90" t="s">
         <v>576</v>
       </c>
@@ -36076,10 +36157,10 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="190" t="s">
+      <c r="A66" s="183" t="s">
         <v>579</v>
       </c>
-      <c r="B66" s="190" t="s">
+      <c r="B66" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C66" s="53" t="s">
@@ -36090,8 +36171,8 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="190"/>
-      <c r="B67" s="190"/>
+      <c r="A67" s="183"/>
+      <c r="B67" s="183"/>
       <c r="C67" s="53" t="s">
         <v>601</v>
       </c>
@@ -36100,8 +36181,8 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="190"/>
-      <c r="B68" s="190"/>
+      <c r="A68" s="183"/>
+      <c r="B68" s="183"/>
       <c r="C68" s="53" t="s">
         <v>602</v>
       </c>
@@ -36110,8 +36191,8 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="190"/>
-      <c r="B69" s="190"/>
+      <c r="A69" s="183"/>
+      <c r="B69" s="183"/>
       <c r="C69" s="53" t="s">
         <v>603</v>
       </c>
@@ -36120,8 +36201,8 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="190"/>
-      <c r="B70" s="190"/>
+      <c r="A70" s="183"/>
+      <c r="B70" s="183"/>
       <c r="C70" s="53" t="s">
         <v>604</v>
       </c>
@@ -36154,10 +36235,10 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="190" t="s">
+      <c r="A73" s="183" t="s">
         <v>369</v>
       </c>
-      <c r="B73" s="190" t="s">
+      <c r="B73" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C73" s="53"/>
@@ -36166,8 +36247,8 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="190"/>
-      <c r="B74" s="190"/>
+      <c r="A74" s="183"/>
+      <c r="B74" s="183"/>
       <c r="C74" s="53" t="s">
         <v>599</v>
       </c>
@@ -36176,8 +36257,8 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="190"/>
-      <c r="B75" s="190"/>
+      <c r="A75" s="183"/>
+      <c r="B75" s="183"/>
       <c r="C75" s="53" t="s">
         <v>601</v>
       </c>
@@ -36186,8 +36267,8 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="190"/>
-      <c r="B76" s="190"/>
+      <c r="A76" s="183"/>
+      <c r="B76" s="183"/>
       <c r="C76" s="53" t="s">
         <v>602</v>
       </c>
@@ -36196,8 +36277,8 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="190"/>
-      <c r="B77" s="190"/>
+      <c r="A77" s="183"/>
+      <c r="B77" s="183"/>
       <c r="C77" s="53" t="s">
         <v>603</v>
       </c>
@@ -36206,8 +36287,8 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="190"/>
-      <c r="B78" s="190"/>
+      <c r="A78" s="183"/>
+      <c r="B78" s="183"/>
       <c r="C78" s="53" t="s">
         <v>604</v>
       </c>
@@ -36216,8 +36297,8 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="190"/>
-      <c r="B79" s="190"/>
+      <c r="A79" s="183"/>
+      <c r="B79" s="183"/>
       <c r="C79" s="53" t="s">
         <v>607</v>
       </c>
@@ -36226,10 +36307,10 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="190" t="s">
+      <c r="A80" s="183" t="s">
         <v>36</v>
       </c>
-      <c r="B80" s="190" t="s">
+      <c r="B80" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C80" s="53"/>
@@ -36238,8 +36319,8 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="190"/>
-      <c r="B81" s="190"/>
+      <c r="A81" s="183"/>
+      <c r="B81" s="183"/>
       <c r="C81" s="53" t="s">
         <v>599</v>
       </c>
@@ -36248,8 +36329,8 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" s="190"/>
-      <c r="B82" s="190"/>
+      <c r="A82" s="183"/>
+      <c r="B82" s="183"/>
       <c r="C82" s="53" t="s">
         <v>601</v>
       </c>
@@ -36258,8 +36339,8 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="190"/>
-      <c r="B83" s="190"/>
+      <c r="A83" s="183"/>
+      <c r="B83" s="183"/>
       <c r="C83" s="53" t="s">
         <v>602</v>
       </c>
@@ -36268,8 +36349,8 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="190"/>
-      <c r="B84" s="190"/>
+      <c r="A84" s="183"/>
+      <c r="B84" s="183"/>
       <c r="C84" s="53" t="s">
         <v>603</v>
       </c>
@@ -36278,8 +36359,8 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="190"/>
-      <c r="B85" s="190"/>
+      <c r="A85" s="183"/>
+      <c r="B85" s="183"/>
       <c r="C85" s="53" t="s">
         <v>604</v>
       </c>
@@ -36288,8 +36369,8 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="190"/>
-      <c r="B86" s="190"/>
+      <c r="A86" s="183"/>
+      <c r="B86" s="183"/>
       <c r="C86" s="53" t="s">
         <v>607</v>
       </c>
@@ -36396,10 +36477,10 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" s="194" t="s">
+      <c r="A95" s="197" t="s">
         <v>610</v>
       </c>
-      <c r="B95" s="194" t="s">
+      <c r="B95" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C95" s="53" t="s">
@@ -36410,8 +36491,8 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" s="195"/>
-      <c r="B96" s="195"/>
+      <c r="A96" s="198"/>
+      <c r="B96" s="198"/>
       <c r="C96" s="53" t="s">
         <v>623</v>
       </c>
@@ -36420,8 +36501,8 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" s="195"/>
-      <c r="B97" s="195"/>
+      <c r="A97" s="198"/>
+      <c r="B97" s="198"/>
       <c r="C97" s="53" t="s">
         <v>625</v>
       </c>
@@ -36430,8 +36511,8 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" s="196"/>
-      <c r="B98" s="196"/>
+      <c r="A98" s="199"/>
+      <c r="B98" s="199"/>
       <c r="C98" s="53" t="s">
         <v>627</v>
       </c>
@@ -36482,10 +36563,10 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" s="194" t="s">
+      <c r="A102" s="197" t="s">
         <v>369</v>
       </c>
-      <c r="B102" s="194" t="s">
+      <c r="B102" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C102" s="53" t="s">
@@ -36496,8 +36577,8 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" s="195"/>
-      <c r="B103" s="195"/>
+      <c r="A103" s="198"/>
+      <c r="B103" s="198"/>
       <c r="C103" s="116" t="s">
         <v>557</v>
       </c>
@@ -36506,8 +36587,8 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" s="195"/>
-      <c r="B104" s="195"/>
+      <c r="A104" s="198"/>
+      <c r="B104" s="198"/>
       <c r="C104" s="53" t="s">
         <v>565</v>
       </c>
@@ -36516,8 +36597,8 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" s="196"/>
-      <c r="B105" s="196"/>
+      <c r="A105" s="199"/>
+      <c r="B105" s="199"/>
       <c r="C105" s="53" t="s">
         <v>564</v>
       </c>
@@ -36526,10 +36607,10 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" s="194" t="s">
+      <c r="A106" s="197" t="s">
         <v>36</v>
       </c>
-      <c r="B106" s="194" t="s">
+      <c r="B106" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C106" s="53" t="s">
@@ -36540,8 +36621,8 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" s="195"/>
-      <c r="B107" s="195"/>
+      <c r="A107" s="198"/>
+      <c r="B107" s="198"/>
       <c r="C107" s="116" t="s">
         <v>557</v>
       </c>
@@ -36550,8 +36631,8 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" s="195"/>
-      <c r="B108" s="195"/>
+      <c r="A108" s="198"/>
+      <c r="B108" s="198"/>
       <c r="C108" s="53" t="s">
         <v>565</v>
       </c>
@@ -36560,8 +36641,8 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" s="196"/>
-      <c r="B109" s="196"/>
+      <c r="A109" s="199"/>
+      <c r="B109" s="199"/>
       <c r="C109" s="53" t="s">
         <v>564</v>
       </c>
@@ -36764,10 +36845,10 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" s="190" t="s">
+      <c r="A125" s="183" t="s">
         <v>583</v>
       </c>
-      <c r="B125" s="190" t="s">
+      <c r="B125" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C125" s="89" t="s">
@@ -36778,8 +36859,8 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" s="190"/>
-      <c r="B126" s="190"/>
+      <c r="A126" s="183"/>
+      <c r="B126" s="183"/>
       <c r="C126" s="53" t="s">
         <v>653</v>
       </c>
@@ -36788,8 +36869,8 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" s="190"/>
-      <c r="B127" s="190"/>
+      <c r="A127" s="183"/>
+      <c r="B127" s="183"/>
       <c r="C127" s="53" t="s">
         <v>655</v>
       </c>
@@ -36798,8 +36879,8 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" s="190"/>
-      <c r="B128" s="190"/>
+      <c r="A128" s="183"/>
+      <c r="B128" s="183"/>
       <c r="C128" s="53" t="s">
         <v>657</v>
       </c>
@@ -36808,8 +36889,8 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" s="190"/>
-      <c r="B129" s="190"/>
+      <c r="A129" s="183"/>
+      <c r="B129" s="183"/>
       <c r="C129" s="53" t="s">
         <v>659</v>
       </c>
@@ -36846,7 +36927,7 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" s="161" t="s">
+      <c r="A132" s="174" t="s">
         <v>663</v>
       </c>
       <c r="B132" s="117" t="s">
@@ -36860,7 +36941,7 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" s="162"/>
+      <c r="A133" s="175"/>
       <c r="B133" s="118" t="s">
         <v>244</v>
       </c>
@@ -36928,10 +37009,10 @@
       </c>
     </row>
     <row r="138" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="190" t="s">
+      <c r="A138" s="183" t="s">
         <v>574</v>
       </c>
-      <c r="B138" s="190" t="s">
+      <c r="B138" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C138" s="53" t="s">
@@ -36942,8 +37023,8 @@
       </c>
     </row>
     <row r="139" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="190"/>
-      <c r="B139" s="190"/>
+      <c r="A139" s="183"/>
+      <c r="B139" s="183"/>
       <c r="C139" s="53" t="s">
         <v>684</v>
       </c>
@@ -36966,10 +37047,10 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" s="161" t="s">
+      <c r="A141" s="174" t="s">
         <v>681</v>
       </c>
-      <c r="B141" s="194" t="s">
+      <c r="B141" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C141" s="53" t="s">
@@ -36980,8 +37061,8 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" s="162"/>
-      <c r="B142" s="196"/>
+      <c r="A142" s="175"/>
+      <c r="B142" s="199"/>
       <c r="C142" s="53" t="s">
         <v>686</v>
       </c>
@@ -37144,7 +37225,7 @@
       </c>
     </row>
     <row r="154" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A154" s="141" t="s">
+      <c r="A154" s="140" t="s">
         <v>718</v>
       </c>
       <c r="B154" s="138" t="s">
@@ -37173,17 +37254,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="A2:A20"/>
-    <mergeCell ref="B2:B20"/>
-    <mergeCell ref="A21:A39"/>
-    <mergeCell ref="B21:B39"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="B40:B42"/>
     <mergeCell ref="A141:A142"/>
     <mergeCell ref="B141:B142"/>
     <mergeCell ref="A66:A70"/>
@@ -37200,6 +37270,17 @@
     <mergeCell ref="A125:A129"/>
     <mergeCell ref="B125:B129"/>
     <mergeCell ref="A102:A105"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="A2:A20"/>
+    <mergeCell ref="B2:B20"/>
+    <mergeCell ref="A21:A39"/>
+    <mergeCell ref="B21:B39"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="B40:B42"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -37208,6 +37289,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <nb82aa7489a64919aab5fd247ffa0d1e xmlns="184185d0-04c6-4ef5-ba23-3d0ec5a17fb8">
@@ -37250,15 +37340,6 @@
     </l29cd52af9b640b690e3347aa75f97a9>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -37482,19 +37563,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E83ECEA-8E14-42A0-80EE-042ED267BA0C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F5A24BE-BB8C-4A62-B10D-ABDF1081592A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="184185d0-04c6-4ef5-ba23-3d0ec5a17fb8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E83ECEA-8E14-42A0-80EE-042ED267BA0C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/PIT4/Schema Publication Changelog.xlsx
+++ b/PIT4/Schema Publication Changelog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ctrowell\Desktop\GitHub Docs\PIT4 Github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ctrowell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E820892C-0EBA-4338-8BD8-4246D7E18553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D0422A-8779-4DA4-801D-853D61E5D42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="0" windowWidth="16260" windowHeight="10210" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="v0.10" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="723">
   <si>
     <t>Document</t>
   </si>
@@ -4066,30 +4066,6 @@
   </si>
   <si>
     <t>PAYE Modernisation - RPN Data Items</t>
-  </si>
-  <si>
-    <t>Payroll Employer Submission - Employee Level Validation</t>
-  </si>
-  <si>
-    <t>PRSI Class and Subclass</t>
-  </si>
-  <si>
-    <t>Warning added on PRSI Class and Subclass</t>
-  </si>
-  <si>
-    <t>Added SPS fields</t>
-  </si>
-  <si>
-    <t>Single Pension Scheme</t>
-  </si>
-  <si>
-    <t>Single Pension scheme fields added</t>
-  </si>
-  <si>
-    <t>payrollSubmission</t>
-  </si>
-  <si>
-    <t>Added SPS fields to example 1.3 REST and SOAP</t>
   </si>
 </sst>
 </file>
@@ -4719,7 +4695,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5092,21 +5068,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -5338,8 +5299,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5679,15 +5640,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.453125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49.453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5701,15 +5662,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="145" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="140" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="147"/>
-    </row>
-    <row r="3" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142"/>
+    </row>
+    <row r="3" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
         <v>5</v>
       </c>
@@ -5723,15 +5684,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="145" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="146"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="147"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B4" s="141"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="142"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>9</v>
       </c>
@@ -5745,7 +5706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>12</v>
       </c>
@@ -5759,11 +5720,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A7" s="148" t="s">
+    <row r="7" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="143" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="151">
+      <c r="B7" s="146">
         <v>0.1</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -5773,9 +5734,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="149"/>
-      <c r="B8" s="152"/>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="144"/>
+      <c r="B8" s="147"/>
       <c r="C8" s="10" t="s">
         <v>16</v>
       </c>
@@ -5783,9 +5744,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A9" s="149"/>
-      <c r="B9" s="152"/>
+    <row r="9" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="144"/>
+      <c r="B9" s="147"/>
       <c r="C9" s="10" t="s">
         <v>18</v>
       </c>
@@ -5793,9 +5754,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="149"/>
-      <c r="B10" s="152"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="144"/>
+      <c r="B10" s="147"/>
       <c r="C10" s="10" t="s">
         <v>20</v>
       </c>
@@ -5803,9 +5764,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="149"/>
-      <c r="B11" s="152"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="144"/>
+      <c r="B11" s="147"/>
       <c r="C11" s="10" t="s">
         <v>22</v>
       </c>
@@ -5813,9 +5774,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="150"/>
-      <c r="B12" s="153"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="145"/>
+      <c r="B12" s="148"/>
       <c r="C12" s="10" t="s">
         <v>24</v>
       </c>
@@ -5823,11 +5784,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="156" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="151" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="151">
+      <c r="B13" s="146">
         <v>0.1</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -5837,9 +5798,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="157"/>
-      <c r="B14" s="153"/>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="152"/>
+      <c r="B14" s="148"/>
       <c r="C14" s="10" t="s">
         <v>29</v>
       </c>
@@ -5847,7 +5808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
         <v>31</v>
       </c>
@@ -5861,7 +5822,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
         <v>33</v>
       </c>
@@ -5875,15 +5836,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="145" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="146"/>
-      <c r="C17" s="146"/>
-      <c r="D17" s="147"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="141"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="142"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>35</v>
       </c>
@@ -5897,7 +5858,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>36</v>
       </c>
@@ -5911,19 +5872,19 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="145" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="146"/>
-      <c r="C20" s="146"/>
-      <c r="D20" s="147"/>
-    </row>
-    <row r="21" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A21" s="158" t="s">
+      <c r="B20" s="141"/>
+      <c r="C20" s="141"/>
+      <c r="D20" s="142"/>
+    </row>
+    <row r="21" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="153" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="155">
+      <c r="B21" s="150">
         <v>0.1</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -5933,9 +5894,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="157"/>
-      <c r="B22" s="153"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="152"/>
+      <c r="B22" s="148"/>
       <c r="C22" s="26" t="s">
         <v>41</v>
       </c>
@@ -5943,7 +5904,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>43</v>
       </c>
@@ -5957,19 +5918,19 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="145" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="146"/>
-      <c r="C24" s="146"/>
-      <c r="D24" s="147"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="154" t="s">
+      <c r="B24" s="141"/>
+      <c r="C24" s="141"/>
+      <c r="D24" s="142"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="149" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="155">
+      <c r="B25" s="150">
         <v>0.1</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -5979,9 +5940,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A26" s="149"/>
-      <c r="B26" s="152"/>
+    <row r="26" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="144"/>
+      <c r="B26" s="147"/>
       <c r="C26" s="10" t="s">
         <v>48</v>
       </c>
@@ -5989,9 +5950,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="149"/>
-      <c r="B27" s="152"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="144"/>
+      <c r="B27" s="147"/>
       <c r="C27" s="10" t="s">
         <v>50</v>
       </c>
@@ -5999,9 +5960,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="149"/>
-      <c r="B28" s="152"/>
+    <row r="28" spans="1:4" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="144"/>
+      <c r="B28" s="147"/>
       <c r="C28" s="20" t="s">
         <v>52</v>
       </c>
@@ -6009,9 +5970,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="149"/>
-      <c r="B29" s="152"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="144"/>
+      <c r="B29" s="147"/>
       <c r="C29" s="10" t="s">
         <v>54</v>
       </c>
@@ -6019,9 +5980,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="149"/>
-      <c r="B30" s="152"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="144"/>
+      <c r="B30" s="147"/>
       <c r="C30" s="10" t="s">
         <v>56</v>
       </c>
@@ -6029,9 +5990,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="149"/>
-      <c r="B31" s="152"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="144"/>
+      <c r="B31" s="147"/>
       <c r="C31" s="10" t="s">
         <v>58</v>
       </c>
@@ -6039,9 +6000,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="150"/>
-      <c r="B32" s="153"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="145"/>
+      <c r="B32" s="148"/>
       <c r="C32" s="10" t="s">
         <v>60</v>
       </c>
@@ -6049,7 +6010,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>62</v>
       </c>
@@ -6063,7 +6024,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>64</v>
       </c>
@@ -6077,7 +6038,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>65</v>
       </c>
@@ -6091,7 +6052,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>66</v>
       </c>
@@ -6105,7 +6066,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>67</v>
       </c>
@@ -6119,7 +6080,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>68</v>
       </c>
@@ -6133,7 +6094,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
         <v>69</v>
       </c>
@@ -6147,7 +6108,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="24" t="s">
         <v>71</v>
       </c>
@@ -6161,15 +6122,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="145" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="140" t="s">
         <v>72</v>
       </c>
-      <c r="B41" s="146"/>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="141"/>
+      <c r="C41" s="141"/>
+      <c r="D41" s="142"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>73</v>
       </c>
@@ -6183,7 +6144,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>74</v>
       </c>
@@ -6197,7 +6158,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>75</v>
       </c>
@@ -6211,7 +6172,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>76</v>
       </c>
@@ -6267,15 +6228,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:XFC79"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.453125" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" customWidth="1"/>
-    <col min="4" max="4" width="51.26953125" style="38" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="51.28515625" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -6289,7 +6250,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>77</v>
       </c>
@@ -6297,7 +6258,7 @@
       <c r="C2" s="35"/>
       <c r="D2" s="40"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="44" t="s">
         <v>78</v>
       </c>
@@ -6309,7 +6270,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="44" t="s">
         <v>79</v>
       </c>
@@ -6321,7 +6282,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
         <v>80</v>
       </c>
@@ -6333,7 +6294,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>8</v>
       </c>
@@ -6341,11 +6302,11 @@
       <c r="C6" s="35"/>
       <c r="D6" s="40"/>
     </row>
-    <row r="7" spans="1:4" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="159" t="s">
+    <row r="7" spans="1:4" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="154" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="160" t="s">
+      <c r="B7" s="155" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="39" t="s">
@@ -6355,9 +6316,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A8" s="159"/>
-      <c r="B8" s="160"/>
+    <row r="8" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="154"/>
+      <c r="B8" s="155"/>
       <c r="C8" s="34" t="s">
         <v>84</v>
       </c>
@@ -6365,9 +6326,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="159"/>
-      <c r="B9" s="160"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="154"/>
+      <c r="B9" s="155"/>
       <c r="C9" s="34" t="s">
         <v>86</v>
       </c>
@@ -6375,9 +6336,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="159"/>
-      <c r="B10" s="160"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="154"/>
+      <c r="B10" s="155"/>
       <c r="C10" s="34" t="s">
         <v>18</v>
       </c>
@@ -6385,9 +6346,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="159"/>
-      <c r="B11" s="160"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="154"/>
+      <c r="B11" s="155"/>
       <c r="C11" s="34" t="s">
         <v>89</v>
       </c>
@@ -6395,9 +6356,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="159"/>
-      <c r="B12" s="160"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="154"/>
+      <c r="B12" s="155"/>
       <c r="C12" s="34" t="s">
         <v>91</v>
       </c>
@@ -6405,11 +6366,11 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="162" t="s">
+    <row r="13" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="157" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="160" t="s">
+      <c r="B13" s="155" t="s">
         <v>81</v>
       </c>
       <c r="C13" s="34" t="s">
@@ -6419,9 +6380,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="162"/>
-      <c r="B14" s="160"/>
+    <row r="14" spans="1:4" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="157"/>
+      <c r="B14" s="155"/>
       <c r="C14" s="34" t="s">
         <v>96</v>
       </c>
@@ -6429,9 +6390,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="162"/>
-      <c r="B15" s="160"/>
+    <row r="15" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="157"/>
+      <c r="B15" s="155"/>
       <c r="C15" s="39" t="s">
         <v>98</v>
       </c>
@@ -6439,11 +6400,11 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="163" t="s">
+    <row r="16" spans="1:4" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="158" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="164" t="s">
+      <c r="B16" s="159" t="s">
         <v>81</v>
       </c>
       <c r="C16" s="54" t="s">
@@ -6453,9 +6414,9 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="163"/>
-      <c r="B17" s="164"/>
+    <row r="17" spans="1:4" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="158"/>
+      <c r="B17" s="159"/>
       <c r="C17" s="53" t="s">
         <v>102</v>
       </c>
@@ -6463,9 +6424,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="163"/>
-      <c r="B18" s="164"/>
+    <row r="18" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="158"/>
+      <c r="B18" s="159"/>
       <c r="C18" s="53" t="s">
         <v>89</v>
       </c>
@@ -6473,9 +6434,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="163"/>
-      <c r="B19" s="164"/>
+    <row r="19" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="158"/>
+      <c r="B19" s="159"/>
       <c r="C19" s="53" t="s">
         <v>105</v>
       </c>
@@ -6483,9 +6444,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="163"/>
-      <c r="B20" s="164"/>
+    <row r="20" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="158"/>
+      <c r="B20" s="159"/>
       <c r="C20" s="53" t="s">
         <v>107</v>
       </c>
@@ -6493,9 +6454,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="163"/>
-      <c r="B21" s="164"/>
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="158"/>
+      <c r="B21" s="159"/>
       <c r="C21" s="53" t="s">
         <v>109</v>
       </c>
@@ -6503,9 +6464,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="163"/>
-      <c r="B22" s="164"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="158"/>
+      <c r="B22" s="159"/>
       <c r="C22" s="53" t="s">
         <v>111</v>
       </c>
@@ -6513,9 +6474,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="163"/>
-      <c r="B23" s="164"/>
+    <row r="23" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="158"/>
+      <c r="B23" s="159"/>
       <c r="C23" s="61" t="s">
         <v>113</v>
       </c>
@@ -6523,27 +6484,27 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="163"/>
-      <c r="B24" s="164"/>
-      <c r="C24" s="163" t="s">
+    <row r="24" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="158"/>
+      <c r="B24" s="159"/>
+      <c r="C24" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="D24" s="170" t="s">
+      <c r="D24" s="165" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="163"/>
-      <c r="B25" s="164"/>
-      <c r="C25" s="163"/>
-      <c r="D25" s="170"/>
-    </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="159" t="s">
+    <row r="25" spans="1:4" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="158"/>
+      <c r="B25" s="159"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="165"/>
+    </row>
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="160" t="s">
+      <c r="B26" s="155" t="s">
         <v>81</v>
       </c>
       <c r="C26" s="34" t="s">
@@ -6553,15 +6514,15 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="159"/>
-      <c r="B27" s="160"/>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="154"/>
+      <c r="B27" s="155"/>
       <c r="C27" s="34"/>
       <c r="D27" s="37" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="44" t="s">
         <v>121</v>
       </c>
@@ -6573,7 +6534,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="35" t="s">
         <v>34</v>
       </c>
@@ -6581,29 +6542,29 @@
       <c r="C29" s="35"/>
       <c r="D29" s="35"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="161" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="156" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="160" t="s">
+      <c r="B30" s="155" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="163" t="s">
+      <c r="C30" s="158" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="173" t="s">
+      <c r="D30" s="168" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="161"/>
-      <c r="B31" s="160"/>
-      <c r="C31" s="163"/>
-      <c r="D31" s="173"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="161"/>
-      <c r="B32" s="160"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="156"/>
+      <c r="B31" s="155"/>
+      <c r="C31" s="158"/>
+      <c r="D31" s="168"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="156"/>
+      <c r="B32" s="155"/>
       <c r="C32" s="53" t="s">
         <v>125</v>
       </c>
@@ -6611,9 +6572,9 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="161"/>
-      <c r="B33" s="160"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="156"/>
+      <c r="B33" s="155"/>
       <c r="C33" s="53" t="s">
         <v>127</v>
       </c>
@@ -6621,9 +6582,9 @@
         <v>128</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="161"/>
-      <c r="B34" s="160"/>
+    <row r="34" spans="1:4" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="156"/>
+      <c r="B34" s="155"/>
       <c r="C34" s="62" t="s">
         <v>129</v>
       </c>
@@ -6631,9 +6592,9 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="161"/>
-      <c r="B35" s="160"/>
+    <row r="35" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="156"/>
+      <c r="B35" s="155"/>
       <c r="C35" s="53" t="s">
         <v>111</v>
       </c>
@@ -6641,9 +6602,9 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="161"/>
-      <c r="B36" s="160"/>
+    <row r="36" spans="1:4" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="156"/>
+      <c r="B36" s="155"/>
       <c r="C36" s="62" t="s">
         <v>113</v>
       </c>
@@ -6651,27 +6612,27 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="161"/>
-      <c r="B37" s="160"/>
-      <c r="C37" s="174" t="s">
+    <row r="37" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="156"/>
+      <c r="B37" s="155"/>
+      <c r="C37" s="169" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="176" t="s">
+      <c r="D37" s="171" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="6.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="161"/>
-      <c r="B38" s="160"/>
-      <c r="C38" s="175"/>
-      <c r="D38" s="176"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="159" t="s">
+    <row r="38" spans="1:4" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="156"/>
+      <c r="B38" s="155"/>
+      <c r="C38" s="170"/>
+      <c r="D38" s="171"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="154" t="s">
         <v>134</v>
       </c>
-      <c r="B39" s="160" t="s">
+      <c r="B39" s="155" t="s">
         <v>81</v>
       </c>
       <c r="C39" s="34" t="s">
@@ -6681,15 +6642,15 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="159"/>
-      <c r="B40" s="160"/>
+    <row r="40" spans="1:4" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="154"/>
+      <c r="B40" s="155"/>
       <c r="C40" s="34"/>
       <c r="D40" s="45" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="44" t="s">
         <v>36</v>
       </c>
@@ -6701,7 +6662,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="35" t="s">
         <v>37</v>
       </c>
@@ -6709,11 +6670,11 @@
       <c r="C42" s="35"/>
       <c r="D42" s="40"/>
     </row>
-    <row r="43" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="161" t="s">
+    <row r="43" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="156" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="160" t="s">
+      <c r="B43" s="155" t="s">
         <v>81</v>
       </c>
       <c r="C43" s="34"/>
@@ -6721,9 +6682,9 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="161"/>
-      <c r="B44" s="160"/>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="156"/>
+      <c r="B44" s="155"/>
       <c r="C44" s="34" t="s">
         <v>118</v>
       </c>
@@ -6731,11 +6692,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="167" t="s">
+    <row r="45" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="162" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="160" t="s">
+      <c r="B45" s="155" t="s">
         <v>81</v>
       </c>
       <c r="C45" s="34"/>
@@ -6743,9 +6704,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="168"/>
-      <c r="B46" s="160"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="163"/>
+      <c r="B46" s="155"/>
       <c r="C46" s="34" t="s">
         <v>141</v>
       </c>
@@ -6753,9 +6714,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="168"/>
-      <c r="B47" s="160"/>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="163"/>
+      <c r="B47" s="155"/>
       <c r="C47" s="34" t="s">
         <v>143</v>
       </c>
@@ -6763,9 +6724,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="169"/>
-      <c r="B48" s="160"/>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="164"/>
+      <c r="B48" s="155"/>
       <c r="C48" s="34" t="s">
         <v>118</v>
       </c>
@@ -6773,11 +6734,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A49" s="164" t="s">
+    <row r="49" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A49" s="159" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="164" t="s">
+      <c r="B49" s="159" t="s">
         <v>81</v>
       </c>
       <c r="C49" s="53"/>
@@ -10880,9 +10841,9 @@
       <c r="XEY49" s="38"/>
       <c r="XFC49" s="38"/>
     </row>
-    <row r="50" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="164"/>
-      <c r="B50" s="164"/>
+    <row r="50" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="159"/>
+      <c r="B50" s="159"/>
       <c r="C50" s="54" t="s">
         <v>146</v>
       </c>
@@ -14985,9 +14946,9 @@
       <c r="XEY50" s="38"/>
       <c r="XFC50" s="38"/>
     </row>
-    <row r="51" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A51" s="164"/>
-      <c r="B51" s="164"/>
+    <row r="51" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A51" s="159"/>
+      <c r="B51" s="159"/>
       <c r="C51" s="34" t="s">
         <v>148</v>
       </c>
@@ -19090,9 +19051,9 @@
       <c r="XEY51" s="38"/>
       <c r="XFC51" s="38"/>
     </row>
-    <row r="52" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A52" s="164"/>
-      <c r="B52" s="164"/>
+    <row r="52" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A52" s="159"/>
+      <c r="B52" s="159"/>
       <c r="C52" s="53" t="s">
         <v>150</v>
       </c>
@@ -23195,13 +23156,13 @@
       <c r="XEY52" s="38"/>
       <c r="XFC52" s="38"/>
     </row>
-    <row r="53" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A53" s="164"/>
-      <c r="B53" s="164"/>
-      <c r="C53" s="172" t="s">
+    <row r="53" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A53" s="159"/>
+      <c r="B53" s="159"/>
+      <c r="C53" s="167" t="s">
         <v>152</v>
       </c>
-      <c r="D53" s="173" t="s">
+      <c r="D53" s="168" t="s">
         <v>153</v>
       </c>
       <c r="G53" s="38"/>
@@ -27300,11 +27261,11 @@
       <c r="XEY53" s="38"/>
       <c r="XFC53" s="38"/>
     </row>
-    <row r="54" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="13.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="164"/>
-      <c r="B54" s="164"/>
-      <c r="C54" s="172"/>
-      <c r="D54" s="173"/>
+    <row r="54" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="159"/>
+      <c r="B54" s="159"/>
+      <c r="C54" s="167"/>
+      <c r="D54" s="168"/>
       <c r="G54" s="38"/>
       <c r="K54" s="38"/>
       <c r="O54" s="38"/>
@@ -31401,7 +31362,7 @@
       <c r="XEY54" s="38"/>
       <c r="XFC54" s="38"/>
     </row>
-    <row r="55" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
       <c r="A55" s="35" t="s">
         <v>44</v>
       </c>
@@ -31409,7 +31370,7 @@
       <c r="C55" s="35"/>
       <c r="D55" s="40"/>
     </row>
-    <row r="56" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="26" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A56" s="44" t="s">
         <v>154</v>
       </c>
@@ -31421,11 +31382,11 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A57" s="165" t="s">
+    <row r="57" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A57" s="160" t="s">
         <v>156</v>
       </c>
-      <c r="B57" s="164" t="s">
+      <c r="B57" s="159" t="s">
         <v>81</v>
       </c>
       <c r="C57" s="53" t="s">
@@ -31435,9 +31396,9 @@
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="29" x14ac:dyDescent="0.35">
-      <c r="A58" s="165"/>
-      <c r="B58" s="164"/>
+    <row r="58" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="160"/>
+      <c r="B58" s="159"/>
       <c r="C58" s="56" t="s">
         <v>159</v>
       </c>
@@ -31445,9 +31406,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="59" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A59" s="165"/>
-      <c r="B59" s="164"/>
+    <row r="59" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A59" s="160"/>
+      <c r="B59" s="159"/>
       <c r="C59" s="53" t="s">
         <v>161</v>
       </c>
@@ -31455,9 +31416,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="60" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="29" x14ac:dyDescent="0.35">
-      <c r="A60" s="165"/>
-      <c r="B60" s="164"/>
+    <row r="60" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="160"/>
+      <c r="B60" s="159"/>
       <c r="C60" s="53" t="s">
         <v>163</v>
       </c>
@@ -31465,9 +31426,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A61" s="165"/>
-      <c r="B61" s="164"/>
+    <row r="61" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A61" s="160"/>
+      <c r="B61" s="159"/>
       <c r="C61" s="34" t="s">
         <v>118</v>
       </c>
@@ -31475,9 +31436,9 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A62" s="165"/>
-      <c r="B62" s="164"/>
+    <row r="62" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A62" s="160"/>
+      <c r="B62" s="159"/>
       <c r="C62" s="53" t="s">
         <v>166</v>
       </c>
@@ -31485,9 +31446,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A63" s="165"/>
-      <c r="B63" s="164"/>
+    <row r="63" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A63" s="160"/>
+      <c r="B63" s="159"/>
       <c r="C63" s="53" t="s">
         <v>166</v>
       </c>
@@ -31495,17 +31456,17 @@
         <v>168</v>
       </c>
     </row>
-    <row r="64" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
-      <c r="A64" s="165"/>
-      <c r="B64" s="164"/>
+    <row r="64" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A64" s="160"/>
+      <c r="B64" s="159"/>
       <c r="C64" s="53"/>
       <c r="D64" s="43" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="165"/>
-      <c r="B65" s="164"/>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="160"/>
+      <c r="B65" s="159"/>
       <c r="C65" s="53" t="s">
         <v>169</v>
       </c>
@@ -31513,17 +31474,17 @@
         <v>170</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="165"/>
-      <c r="B66" s="164"/>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="160"/>
+      <c r="B66" s="159"/>
       <c r="C66" s="53"/>
       <c r="D66" s="42" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="165"/>
-      <c r="B67" s="164"/>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="160"/>
+      <c r="B67" s="159"/>
       <c r="C67" s="53" t="s">
         <v>172</v>
       </c>
@@ -31531,9 +31492,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="165"/>
-      <c r="B68" s="164"/>
+    <row r="68" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="160"/>
+      <c r="B68" s="159"/>
       <c r="C68" s="53" t="s">
         <v>174</v>
       </c>
@@ -31541,9 +31502,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A69" s="165"/>
-      <c r="B69" s="164"/>
+    <row r="69" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A69" s="160"/>
+      <c r="B69" s="159"/>
       <c r="C69" s="56" t="s">
         <v>176</v>
       </c>
@@ -31551,9 +31512,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A70" s="165"/>
-      <c r="B70" s="164"/>
+    <row r="70" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A70" s="160"/>
+      <c r="B70" s="159"/>
       <c r="C70" s="56" t="s">
         <v>178</v>
       </c>
@@ -31561,9 +31522,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="165"/>
-      <c r="B71" s="164"/>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="160"/>
+      <c r="B71" s="159"/>
       <c r="C71" s="53" t="s">
         <v>179</v>
       </c>
@@ -31571,9 +31532,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="165"/>
-      <c r="B72" s="164"/>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="160"/>
+      <c r="B72" s="159"/>
       <c r="C72" s="53" t="s">
         <v>181</v>
       </c>
@@ -31581,17 +31542,17 @@
         <v>173</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="165"/>
-      <c r="B73" s="164"/>
+    <row r="73" spans="1:4" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="160"/>
+      <c r="B73" s="159"/>
       <c r="C73" s="53"/>
       <c r="D73" s="45" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="165"/>
-      <c r="B74" s="164"/>
+    <row r="74" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="160"/>
+      <c r="B74" s="159"/>
       <c r="C74" s="53" t="s">
         <v>182</v>
       </c>
@@ -31599,21 +31560,21 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="165"/>
-      <c r="B75" s="164"/>
-      <c r="C75" s="171"/>
-      <c r="D75" s="166" t="s">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="160"/>
+      <c r="B75" s="159"/>
+      <c r="C75" s="166"/>
+      <c r="D75" s="161" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="165"/>
-      <c r="B76" s="164"/>
-      <c r="C76" s="171"/>
-      <c r="D76" s="166"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="160"/>
+      <c r="B76" s="159"/>
+      <c r="C76" s="166"/>
+      <c r="D76" s="161"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="35" t="s">
         <v>72</v>
       </c>
@@ -31621,13 +31582,13 @@
       <c r="C77" s="35"/>
       <c r="D77" s="40"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="44"/>
       <c r="B78" s="36"/>
       <c r="C78" s="34"/>
       <c r="D78" s="46"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="44"/>
       <c r="B79" s="36"/>
       <c r="C79" s="34"/>
@@ -31691,15 +31652,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D72"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.26953125" customWidth="1"/>
-    <col min="2" max="2" width="45.7265625" customWidth="1"/>
-    <col min="3" max="3" width="49.26953125" customWidth="1"/>
-    <col min="4" max="4" width="80.81640625" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" customWidth="1"/>
+    <col min="3" max="3" width="49.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="44.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="44.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -31713,7 +31674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>77</v>
       </c>
@@ -31721,7 +31682,7 @@
       <c r="C2" s="35"/>
       <c r="D2" s="40"/>
     </row>
-    <row r="3" spans="1:4" ht="45.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="45.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
         <v>8</v>
       </c>
@@ -31729,11 +31690,11 @@
       <c r="C3" s="35"/>
       <c r="D3" s="40"/>
     </row>
-    <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="159" t="s">
+    <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="154" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="160" t="s">
+      <c r="B4" s="155" t="s">
         <v>185</v>
       </c>
       <c r="C4" s="67" t="s">
@@ -31743,139 +31704,139 @@
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="159"/>
-      <c r="B5" s="160"/>
-      <c r="C5" s="186" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="154"/>
+      <c r="B5" s="155"/>
+      <c r="C5" s="181" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="185" t="s">
+      <c r="D5" s="180" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="7.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="159"/>
-      <c r="B6" s="160"/>
-      <c r="C6" s="186"/>
-      <c r="D6" s="185"/>
-    </row>
-    <row r="7" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="159"/>
-      <c r="B7" s="160"/>
+    <row r="6" spans="1:4" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="154"/>
+      <c r="B6" s="155"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="180"/>
+    </row>
+    <row r="7" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="154"/>
+      <c r="B7" s="155"/>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
     </row>
-    <row r="8" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="159"/>
-      <c r="B8" s="160"/>
+    <row r="8" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="154"/>
+      <c r="B8" s="155"/>
       <c r="C8" s="53"/>
       <c r="D8" s="53"/>
     </row>
-    <row r="9" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="159"/>
-      <c r="B9" s="160"/>
+    <row r="9" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="154"/>
+      <c r="B9" s="155"/>
       <c r="C9" s="66"/>
       <c r="D9" s="45"/>
     </row>
-    <row r="10" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="162" t="s">
+    <row r="10" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="157" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="160" t="s">
+      <c r="B10" s="155" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="184"/>
-      <c r="D10" s="185" t="s">
+      <c r="C10" s="179"/>
+      <c r="D10" s="180" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="162"/>
-      <c r="B11" s="160"/>
-      <c r="C11" s="184"/>
-      <c r="D11" s="185"/>
-    </row>
-    <row r="12" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="162"/>
-      <c r="B12" s="160"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="185"/>
-    </row>
-    <row r="13" spans="1:4" ht="31.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="163" t="s">
+    <row r="11" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="157"/>
+      <c r="B11" s="155"/>
+      <c r="C11" s="179"/>
+      <c r="D11" s="180"/>
+    </row>
+    <row r="12" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="157"/>
+      <c r="B12" s="155"/>
+      <c r="C12" s="179"/>
+      <c r="D12" s="180"/>
+    </row>
+    <row r="13" spans="1:4" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="158" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="164" t="s">
+      <c r="B13" s="159" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="187"/>
-      <c r="D13" s="185" t="s">
+      <c r="C13" s="182"/>
+      <c r="D13" s="180" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="163"/>
-      <c r="B14" s="164"/>
-      <c r="C14" s="187"/>
-      <c r="D14" s="185"/>
-    </row>
-    <row r="15" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="163"/>
-      <c r="B15" s="164"/>
-      <c r="C15" s="187"/>
+    <row r="14" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="158"/>
+      <c r="B14" s="159"/>
+      <c r="C14" s="182"/>
+      <c r="D14" s="180"/>
+    </row>
+    <row r="15" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="158"/>
+      <c r="B15" s="159"/>
+      <c r="C15" s="182"/>
       <c r="D15" s="45"/>
     </row>
-    <row r="16" spans="1:4" ht="27.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="163"/>
-      <c r="B16" s="164"/>
-      <c r="C16" s="187"/>
+    <row r="16" spans="1:4" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="158"/>
+      <c r="B16" s="159"/>
+      <c r="C16" s="182"/>
       <c r="D16" s="45"/>
     </row>
-    <row r="17" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="163"/>
-      <c r="B17" s="164"/>
-      <c r="C17" s="187"/>
+    <row r="17" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="158"/>
+      <c r="B17" s="159"/>
+      <c r="C17" s="182"/>
       <c r="D17" s="45"/>
     </row>
-    <row r="18" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="163"/>
-      <c r="B18" s="164"/>
-      <c r="C18" s="187"/>
+    <row r="18" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="158"/>
+      <c r="B18" s="159"/>
+      <c r="C18" s="182"/>
       <c r="D18" s="45"/>
     </row>
-    <row r="19" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="163"/>
-      <c r="B19" s="164"/>
-      <c r="C19" s="187"/>
+    <row r="19" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="158"/>
+      <c r="B19" s="159"/>
+      <c r="C19" s="182"/>
       <c r="D19" s="45"/>
     </row>
-    <row r="20" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="163"/>
-      <c r="B20" s="164"/>
-      <c r="C20" s="187"/>
+    <row r="20" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="158"/>
+      <c r="B20" s="159"/>
+      <c r="C20" s="182"/>
       <c r="D20" s="45"/>
     </row>
-    <row r="21" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="163"/>
-      <c r="B21" s="164"/>
-      <c r="C21" s="187"/>
+    <row r="21" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="158"/>
+      <c r="B21" s="159"/>
+      <c r="C21" s="182"/>
       <c r="D21" s="45"/>
     </row>
-    <row r="22" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="163"/>
-      <c r="B22" s="164"/>
-      <c r="C22" s="187"/>
+    <row r="22" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="158"/>
+      <c r="B22" s="159"/>
+      <c r="C22" s="182"/>
       <c r="D22" s="45"/>
     </row>
-    <row r="23" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="163"/>
-      <c r="B23" s="164"/>
-      <c r="C23" s="187"/>
+    <row r="23" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="158"/>
+      <c r="B23" s="159"/>
+      <c r="C23" s="182"/>
       <c r="D23" s="53" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="68" t="s">
         <v>193</v>
       </c>
@@ -31889,7 +31850,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="68" t="s">
         <v>195</v>
       </c>
@@ -31903,7 +31864,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="44" t="s">
         <v>121</v>
       </c>
@@ -31915,7 +31876,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="35" t="s">
         <v>34</v>
       </c>
@@ -31923,7 +31884,7 @@
       <c r="C27" s="35"/>
       <c r="D27" s="35"/>
     </row>
-    <row r="28" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="75" t="s">
         <v>35</v>
       </c>
@@ -31937,7 +31898,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="75"/>
       <c r="B29" s="47"/>
       <c r="C29" s="65" t="s">
@@ -31947,7 +31908,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="75"/>
       <c r="B30" s="47"/>
       <c r="C30" s="65" t="s">
@@ -31957,7 +31918,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="75"/>
       <c r="B31" s="47"/>
       <c r="C31" s="77" t="s">
@@ -31967,11 +31928,11 @@
         <v>204</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="188" t="s">
+    <row r="32" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="183" t="s">
         <v>205</v>
       </c>
-      <c r="B32" s="191" t="s">
+      <c r="B32" s="186" t="s">
         <v>185</v>
       </c>
       <c r="C32" s="79" t="s">
@@ -31981,27 +31942,27 @@
         <v>207</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="189"/>
-      <c r="B33" s="192"/>
+    <row r="33" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="184"/>
+      <c r="B33" s="187"/>
       <c r="C33" s="65"/>
       <c r="D33" s="69"/>
     </row>
-    <row r="34" spans="1:4" ht="9.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="189"/>
-      <c r="B34" s="192"/>
+    <row r="34" spans="1:4" ht="9.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="184"/>
+      <c r="B34" s="187"/>
       <c r="C34" s="65"/>
       <c r="D34" s="69"/>
     </row>
-    <row r="35" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="189"/>
-      <c r="B35" s="192"/>
+    <row r="35" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="184"/>
+      <c r="B35" s="187"/>
       <c r="C35" s="65"/>
       <c r="D35" s="69"/>
     </row>
-    <row r="36" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="190"/>
-      <c r="B36" s="193"/>
+    <row r="36" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="185"/>
+      <c r="B36" s="188"/>
       <c r="C36" s="65" t="s">
         <v>208</v>
       </c>
@@ -32009,7 +31970,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="44" t="s">
         <v>36</v>
       </c>
@@ -32021,7 +31982,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
         <v>37</v>
       </c>
@@ -32029,11 +31990,11 @@
       <c r="C38" s="35"/>
       <c r="D38" s="40"/>
     </row>
-    <row r="39" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="161" t="s">
+    <row r="39" spans="1:4" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="156" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="160" t="s">
+      <c r="B39" s="155" t="s">
         <v>185</v>
       </c>
       <c r="C39" s="70" t="s">
@@ -32043,9 +32004,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="161"/>
-      <c r="B40" s="160"/>
+    <row r="40" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="156"/>
+      <c r="B40" s="155"/>
       <c r="C40" s="64" t="s">
         <v>188</v>
       </c>
@@ -32053,87 +32014,87 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="159" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="154" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="160" t="s">
+      <c r="B41" s="155" t="s">
         <v>185</v>
       </c>
-      <c r="C41" s="184" t="s">
+      <c r="C41" s="179" t="s">
         <v>212</v>
       </c>
-      <c r="D41" s="163" t="s">
+      <c r="D41" s="158" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="159"/>
-      <c r="B42" s="160"/>
-      <c r="C42" s="184"/>
-      <c r="D42" s="163"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="159"/>
-      <c r="B43" s="160"/>
-      <c r="C43" s="184" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="154"/>
+      <c r="B42" s="155"/>
+      <c r="C42" s="179"/>
+      <c r="D42" s="158"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="154"/>
+      <c r="B43" s="155"/>
+      <c r="C43" s="179" t="s">
         <v>188</v>
       </c>
-      <c r="D43" s="166" t="s">
+      <c r="D43" s="161" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="159"/>
-      <c r="B44" s="160"/>
-      <c r="C44" s="184"/>
-      <c r="D44" s="166"/>
-    </row>
-    <row r="45" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="165" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="154"/>
+      <c r="B44" s="155"/>
+      <c r="C44" s="179"/>
+      <c r="D44" s="161"/>
+    </row>
+    <row r="45" spans="1:4" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="160" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="164" t="s">
+      <c r="B45" s="159" t="s">
         <v>185</v>
       </c>
-      <c r="C45" s="180"/>
+      <c r="C45" s="175"/>
       <c r="D45" s="78" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="165"/>
-      <c r="B46" s="164"/>
-      <c r="C46" s="181"/>
-      <c r="D46" s="177" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="160"/>
+      <c r="B46" s="159"/>
+      <c r="C46" s="176"/>
+      <c r="D46" s="172" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="165"/>
-      <c r="B47" s="164"/>
-      <c r="C47" s="181"/>
-      <c r="D47" s="178"/>
-    </row>
-    <row r="48" spans="1:4" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="165"/>
-      <c r="B48" s="164"/>
-      <c r="C48" s="182"/>
-      <c r="D48" s="178"/>
-    </row>
-    <row r="49" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="165"/>
-      <c r="B49" s="164"/>
-      <c r="C49" s="172"/>
-      <c r="D49" s="178"/>
-    </row>
-    <row r="50" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="165"/>
-      <c r="B50" s="164"/>
-      <c r="C50" s="172"/>
-      <c r="D50" s="179"/>
-    </row>
-    <row r="51" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="160"/>
+      <c r="B47" s="159"/>
+      <c r="C47" s="176"/>
+      <c r="D47" s="173"/>
+    </row>
+    <row r="48" spans="1:4" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="160"/>
+      <c r="B48" s="159"/>
+      <c r="C48" s="177"/>
+      <c r="D48" s="173"/>
+    </row>
+    <row r="49" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="160"/>
+      <c r="B49" s="159"/>
+      <c r="C49" s="167"/>
+      <c r="D49" s="173"/>
+    </row>
+    <row r="50" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="160"/>
+      <c r="B50" s="159"/>
+      <c r="C50" s="167"/>
+      <c r="D50" s="174"/>
+    </row>
+    <row r="51" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="35" t="s">
         <v>44</v>
       </c>
@@ -32141,7 +32102,7 @@
       <c r="C51" s="35"/>
       <c r="D51" s="40"/>
     </row>
-    <row r="52" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A52" s="44" t="s">
         <v>154</v>
       </c>
@@ -32153,11 +32114,11 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="164" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="159" t="s">
         <v>156</v>
       </c>
-      <c r="B53" s="164" t="s">
+      <c r="B53" s="159" t="s">
         <v>185</v>
       </c>
       <c r="C53" s="65" t="s">
@@ -32167,9 +32128,9 @@
         <v>217</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="164"/>
-      <c r="B54" s="164"/>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="159"/>
+      <c r="B54" s="159"/>
       <c r="C54" s="65" t="s">
         <v>188</v>
       </c>
@@ -32177,9 +32138,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="164"/>
-      <c r="B55" s="164"/>
+    <row r="55" spans="1:4" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="159"/>
+      <c r="B55" s="159"/>
       <c r="C55" s="65" t="s">
         <v>218</v>
       </c>
@@ -32187,27 +32148,27 @@
         <v>219</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="34.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="164"/>
-      <c r="B56" s="164"/>
-      <c r="C56" s="183" t="s">
+    <row r="56" spans="1:4" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="159"/>
+      <c r="B56" s="159"/>
+      <c r="C56" s="178" t="s">
         <v>220</v>
       </c>
       <c r="D56" s="71" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="164"/>
-      <c r="B57" s="164"/>
-      <c r="C57" s="183"/>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="159"/>
+      <c r="B57" s="159"/>
+      <c r="C57" s="178"/>
       <c r="D57" s="43" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="164"/>
-      <c r="B58" s="164"/>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="159"/>
+      <c r="B58" s="159"/>
       <c r="C58" s="65" t="s">
         <v>223</v>
       </c>
@@ -32215,9 +32176,9 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="164"/>
-      <c r="B59" s="164"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="159"/>
+      <c r="B59" s="159"/>
       <c r="C59" s="65" t="s">
         <v>225</v>
       </c>
@@ -32225,87 +32186,87 @@
         <v>226</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="164"/>
-      <c r="B60" s="164"/>
-      <c r="C60" s="183" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="159"/>
+      <c r="B60" s="159"/>
+      <c r="C60" s="178" t="s">
         <v>227</v>
       </c>
       <c r="D60" s="42" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="164"/>
-      <c r="B61" s="164"/>
-      <c r="C61" s="183"/>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="159"/>
+      <c r="B61" s="159"/>
+      <c r="C61" s="178"/>
       <c r="D61" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="164"/>
-      <c r="B62" s="164"/>
-      <c r="C62" s="183"/>
+    <row r="62" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="159"/>
+      <c r="B62" s="159"/>
+      <c r="C62" s="178"/>
       <c r="D62" s="71" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="164"/>
-      <c r="B63" s="164"/>
-      <c r="C63" s="184" t="s">
+    <row r="63" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="159"/>
+      <c r="B63" s="159"/>
+      <c r="C63" s="179" t="s">
         <v>231</v>
       </c>
       <c r="D63" s="41" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="164"/>
-      <c r="B64" s="164"/>
-      <c r="C64" s="184"/>
-      <c r="D64" s="166" t="s">
+    <row r="64" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="159"/>
+      <c r="B64" s="159"/>
+      <c r="C64" s="179"/>
+      <c r="D64" s="161" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="12.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="164"/>
-      <c r="B65" s="164"/>
-      <c r="C65" s="184"/>
-      <c r="D65" s="166"/>
-    </row>
-    <row r="66" spans="1:4" ht="13.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="164"/>
-      <c r="B66" s="164"/>
-      <c r="C66" s="184"/>
-      <c r="D66" s="166"/>
-    </row>
-    <row r="67" spans="1:4" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="164"/>
-      <c r="B67" s="164"/>
-      <c r="C67" s="184"/>
-      <c r="D67" s="166"/>
-    </row>
-    <row r="68" spans="1:4" ht="11.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" ht="12.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="159"/>
+      <c r="B65" s="159"/>
+      <c r="C65" s="179"/>
+      <c r="D65" s="161"/>
+    </row>
+    <row r="66" spans="1:4" ht="13.15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="159"/>
+      <c r="B66" s="159"/>
+      <c r="C66" s="179"/>
+      <c r="D66" s="161"/>
+    </row>
+    <row r="67" spans="1:4" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="159"/>
+      <c r="B67" s="159"/>
+      <c r="C67" s="179"/>
+      <c r="D67" s="161"/>
+    </row>
+    <row r="68" spans="1:4" ht="11.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="35"/>
       <c r="D68" s="40"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="73"/>
       <c r="B69" s="74"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="73"/>
       <c r="B70" s="74"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="73"/>
       <c r="B71" s="74"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="73"/>
       <c r="B72" s="74"/>
     </row>
@@ -32352,16 +32313,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D282"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D277"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="46.54296875" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" customWidth="1"/>
+    <col min="2" max="2" width="46.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -32375,7 +32336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="87" t="s">
         <v>235</v>
       </c>
@@ -32383,11 +32344,11 @@
       <c r="C2" s="87"/>
       <c r="D2" s="88"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="194" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="189" t="s">
         <v>236</v>
       </c>
-      <c r="B3" s="194" t="s">
+      <c r="B3" s="189" t="s">
         <v>237</v>
       </c>
       <c r="C3" s="85" t="s">
@@ -32397,9 +32358,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="195"/>
-      <c r="B4" s="195"/>
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="190"/>
+      <c r="B4" s="190"/>
       <c r="C4" s="84" t="s">
         <v>240</v>
       </c>
@@ -32407,9 +32368,9 @@
         <v>241</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="196"/>
-      <c r="B5" s="196"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="191"/>
+      <c r="B5" s="191"/>
       <c r="C5" s="84" t="s">
         <v>240</v>
       </c>
@@ -32417,11 +32378,11 @@
         <v>242</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="203" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="198" t="s">
         <v>243</v>
       </c>
-      <c r="B6" s="197" t="s">
+      <c r="B6" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C6" s="84"/>
@@ -32429,33 +32390,33 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="204"/>
-      <c r="B7" s="198"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="199"/>
+      <c r="B7" s="193"/>
       <c r="C7" s="84"/>
       <c r="D7" s="53" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="204"/>
-      <c r="B8" s="198"/>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="199"/>
+      <c r="B8" s="193"/>
       <c r="C8" s="84"/>
       <c r="D8" s="104" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="204"/>
-      <c r="B9" s="198"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="199"/>
+      <c r="B9" s="193"/>
       <c r="C9" s="84"/>
       <c r="D9" s="104" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="205"/>
-      <c r="B10" s="199"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="200"/>
+      <c r="B10" s="194"/>
       <c r="C10" s="84" t="s">
         <v>248</v>
       </c>
@@ -32463,11 +32424,11 @@
         <v>249</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="194" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="189" t="s">
         <v>250</v>
       </c>
-      <c r="B11" s="197" t="s">
+      <c r="B11" s="192" t="s">
         <v>237</v>
       </c>
       <c r="C11" s="84" t="s">
@@ -32477,9 +32438,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="195"/>
-      <c r="B12" s="198"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="190"/>
+      <c r="B12" s="193"/>
       <c r="C12" s="84" t="s">
         <v>251</v>
       </c>
@@ -32487,9 +32448,9 @@
         <v>252</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="196"/>
-      <c r="B13" s="199"/>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="191"/>
+      <c r="B13" s="194"/>
       <c r="C13" s="84" t="s">
         <v>253</v>
       </c>
@@ -32497,7 +32458,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="87" t="s">
         <v>255</v>
       </c>
@@ -32505,11 +32466,11 @@
       <c r="C14" s="87"/>
       <c r="D14" s="88"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="174" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="169" t="s">
         <v>256</v>
       </c>
-      <c r="B15" s="197" t="s">
+      <c r="B15" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C15" s="99" t="s">
@@ -32519,9 +32480,9 @@
         <v>258</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="175"/>
-      <c r="B16" s="199"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="170"/>
+      <c r="B16" s="194"/>
       <c r="C16" s="99" t="s">
         <v>259</v>
       </c>
@@ -32529,7 +32490,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="102" t="s">
         <v>261</v>
       </c>
@@ -32543,7 +32504,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="100" t="s">
         <v>264</v>
       </c>
@@ -32555,11 +32516,11 @@
         <v>265</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="194" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="189" t="s">
         <v>266</v>
       </c>
-      <c r="B19" s="197" t="s">
+      <c r="B19" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C19" s="80" t="s">
@@ -32569,9 +32530,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="195"/>
-      <c r="B20" s="198"/>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="190"/>
+      <c r="B20" s="193"/>
       <c r="C20" s="53" t="s">
         <v>268</v>
       </c>
@@ -32579,9 +32540,9 @@
         <v>269</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="195"/>
-      <c r="B21" s="198"/>
+    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="190"/>
+      <c r="B21" s="193"/>
       <c r="C21" s="99" t="s">
         <v>270</v>
       </c>
@@ -32589,9 +32550,9 @@
         <v>271</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="195"/>
-      <c r="B22" s="198"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="190"/>
+      <c r="B22" s="193"/>
       <c r="C22" s="99" t="s">
         <v>5</v>
       </c>
@@ -32599,9 +32560,9 @@
         <v>272</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="195"/>
-      <c r="B23" s="198"/>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="190"/>
+      <c r="B23" s="193"/>
       <c r="C23" s="84" t="s">
         <v>238</v>
       </c>
@@ -32609,9 +32570,9 @@
         <v>273</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="195"/>
-      <c r="B24" s="198"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="190"/>
+      <c r="B24" s="193"/>
       <c r="C24" s="84" t="s">
         <v>274</v>
       </c>
@@ -32619,9 +32580,9 @@
         <v>275</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="195"/>
-      <c r="B25" s="198"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="190"/>
+      <c r="B25" s="193"/>
       <c r="C25" s="84" t="s">
         <v>276</v>
       </c>
@@ -32629,9 +32590,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="195"/>
-      <c r="B26" s="198"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="190"/>
+      <c r="B26" s="193"/>
       <c r="C26" s="84" t="s">
         <v>238</v>
       </c>
@@ -32639,9 +32600,9 @@
         <v>278</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="195"/>
-      <c r="B27" s="198"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="190"/>
+      <c r="B27" s="193"/>
       <c r="C27" s="99" t="s">
         <v>279</v>
       </c>
@@ -32649,9 +32610,9 @@
         <v>280</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="196"/>
-      <c r="B28" s="199"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="191"/>
+      <c r="B28" s="194"/>
       <c r="C28" s="99">
         <v>1.1000000000000001</v>
       </c>
@@ -32659,11 +32620,11 @@
         <v>242</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="203" t="s">
+    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="198" t="s">
         <v>281</v>
       </c>
-      <c r="B29" s="197" t="s">
+      <c r="B29" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C29" s="84" t="s">
@@ -32673,9 +32634,9 @@
         <v>282</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="204"/>
-      <c r="B30" s="198"/>
+    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="199"/>
+      <c r="B30" s="193"/>
       <c r="C30" s="84" t="s">
         <v>279</v>
       </c>
@@ -32683,9 +32644,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="204"/>
-      <c r="B31" s="198"/>
+    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="199"/>
+      <c r="B31" s="193"/>
       <c r="C31" s="84">
         <v>3.3</v>
       </c>
@@ -32693,9 +32654,9 @@
         <v>284</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="204"/>
-      <c r="B32" s="198"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="199"/>
+      <c r="B32" s="193"/>
       <c r="C32" s="90">
         <v>3</v>
       </c>
@@ -32703,9 +32664,9 @@
         <v>285</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="205"/>
-      <c r="B33" s="199"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="200"/>
+      <c r="B33" s="194"/>
       <c r="C33" s="90">
         <v>3.5</v>
       </c>
@@ -32713,11 +32674,11 @@
         <v>286</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="203" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="198" t="s">
         <v>287</v>
       </c>
-      <c r="B34" s="197" t="s">
+      <c r="B34" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C34" s="90"/>
@@ -32725,28 +32686,28 @@
         <v>288</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="205"/>
-      <c r="B35" s="199"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="200"/>
+      <c r="B35" s="194"/>
       <c r="C35" s="84"/>
       <c r="D35" s="62" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="206" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="201" t="s">
         <v>290</v>
       </c>
-      <c r="B36" s="197" t="s">
+      <c r="B36" s="192" t="s">
         <v>244</v>
       </c>
       <c r="D36" s="62" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="206"/>
-      <c r="B37" s="198"/>
+    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="201"/>
+      <c r="B37" s="193"/>
       <c r="C37" s="106" t="s">
         <v>292</v>
       </c>
@@ -32754,9 +32715,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="206"/>
-      <c r="B38" s="198"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="201"/>
+      <c r="B38" s="193"/>
       <c r="C38" s="53" t="s">
         <v>294</v>
       </c>
@@ -32764,9 +32725,9 @@
         <v>295</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A39" s="206"/>
-      <c r="B39" s="198"/>
+    <row r="39" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" s="201"/>
+      <c r="B39" s="193"/>
       <c r="C39" s="56" t="s">
         <v>296</v>
       </c>
@@ -32774,11 +32735,11 @@
         <v>293</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="108" t="s">
         <v>297</v>
       </c>
-      <c r="B40" s="197" t="s">
+      <c r="B40" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C40" s="84"/>
@@ -32786,9 +32747,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="109"/>
-      <c r="B41" s="198"/>
+      <c r="B41" s="193"/>
       <c r="C41" s="84" t="s">
         <v>298</v>
       </c>
@@ -32796,19 +32757,19 @@
         <v>299</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="100"/>
-      <c r="B42" s="199"/>
+      <c r="B42" s="194"/>
       <c r="C42" s="84"/>
       <c r="D42" s="107" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="108" t="s">
         <v>300</v>
       </c>
-      <c r="B43" s="197" t="s">
+      <c r="B43" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C43" s="84"/>
@@ -32816,35 +32777,35 @@
         <v>249</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="100"/>
-      <c r="B44" s="199"/>
+      <c r="B44" s="194"/>
       <c r="C44" s="84"/>
       <c r="D44" s="107" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="194" t="s">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="189" t="s">
         <v>301</v>
       </c>
-      <c r="B45" s="197" t="s">
+      <c r="B45" s="192" t="s">
         <v>244</v>
       </c>
-      <c r="C45" s="207"/>
+      <c r="C45" s="202"/>
       <c r="D45" s="107" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="196"/>
-      <c r="B46" s="199"/>
-      <c r="C46" s="208"/>
+    <row r="46" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="191"/>
+      <c r="B46" s="194"/>
+      <c r="C46" s="203"/>
       <c r="D46" s="107" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="100" t="s">
         <v>303</v>
       </c>
@@ -32856,7 +32817,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="100" t="s">
         <v>304</v>
       </c>
@@ -32868,7 +32829,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="100" t="s">
         <v>305</v>
       </c>
@@ -32880,7 +32841,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="87" t="s">
         <v>306</v>
       </c>
@@ -32888,11 +32849,11 @@
       <c r="C50" s="87"/>
       <c r="D50" s="88"/>
     </row>
-    <row r="51" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A51" s="206" t="s">
+    <row r="51" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="201" t="s">
         <v>307</v>
       </c>
-      <c r="B51" s="212" t="s">
+      <c r="B51" s="207" t="s">
         <v>244</v>
       </c>
       <c r="C51" s="84" t="s">
@@ -32902,9 +32863,9 @@
         <v>309</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A52" s="206"/>
-      <c r="B52" s="212"/>
+    <row r="52" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="201"/>
+      <c r="B52" s="207"/>
       <c r="C52" s="84" t="s">
         <v>310</v>
       </c>
@@ -32912,9 +32873,9 @@
         <v>311</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A53" s="206"/>
-      <c r="B53" s="212"/>
+    <row r="53" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="201"/>
+      <c r="B53" s="207"/>
       <c r="C53" s="84" t="s">
         <v>308</v>
       </c>
@@ -32922,7 +32883,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="45.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="45.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="87" t="s">
         <v>8</v>
       </c>
@@ -32930,11 +32891,11 @@
       <c r="C54" s="87"/>
       <c r="D54" s="88"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="163" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="158" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="183" t="s">
+      <c r="B55" s="178" t="s">
         <v>244</v>
       </c>
       <c r="C55" s="53"/>
@@ -32942,9 +32903,9 @@
         <v>313</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="163"/>
-      <c r="B56" s="183"/>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="158"/>
+      <c r="B56" s="178"/>
       <c r="C56" s="65" t="s">
         <v>314</v>
       </c>
@@ -32952,9 +32913,9 @@
         <v>315</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="163"/>
-      <c r="B57" s="183"/>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="158"/>
+      <c r="B57" s="178"/>
       <c r="C57" s="65" t="s">
         <v>316</v>
       </c>
@@ -32962,9 +32923,9 @@
         <v>317</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="163"/>
-      <c r="B58" s="183"/>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="158"/>
+      <c r="B58" s="178"/>
       <c r="C58" s="65" t="s">
         <v>316</v>
       </c>
@@ -32972,9 +32933,9 @@
         <v>318</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="163"/>
-      <c r="B59" s="183"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="158"/>
+      <c r="B59" s="178"/>
       <c r="C59" s="65" t="s">
         <v>248</v>
       </c>
@@ -32982,9 +32943,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="163"/>
-      <c r="B60" s="183"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="158"/>
+      <c r="B60" s="178"/>
       <c r="C60" s="70" t="s">
         <v>248</v>
       </c>
@@ -32992,11 +32953,11 @@
         <v>320</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="174" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="B61" s="197" t="s">
+      <c r="B61" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C61" s="65" t="s">
@@ -33006,9 +32967,9 @@
         <v>321</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="215"/>
-      <c r="B62" s="198"/>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="210"/>
+      <c r="B62" s="193"/>
       <c r="C62" s="65" t="s">
         <v>322</v>
       </c>
@@ -33016,9 +32977,9 @@
         <v>323</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A63" s="175"/>
-      <c r="B63" s="199"/>
+    <row r="63" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="170"/>
+      <c r="B63" s="194"/>
       <c r="C63" s="103" t="s">
         <v>324</v>
       </c>
@@ -33026,7 +32987,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="90" t="s">
         <v>326</v>
       </c>
@@ -33040,7 +33001,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="90" t="s">
         <v>327</v>
       </c>
@@ -33054,7 +33015,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="90" t="s">
         <v>328</v>
       </c>
@@ -33066,11 +33027,11 @@
         <v>329</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="163" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="158" t="s">
         <v>330</v>
       </c>
-      <c r="B67" s="183" t="s">
+      <c r="B67" s="178" t="s">
         <v>244</v>
       </c>
       <c r="C67" s="53" t="s">
@@ -33080,25 +33041,25 @@
         <v>332</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="163"/>
-      <c r="B68" s="183"/>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="158"/>
+      <c r="B68" s="178"/>
       <c r="C68" s="53"/>
       <c r="D68" s="71" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="163"/>
-      <c r="B69" s="183"/>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="158"/>
+      <c r="B69" s="178"/>
       <c r="C69" s="53"/>
       <c r="D69" s="53" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="163"/>
-      <c r="B70" s="183"/>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="158"/>
+      <c r="B70" s="178"/>
       <c r="C70" s="65" t="s">
         <v>335</v>
       </c>
@@ -33106,9 +33067,9 @@
         <v>336</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="163"/>
-      <c r="B71" s="183"/>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="158"/>
+      <c r="B71" s="178"/>
       <c r="C71" s="70" t="s">
         <v>337</v>
       </c>
@@ -33116,7 +33077,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="90" t="s">
         <v>339</v>
       </c>
@@ -33128,11 +33089,11 @@
       </c>
       <c r="D72" s="53"/>
     </row>
-    <row r="73" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A73" s="209" t="s">
+    <row r="73" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A73" s="204" t="s">
         <v>121</v>
       </c>
-      <c r="B73" s="197" t="s">
+      <c r="B73" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C73" s="53"/>
@@ -33140,9 +33101,9 @@
         <v>340</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="210"/>
-      <c r="B74" s="198"/>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="205"/>
+      <c r="B74" s="193"/>
       <c r="C74" s="70" t="s">
         <v>341</v>
       </c>
@@ -33150,9 +33111,9 @@
         <v>342</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="210"/>
-      <c r="B75" s="198"/>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="205"/>
+      <c r="B75" s="193"/>
       <c r="C75" s="70" t="s">
         <v>343</v>
       </c>
@@ -33160,9 +33121,9 @@
         <v>344</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="210"/>
-      <c r="B76" s="198"/>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="205"/>
+      <c r="B76" s="193"/>
       <c r="C76" s="91" t="s">
         <v>345</v>
       </c>
@@ -33170,9 +33131,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="210"/>
-      <c r="B77" s="198"/>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="205"/>
+      <c r="B77" s="193"/>
       <c r="C77" s="70" t="s">
         <v>343</v>
       </c>
@@ -33180,9 +33141,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="210"/>
-      <c r="B78" s="198"/>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="205"/>
+      <c r="B78" s="193"/>
       <c r="C78" s="70" t="s">
         <v>348</v>
       </c>
@@ -33190,9 +33151,9 @@
         <v>349</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="210"/>
-      <c r="B79" s="198"/>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="205"/>
+      <c r="B79" s="193"/>
       <c r="C79" s="70" t="s">
         <v>343</v>
       </c>
@@ -33200,9 +33161,9 @@
         <v>350</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="210"/>
-      <c r="B80" s="198"/>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="205"/>
+      <c r="B80" s="193"/>
       <c r="C80" s="70" t="s">
         <v>351</v>
       </c>
@@ -33210,9 +33171,9 @@
         <v>352</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="210"/>
-      <c r="B81" s="198"/>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="205"/>
+      <c r="B81" s="193"/>
       <c r="C81" s="70" t="s">
         <v>353</v>
       </c>
@@ -33220,9 +33181,9 @@
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" s="210"/>
-      <c r="B82" s="198"/>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="205"/>
+      <c r="B82" s="193"/>
       <c r="C82" s="70" t="s">
         <v>343</v>
       </c>
@@ -33230,9 +33191,9 @@
         <v>355</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="210"/>
-      <c r="B83" s="198"/>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="205"/>
+      <c r="B83" s="193"/>
       <c r="C83" s="70" t="s">
         <v>353</v>
       </c>
@@ -33240,9 +33201,9 @@
         <v>356</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="210"/>
-      <c r="B84" s="198"/>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="205"/>
+      <c r="B84" s="193"/>
       <c r="C84" s="70" t="s">
         <v>343</v>
       </c>
@@ -33250,9 +33211,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="210"/>
-      <c r="B85" s="198"/>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="205"/>
+      <c r="B85" s="193"/>
       <c r="C85" s="70" t="s">
         <v>248</v>
       </c>
@@ -33260,9 +33221,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="210"/>
-      <c r="B86" s="198"/>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="205"/>
+      <c r="B86" s="193"/>
       <c r="C86" s="70" t="s">
         <v>248</v>
       </c>
@@ -33270,9 +33231,9 @@
         <v>358</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A87" s="210"/>
-      <c r="B87" s="198"/>
+    <row r="87" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A87" s="205"/>
+      <c r="B87" s="193"/>
       <c r="C87" s="91" t="s">
         <v>359</v>
       </c>
@@ -33280,9 +33241,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" s="211"/>
-      <c r="B88" s="199"/>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="206"/>
+      <c r="B88" s="194"/>
       <c r="C88" s="70" t="s">
         <v>248</v>
       </c>
@@ -33290,7 +33251,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="90" t="s">
         <v>361</v>
       </c>
@@ -33304,7 +33265,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="90" t="s">
         <v>364</v>
       </c>
@@ -33318,7 +33279,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="90" t="s">
         <v>367</v>
       </c>
@@ -33330,11 +33291,11 @@
       </c>
       <c r="D91" s="53"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" s="174" t="s">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="169" t="s">
         <v>368</v>
       </c>
-      <c r="B92" s="197" t="s">
+      <c r="B92" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C92" s="70" t="s">
@@ -33342,9 +33303,9 @@
       </c>
       <c r="D92" s="53"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" s="175"/>
-      <c r="B93" s="199"/>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="170"/>
+      <c r="B93" s="194"/>
       <c r="C93" s="70" t="s">
         <v>337</v>
       </c>
@@ -33352,7 +33313,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="87" t="s">
         <v>34</v>
       </c>
@@ -33360,11 +33321,11 @@
       <c r="C94" s="87"/>
       <c r="D94" s="87"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" s="174" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="169" t="s">
         <v>369</v>
       </c>
-      <c r="B95" s="197" t="s">
+      <c r="B95" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C95" s="53"/>
@@ -33372,25 +33333,25 @@
         <v>370</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" s="215"/>
-      <c r="B96" s="198"/>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="210"/>
+      <c r="B96" s="193"/>
       <c r="C96" s="53"/>
       <c r="D96" s="53" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" s="215"/>
-      <c r="B97" s="198"/>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="210"/>
+      <c r="B97" s="193"/>
       <c r="C97" s="53"/>
       <c r="D97" s="53" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" s="215"/>
-      <c r="B98" s="198"/>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="210"/>
+      <c r="B98" s="193"/>
       <c r="C98" s="53" t="s">
         <v>373</v>
       </c>
@@ -33398,9 +33359,9 @@
         <v>374</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" s="215"/>
-      <c r="B99" s="198"/>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="210"/>
+      <c r="B99" s="193"/>
       <c r="C99" s="53" t="s">
         <v>375</v>
       </c>
@@ -33408,9 +33369,9 @@
         <v>376</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" s="215"/>
-      <c r="B100" s="198"/>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="210"/>
+      <c r="B100" s="193"/>
       <c r="C100" s="53" t="s">
         <v>377</v>
       </c>
@@ -33418,9 +33379,9 @@
         <v>378</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" s="215"/>
-      <c r="B101" s="198"/>
+    <row r="101" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A101" s="210"/>
+      <c r="B101" s="193"/>
       <c r="C101" s="56" t="s">
         <v>379</v>
       </c>
@@ -33428,9 +33389,9 @@
         <v>349</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" s="215"/>
-      <c r="B102" s="198"/>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="210"/>
+      <c r="B102" s="193"/>
       <c r="C102" s="53" t="s">
         <v>41</v>
       </c>
@@ -33438,9 +33399,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" s="215"/>
-      <c r="B103" s="198"/>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="210"/>
+      <c r="B103" s="193"/>
       <c r="C103" s="90" t="s">
         <v>343</v>
       </c>
@@ -33448,9 +33409,9 @@
         <v>355</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" s="215"/>
-      <c r="B104" s="198"/>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="210"/>
+      <c r="B104" s="193"/>
       <c r="C104" s="90" t="s">
         <v>353</v>
       </c>
@@ -33458,9 +33419,9 @@
         <v>381</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" s="215"/>
-      <c r="B105" s="198"/>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="210"/>
+      <c r="B105" s="193"/>
       <c r="C105" s="90" t="s">
         <v>377</v>
       </c>
@@ -33468,9 +33429,9 @@
         <v>382</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" s="215"/>
-      <c r="B106" s="198"/>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="210"/>
+      <c r="B106" s="193"/>
       <c r="C106" s="90" t="s">
         <v>343</v>
       </c>
@@ -33478,9 +33439,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" s="215"/>
-      <c r="B107" s="198"/>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="210"/>
+      <c r="B107" s="193"/>
       <c r="C107" s="90" t="s">
         <v>248</v>
       </c>
@@ -33488,9 +33449,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" s="215"/>
-      <c r="B108" s="198"/>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="210"/>
+      <c r="B108" s="193"/>
       <c r="C108" s="90" t="s">
         <v>248</v>
       </c>
@@ -33498,9 +33459,9 @@
         <v>358</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A109" s="215"/>
-      <c r="B109" s="198"/>
+    <row r="109" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A109" s="210"/>
+      <c r="B109" s="193"/>
       <c r="C109" s="91" t="s">
         <v>359</v>
       </c>
@@ -33508,9 +33469,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" s="175"/>
-      <c r="B110" s="199"/>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="170"/>
+      <c r="B110" s="194"/>
       <c r="C110" s="90" t="s">
         <v>248</v>
       </c>
@@ -33518,11 +33479,11 @@
         <v>320</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" s="216" t="s">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="211" t="s">
         <v>36</v>
       </c>
-      <c r="B111" s="197" t="s">
+      <c r="B111" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C111" s="113" t="s">
@@ -33532,9 +33493,9 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" s="217"/>
-      <c r="B112" s="198"/>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="212"/>
+      <c r="B112" s="193"/>
       <c r="C112" s="53" t="s">
         <v>383</v>
       </c>
@@ -33542,17 +33503,17 @@
         <v>384</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" s="217"/>
-      <c r="B113" s="198"/>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="212"/>
+      <c r="B113" s="193"/>
       <c r="C113" s="53"/>
       <c r="D113" s="53" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A114" s="217"/>
-      <c r="B114" s="198"/>
+    <row r="114" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A114" s="212"/>
+      <c r="B114" s="193"/>
       <c r="C114" s="56" t="s">
         <v>386</v>
       </c>
@@ -33560,9 +33521,9 @@
         <v>387</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" s="217"/>
-      <c r="B115" s="198"/>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="212"/>
+      <c r="B115" s="193"/>
       <c r="C115" s="56" t="s">
         <v>343</v>
       </c>
@@ -33570,9 +33531,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" s="217"/>
-      <c r="B116" s="198"/>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="212"/>
+      <c r="B116" s="193"/>
       <c r="C116" s="56" t="s">
         <v>345</v>
       </c>
@@ -33580,9 +33541,9 @@
         <v>388</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" s="217"/>
-      <c r="B117" s="198"/>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="212"/>
+      <c r="B117" s="193"/>
       <c r="C117" s="56" t="s">
         <v>348</v>
       </c>
@@ -33590,9 +33551,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A118" s="217"/>
-      <c r="B118" s="198"/>
+    <row r="118" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A118" s="212"/>
+      <c r="B118" s="193"/>
       <c r="C118" s="56" t="s">
         <v>389</v>
       </c>
@@ -33600,9 +33561,9 @@
         <v>390</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" s="217"/>
-      <c r="B119" s="198"/>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="212"/>
+      <c r="B119" s="193"/>
       <c r="C119" s="90" t="s">
         <v>343</v>
       </c>
@@ -33610,9 +33571,9 @@
         <v>391</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" s="217"/>
-      <c r="B120" s="198"/>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="212"/>
+      <c r="B120" s="193"/>
       <c r="C120" s="90" t="s">
         <v>351</v>
       </c>
@@ -33620,9 +33581,9 @@
         <v>352</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" s="217"/>
-      <c r="B121" s="198"/>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="212"/>
+      <c r="B121" s="193"/>
       <c r="C121" s="90" t="s">
         <v>353</v>
       </c>
@@ -33630,9 +33591,9 @@
         <v>354</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" s="217"/>
-      <c r="B122" s="198"/>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="212"/>
+      <c r="B122" s="193"/>
       <c r="C122" s="90" t="s">
         <v>343</v>
       </c>
@@ -33640,9 +33601,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" s="217"/>
-      <c r="B123" s="198"/>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="212"/>
+      <c r="B123" s="193"/>
       <c r="C123" s="90" t="s">
         <v>353</v>
       </c>
@@ -33650,9 +33611,9 @@
         <v>381</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" s="217"/>
-      <c r="B124" s="198"/>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="212"/>
+      <c r="B124" s="193"/>
       <c r="C124" s="90" t="s">
         <v>377</v>
       </c>
@@ -33660,9 +33621,9 @@
         <v>382</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" s="217"/>
-      <c r="B125" s="198"/>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="212"/>
+      <c r="B125" s="193"/>
       <c r="C125" s="90" t="s">
         <v>343</v>
       </c>
@@ -33670,9 +33631,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" s="217"/>
-      <c r="B126" s="198"/>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="212"/>
+      <c r="B126" s="193"/>
       <c r="C126" s="90" t="s">
         <v>248</v>
       </c>
@@ -33680,9 +33641,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" s="217"/>
-      <c r="B127" s="198"/>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="212"/>
+      <c r="B127" s="193"/>
       <c r="C127" s="90" t="s">
         <v>248</v>
       </c>
@@ -33690,9 +33651,9 @@
         <v>358</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A128" s="217"/>
-      <c r="B128" s="198"/>
+    <row r="128" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A128" s="212"/>
+      <c r="B128" s="193"/>
       <c r="C128" s="91" t="s">
         <v>359</v>
       </c>
@@ -33700,9 +33661,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" s="218"/>
-      <c r="B129" s="199"/>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="213"/>
+      <c r="B129" s="194"/>
       <c r="C129" s="90" t="s">
         <v>248</v>
       </c>
@@ -33710,49 +33671,49 @@
         <v>320</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" s="174" t="s">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="169" t="s">
         <v>205</v>
       </c>
-      <c r="B130" s="197" t="s">
+      <c r="B130" s="192" t="s">
         <v>244</v>
       </c>
-      <c r="C130" s="219" t="s">
+      <c r="C130" s="214" t="s">
         <v>392</v>
       </c>
       <c r="D130" s="80" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" s="215"/>
-      <c r="B131" s="198"/>
-      <c r="C131" s="220"/>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="210"/>
+      <c r="B131" s="193"/>
+      <c r="C131" s="215"/>
       <c r="D131" s="53" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" s="215"/>
-      <c r="B132" s="198"/>
-      <c r="C132" s="221" t="s">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="210"/>
+      <c r="B132" s="193"/>
+      <c r="C132" s="216" t="s">
         <v>395</v>
       </c>
       <c r="D132" s="53" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A133" s="215"/>
-      <c r="B133" s="198"/>
-      <c r="C133" s="221"/>
+    <row r="133" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A133" s="210"/>
+      <c r="B133" s="193"/>
+      <c r="C133" s="216"/>
       <c r="D133" s="56" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" s="215"/>
-      <c r="B134" s="198"/>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="210"/>
+      <c r="B134" s="193"/>
       <c r="C134" s="70" t="s">
         <v>398</v>
       </c>
@@ -33760,9 +33721,9 @@
         <v>399</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" s="215"/>
-      <c r="B135" s="198"/>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="210"/>
+      <c r="B135" s="193"/>
       <c r="C135" s="70">
         <v>2.1</v>
       </c>
@@ -33770,9 +33731,9 @@
         <v>400</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" s="215"/>
-      <c r="B136" s="198"/>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="210"/>
+      <c r="B136" s="193"/>
       <c r="C136" s="70" t="s">
         <v>392</v>
       </c>
@@ -33780,9 +33741,9 @@
         <v>401</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" s="215"/>
-      <c r="B137" s="198"/>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="210"/>
+      <c r="B137" s="193"/>
       <c r="C137" s="70" t="s">
         <v>392</v>
       </c>
@@ -33790,9 +33751,9 @@
         <v>402</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" s="215"/>
-      <c r="B138" s="198"/>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="210"/>
+      <c r="B138" s="193"/>
       <c r="C138" s="70" t="s">
         <v>392</v>
       </c>
@@ -33800,9 +33761,9 @@
         <v>403</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" s="215"/>
-      <c r="B139" s="198"/>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="210"/>
+      <c r="B139" s="193"/>
       <c r="C139" s="93" t="s">
         <v>404</v>
       </c>
@@ -33810,9 +33771,9 @@
         <v>405</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" s="215"/>
-      <c r="B140" s="198"/>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="210"/>
+      <c r="B140" s="193"/>
       <c r="C140" s="70">
         <v>2.1</v>
       </c>
@@ -33820,9 +33781,9 @@
         <v>406</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" s="215"/>
-      <c r="B141" s="198"/>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="210"/>
+      <c r="B141" s="193"/>
       <c r="C141" s="70" t="s">
         <v>392</v>
       </c>
@@ -33830,9 +33791,9 @@
         <v>338</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" s="215"/>
-      <c r="B142" s="198"/>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="210"/>
+      <c r="B142" s="193"/>
       <c r="C142" s="70" t="s">
         <v>392</v>
       </c>
@@ -33840,9 +33801,9 @@
         <v>407</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" s="215"/>
-      <c r="B143" s="198"/>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="210"/>
+      <c r="B143" s="193"/>
       <c r="C143" s="70">
         <v>2.1</v>
       </c>
@@ -33850,11 +33811,11 @@
         <v>408</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="216" t="s">
+    <row r="144" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="211" t="s">
         <v>409</v>
       </c>
-      <c r="B144" s="197" t="s">
+      <c r="B144" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C144" s="53" t="s">
@@ -33864,9 +33825,9 @@
         <v>411</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A145" s="217"/>
-      <c r="B145" s="198"/>
+    <row r="145" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A145" s="212"/>
+      <c r="B145" s="193"/>
       <c r="C145" s="56" t="s">
         <v>412</v>
       </c>
@@ -33874,9 +33835,9 @@
         <v>413</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="218"/>
-      <c r="B146" s="199"/>
+    <row r="146" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="213"/>
+      <c r="B146" s="194"/>
       <c r="C146" s="53" t="s">
         <v>414</v>
       </c>
@@ -33884,11 +33845,11 @@
         <v>415</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="174" t="s">
+    <row r="147" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="169" t="s">
         <v>416</v>
       </c>
-      <c r="B147" s="197" t="s">
+      <c r="B147" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C147" s="70" t="s">
@@ -33896,9 +33857,9 @@
       </c>
       <c r="D147" s="53"/>
     </row>
-    <row r="148" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="215"/>
-      <c r="B148" s="198"/>
+    <row r="148" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="210"/>
+      <c r="B148" s="193"/>
       <c r="C148" s="70" t="s">
         <v>404</v>
       </c>
@@ -33906,9 +33867,9 @@
         <v>405</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="215"/>
-      <c r="B149" s="198"/>
+    <row r="149" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="210"/>
+      <c r="B149" s="193"/>
       <c r="C149" s="70">
         <v>2.1</v>
       </c>
@@ -33916,9 +33877,9 @@
         <v>406</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="215"/>
-      <c r="B150" s="198"/>
+    <row r="150" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="210"/>
+      <c r="B150" s="193"/>
       <c r="C150" s="70" t="s">
         <v>395</v>
       </c>
@@ -33926,9 +33887,9 @@
         <v>417</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="215"/>
-      <c r="B151" s="198"/>
+    <row r="151" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="210"/>
+      <c r="B151" s="193"/>
       <c r="C151" s="70" t="s">
         <v>392</v>
       </c>
@@ -33936,7 +33897,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="87" t="s">
         <v>37</v>
       </c>
@@ -33944,7 +33905,7 @@
       <c r="C152" s="87"/>
       <c r="D152" s="88"/>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="90" t="s">
         <v>418</v>
       </c>
@@ -33956,11 +33917,11 @@
       </c>
       <c r="D153" s="53"/>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A154" s="174" t="s">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="169" t="s">
         <v>420</v>
       </c>
-      <c r="B154" s="197" t="s">
+      <c r="B154" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C154" s="53"/>
@@ -33968,25 +33929,25 @@
         <v>333</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A155" s="215"/>
-      <c r="B155" s="198"/>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="210"/>
+      <c r="B155" s="193"/>
       <c r="C155" s="53"/>
       <c r="D155" s="53" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A156" s="215"/>
-      <c r="B156" s="198"/>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="210"/>
+      <c r="B156" s="193"/>
       <c r="C156" s="53"/>
       <c r="D156" s="53" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A157" s="215"/>
-      <c r="B157" s="198"/>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="210"/>
+      <c r="B157" s="193"/>
       <c r="C157" s="53" t="s">
         <v>422</v>
       </c>
@@ -33994,9 +33955,9 @@
         <v>318</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A158" s="215"/>
-      <c r="B158" s="198"/>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="210"/>
+      <c r="B158" s="193"/>
       <c r="C158" s="53" t="s">
         <v>423</v>
       </c>
@@ -34004,9 +33965,9 @@
         <v>424</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A159" s="215"/>
-      <c r="B159" s="198"/>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" s="210"/>
+      <c r="B159" s="193"/>
       <c r="C159" s="53" t="s">
         <v>316</v>
       </c>
@@ -34014,9 +33975,9 @@
         <v>349</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A160" s="215"/>
-      <c r="B160" s="198"/>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="210"/>
+      <c r="B160" s="193"/>
       <c r="C160" s="53" t="s">
         <v>248</v>
       </c>
@@ -34024,11 +33985,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A161" s="163" t="s">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" s="158" t="s">
         <v>426</v>
       </c>
-      <c r="B161" s="183" t="s">
+      <c r="B161" s="178" t="s">
         <v>244</v>
       </c>
       <c r="C161" s="71" t="s">
@@ -34038,9 +33999,9 @@
         <v>428</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A162" s="163"/>
-      <c r="B162" s="183"/>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" s="158"/>
+      <c r="B162" s="178"/>
       <c r="C162" s="53" t="s">
         <v>429</v>
       </c>
@@ -34048,43 +34009,43 @@
         <v>430</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A163" s="163"/>
-      <c r="B163" s="183"/>
+    <row r="163" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A163" s="158"/>
+      <c r="B163" s="178"/>
       <c r="C163" s="94" t="s">
         <v>431</v>
       </c>
-      <c r="D163" s="197" t="s">
+      <c r="D163" s="192" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A164" s="163"/>
-      <c r="B164" s="183"/>
+    <row r="164" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A164" s="158"/>
+      <c r="B164" s="178"/>
       <c r="C164" s="94" t="s">
         <v>433</v>
       </c>
-      <c r="D164" s="198"/>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A165" s="163"/>
-      <c r="B165" s="183"/>
+      <c r="D164" s="193"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" s="158"/>
+      <c r="B165" s="178"/>
       <c r="C165" s="94" t="s">
         <v>434</v>
       </c>
-      <c r="D165" s="198"/>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A166" s="163"/>
-      <c r="B166" s="183"/>
+      <c r="D165" s="193"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" s="158"/>
+      <c r="B166" s="178"/>
       <c r="C166" s="94" t="s">
         <v>435</v>
       </c>
-      <c r="D166" s="198"/>
-    </row>
-    <row r="167" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A167" s="163"/>
-      <c r="B167" s="183"/>
+      <c r="D166" s="193"/>
+    </row>
+    <row r="167" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A167" s="158"/>
+      <c r="B167" s="178"/>
       <c r="C167" s="94" t="s">
         <v>436</v>
       </c>
@@ -34092,7 +34053,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="90" t="s">
         <v>437</v>
       </c>
@@ -34106,11 +34067,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="200" t="s">
+    <row r="169" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="195" t="s">
         <v>43</v>
       </c>
-      <c r="B169" s="197" t="s">
+      <c r="B169" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C169" s="53" t="s">
@@ -34120,9 +34081,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A170" s="201"/>
-      <c r="B170" s="198"/>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" s="196"/>
+      <c r="B170" s="193"/>
       <c r="C170" s="53" t="s">
         <v>439</v>
       </c>
@@ -34130,9 +34091,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A171" s="201"/>
-      <c r="B171" s="198"/>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" s="196"/>
+      <c r="B171" s="193"/>
       <c r="C171" s="53" t="s">
         <v>440</v>
       </c>
@@ -34140,9 +34101,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A172" s="201"/>
-      <c r="B172" s="198"/>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" s="196"/>
+      <c r="B172" s="193"/>
       <c r="C172" s="53" t="s">
         <v>441</v>
       </c>
@@ -34150,9 +34111,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A173" s="201"/>
-      <c r="B173" s="198"/>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" s="196"/>
+      <c r="B173" s="193"/>
       <c r="C173" s="53" t="s">
         <v>442</v>
       </c>
@@ -34160,9 +34121,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A174" s="201"/>
-      <c r="B174" s="198"/>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" s="196"/>
+      <c r="B174" s="193"/>
       <c r="C174" s="53" t="s">
         <v>443</v>
       </c>
@@ -34170,9 +34131,9 @@
         <v>444</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A175" s="201"/>
-      <c r="B175" s="198"/>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" s="196"/>
+      <c r="B175" s="193"/>
       <c r="C175" s="53" t="s">
         <v>445</v>
       </c>
@@ -34180,9 +34141,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A176" s="201"/>
-      <c r="B176" s="198"/>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="196"/>
+      <c r="B176" s="193"/>
       <c r="C176" s="53" t="s">
         <v>446</v>
       </c>
@@ -34190,9 +34151,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A177" s="201"/>
-      <c r="B177" s="198"/>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="196"/>
+      <c r="B177" s="193"/>
       <c r="C177" s="53" t="s">
         <v>447</v>
       </c>
@@ -34200,9 +34161,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A178" s="201"/>
-      <c r="B178" s="198"/>
+    <row r="178" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A178" s="196"/>
+      <c r="B178" s="193"/>
       <c r="C178" s="95" t="s">
         <v>448</v>
       </c>
@@ -34210,9 +34171,9 @@
         <v>449</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A179" s="201"/>
-      <c r="B179" s="198"/>
+    <row r="179" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A179" s="196"/>
+      <c r="B179" s="193"/>
       <c r="C179" s="56" t="s">
         <v>450</v>
       </c>
@@ -34220,9 +34181,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A180" s="201"/>
-      <c r="B180" s="198"/>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" s="196"/>
+      <c r="B180" s="193"/>
       <c r="C180" s="53" t="s">
         <v>451</v>
       </c>
@@ -34230,9 +34191,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A181" s="201"/>
-      <c r="B181" s="198"/>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" s="196"/>
+      <c r="B181" s="193"/>
       <c r="C181" s="53" t="s">
         <v>452</v>
       </c>
@@ -34240,9 +34201,9 @@
         <v>453</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A182" s="201"/>
-      <c r="B182" s="198"/>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="196"/>
+      <c r="B182" s="193"/>
       <c r="C182" s="53" t="s">
         <v>454</v>
       </c>
@@ -34250,9 +34211,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A183" s="201"/>
-      <c r="B183" s="198"/>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" s="196"/>
+      <c r="B183" s="193"/>
       <c r="C183" s="53" t="s">
         <v>438</v>
       </c>
@@ -34260,9 +34221,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A184" s="201"/>
-      <c r="B184" s="198"/>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="196"/>
+      <c r="B184" s="193"/>
       <c r="C184" s="53" t="s">
         <v>455</v>
       </c>
@@ -34270,9 +34231,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A185" s="201"/>
-      <c r="B185" s="198"/>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" s="196"/>
+      <c r="B185" s="193"/>
       <c r="C185" s="53" t="s">
         <v>443</v>
       </c>
@@ -34280,9 +34241,9 @@
         <v>456</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A186" s="201"/>
-      <c r="B186" s="198"/>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="196"/>
+      <c r="B186" s="193"/>
       <c r="C186" s="53" t="s">
         <v>457</v>
       </c>
@@ -34290,17 +34251,17 @@
         <v>249</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A187" s="201"/>
-      <c r="B187" s="198"/>
+    <row r="187" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A187" s="196"/>
+      <c r="B187" s="193"/>
       <c r="C187" s="53"/>
       <c r="D187" s="81" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A188" s="201"/>
-      <c r="B188" s="198"/>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="196"/>
+      <c r="B188" s="193"/>
       <c r="C188" s="53" t="s">
         <v>459</v>
       </c>
@@ -34308,9 +34269,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A189" s="201"/>
-      <c r="B189" s="198"/>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="196"/>
+      <c r="B189" s="193"/>
       <c r="C189" s="53" t="s">
         <v>438</v>
       </c>
@@ -34318,9 +34279,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A190" s="201"/>
-      <c r="B190" s="198"/>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="196"/>
+      <c r="B190" s="193"/>
       <c r="C190" s="53" t="s">
         <v>460</v>
       </c>
@@ -34328,9 +34289,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A191" s="201"/>
-      <c r="B191" s="198"/>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="196"/>
+      <c r="B191" s="193"/>
       <c r="C191" s="53" t="s">
         <v>461</v>
       </c>
@@ -34338,9 +34299,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A192" s="201"/>
-      <c r="B192" s="198"/>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="196"/>
+      <c r="B192" s="193"/>
       <c r="C192" s="53" t="s">
         <v>462</v>
       </c>
@@ -34348,9 +34309,9 @@
         <v>463</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A193" s="201"/>
-      <c r="B193" s="198"/>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="196"/>
+      <c r="B193" s="193"/>
       <c r="C193" s="53" t="s">
         <v>464</v>
       </c>
@@ -34358,9 +34319,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A194" s="201"/>
-      <c r="B194" s="198"/>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="196"/>
+      <c r="B194" s="193"/>
       <c r="C194" s="53" t="s">
         <v>465</v>
       </c>
@@ -34368,9 +34329,9 @@
         <v>466</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A195" s="201"/>
-      <c r="B195" s="198"/>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="196"/>
+      <c r="B195" s="193"/>
       <c r="C195" s="53" t="s">
         <v>467</v>
       </c>
@@ -34378,9 +34339,9 @@
         <v>468</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A196" s="201"/>
-      <c r="B196" s="198"/>
+    <row r="196" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A196" s="196"/>
+      <c r="B196" s="193"/>
       <c r="C196" s="85" t="s">
         <v>469</v>
       </c>
@@ -34388,9 +34349,9 @@
         <v>470</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A197" s="201"/>
-      <c r="B197" s="198"/>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="196"/>
+      <c r="B197" s="193"/>
       <c r="C197" s="53" t="s">
         <v>471</v>
       </c>
@@ -34398,9 +34359,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A198" s="201"/>
-      <c r="B198" s="198"/>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="196"/>
+      <c r="B198" s="193"/>
       <c r="C198" s="53" t="s">
         <v>472</v>
       </c>
@@ -34408,9 +34369,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A199" s="201"/>
-      <c r="B199" s="198"/>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="196"/>
+      <c r="B199" s="193"/>
       <c r="C199" s="53" t="s">
         <v>473</v>
       </c>
@@ -34418,9 +34379,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A200" s="201"/>
-      <c r="B200" s="198"/>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="196"/>
+      <c r="B200" s="193"/>
       <c r="C200" s="53" t="s">
         <v>474</v>
       </c>
@@ -34428,9 +34389,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A201" s="201"/>
-      <c r="B201" s="198"/>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="196"/>
+      <c r="B201" s="193"/>
       <c r="C201" s="53" t="s">
         <v>475</v>
       </c>
@@ -34438,9 +34399,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A202" s="201"/>
-      <c r="B202" s="198"/>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="196"/>
+      <c r="B202" s="193"/>
       <c r="C202" s="53" t="s">
         <v>473</v>
       </c>
@@ -34448,9 +34409,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A203" s="201"/>
-      <c r="B203" s="198"/>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" s="196"/>
+      <c r="B203" s="193"/>
       <c r="C203" s="92" t="s">
         <v>476</v>
       </c>
@@ -34458,9 +34419,9 @@
         <v>477</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A204" s="201"/>
-      <c r="B204" s="198"/>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" s="196"/>
+      <c r="B204" s="193"/>
       <c r="C204" s="53" t="s">
         <v>478</v>
       </c>
@@ -34468,9 +34429,9 @@
         <v>479</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A205" s="201"/>
-      <c r="B205" s="198"/>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="196"/>
+      <c r="B205" s="193"/>
       <c r="C205" s="53" t="s">
         <v>480</v>
       </c>
@@ -34478,9 +34439,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A206" s="201"/>
-      <c r="B206" s="198"/>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="196"/>
+      <c r="B206" s="193"/>
       <c r="C206" s="53" t="s">
         <v>482</v>
       </c>
@@ -34488,9 +34449,9 @@
         <v>483</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A207" s="201"/>
-      <c r="B207" s="198"/>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" s="196"/>
+      <c r="B207" s="193"/>
       <c r="C207" s="53" t="s">
         <v>484</v>
       </c>
@@ -34498,9 +34459,9 @@
         <v>483</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A208" s="201"/>
-      <c r="B208" s="198"/>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="196"/>
+      <c r="B208" s="193"/>
       <c r="C208" s="53" t="s">
         <v>485</v>
       </c>
@@ -34508,9 +34469,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A209" s="201"/>
-      <c r="B209" s="198"/>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" s="196"/>
+      <c r="B209" s="193"/>
       <c r="C209" s="53" t="s">
         <v>486</v>
       </c>
@@ -34518,9 +34479,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A210" s="201"/>
-      <c r="B210" s="198"/>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210" s="196"/>
+      <c r="B210" s="193"/>
       <c r="C210" s="53" t="s">
         <v>487</v>
       </c>
@@ -34528,9 +34489,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A211" s="201"/>
-      <c r="B211" s="198"/>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211" s="196"/>
+      <c r="B211" s="193"/>
       <c r="C211" s="53" t="s">
         <v>488</v>
       </c>
@@ -34538,9 +34499,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A212" s="201"/>
-      <c r="B212" s="198"/>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212" s="196"/>
+      <c r="B212" s="193"/>
       <c r="C212" s="53" t="s">
         <v>489</v>
       </c>
@@ -34548,9 +34509,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A213" s="201"/>
-      <c r="B213" s="198"/>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213" s="196"/>
+      <c r="B213" s="193"/>
       <c r="C213" s="53" t="s">
         <v>490</v>
       </c>
@@ -34558,9 +34519,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A214" s="201"/>
-      <c r="B214" s="198"/>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214" s="196"/>
+      <c r="B214" s="193"/>
       <c r="C214" s="53" t="s">
         <v>491</v>
       </c>
@@ -34568,9 +34529,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A215" s="201"/>
-      <c r="B215" s="198"/>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215" s="196"/>
+      <c r="B215" s="193"/>
       <c r="C215" s="53" t="s">
         <v>492</v>
       </c>
@@ -34578,9 +34539,9 @@
         <v>493</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A216" s="201"/>
-      <c r="B216" s="198"/>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216" s="196"/>
+      <c r="B216" s="193"/>
       <c r="C216" s="53" t="s">
         <v>494</v>
       </c>
@@ -34588,9 +34549,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A217" s="201"/>
-      <c r="B217" s="198"/>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217" s="196"/>
+      <c r="B217" s="193"/>
       <c r="C217" s="53" t="s">
         <v>490</v>
       </c>
@@ -34598,9 +34559,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A218" s="201"/>
-      <c r="B218" s="198"/>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" s="196"/>
+      <c r="B218" s="193"/>
       <c r="C218" s="53" t="s">
         <v>495</v>
       </c>
@@ -34608,9 +34569,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A219" s="201"/>
-      <c r="B219" s="198"/>
+    <row r="219" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A219" s="196"/>
+      <c r="B219" s="193"/>
       <c r="C219" s="56" t="s">
         <v>496</v>
       </c>
@@ -34618,9 +34579,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A220" s="202"/>
-      <c r="B220" s="199"/>
+    <row r="220" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A220" s="197"/>
+      <c r="B220" s="194"/>
       <c r="C220" s="56" t="s">
         <v>465</v>
       </c>
@@ -34628,11 +34589,11 @@
         <v>466</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A221" s="200" t="s">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221" s="195" t="s">
         <v>497</v>
       </c>
-      <c r="B221" s="197" t="s">
+      <c r="B221" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C221" s="53" t="s">
@@ -34642,9 +34603,9 @@
         <v>498</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A222" s="201"/>
-      <c r="B222" s="198"/>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222" s="196"/>
+      <c r="B222" s="193"/>
       <c r="C222" s="92" t="s">
         <v>499</v>
       </c>
@@ -34652,9 +34613,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A223" s="202"/>
-      <c r="B223" s="199"/>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" s="197"/>
+      <c r="B223" s="194"/>
       <c r="C223" s="53" t="s">
         <v>500</v>
       </c>
@@ -34662,7 +34623,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="90" t="s">
         <v>501</v>
       </c>
@@ -34676,7 +34637,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="90" t="s">
         <v>502</v>
       </c>
@@ -34690,7 +34651,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="87" t="s">
         <v>44</v>
       </c>
@@ -34698,11 +34659,11 @@
       <c r="C226" s="87"/>
       <c r="D226" s="88"/>
     </row>
-    <row r="227" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A227" s="174" t="s">
+    <row r="227" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="169" t="s">
         <v>156</v>
       </c>
-      <c r="B227" s="197" t="s">
+      <c r="B227" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C227" s="53"/>
@@ -34710,9 +34671,9 @@
         <v>333</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A228" s="215"/>
-      <c r="B228" s="198"/>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" s="210"/>
+      <c r="B228" s="193"/>
       <c r="C228" s="65" t="s">
         <v>503</v>
       </c>
@@ -34720,9 +34681,9 @@
         <v>504</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A229" s="215"/>
-      <c r="B229" s="198"/>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" s="210"/>
+      <c r="B229" s="193"/>
       <c r="C229" s="65">
         <v>10.1</v>
       </c>
@@ -34730,9 +34691,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A230" s="215"/>
-      <c r="B230" s="198"/>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" s="210"/>
+      <c r="B230" s="193"/>
       <c r="C230" s="65">
         <v>10.199999999999999</v>
       </c>
@@ -34740,9 +34701,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A231" s="215"/>
-      <c r="B231" s="198"/>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" s="210"/>
+      <c r="B231" s="193"/>
       <c r="C231" s="82" t="s">
         <v>506</v>
       </c>
@@ -34750,9 +34711,9 @@
         <v>507</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A232" s="215"/>
-      <c r="B232" s="198"/>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" s="210"/>
+      <c r="B232" s="193"/>
       <c r="C232" s="82" t="s">
         <v>508</v>
       </c>
@@ -34760,9 +34721,9 @@
         <v>509</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A233" s="215"/>
-      <c r="B233" s="198"/>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" s="210"/>
+      <c r="B233" s="193"/>
       <c r="C233" s="82" t="s">
         <v>166</v>
       </c>
@@ -34770,9 +34731,9 @@
         <v>510</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A234" s="215"/>
-      <c r="B234" s="198"/>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" s="210"/>
+      <c r="B234" s="193"/>
       <c r="C234" s="82" t="s">
         <v>511</v>
       </c>
@@ -34780,9 +34741,9 @@
         <v>512</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A235" s="215"/>
-      <c r="B235" s="198"/>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" s="210"/>
+      <c r="B235" s="193"/>
       <c r="C235" s="82" t="s">
         <v>60</v>
       </c>
@@ -34790,9 +34751,9 @@
         <v>513</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A236" s="215"/>
-      <c r="B236" s="198"/>
+    <row r="236" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A236" s="210"/>
+      <c r="B236" s="193"/>
       <c r="C236" s="82" t="s">
         <v>514</v>
       </c>
@@ -34800,9 +34761,9 @@
         <v>515</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A237" s="175"/>
-      <c r="B237" s="199"/>
+    <row r="237" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A237" s="170"/>
+      <c r="B237" s="194"/>
       <c r="C237" s="82" t="s">
         <v>514</v>
       </c>
@@ -34810,11 +34771,11 @@
         <v>516</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A238" s="174" t="s">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238" s="169" t="s">
         <v>517</v>
       </c>
-      <c r="B238" s="197" t="s">
+      <c r="B238" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C238" s="82"/>
@@ -34822,9 +34783,9 @@
         <v>333</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A239" s="215"/>
-      <c r="B239" s="198"/>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" s="210"/>
+      <c r="B239" s="193"/>
       <c r="C239" s="62" t="s">
         <v>518</v>
       </c>
@@ -34832,7 +34793,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="61" t="s">
         <v>520</v>
       </c>
@@ -34846,7 +34807,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="98" t="s">
         <v>72</v>
       </c>
@@ -34854,11 +34815,11 @@
       <c r="C241" s="98"/>
       <c r="D241" s="98"/>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A242" s="174" t="s">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242" s="169" t="s">
         <v>74</v>
       </c>
-      <c r="B242" s="197" t="s">
+      <c r="B242" s="192" t="s">
         <v>522</v>
       </c>
       <c r="C242" s="99" t="s">
@@ -34868,9 +34829,9 @@
         <v>523</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A243" s="215"/>
-      <c r="B243" s="198"/>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243" s="210"/>
+      <c r="B243" s="193"/>
       <c r="C243" s="99" t="s">
         <v>257</v>
       </c>
@@ -34878,19 +34839,19 @@
         <v>524</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="175"/>
-      <c r="B244" s="199"/>
+    <row r="244" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="170"/>
+      <c r="B244" s="194"/>
       <c r="C244" s="53"/>
       <c r="D244" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A245" s="213" t="s">
+    <row r="245" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A245" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="B245" s="197" t="s">
+      <c r="B245" s="192" t="s">
         <v>522</v>
       </c>
       <c r="C245" s="56" t="s">
@@ -34900,19 +34861,19 @@
         <v>144</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A246" s="214"/>
-      <c r="B246" s="199"/>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246" s="209"/>
+      <c r="B246" s="194"/>
       <c r="C246" s="56"/>
       <c r="D246" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A247" s="213" t="s">
+    <row r="247" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A247" s="208" t="s">
         <v>527</v>
       </c>
-      <c r="B247" s="197" t="s">
+      <c r="B247" s="192" t="s">
         <v>522</v>
       </c>
       <c r="C247" s="56"/>
@@ -34920,19 +34881,19 @@
         <v>528</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A248" s="214"/>
-      <c r="B248" s="199"/>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248" s="209"/>
+      <c r="B248" s="194"/>
       <c r="C248" s="53"/>
       <c r="D248" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A249" s="213" t="s">
+    <row r="249" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A249" s="208" t="s">
         <v>76</v>
       </c>
-      <c r="B249" s="197" t="s">
+      <c r="B249" s="192" t="s">
         <v>522</v>
       </c>
       <c r="C249" s="56" t="s">
@@ -34942,15 +34903,15 @@
         <v>529</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A250" s="214"/>
-      <c r="B250" s="199"/>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250" s="209"/>
+      <c r="B250" s="194"/>
       <c r="C250" s="53"/>
       <c r="D250" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="98" t="s">
         <v>530</v>
       </c>
@@ -34958,7 +34919,7 @@
       <c r="C251" s="98"/>
       <c r="D251" s="98"/>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="53"/>
       <c r="B252" s="65" t="s">
         <v>244</v>
@@ -34970,7 +34931,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="98" t="s">
         <v>531</v>
       </c>
@@ -34978,7 +34939,7 @@
       <c r="C253" s="98"/>
       <c r="D253" s="98"/>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="53"/>
       <c r="B254" s="65" t="s">
         <v>244</v>
@@ -34990,7 +34951,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="53"/>
       <c r="B255" s="65"/>
       <c r="C255" s="53" t="s">
@@ -35000,13 +34961,13 @@
         <v>533</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B256" s="115"/>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B257" s="115"/>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="62" t="s">
         <v>13</v>
       </c>
@@ -35018,7 +34979,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="62" t="s">
         <v>369</v>
       </c>
@@ -35030,7 +34991,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="62" t="s">
         <v>36</v>
       </c>
@@ -35042,7 +35003,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="62" t="s">
         <v>535</v>
       </c>
@@ -35054,7 +35015,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="62" t="s">
         <v>536</v>
       </c>
@@ -35066,7 +35027,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="62" t="s">
         <v>537</v>
       </c>
@@ -35078,7 +35039,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="62" t="s">
         <v>538</v>
       </c>
@@ -35092,7 +35053,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="62" t="s">
         <v>369</v>
       </c>
@@ -35106,7 +35067,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="62" t="s">
         <v>36</v>
       </c>
@@ -35120,7 +35081,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="62" t="s">
         <v>542</v>
       </c>
@@ -35134,7 +35095,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="53" t="s">
         <v>36</v>
       </c>
@@ -35148,7 +35109,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="90" t="s">
         <v>535</v>
       </c>
@@ -35162,7 +35123,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="90" t="s">
         <v>703</v>
       </c>
@@ -35176,7 +35137,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="90" t="s">
         <v>705</v>
       </c>
@@ -35191,7 +35152,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="90" t="s">
         <v>707</v>
       </c>
@@ -35206,7 +35167,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="90" t="s">
         <v>287</v>
       </c>
@@ -35221,7 +35182,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="90" t="s">
         <v>714</v>
       </c>
@@ -35236,7 +35197,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="90" t="s">
         <v>715</v>
       </c>
@@ -35251,12 +35212,12 @@
         <v>713</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A276" s="56" t="s">
         <v>721</v>
       </c>
       <c r="B276" s="138" t="str">
-        <f t="shared" ref="B276:B279" si="0">$B$270</f>
+        <f t="shared" ref="B276:B277" si="0">$B$270</f>
         <v>PIT Next Version</v>
       </c>
       <c r="C276" s="90" t="s">
@@ -35266,7 +35227,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="53" t="s">
         <v>722</v>
       </c>
@@ -35279,78 +35240,6 @@
       </c>
       <c r="D277" s="90" t="s">
         <v>719</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A278" s="144" t="s">
-        <v>723</v>
-      </c>
-      <c r="B278" s="142" t="str">
-        <f t="shared" si="0"/>
-        <v>PIT Next Version</v>
-      </c>
-      <c r="C278" t="s">
-        <v>724</v>
-      </c>
-      <c r="D278" s="144" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A279" s="56" t="s">
-        <v>721</v>
-      </c>
-      <c r="B279" s="141" t="str">
-        <f t="shared" si="0"/>
-        <v>PIT Next Version</v>
-      </c>
-      <c r="C279" s="222" t="s">
-        <v>727</v>
-      </c>
-      <c r="D279" s="62" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A280" s="62" t="s">
-        <v>538</v>
-      </c>
-      <c r="B280" s="143" t="s">
-        <v>244</v>
-      </c>
-      <c r="C280" s="53" t="s">
-        <v>729</v>
-      </c>
-      <c r="D280" s="53" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A281" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="B281" s="143" t="s">
-        <v>244</v>
-      </c>
-      <c r="C281" s="222" t="s">
-        <v>727</v>
-      </c>
-      <c r="D281" s="53" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A282" s="90" t="s">
-        <v>535</v>
-      </c>
-      <c r="B282" s="141" t="s">
-        <v>244</v>
-      </c>
-      <c r="C282" s="222" t="s">
-        <v>727</v>
-      </c>
-      <c r="D282" s="62" t="s">
-        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -35430,15 +35319,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DBC65A-63D2-46B3-B8B5-A94A70B9EDFE}">
   <dimension ref="A1:D155"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.7265625" customWidth="1"/>
-    <col min="2" max="2" width="32.453125" customWidth="1"/>
-    <col min="3" max="3" width="85.453125" customWidth="1"/>
-    <col min="4" max="4" width="128.453125" customWidth="1"/>
+    <col min="1" max="1" width="52.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="3" width="85.42578125" customWidth="1"/>
+    <col min="4" max="4" width="128.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -35452,11 +35341,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="197" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="192" t="s">
         <v>369</v>
       </c>
-      <c r="B2" s="197" t="s">
+      <c r="B2" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C2" s="53" t="s">
@@ -35466,9 +35355,9 @@
         <v>546</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="198"/>
-      <c r="B3" s="198"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="193"/>
+      <c r="B3" s="193"/>
       <c r="C3" s="53" t="s">
         <v>547</v>
       </c>
@@ -35476,9 +35365,9 @@
         <v>548</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="198"/>
-      <c r="B4" s="198"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="193"/>
+      <c r="B4" s="193"/>
       <c r="C4" s="53" t="s">
         <v>549</v>
       </c>
@@ -35486,9 +35375,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="198"/>
-      <c r="B5" s="198"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="193"/>
+      <c r="B5" s="193"/>
       <c r="C5" s="53" t="s">
         <v>551</v>
       </c>
@@ -35496,9 +35385,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="198"/>
-      <c r="B6" s="198"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="193"/>
+      <c r="B6" s="193"/>
       <c r="C6" s="53" t="s">
         <v>552</v>
       </c>
@@ -35506,9 +35395,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="193"/>
+      <c r="B7" s="193"/>
       <c r="C7" s="53" t="s">
         <v>553</v>
       </c>
@@ -35516,9 +35405,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="198"/>
-      <c r="B8" s="198"/>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="193"/>
+      <c r="B8" s="193"/>
       <c r="C8" s="53" t="s">
         <v>554</v>
       </c>
@@ -35526,9 +35415,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="198"/>
-      <c r="B9" s="198"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="193"/>
+      <c r="B9" s="193"/>
       <c r="C9" s="53" t="s">
         <v>555</v>
       </c>
@@ -35536,9 +35425,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="198"/>
-      <c r="B10" s="198"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="193"/>
+      <c r="B10" s="193"/>
       <c r="C10" s="53" t="s">
         <v>556</v>
       </c>
@@ -35546,9 +35435,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="198"/>
-      <c r="B11" s="198"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="193"/>
+      <c r="B11" s="193"/>
       <c r="C11" s="53" t="s">
         <v>557</v>
       </c>
@@ -35556,9 +35445,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="198"/>
-      <c r="B12" s="198"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="193"/>
+      <c r="B12" s="193"/>
       <c r="C12" s="53" t="s">
         <v>558</v>
       </c>
@@ -35566,9 +35455,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="198"/>
-      <c r="B13" s="198"/>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="193"/>
+      <c r="B13" s="193"/>
       <c r="C13" s="53" t="s">
         <v>559</v>
       </c>
@@ -35576,9 +35465,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="198"/>
-      <c r="B14" s="198"/>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="193"/>
+      <c r="B14" s="193"/>
       <c r="C14" s="53" t="s">
         <v>560</v>
       </c>
@@ -35586,9 +35475,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="198"/>
-      <c r="B15" s="198"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="193"/>
+      <c r="B15" s="193"/>
       <c r="C15" s="53" t="s">
         <v>561</v>
       </c>
@@ -35596,9 +35485,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="198"/>
-      <c r="B16" s="198"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="193"/>
+      <c r="B16" s="193"/>
       <c r="C16" s="53" t="s">
         <v>562</v>
       </c>
@@ -35606,9 +35495,9 @@
         <v>563</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="198"/>
-      <c r="B17" s="198"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="193"/>
+      <c r="B17" s="193"/>
       <c r="C17" s="53" t="s">
         <v>564</v>
       </c>
@@ -35616,9 +35505,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="198"/>
-      <c r="B18" s="198"/>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="193"/>
+      <c r="B18" s="193"/>
       <c r="C18" s="56" t="s">
         <v>565</v>
       </c>
@@ -35626,9 +35515,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="198"/>
-      <c r="B19" s="198"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="193"/>
+      <c r="B19" s="193"/>
       <c r="C19" s="53" t="s">
         <v>566</v>
       </c>
@@ -35636,9 +35525,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="199"/>
-      <c r="B20" s="199"/>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="194"/>
+      <c r="B20" s="194"/>
       <c r="C20" s="56" t="s">
         <v>567</v>
       </c>
@@ -35646,11 +35535,11 @@
         <v>550</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="164" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="159" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="183" t="s">
+      <c r="B21" s="178" t="s">
         <v>244</v>
       </c>
       <c r="C21" s="53" t="s">
@@ -35660,9 +35549,9 @@
         <v>546</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="164"/>
-      <c r="B22" s="183"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="159"/>
+      <c r="B22" s="178"/>
       <c r="C22" s="53" t="s">
         <v>547</v>
       </c>
@@ -35670,9 +35559,9 @@
         <v>548</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="164"/>
-      <c r="B23" s="183"/>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="159"/>
+      <c r="B23" s="178"/>
       <c r="C23" s="53" t="s">
         <v>549</v>
       </c>
@@ -35680,9 +35569,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="164"/>
-      <c r="B24" s="183"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="159"/>
+      <c r="B24" s="178"/>
       <c r="C24" s="53" t="s">
         <v>551</v>
       </c>
@@ -35690,9 +35579,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="164"/>
-      <c r="B25" s="183"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="159"/>
+      <c r="B25" s="178"/>
       <c r="C25" s="53" t="s">
         <v>552</v>
       </c>
@@ -35700,9 +35589,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="164"/>
-      <c r="B26" s="183"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="159"/>
+      <c r="B26" s="178"/>
       <c r="C26" s="53" t="s">
         <v>553</v>
       </c>
@@ -35710,9 +35599,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="164"/>
-      <c r="B27" s="183"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="159"/>
+      <c r="B27" s="178"/>
       <c r="C27" s="53" t="s">
         <v>554</v>
       </c>
@@ -35720,9 +35609,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="164"/>
-      <c r="B28" s="183"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="159"/>
+      <c r="B28" s="178"/>
       <c r="C28" s="53" t="s">
         <v>555</v>
       </c>
@@ -35730,9 +35619,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="164"/>
-      <c r="B29" s="183"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="159"/>
+      <c r="B29" s="178"/>
       <c r="C29" s="53" t="s">
         <v>556</v>
       </c>
@@ -35740,9 +35629,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="164"/>
-      <c r="B30" s="183"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="159"/>
+      <c r="B30" s="178"/>
       <c r="C30" s="53" t="s">
         <v>557</v>
       </c>
@@ -35750,9 +35639,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="164"/>
-      <c r="B31" s="183"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="159"/>
+      <c r="B31" s="178"/>
       <c r="C31" s="53" t="s">
         <v>558</v>
       </c>
@@ -35760,9 +35649,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="164"/>
-      <c r="B32" s="183"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="159"/>
+      <c r="B32" s="178"/>
       <c r="C32" s="53" t="s">
         <v>559</v>
       </c>
@@ -35770,9 +35659,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="164"/>
-      <c r="B33" s="183"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="159"/>
+      <c r="B33" s="178"/>
       <c r="C33" s="53" t="s">
         <v>560</v>
       </c>
@@ -35780,9 +35669,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="164"/>
-      <c r="B34" s="183"/>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="159"/>
+      <c r="B34" s="178"/>
       <c r="C34" s="53" t="s">
         <v>561</v>
       </c>
@@ -35790,9 +35679,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="164"/>
-      <c r="B35" s="183"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="159"/>
+      <c r="B35" s="178"/>
       <c r="C35" s="53" t="s">
         <v>562</v>
       </c>
@@ -35800,9 +35689,9 @@
         <v>563</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="164"/>
-      <c r="B36" s="183"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="159"/>
+      <c r="B36" s="178"/>
       <c r="C36" s="53" t="s">
         <v>564</v>
       </c>
@@ -35810,9 +35699,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="164"/>
-      <c r="B37" s="183"/>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="159"/>
+      <c r="B37" s="178"/>
       <c r="C37" s="56" t="s">
         <v>565</v>
       </c>
@@ -35820,9 +35709,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="164"/>
-      <c r="B38" s="183"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="159"/>
+      <c r="B38" s="178"/>
       <c r="C38" s="53" t="s">
         <v>566</v>
       </c>
@@ -35830,9 +35719,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="164"/>
-      <c r="B39" s="183"/>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="159"/>
+      <c r="B39" s="178"/>
       <c r="C39" s="56" t="s">
         <v>567</v>
       </c>
@@ -35840,11 +35729,11 @@
         <v>550</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="197" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="192" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="197" t="s">
+      <c r="B40" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C40" s="90" t="s">
@@ -35854,9 +35743,9 @@
         <v>569</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="198"/>
-      <c r="B41" s="198"/>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="193"/>
+      <c r="B41" s="193"/>
       <c r="C41" s="53" t="s">
         <v>570</v>
       </c>
@@ -35864,9 +35753,9 @@
         <v>571</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="198"/>
-      <c r="B42" s="198"/>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="193"/>
+      <c r="B42" s="193"/>
       <c r="C42" s="53" t="s">
         <v>572</v>
       </c>
@@ -35874,7 +35763,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="90" t="s">
         <v>574</v>
       </c>
@@ -35886,11 +35775,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="197" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="192" t="s">
         <v>330</v>
       </c>
-      <c r="B44" s="197" t="s">
+      <c r="B44" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C44" s="90" t="s">
@@ -35900,9 +35789,9 @@
         <v>569</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="198"/>
-      <c r="B45" s="198"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="193"/>
+      <c r="B45" s="193"/>
       <c r="C45" s="90" t="s">
         <v>575</v>
       </c>
@@ -35910,9 +35799,9 @@
         <v>571</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="199"/>
-      <c r="B46" s="199"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="194"/>
+      <c r="B46" s="194"/>
       <c r="C46" s="90" t="s">
         <v>576</v>
       </c>
@@ -35920,7 +35809,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="62" t="s">
         <v>577</v>
       </c>
@@ -35932,7 +35821,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="62" t="s">
         <v>579</v>
       </c>
@@ -35944,7 +35833,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="62" t="s">
         <v>328</v>
       </c>
@@ -35956,7 +35845,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="62" t="s">
         <v>581</v>
       </c>
@@ -35968,7 +35857,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="62" t="s">
         <v>582</v>
       </c>
@@ -35980,7 +35869,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="62" t="s">
         <v>583</v>
       </c>
@@ -35992,7 +35881,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="62" t="s">
         <v>535</v>
       </c>
@@ -36004,7 +35893,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="62" t="s">
         <v>583</v>
       </c>
@@ -36018,7 +35907,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="62" t="s">
         <v>583</v>
       </c>
@@ -36032,7 +35921,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="62" t="s">
         <v>589</v>
       </c>
@@ -36044,7 +35933,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="62" t="s">
         <v>369</v>
       </c>
@@ -36058,7 +35947,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="62" t="s">
         <v>36</v>
       </c>
@@ -36072,7 +35961,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="62" t="s">
         <v>593</v>
       </c>
@@ -36084,7 +35973,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="62" t="s">
         <v>583</v>
       </c>
@@ -36096,7 +35985,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="90" t="s">
         <v>574</v>
       </c>
@@ -36108,7 +35997,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="62" t="s">
         <v>596</v>
       </c>
@@ -36120,7 +36009,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="62" t="s">
         <v>205</v>
       </c>
@@ -36132,7 +36021,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="62" t="s">
         <v>330</v>
       </c>
@@ -36144,7 +36033,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="62" t="s">
         <v>577</v>
       </c>
@@ -36156,11 +36045,11 @@
         <v>598</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="183" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="178" t="s">
         <v>579</v>
       </c>
-      <c r="B66" s="183" t="s">
+      <c r="B66" s="178" t="s">
         <v>244</v>
       </c>
       <c r="C66" s="53" t="s">
@@ -36170,9 +36059,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="183"/>
-      <c r="B67" s="183"/>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="178"/>
+      <c r="B67" s="178"/>
       <c r="C67" s="53" t="s">
         <v>601</v>
       </c>
@@ -36180,9 +36069,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="183"/>
-      <c r="B68" s="183"/>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="178"/>
+      <c r="B68" s="178"/>
       <c r="C68" s="53" t="s">
         <v>602</v>
       </c>
@@ -36190,9 +36079,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="183"/>
-      <c r="B69" s="183"/>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="178"/>
+      <c r="B69" s="178"/>
       <c r="C69" s="53" t="s">
         <v>603</v>
       </c>
@@ -36200,9 +36089,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="183"/>
-      <c r="B70" s="183"/>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="178"/>
+      <c r="B70" s="178"/>
       <c r="C70" s="53" t="s">
         <v>604</v>
       </c>
@@ -36210,7 +36099,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="62" t="s">
         <v>328</v>
       </c>
@@ -36222,7 +36111,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="62" t="s">
         <v>582</v>
       </c>
@@ -36234,11 +36123,11 @@
         <v>606</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="183" t="s">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="178" t="s">
         <v>369</v>
       </c>
-      <c r="B73" s="183" t="s">
+      <c r="B73" s="178" t="s">
         <v>244</v>
       </c>
       <c r="C73" s="53"/>
@@ -36246,9 +36135,9 @@
         <v>597</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="183"/>
-      <c r="B74" s="183"/>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="178"/>
+      <c r="B74" s="178"/>
       <c r="C74" s="53" t="s">
         <v>599</v>
       </c>
@@ -36256,9 +36145,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="183"/>
-      <c r="B75" s="183"/>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="178"/>
+      <c r="B75" s="178"/>
       <c r="C75" s="53" t="s">
         <v>601</v>
       </c>
@@ -36266,9 +36155,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="183"/>
-      <c r="B76" s="183"/>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="178"/>
+      <c r="B76" s="178"/>
       <c r="C76" s="53" t="s">
         <v>602</v>
       </c>
@@ -36276,9 +36165,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="183"/>
-      <c r="B77" s="183"/>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="178"/>
+      <c r="B77" s="178"/>
       <c r="C77" s="53" t="s">
         <v>603</v>
       </c>
@@ -36286,9 +36175,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="183"/>
-      <c r="B78" s="183"/>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="178"/>
+      <c r="B78" s="178"/>
       <c r="C78" s="53" t="s">
         <v>604</v>
       </c>
@@ -36296,9 +36185,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="183"/>
-      <c r="B79" s="183"/>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="178"/>
+      <c r="B79" s="178"/>
       <c r="C79" s="53" t="s">
         <v>607</v>
       </c>
@@ -36306,11 +36195,11 @@
         <v>550</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="183" t="s">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="178" t="s">
         <v>36</v>
       </c>
-      <c r="B80" s="183" t="s">
+      <c r="B80" s="178" t="s">
         <v>244</v>
       </c>
       <c r="C80" s="53"/>
@@ -36318,9 +36207,9 @@
         <v>597</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="183"/>
-      <c r="B81" s="183"/>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="178"/>
+      <c r="B81" s="178"/>
       <c r="C81" s="53" t="s">
         <v>599</v>
       </c>
@@ -36328,9 +36217,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" s="183"/>
-      <c r="B82" s="183"/>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="178"/>
+      <c r="B82" s="178"/>
       <c r="C82" s="53" t="s">
         <v>601</v>
       </c>
@@ -36338,9 +36227,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="183"/>
-      <c r="B83" s="183"/>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="178"/>
+      <c r="B83" s="178"/>
       <c r="C83" s="53" t="s">
         <v>602</v>
       </c>
@@ -36348,9 +36237,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="183"/>
-      <c r="B84" s="183"/>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="178"/>
+      <c r="B84" s="178"/>
       <c r="C84" s="53" t="s">
         <v>603</v>
       </c>
@@ -36358,9 +36247,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="183"/>
-      <c r="B85" s="183"/>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="178"/>
+      <c r="B85" s="178"/>
       <c r="C85" s="53" t="s">
         <v>604</v>
       </c>
@@ -36368,9 +36257,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="183"/>
-      <c r="B86" s="183"/>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="178"/>
+      <c r="B86" s="178"/>
       <c r="C86" s="53" t="s">
         <v>607</v>
       </c>
@@ -36378,7 +36267,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="62" t="s">
         <v>535</v>
       </c>
@@ -36390,7 +36279,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="62" t="s">
         <v>583</v>
       </c>
@@ -36404,7 +36293,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="62" t="s">
         <v>610</v>
       </c>
@@ -36416,7 +36305,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="62" t="s">
         <v>611</v>
       </c>
@@ -36428,7 +36317,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="62" t="s">
         <v>613</v>
       </c>
@@ -36440,7 +36329,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="62" t="s">
         <v>615</v>
       </c>
@@ -36452,7 +36341,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="62" t="s">
         <v>617</v>
       </c>
@@ -36464,7 +36353,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="62" t="s">
         <v>619</v>
       </c>
@@ -36476,11 +36365,11 @@
         <v>620</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" s="197" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="192" t="s">
         <v>610</v>
       </c>
-      <c r="B95" s="197" t="s">
+      <c r="B95" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C95" s="53" t="s">
@@ -36490,9 +36379,9 @@
         <v>622</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" s="198"/>
-      <c r="B96" s="198"/>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="193"/>
+      <c r="B96" s="193"/>
       <c r="C96" s="53" t="s">
         <v>623</v>
       </c>
@@ -36500,9 +36389,9 @@
         <v>624</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" s="198"/>
-      <c r="B97" s="198"/>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="193"/>
+      <c r="B97" s="193"/>
       <c r="C97" s="53" t="s">
         <v>625</v>
       </c>
@@ -36510,9 +36399,9 @@
         <v>626</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" s="199"/>
-      <c r="B98" s="199"/>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="194"/>
+      <c r="B98" s="194"/>
       <c r="C98" s="53" t="s">
         <v>627</v>
       </c>
@@ -36520,7 +36409,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="65" t="s">
         <v>369</v>
       </c>
@@ -36534,7 +36423,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="65" t="s">
         <v>36</v>
       </c>
@@ -36548,7 +36437,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="53" t="s">
         <v>631</v>
       </c>
@@ -36562,11 +36451,11 @@
         <v>633</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" s="197" t="s">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="192" t="s">
         <v>369</v>
       </c>
-      <c r="B102" s="197" t="s">
+      <c r="B102" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C102" s="53" t="s">
@@ -36576,9 +36465,9 @@
         <v>635</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" s="198"/>
-      <c r="B103" s="198"/>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="193"/>
+      <c r="B103" s="193"/>
       <c r="C103" s="116" t="s">
         <v>557</v>
       </c>
@@ -36586,9 +36475,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" s="198"/>
-      <c r="B104" s="198"/>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="193"/>
+      <c r="B104" s="193"/>
       <c r="C104" s="53" t="s">
         <v>565</v>
       </c>
@@ -36596,9 +36485,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" s="199"/>
-      <c r="B105" s="199"/>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="194"/>
+      <c r="B105" s="194"/>
       <c r="C105" s="53" t="s">
         <v>564</v>
       </c>
@@ -36606,11 +36495,11 @@
         <v>637</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" s="197" t="s">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="192" t="s">
         <v>36</v>
       </c>
-      <c r="B106" s="197" t="s">
+      <c r="B106" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C106" s="53" t="s">
@@ -36620,9 +36509,9 @@
         <v>635</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" s="198"/>
-      <c r="B107" s="198"/>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="193"/>
+      <c r="B107" s="193"/>
       <c r="C107" s="116" t="s">
         <v>557</v>
       </c>
@@ -36630,9 +36519,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" s="198"/>
-      <c r="B108" s="198"/>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="193"/>
+      <c r="B108" s="193"/>
       <c r="C108" s="53" t="s">
         <v>565</v>
       </c>
@@ -36640,9 +36529,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" s="199"/>
-      <c r="B109" s="199"/>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="194"/>
+      <c r="B109" s="194"/>
       <c r="C109" s="53" t="s">
         <v>564</v>
       </c>
@@ -36650,7 +36539,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="53" t="s">
         <v>535</v>
       </c>
@@ -36662,7 +36551,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="53" t="s">
         <v>328</v>
       </c>
@@ -36674,7 +36563,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="53" t="s">
         <v>579</v>
       </c>
@@ -36686,7 +36575,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="53" t="s">
         <v>535</v>
       </c>
@@ -36700,7 +36589,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="53" t="s">
         <v>579</v>
       </c>
@@ -36714,7 +36603,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="62" t="s">
         <v>639</v>
       </c>
@@ -36728,7 +36617,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="62" t="s">
         <v>369</v>
       </c>
@@ -36740,7 +36629,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="53" t="s">
         <v>36</v>
       </c>
@@ -36752,7 +36641,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="53" t="s">
         <v>643</v>
       </c>
@@ -36764,7 +36653,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="53" t="s">
         <v>619</v>
       </c>
@@ -36776,7 +36665,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="53" t="s">
         <v>646</v>
       </c>
@@ -36788,7 +36677,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="53" t="s">
         <v>535</v>
       </c>
@@ -36802,7 +36691,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="53" t="s">
         <v>582</v>
       </c>
@@ -36816,7 +36705,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="53" t="s">
         <v>579</v>
       </c>
@@ -36830,7 +36719,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="53" t="s">
         <v>36</v>
       </c>
@@ -36844,11 +36733,11 @@
         <v>512</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" s="183" t="s">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="178" t="s">
         <v>583</v>
       </c>
-      <c r="B125" s="183" t="s">
+      <c r="B125" s="178" t="s">
         <v>244</v>
       </c>
       <c r="C125" s="89" t="s">
@@ -36858,9 +36747,9 @@
         <v>652</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" s="183"/>
-      <c r="B126" s="183"/>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="178"/>
+      <c r="B126" s="178"/>
       <c r="C126" s="53" t="s">
         <v>653</v>
       </c>
@@ -36868,9 +36757,9 @@
         <v>654</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" s="183"/>
-      <c r="B127" s="183"/>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="178"/>
+      <c r="B127" s="178"/>
       <c r="C127" s="53" t="s">
         <v>655</v>
       </c>
@@ -36878,9 +36767,9 @@
         <v>656</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" s="183"/>
-      <c r="B128" s="183"/>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="178"/>
+      <c r="B128" s="178"/>
       <c r="C128" s="53" t="s">
         <v>657</v>
       </c>
@@ -36888,9 +36777,9 @@
         <v>658</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" s="183"/>
-      <c r="B129" s="183"/>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="178"/>
+      <c r="B129" s="178"/>
       <c r="C129" s="53" t="s">
         <v>659</v>
       </c>
@@ -36898,7 +36787,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="53" t="s">
         <v>631</v>
       </c>
@@ -36912,7 +36801,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="121" t="s">
         <v>667</v>
       </c>
@@ -36926,8 +36815,8 @@
         <v>669</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" s="174" t="s">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="169" t="s">
         <v>663</v>
       </c>
       <c r="B132" s="117" t="s">
@@ -36940,8 +36829,8 @@
         <v>664</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" s="175"/>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="170"/>
       <c r="B133" s="118" t="s">
         <v>244</v>
       </c>
@@ -36952,7 +36841,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="53" t="s">
         <v>583</v>
       </c>
@@ -36966,7 +36855,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="121" t="s">
         <v>631</v>
       </c>
@@ -36980,7 +36869,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="136" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="53" t="s">
         <v>674</v>
       </c>
@@ -36994,7 +36883,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="137" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="53" t="s">
         <v>674</v>
       </c>
@@ -37008,11 +36897,11 @@
         <v>677</v>
       </c>
     </row>
-    <row r="138" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="183" t="s">
+    <row r="138" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="178" t="s">
         <v>574</v>
       </c>
-      <c r="B138" s="183" t="s">
+      <c r="B138" s="178" t="s">
         <v>244</v>
       </c>
       <c r="C138" s="53" t="s">
@@ -37022,9 +36911,9 @@
         <v>685</v>
       </c>
     </row>
-    <row r="139" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="183"/>
-      <c r="B139" s="183"/>
+    <row r="139" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="178"/>
+      <c r="B139" s="178"/>
       <c r="C139" s="53" t="s">
         <v>684</v>
       </c>
@@ -37032,7 +36921,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="140" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="62" t="s">
         <v>593</v>
       </c>
@@ -37046,11 +36935,11 @@
         <v>680</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" s="174" t="s">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="169" t="s">
         <v>681</v>
       </c>
-      <c r="B141" s="197" t="s">
+      <c r="B141" s="192" t="s">
         <v>244</v>
       </c>
       <c r="C141" s="53" t="s">
@@ -37060,9 +36949,9 @@
         <v>683</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" s="175"/>
-      <c r="B142" s="199"/>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="170"/>
+      <c r="B142" s="194"/>
       <c r="C142" s="53" t="s">
         <v>686</v>
       </c>
@@ -37070,7 +36959,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="53" t="s">
         <v>579</v>
       </c>
@@ -37084,7 +36973,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="53" t="s">
         <v>328</v>
       </c>
@@ -37098,7 +36987,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="53" t="s">
         <v>535</v>
       </c>
@@ -37112,7 +37001,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="53" t="s">
         <v>36</v>
       </c>
@@ -37126,7 +37015,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A147" s="53" t="s">
         <v>369</v>
       </c>
@@ -37140,7 +37029,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="62" t="s">
         <v>639</v>
       </c>
@@ -37154,7 +37043,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="53" t="s">
         <v>696</v>
       </c>
@@ -37168,7 +37057,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="90" t="s">
         <v>681</v>
       </c>
@@ -37182,7 +37071,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="90" t="s">
         <v>681</v>
       </c>
@@ -37196,7 +37085,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="90" t="s">
         <v>681</v>
       </c>
@@ -37210,7 +37099,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="90" t="s">
         <v>681</v>
       </c>
@@ -37224,8 +37113,8 @@
         <v>717</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A154" s="140" t="s">
+    <row r="154" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A154" s="217" t="s">
         <v>718</v>
       </c>
       <c r="B154" s="138" t="s">
@@ -37238,7 +37127,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="56" t="s">
         <v>720</v>
       </c>

--- a/PIT4/Schema Publication Changelog.xlsx
+++ b/PIT4/Schema Publication Changelog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ctrowell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ctrowell\Desktop\GitHub Docs\PIT4 Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D0422A-8779-4DA4-801D-853D61E5D42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E820892C-0EBA-4338-8BD8-4246D7E18553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="0" windowWidth="16260" windowHeight="10210" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="v0.10" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="731">
   <si>
     <t>Document</t>
   </si>
@@ -4066,6 +4066,30 @@
   </si>
   <si>
     <t>PAYE Modernisation - RPN Data Items</t>
+  </si>
+  <si>
+    <t>Payroll Employer Submission - Employee Level Validation</t>
+  </si>
+  <si>
+    <t>PRSI Class and Subclass</t>
+  </si>
+  <si>
+    <t>Warning added on PRSI Class and Subclass</t>
+  </si>
+  <si>
+    <t>Added SPS fields</t>
+  </si>
+  <si>
+    <t>Single Pension Scheme</t>
+  </si>
+  <si>
+    <t>Single Pension scheme fields added</t>
+  </si>
+  <si>
+    <t>payrollSubmission</t>
+  </si>
+  <si>
+    <t>Added SPS fields to example 1.3 REST and SOAP</t>
   </si>
 </sst>
 </file>
@@ -4695,7 +4719,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5068,6 +5092,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -5299,8 +5338,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5640,15 +5679,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="48.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5662,15 +5701,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="140" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="142"/>
-    </row>
-    <row r="3" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="146"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="147"/>
+    </row>
+    <row r="3" spans="1:4" ht="26" x14ac:dyDescent="0.35">
       <c r="A3" s="29" t="s">
         <v>5</v>
       </c>
@@ -5684,15 +5723,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="140" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="142"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="147"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="27" t="s">
         <v>9</v>
       </c>
@@ -5706,7 +5745,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
         <v>12</v>
       </c>
@@ -5720,11 +5759,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="143" t="s">
+    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A7" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="146">
+      <c r="B7" s="151">
         <v>0.1</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -5734,9 +5773,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="144"/>
-      <c r="B8" s="147"/>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="149"/>
+      <c r="B8" s="152"/>
       <c r="C8" s="10" t="s">
         <v>16</v>
       </c>
@@ -5744,9 +5783,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
-      <c r="B9" s="147"/>
+    <row r="9" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A9" s="149"/>
+      <c r="B9" s="152"/>
       <c r="C9" s="10" t="s">
         <v>18</v>
       </c>
@@ -5754,9 +5793,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="144"/>
-      <c r="B10" s="147"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="149"/>
+      <c r="B10" s="152"/>
       <c r="C10" s="10" t="s">
         <v>20</v>
       </c>
@@ -5764,9 +5803,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="144"/>
-      <c r="B11" s="147"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="149"/>
+      <c r="B11" s="152"/>
       <c r="C11" s="10" t="s">
         <v>22</v>
       </c>
@@ -5774,9 +5813,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="145"/>
-      <c r="B12" s="148"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="150"/>
+      <c r="B12" s="153"/>
       <c r="C12" s="10" t="s">
         <v>24</v>
       </c>
@@ -5784,11 +5823,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="151" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="146">
+      <c r="B13" s="151">
         <v>0.1</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -5798,9 +5837,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="152"/>
-      <c r="B14" s="148"/>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="157"/>
+      <c r="B14" s="153"/>
       <c r="C14" s="10" t="s">
         <v>29</v>
       </c>
@@ -5808,7 +5847,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
         <v>31</v>
       </c>
@@ -5822,7 +5861,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="33" t="s">
         <v>33</v>
       </c>
@@ -5836,15 +5875,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="140" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="145" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="141"/>
-      <c r="C17" s="141"/>
-      <c r="D17" s="142"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="146"/>
+      <c r="C17" s="146"/>
+      <c r="D17" s="147"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>35</v>
       </c>
@@ -5858,7 +5897,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>36</v>
       </c>
@@ -5872,19 +5911,19 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="140" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="141"/>
-      <c r="C20" s="141"/>
-      <c r="D20" s="142"/>
-    </row>
-    <row r="21" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="153" t="s">
+      <c r="B20" s="146"/>
+      <c r="C20" s="146"/>
+      <c r="D20" s="147"/>
+    </row>
+    <row r="21" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A21" s="158" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="150">
+      <c r="B21" s="155">
         <v>0.1</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -5894,9 +5933,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="152"/>
-      <c r="B22" s="148"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="157"/>
+      <c r="B22" s="153"/>
       <c r="C22" s="26" t="s">
         <v>41</v>
       </c>
@@ -5904,7 +5943,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>43</v>
       </c>
@@ -5918,19 +5957,19 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="140" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="145" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="141"/>
-      <c r="C24" s="141"/>
-      <c r="D24" s="142"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="149" t="s">
+      <c r="B24" s="146"/>
+      <c r="C24" s="146"/>
+      <c r="D24" s="147"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="154" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="150">
+      <c r="B25" s="155">
         <v>0.1</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -5940,9 +5979,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="144"/>
-      <c r="B26" s="147"/>
+    <row r="26" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A26" s="149"/>
+      <c r="B26" s="152"/>
       <c r="C26" s="10" t="s">
         <v>48</v>
       </c>
@@ -5950,9 +5989,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="144"/>
-      <c r="B27" s="147"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="149"/>
+      <c r="B27" s="152"/>
       <c r="C27" s="10" t="s">
         <v>50</v>
       </c>
@@ -5960,9 +5999,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="144"/>
-      <c r="B28" s="147"/>
+    <row r="28" spans="1:4" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="149"/>
+      <c r="B28" s="152"/>
       <c r="C28" s="20" t="s">
         <v>52</v>
       </c>
@@ -5970,9 +6009,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="144"/>
-      <c r="B29" s="147"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="149"/>
+      <c r="B29" s="152"/>
       <c r="C29" s="10" t="s">
         <v>54</v>
       </c>
@@ -5980,9 +6019,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="144"/>
-      <c r="B30" s="147"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="149"/>
+      <c r="B30" s="152"/>
       <c r="C30" s="10" t="s">
         <v>56</v>
       </c>
@@ -5990,9 +6029,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="144"/>
-      <c r="B31" s="147"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="149"/>
+      <c r="B31" s="152"/>
       <c r="C31" s="10" t="s">
         <v>58</v>
       </c>
@@ -6000,9 +6039,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="145"/>
-      <c r="B32" s="148"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="150"/>
+      <c r="B32" s="153"/>
       <c r="C32" s="10" t="s">
         <v>60</v>
       </c>
@@ -6010,7 +6049,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>62</v>
       </c>
@@ -6024,7 +6063,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
         <v>64</v>
       </c>
@@ -6038,7 +6077,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>65</v>
       </c>
@@ -6052,7 +6091,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>66</v>
       </c>
@@ -6066,7 +6105,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>67</v>
       </c>
@@ -6080,7 +6119,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>68</v>
       </c>
@@ -6094,7 +6133,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="22" t="s">
         <v>69</v>
       </c>
@@ -6108,7 +6147,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="24" t="s">
         <v>71</v>
       </c>
@@ -6122,15 +6161,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="140" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="145" t="s">
         <v>72</v>
       </c>
-      <c r="B41" s="141"/>
-      <c r="C41" s="141"/>
-      <c r="D41" s="142"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="146"/>
+      <c r="C41" s="146"/>
+      <c r="D41" s="147"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>73</v>
       </c>
@@ -6144,7 +6183,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
         <v>74</v>
       </c>
@@ -6158,7 +6197,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>75</v>
       </c>
@@ -6172,7 +6211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="12" t="s">
         <v>76</v>
       </c>
@@ -6228,15 +6267,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:XFC79"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="51.28515625" style="38" customWidth="1"/>
+    <col min="1" max="1" width="31.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" customWidth="1"/>
+    <col min="4" max="4" width="51.26953125" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -6250,7 +6289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
         <v>77</v>
       </c>
@@ -6258,7 +6297,7 @@
       <c r="C2" s="35"/>
       <c r="D2" s="40"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="44" t="s">
         <v>78</v>
       </c>
@@ -6270,7 +6309,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="44" t="s">
         <v>79</v>
       </c>
@@ -6282,7 +6321,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="44" t="s">
         <v>80</v>
       </c>
@@ -6294,7 +6333,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>8</v>
       </c>
@@ -6302,11 +6341,11 @@
       <c r="C6" s="35"/>
       <c r="D6" s="40"/>
     </row>
-    <row r="7" spans="1:4" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154" t="s">
+    <row r="7" spans="1:4" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="159" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="39" t="s">
@@ -6316,9 +6355,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="154"/>
-      <c r="B8" s="155"/>
+    <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A8" s="159"/>
+      <c r="B8" s="160"/>
       <c r="C8" s="34" t="s">
         <v>84</v>
       </c>
@@ -6326,9 +6365,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="154"/>
-      <c r="B9" s="155"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="159"/>
+      <c r="B9" s="160"/>
       <c r="C9" s="34" t="s">
         <v>86</v>
       </c>
@@ -6336,9 +6375,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="154"/>
-      <c r="B10" s="155"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="159"/>
+      <c r="B10" s="160"/>
       <c r="C10" s="34" t="s">
         <v>18</v>
       </c>
@@ -6346,9 +6385,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="154"/>
-      <c r="B11" s="155"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="159"/>
+      <c r="B11" s="160"/>
       <c r="C11" s="34" t="s">
         <v>89</v>
       </c>
@@ -6356,9 +6395,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="154"/>
-      <c r="B12" s="155"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="159"/>
+      <c r="B12" s="160"/>
       <c r="C12" s="34" t="s">
         <v>91</v>
       </c>
@@ -6366,11 +6405,11 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="157" t="s">
+    <row r="13" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="162" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="155" t="s">
+      <c r="B13" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C13" s="34" t="s">
@@ -6380,9 +6419,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="157"/>
-      <c r="B14" s="155"/>
+    <row r="14" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="162"/>
+      <c r="B14" s="160"/>
       <c r="C14" s="34" t="s">
         <v>96</v>
       </c>
@@ -6390,9 +6429,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="157"/>
-      <c r="B15" s="155"/>
+    <row r="15" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="162"/>
+      <c r="B15" s="160"/>
       <c r="C15" s="39" t="s">
         <v>98</v>
       </c>
@@ -6400,11 +6439,11 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="158" t="s">
+    <row r="16" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="159" t="s">
+      <c r="B16" s="164" t="s">
         <v>81</v>
       </c>
       <c r="C16" s="54" t="s">
@@ -6414,9 +6453,9 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="158"/>
-      <c r="B17" s="159"/>
+    <row r="17" spans="1:4" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="163"/>
+      <c r="B17" s="164"/>
       <c r="C17" s="53" t="s">
         <v>102</v>
       </c>
@@ -6424,9 +6463,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="158"/>
-      <c r="B18" s="159"/>
+    <row r="18" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="163"/>
+      <c r="B18" s="164"/>
       <c r="C18" s="53" t="s">
         <v>89</v>
       </c>
@@ -6434,9 +6473,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="158"/>
-      <c r="B19" s="159"/>
+    <row r="19" spans="1:4" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="163"/>
+      <c r="B19" s="164"/>
       <c r="C19" s="53" t="s">
         <v>105</v>
       </c>
@@ -6444,9 +6483,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="158"/>
-      <c r="B20" s="159"/>
+    <row r="20" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="163"/>
+      <c r="B20" s="164"/>
       <c r="C20" s="53" t="s">
         <v>107</v>
       </c>
@@ -6454,9 +6493,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="158"/>
-      <c r="B21" s="159"/>
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="163"/>
+      <c r="B21" s="164"/>
       <c r="C21" s="53" t="s">
         <v>109</v>
       </c>
@@ -6464,9 +6503,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="158"/>
-      <c r="B22" s="159"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="163"/>
+      <c r="B22" s="164"/>
       <c r="C22" s="53" t="s">
         <v>111</v>
       </c>
@@ -6474,9 +6513,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="158"/>
-      <c r="B23" s="159"/>
+    <row r="23" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="163"/>
+      <c r="B23" s="164"/>
       <c r="C23" s="61" t="s">
         <v>113</v>
       </c>
@@ -6484,27 +6523,27 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="158"/>
-      <c r="B24" s="159"/>
-      <c r="C24" s="158" t="s">
+    <row r="24" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="163"/>
+      <c r="B24" s="164"/>
+      <c r="C24" s="163" t="s">
         <v>115</v>
       </c>
-      <c r="D24" s="165" t="s">
+      <c r="D24" s="170" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="158"/>
-      <c r="B25" s="159"/>
-      <c r="C25" s="158"/>
-      <c r="D25" s="165"/>
-    </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="154" t="s">
+    <row r="25" spans="1:4" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="163"/>
+      <c r="B25" s="164"/>
+      <c r="C25" s="163"/>
+      <c r="D25" s="170"/>
+    </row>
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="159" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="155" t="s">
+      <c r="B26" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C26" s="34" t="s">
@@ -6514,15 +6553,15 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="154"/>
-      <c r="B27" s="155"/>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="159"/>
+      <c r="B27" s="160"/>
       <c r="C27" s="34"/>
       <c r="D27" s="37" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="44" t="s">
         <v>121</v>
       </c>
@@ -6534,7 +6573,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="26" x14ac:dyDescent="0.35">
       <c r="A29" s="35" t="s">
         <v>34</v>
       </c>
@@ -6542,29 +6581,29 @@
       <c r="C29" s="35"/>
       <c r="D29" s="35"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="156" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="161" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="155" t="s">
+      <c r="B30" s="160" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="158" t="s">
+      <c r="C30" s="163" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="168" t="s">
+      <c r="D30" s="173" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="156"/>
-      <c r="B31" s="155"/>
-      <c r="C31" s="158"/>
-      <c r="D31" s="168"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="156"/>
-      <c r="B32" s="155"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="161"/>
+      <c r="B31" s="160"/>
+      <c r="C31" s="163"/>
+      <c r="D31" s="173"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="161"/>
+      <c r="B32" s="160"/>
       <c r="C32" s="53" t="s">
         <v>125</v>
       </c>
@@ -6572,9 +6611,9 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="156"/>
-      <c r="B33" s="155"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="161"/>
+      <c r="B33" s="160"/>
       <c r="C33" s="53" t="s">
         <v>127</v>
       </c>
@@ -6582,9 +6621,9 @@
         <v>128</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="156"/>
-      <c r="B34" s="155"/>
+    <row r="34" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="161"/>
+      <c r="B34" s="160"/>
       <c r="C34" s="62" t="s">
         <v>129</v>
       </c>
@@ -6592,9 +6631,9 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="156"/>
-      <c r="B35" s="155"/>
+    <row r="35" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="161"/>
+      <c r="B35" s="160"/>
       <c r="C35" s="53" t="s">
         <v>111</v>
       </c>
@@ -6602,9 +6641,9 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="156"/>
-      <c r="B36" s="155"/>
+    <row r="36" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="161"/>
+      <c r="B36" s="160"/>
       <c r="C36" s="62" t="s">
         <v>113</v>
       </c>
@@ -6612,27 +6651,27 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="156"/>
-      <c r="B37" s="155"/>
-      <c r="C37" s="169" t="s">
+    <row r="37" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="161"/>
+      <c r="B37" s="160"/>
+      <c r="C37" s="174" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="171" t="s">
+      <c r="D37" s="176" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="156"/>
-      <c r="B38" s="155"/>
-      <c r="C38" s="170"/>
-      <c r="D38" s="171"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="154" t="s">
+    <row r="38" spans="1:4" ht="6.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="161"/>
+      <c r="B38" s="160"/>
+      <c r="C38" s="175"/>
+      <c r="D38" s="176"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="159" t="s">
         <v>134</v>
       </c>
-      <c r="B39" s="155" t="s">
+      <c r="B39" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C39" s="34" t="s">
@@ -6642,15 +6681,15 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="154"/>
-      <c r="B40" s="155"/>
+    <row r="40" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="159"/>
+      <c r="B40" s="160"/>
       <c r="C40" s="34"/>
       <c r="D40" s="45" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="44" t="s">
         <v>36</v>
       </c>
@@ -6662,7 +6701,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="35" t="s">
         <v>37</v>
       </c>
@@ -6670,11 +6709,11 @@
       <c r="C42" s="35"/>
       <c r="D42" s="40"/>
     </row>
-    <row r="43" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="156" t="s">
+    <row r="43" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="155" t="s">
+      <c r="B43" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C43" s="34"/>
@@ -6682,9 +6721,9 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="156"/>
-      <c r="B44" s="155"/>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="161"/>
+      <c r="B44" s="160"/>
       <c r="C44" s="34" t="s">
         <v>118</v>
       </c>
@@ -6692,11 +6731,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="162" t="s">
+    <row r="45" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="167" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="155" t="s">
+      <c r="B45" s="160" t="s">
         <v>81</v>
       </c>
       <c r="C45" s="34"/>
@@ -6704,9 +6743,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="163"/>
-      <c r="B46" s="155"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="168"/>
+      <c r="B46" s="160"/>
       <c r="C46" s="34" t="s">
         <v>141</v>
       </c>
@@ -6714,9 +6753,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="163"/>
-      <c r="B47" s="155"/>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="168"/>
+      <c r="B47" s="160"/>
       <c r="C47" s="34" t="s">
         <v>143</v>
       </c>
@@ -6724,9 +6763,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="164"/>
-      <c r="B48" s="155"/>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="169"/>
+      <c r="B48" s="160"/>
       <c r="C48" s="34" t="s">
         <v>118</v>
       </c>
@@ -6734,11 +6773,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A49" s="159" t="s">
+    <row r="49" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A49" s="164" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="159" t="s">
+      <c r="B49" s="164" t="s">
         <v>81</v>
       </c>
       <c r="C49" s="53"/>
@@ -10841,9 +10880,9 @@
       <c r="XEY49" s="38"/>
       <c r="XFC49" s="38"/>
     </row>
-    <row r="50" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="159"/>
-      <c r="B50" s="159"/>
+    <row r="50" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="164"/>
+      <c r="B50" s="164"/>
       <c r="C50" s="54" t="s">
         <v>146</v>
       </c>
@@ -14946,9 +14985,9 @@
       <c r="XEY50" s="38"/>
       <c r="XFC50" s="38"/>
     </row>
-    <row r="51" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A51" s="159"/>
-      <c r="B51" s="159"/>
+    <row r="51" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A51" s="164"/>
+      <c r="B51" s="164"/>
       <c r="C51" s="34" t="s">
         <v>148</v>
       </c>
@@ -19051,9 +19090,9 @@
       <c r="XEY51" s="38"/>
       <c r="XFC51" s="38"/>
     </row>
-    <row r="52" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A52" s="159"/>
-      <c r="B52" s="159"/>
+    <row r="52" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A52" s="164"/>
+      <c r="B52" s="164"/>
       <c r="C52" s="53" t="s">
         <v>150</v>
       </c>
@@ -23156,13 +23195,13 @@
       <c r="XEY52" s="38"/>
       <c r="XFC52" s="38"/>
     </row>
-    <row r="53" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A53" s="159"/>
-      <c r="B53" s="159"/>
-      <c r="C53" s="167" t="s">
+    <row r="53" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A53" s="164"/>
+      <c r="B53" s="164"/>
+      <c r="C53" s="172" t="s">
         <v>152</v>
       </c>
-      <c r="D53" s="168" t="s">
+      <c r="D53" s="173" t="s">
         <v>153</v>
       </c>
       <c r="G53" s="38"/>
@@ -27261,11 +27300,11 @@
       <c r="XEY53" s="38"/>
       <c r="XFC53" s="38"/>
     </row>
-    <row r="54" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="159"/>
-      <c r="B54" s="159"/>
-      <c r="C54" s="167"/>
-      <c r="D54" s="168"/>
+    <row r="54" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="13.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="164"/>
+      <c r="B54" s="164"/>
+      <c r="C54" s="172"/>
+      <c r="D54" s="173"/>
       <c r="G54" s="38"/>
       <c r="K54" s="38"/>
       <c r="O54" s="38"/>
@@ -31362,7 +31401,7 @@
       <c r="XEY54" s="38"/>
       <c r="XFC54" s="38"/>
     </row>
-    <row r="55" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
       <c r="A55" s="35" t="s">
         <v>44</v>
       </c>
@@ -31370,7 +31409,7 @@
       <c r="C55" s="35"/>
       <c r="D55" s="40"/>
     </row>
-    <row r="56" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="26" x14ac:dyDescent="0.35">
       <c r="A56" s="44" t="s">
         <v>154</v>
       </c>
@@ -31382,11 +31421,11 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A57" s="160" t="s">
+    <row r="57" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A57" s="165" t="s">
         <v>156</v>
       </c>
-      <c r="B57" s="159" t="s">
+      <c r="B57" s="164" t="s">
         <v>81</v>
       </c>
       <c r="C57" s="53" t="s">
@@ -31396,9 +31435,9 @@
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="160"/>
-      <c r="B58" s="159"/>
+    <row r="58" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="165"/>
+      <c r="B58" s="164"/>
       <c r="C58" s="56" t="s">
         <v>159</v>
       </c>
@@ -31406,9 +31445,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="59" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A59" s="160"/>
-      <c r="B59" s="159"/>
+    <row r="59" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A59" s="165"/>
+      <c r="B59" s="164"/>
       <c r="C59" s="53" t="s">
         <v>161</v>
       </c>
@@ -31416,9 +31455,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="60" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="160"/>
-      <c r="B60" s="159"/>
+    <row r="60" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" ht="29" x14ac:dyDescent="0.35">
+      <c r="A60" s="165"/>
+      <c r="B60" s="164"/>
       <c r="C60" s="53" t="s">
         <v>163</v>
       </c>
@@ -31426,9 +31465,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A61" s="160"/>
-      <c r="B61" s="159"/>
+    <row r="61" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A61" s="165"/>
+      <c r="B61" s="164"/>
       <c r="C61" s="34" t="s">
         <v>118</v>
       </c>
@@ -31436,9 +31475,9 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A62" s="160"/>
-      <c r="B62" s="159"/>
+    <row r="62" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A62" s="165"/>
+      <c r="B62" s="164"/>
       <c r="C62" s="53" t="s">
         <v>166</v>
       </c>
@@ -31446,9 +31485,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A63" s="160"/>
-      <c r="B63" s="159"/>
+    <row r="63" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A63" s="165"/>
+      <c r="B63" s="164"/>
       <c r="C63" s="53" t="s">
         <v>166</v>
       </c>
@@ -31456,17 +31495,17 @@
         <v>168</v>
       </c>
     </row>
-    <row r="64" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.25">
-      <c r="A64" s="160"/>
-      <c r="B64" s="159"/>
+    <row r="64" spans="1:1023 1027:2047 2051:3071 3075:4095 4099:5119 5123:6143 6147:7167 7171:8191 8195:9215 9219:10239 10243:11263 11267:12287 12291:13311 13315:14335 14339:15359 15363:16383" x14ac:dyDescent="0.35">
+      <c r="A64" s="165"/>
+      <c r="B64" s="164"/>
       <c r="C64" s="53"/>
       <c r="D64" s="43" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="160"/>
-      <c r="B65" s="159"/>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="165"/>
+      <c r="B65" s="164"/>
       <c r="C65" s="53" t="s">
         <v>169</v>
       </c>
@@ -31474,17 +31513,17 @@
         <v>170</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="160"/>
-      <c r="B66" s="159"/>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="165"/>
+      <c r="B66" s="164"/>
       <c r="C66" s="53"/>
       <c r="D66" s="42" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="160"/>
-      <c r="B67" s="159"/>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="165"/>
+      <c r="B67" s="164"/>
       <c r="C67" s="53" t="s">
         <v>172</v>
       </c>
@@ -31492,9 +31531,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="160"/>
-      <c r="B68" s="159"/>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="165"/>
+      <c r="B68" s="164"/>
       <c r="C68" s="53" t="s">
         <v>174</v>
       </c>
@@ -31502,9 +31541,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="160"/>
-      <c r="B69" s="159"/>
+    <row r="69" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A69" s="165"/>
+      <c r="B69" s="164"/>
       <c r="C69" s="56" t="s">
         <v>176</v>
       </c>
@@ -31512,9 +31551,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="160"/>
-      <c r="B70" s="159"/>
+    <row r="70" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A70" s="165"/>
+      <c r="B70" s="164"/>
       <c r="C70" s="56" t="s">
         <v>178</v>
       </c>
@@ -31522,9 +31561,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="160"/>
-      <c r="B71" s="159"/>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="165"/>
+      <c r="B71" s="164"/>
       <c r="C71" s="53" t="s">
         <v>179</v>
       </c>
@@ -31532,9 +31571,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="160"/>
-      <c r="B72" s="159"/>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="165"/>
+      <c r="B72" s="164"/>
       <c r="C72" s="53" t="s">
         <v>181</v>
       </c>
@@ -31542,17 +31581,17 @@
         <v>173</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="160"/>
-      <c r="B73" s="159"/>
+    <row r="73" spans="1:4" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="165"/>
+      <c r="B73" s="164"/>
       <c r="C73" s="53"/>
       <c r="D73" s="45" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="160"/>
-      <c r="B74" s="159"/>
+    <row r="74" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="165"/>
+      <c r="B74" s="164"/>
       <c r="C74" s="53" t="s">
         <v>182</v>
       </c>
@@ -31560,21 +31599,21 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="160"/>
-      <c r="B75" s="159"/>
-      <c r="C75" s="166"/>
-      <c r="D75" s="161" t="s">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="165"/>
+      <c r="B75" s="164"/>
+      <c r="C75" s="171"/>
+      <c r="D75" s="166" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="160"/>
-      <c r="B76" s="159"/>
-      <c r="C76" s="166"/>
-      <c r="D76" s="161"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="165"/>
+      <c r="B76" s="164"/>
+      <c r="C76" s="171"/>
+      <c r="D76" s="166"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="35" t="s">
         <v>72</v>
       </c>
@@ -31582,13 +31621,13 @@
       <c r="C77" s="35"/>
       <c r="D77" s="40"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="44"/>
       <c r="B78" s="36"/>
       <c r="C78" s="34"/>
       <c r="D78" s="46"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="44"/>
       <c r="B79" s="36"/>
       <c r="C79" s="34"/>
@@ -31652,15 +31691,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" customWidth="1"/>
-    <col min="2" max="2" width="45.7109375" customWidth="1"/>
-    <col min="3" max="3" width="49.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.85546875" customWidth="1"/>
+    <col min="1" max="1" width="30.26953125" customWidth="1"/>
+    <col min="2" max="2" width="45.7265625" customWidth="1"/>
+    <col min="3" max="3" width="49.26953125" customWidth="1"/>
+    <col min="4" max="4" width="80.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="44.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="44.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -31674,7 +31713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
         <v>77</v>
       </c>
@@ -31682,7 +31721,7 @@
       <c r="C2" s="35"/>
       <c r="D2" s="40"/>
     </row>
-    <row r="3" spans="1:4" ht="45.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="45.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="35" t="s">
         <v>8</v>
       </c>
@@ -31690,11 +31729,11 @@
       <c r="C3" s="35"/>
       <c r="D3" s="40"/>
     </row>
-    <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="154" t="s">
+    <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="159" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="155" t="s">
+      <c r="B4" s="160" t="s">
         <v>185</v>
       </c>
       <c r="C4" s="67" t="s">
@@ -31704,139 +31743,139 @@
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="154"/>
-      <c r="B5" s="155"/>
-      <c r="C5" s="181" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="159"/>
+      <c r="B5" s="160"/>
+      <c r="C5" s="186" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="180" t="s">
+      <c r="D5" s="185" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="154"/>
-      <c r="B6" s="155"/>
-      <c r="C6" s="181"/>
-      <c r="D6" s="180"/>
-    </row>
-    <row r="7" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154"/>
-      <c r="B7" s="155"/>
+    <row r="6" spans="1:4" ht="7.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="159"/>
+      <c r="B6" s="160"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="185"/>
+    </row>
+    <row r="7" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="159"/>
+      <c r="B7" s="160"/>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
     </row>
-    <row r="8" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="154"/>
-      <c r="B8" s="155"/>
+    <row r="8" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="159"/>
+      <c r="B8" s="160"/>
       <c r="C8" s="53"/>
       <c r="D8" s="53"/>
     </row>
-    <row r="9" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="154"/>
-      <c r="B9" s="155"/>
+    <row r="9" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="159"/>
+      <c r="B9" s="160"/>
       <c r="C9" s="66"/>
       <c r="D9" s="45"/>
     </row>
-    <row r="10" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="157" t="s">
+    <row r="10" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="162" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="155" t="s">
+      <c r="B10" s="160" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="179"/>
-      <c r="D10" s="180" t="s">
+      <c r="C10" s="184"/>
+      <c r="D10" s="185" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="157"/>
-      <c r="B11" s="155"/>
-      <c r="C11" s="179"/>
-      <c r="D11" s="180"/>
-    </row>
-    <row r="12" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="157"/>
-      <c r="B12" s="155"/>
-      <c r="C12" s="179"/>
-      <c r="D12" s="180"/>
-    </row>
-    <row r="13" spans="1:4" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="158" t="s">
+    <row r="11" spans="1:4" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="162"/>
+      <c r="B11" s="160"/>
+      <c r="C11" s="184"/>
+      <c r="D11" s="185"/>
+    </row>
+    <row r="12" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="162"/>
+      <c r="B12" s="160"/>
+      <c r="C12" s="184"/>
+      <c r="D12" s="185"/>
+    </row>
+    <row r="13" spans="1:4" ht="31.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="159" t="s">
+      <c r="B13" s="164" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="182"/>
-      <c r="D13" s="180" t="s">
+      <c r="C13" s="187"/>
+      <c r="D13" s="185" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="158"/>
-      <c r="B14" s="159"/>
-      <c r="C14" s="182"/>
-      <c r="D14" s="180"/>
-    </row>
-    <row r="15" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="158"/>
-      <c r="B15" s="159"/>
-      <c r="C15" s="182"/>
+    <row r="14" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="163"/>
+      <c r="B14" s="164"/>
+      <c r="C14" s="187"/>
+      <c r="D14" s="185"/>
+    </row>
+    <row r="15" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="163"/>
+      <c r="B15" s="164"/>
+      <c r="C15" s="187"/>
       <c r="D15" s="45"/>
     </row>
-    <row r="16" spans="1:4" ht="27.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="158"/>
-      <c r="B16" s="159"/>
-      <c r="C16" s="182"/>
+    <row r="16" spans="1:4" ht="27.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="163"/>
+      <c r="B16" s="164"/>
+      <c r="C16" s="187"/>
       <c r="D16" s="45"/>
     </row>
-    <row r="17" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="158"/>
-      <c r="B17" s="159"/>
-      <c r="C17" s="182"/>
+    <row r="17" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="163"/>
+      <c r="B17" s="164"/>
+      <c r="C17" s="187"/>
       <c r="D17" s="45"/>
     </row>
-    <row r="18" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="158"/>
-      <c r="B18" s="159"/>
-      <c r="C18" s="182"/>
+    <row r="18" spans="1:4" ht="41.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="163"/>
+      <c r="B18" s="164"/>
+      <c r="C18" s="187"/>
       <c r="D18" s="45"/>
     </row>
-    <row r="19" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="158"/>
-      <c r="B19" s="159"/>
-      <c r="C19" s="182"/>
+    <row r="19" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="163"/>
+      <c r="B19" s="164"/>
+      <c r="C19" s="187"/>
       <c r="D19" s="45"/>
     </row>
-    <row r="20" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="158"/>
-      <c r="B20" s="159"/>
-      <c r="C20" s="182"/>
+    <row r="20" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="163"/>
+      <c r="B20" s="164"/>
+      <c r="C20" s="187"/>
       <c r="D20" s="45"/>
     </row>
-    <row r="21" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="158"/>
-      <c r="B21" s="159"/>
-      <c r="C21" s="182"/>
+    <row r="21" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="163"/>
+      <c r="B21" s="164"/>
+      <c r="C21" s="187"/>
       <c r="D21" s="45"/>
     </row>
-    <row r="22" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="158"/>
-      <c r="B22" s="159"/>
-      <c r="C22" s="182"/>
+    <row r="22" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="163"/>
+      <c r="B22" s="164"/>
+      <c r="C22" s="187"/>
       <c r="D22" s="45"/>
     </row>
-    <row r="23" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="158"/>
-      <c r="B23" s="159"/>
-      <c r="C23" s="182"/>
+    <row r="23" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="163"/>
+      <c r="B23" s="164"/>
+      <c r="C23" s="187"/>
       <c r="D23" s="53" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="26" x14ac:dyDescent="0.35">
       <c r="A24" s="68" t="s">
         <v>193</v>
       </c>
@@ -31850,7 +31889,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="68" t="s">
         <v>195</v>
       </c>
@@ -31864,7 +31903,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="44" t="s">
         <v>121</v>
       </c>
@@ -31876,7 +31915,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="35" t="s">
         <v>34</v>
       </c>
@@ -31884,7 +31923,7 @@
       <c r="C27" s="35"/>
       <c r="D27" s="35"/>
     </row>
-    <row r="28" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="75" t="s">
         <v>35</v>
       </c>
@@ -31898,7 +31937,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="75"/>
       <c r="B29" s="47"/>
       <c r="C29" s="65" t="s">
@@ -31908,7 +31947,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="75"/>
       <c r="B30" s="47"/>
       <c r="C30" s="65" t="s">
@@ -31918,7 +31957,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="75"/>
       <c r="B31" s="47"/>
       <c r="C31" s="77" t="s">
@@ -31928,11 +31967,11 @@
         <v>204</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="183" t="s">
+    <row r="32" spans="1:4" ht="26.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="188" t="s">
         <v>205</v>
       </c>
-      <c r="B32" s="186" t="s">
+      <c r="B32" s="191" t="s">
         <v>185</v>
       </c>
       <c r="C32" s="79" t="s">
@@ -31942,27 +31981,27 @@
         <v>207</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="184"/>
-      <c r="B33" s="187"/>
+    <row r="33" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="189"/>
+      <c r="B33" s="192"/>
       <c r="C33" s="65"/>
       <c r="D33" s="69"/>
     </row>
-    <row r="34" spans="1:4" ht="9.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="184"/>
-      <c r="B34" s="187"/>
+    <row r="34" spans="1:4" ht="9.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="189"/>
+      <c r="B34" s="192"/>
       <c r="C34" s="65"/>
       <c r="D34" s="69"/>
     </row>
-    <row r="35" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="184"/>
-      <c r="B35" s="187"/>
+    <row r="35" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="189"/>
+      <c r="B35" s="192"/>
       <c r="C35" s="65"/>
       <c r="D35" s="69"/>
     </row>
-    <row r="36" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="185"/>
-      <c r="B36" s="188"/>
+    <row r="36" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="190"/>
+      <c r="B36" s="193"/>
       <c r="C36" s="65" t="s">
         <v>208</v>
       </c>
@@ -31970,7 +32009,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="44" t="s">
         <v>36</v>
       </c>
@@ -31982,7 +32021,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="35" t="s">
         <v>37</v>
       </c>
@@ -31990,11 +32029,11 @@
       <c r="C38" s="35"/>
       <c r="D38" s="40"/>
     </row>
-    <row r="39" spans="1:4" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="156" t="s">
+    <row r="39" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="155" t="s">
+      <c r="B39" s="160" t="s">
         <v>185</v>
       </c>
       <c r="C39" s="70" t="s">
@@ -32004,9 +32043,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="156"/>
-      <c r="B40" s="155"/>
+    <row r="40" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="161"/>
+      <c r="B40" s="160"/>
       <c r="C40" s="64" t="s">
         <v>188</v>
       </c>
@@ -32014,87 +32053,87 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="154" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="159" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="155" t="s">
+      <c r="B41" s="160" t="s">
         <v>185</v>
       </c>
-      <c r="C41" s="179" t="s">
+      <c r="C41" s="184" t="s">
         <v>212</v>
       </c>
-      <c r="D41" s="158" t="s">
+      <c r="D41" s="163" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="154"/>
-      <c r="B42" s="155"/>
-      <c r="C42" s="179"/>
-      <c r="D42" s="158"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="154"/>
-      <c r="B43" s="155"/>
-      <c r="C43" s="179" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="159"/>
+      <c r="B42" s="160"/>
+      <c r="C42" s="184"/>
+      <c r="D42" s="163"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="159"/>
+      <c r="B43" s="160"/>
+      <c r="C43" s="184" t="s">
         <v>188</v>
       </c>
-      <c r="D43" s="161" t="s">
+      <c r="D43" s="166" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="154"/>
-      <c r="B44" s="155"/>
-      <c r="C44" s="179"/>
-      <c r="D44" s="161"/>
-    </row>
-    <row r="45" spans="1:4" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="160" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="159"/>
+      <c r="B44" s="160"/>
+      <c r="C44" s="184"/>
+      <c r="D44" s="166"/>
+    </row>
+    <row r="45" spans="1:4" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="165" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="159" t="s">
+      <c r="B45" s="164" t="s">
         <v>185</v>
       </c>
-      <c r="C45" s="175"/>
+      <c r="C45" s="180"/>
       <c r="D45" s="78" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="160"/>
-      <c r="B46" s="159"/>
-      <c r="C46" s="176"/>
-      <c r="D46" s="172" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="165"/>
+      <c r="B46" s="164"/>
+      <c r="C46" s="181"/>
+      <c r="D46" s="177" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="160"/>
-      <c r="B47" s="159"/>
-      <c r="C47" s="176"/>
-      <c r="D47" s="173"/>
-    </row>
-    <row r="48" spans="1:4" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="160"/>
-      <c r="B48" s="159"/>
-      <c r="C48" s="177"/>
-      <c r="D48" s="173"/>
-    </row>
-    <row r="49" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="160"/>
-      <c r="B49" s="159"/>
-      <c r="C49" s="167"/>
-      <c r="D49" s="173"/>
-    </row>
-    <row r="50" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="160"/>
-      <c r="B50" s="159"/>
-      <c r="C50" s="167"/>
-      <c r="D50" s="174"/>
-    </row>
-    <row r="51" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="165"/>
+      <c r="B47" s="164"/>
+      <c r="C47" s="181"/>
+      <c r="D47" s="178"/>
+    </row>
+    <row r="48" spans="1:4" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="165"/>
+      <c r="B48" s="164"/>
+      <c r="C48" s="182"/>
+      <c r="D48" s="178"/>
+    </row>
+    <row r="49" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="165"/>
+      <c r="B49" s="164"/>
+      <c r="C49" s="172"/>
+      <c r="D49" s="178"/>
+    </row>
+    <row r="50" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="165"/>
+      <c r="B50" s="164"/>
+      <c r="C50" s="172"/>
+      <c r="D50" s="179"/>
+    </row>
+    <row r="51" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="35" t="s">
         <v>44</v>
       </c>
@@ -32102,7 +32141,7 @@
       <c r="C51" s="35"/>
       <c r="D51" s="40"/>
     </row>
-    <row r="52" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="26" x14ac:dyDescent="0.35">
       <c r="A52" s="44" t="s">
         <v>154</v>
       </c>
@@ -32114,11 +32153,11 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="159" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="164" t="s">
         <v>156</v>
       </c>
-      <c r="B53" s="159" t="s">
+      <c r="B53" s="164" t="s">
         <v>185</v>
       </c>
       <c r="C53" s="65" t="s">
@@ -32128,9 +32167,9 @@
         <v>217</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="159"/>
-      <c r="B54" s="159"/>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="164"/>
+      <c r="B54" s="164"/>
       <c r="C54" s="65" t="s">
         <v>188</v>
       </c>
@@ -32138,9 +32177,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="159"/>
-      <c r="B55" s="159"/>
+    <row r="55" spans="1:4" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="164"/>
+      <c r="B55" s="164"/>
       <c r="C55" s="65" t="s">
         <v>218</v>
       </c>
@@ -32148,27 +32187,27 @@
         <v>219</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="34.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="159"/>
-      <c r="B56" s="159"/>
-      <c r="C56" s="178" t="s">
+    <row r="56" spans="1:4" ht="34.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="164"/>
+      <c r="B56" s="164"/>
+      <c r="C56" s="183" t="s">
         <v>220</v>
       </c>
       <c r="D56" s="71" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="159"/>
-      <c r="B57" s="159"/>
-      <c r="C57" s="178"/>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="164"/>
+      <c r="B57" s="164"/>
+      <c r="C57" s="183"/>
       <c r="D57" s="43" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="159"/>
-      <c r="B58" s="159"/>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="164"/>
+      <c r="B58" s="164"/>
       <c r="C58" s="65" t="s">
         <v>223</v>
       </c>
@@ -32176,9 +32215,9 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="159"/>
-      <c r="B59" s="159"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="164"/>
+      <c r="B59" s="164"/>
       <c r="C59" s="65" t="s">
         <v>225</v>
       </c>
@@ -32186,87 +32225,87 @@
         <v>226</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="159"/>
-      <c r="B60" s="159"/>
-      <c r="C60" s="178" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="164"/>
+      <c r="B60" s="164"/>
+      <c r="C60" s="183" t="s">
         <v>227</v>
       </c>
       <c r="D60" s="42" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="159"/>
-      <c r="B61" s="159"/>
-      <c r="C61" s="178"/>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="164"/>
+      <c r="B61" s="164"/>
+      <c r="C61" s="183"/>
       <c r="D61" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="159"/>
-      <c r="B62" s="159"/>
-      <c r="C62" s="178"/>
+    <row r="62" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="164"/>
+      <c r="B62" s="164"/>
+      <c r="C62" s="183"/>
       <c r="D62" s="71" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="159"/>
-      <c r="B63" s="159"/>
-      <c r="C63" s="179" t="s">
+    <row r="63" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="164"/>
+      <c r="B63" s="164"/>
+      <c r="C63" s="184" t="s">
         <v>231</v>
       </c>
       <c r="D63" s="41" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="159"/>
-      <c r="B64" s="159"/>
-      <c r="C64" s="179"/>
-      <c r="D64" s="161" t="s">
+    <row r="64" spans="1:4" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="164"/>
+      <c r="B64" s="164"/>
+      <c r="C64" s="184"/>
+      <c r="D64" s="166" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="12.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="159"/>
-      <c r="B65" s="159"/>
-      <c r="C65" s="179"/>
-      <c r="D65" s="161"/>
-    </row>
-    <row r="66" spans="1:4" ht="13.15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="159"/>
-      <c r="B66" s="159"/>
-      <c r="C66" s="179"/>
-      <c r="D66" s="161"/>
-    </row>
-    <row r="67" spans="1:4" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="159"/>
-      <c r="B67" s="159"/>
-      <c r="C67" s="179"/>
-      <c r="D67" s="161"/>
-    </row>
-    <row r="68" spans="1:4" ht="11.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="12.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="164"/>
+      <c r="B65" s="164"/>
+      <c r="C65" s="184"/>
+      <c r="D65" s="166"/>
+    </row>
+    <row r="66" spans="1:4" ht="13.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="164"/>
+      <c r="B66" s="164"/>
+      <c r="C66" s="184"/>
+      <c r="D66" s="166"/>
+    </row>
+    <row r="67" spans="1:4" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="164"/>
+      <c r="B67" s="164"/>
+      <c r="C67" s="184"/>
+      <c r="D67" s="166"/>
+    </row>
+    <row r="68" spans="1:4" ht="11.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="35"/>
       <c r="D68" s="40"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="73"/>
       <c r="B69" s="74"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="73"/>
       <c r="B70" s="74"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="73"/>
       <c r="B71" s="74"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="73"/>
       <c r="B72" s="74"/>
     </row>
@@ -32313,16 +32352,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D277"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D282"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="46.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="46.54296875" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" customWidth="1"/>
     <col min="4" max="4" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -32336,7 +32375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="87" t="s">
         <v>235</v>
       </c>
@@ -32344,11 +32383,11 @@
       <c r="C2" s="87"/>
       <c r="D2" s="88"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="189" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="194" t="s">
         <v>236</v>
       </c>
-      <c r="B3" s="189" t="s">
+      <c r="B3" s="194" t="s">
         <v>237</v>
       </c>
       <c r="C3" s="85" t="s">
@@ -32358,9 +32397,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="190"/>
-      <c r="B4" s="190"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="195"/>
+      <c r="B4" s="195"/>
       <c r="C4" s="84" t="s">
         <v>240</v>
       </c>
@@ -32368,9 +32407,9 @@
         <v>241</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="191"/>
-      <c r="B5" s="191"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="196"/>
+      <c r="B5" s="196"/>
       <c r="C5" s="84" t="s">
         <v>240</v>
       </c>
@@ -32378,11 +32417,11 @@
         <v>242</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="198" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="203" t="s">
         <v>243</v>
       </c>
-      <c r="B6" s="192" t="s">
+      <c r="B6" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C6" s="84"/>
@@ -32390,33 +32429,33 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="199"/>
-      <c r="B7" s="193"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="204"/>
+      <c r="B7" s="198"/>
       <c r="C7" s="84"/>
       <c r="D7" s="53" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="199"/>
-      <c r="B8" s="193"/>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="204"/>
+      <c r="B8" s="198"/>
       <c r="C8" s="84"/>
       <c r="D8" s="104" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="199"/>
-      <c r="B9" s="193"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="204"/>
+      <c r="B9" s="198"/>
       <c r="C9" s="84"/>
       <c r="D9" s="104" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="200"/>
-      <c r="B10" s="194"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="205"/>
+      <c r="B10" s="199"/>
       <c r="C10" s="84" t="s">
         <v>248</v>
       </c>
@@ -32424,11 +32463,11 @@
         <v>249</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="189" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="194" t="s">
         <v>250</v>
       </c>
-      <c r="B11" s="192" t="s">
+      <c r="B11" s="197" t="s">
         <v>237</v>
       </c>
       <c r="C11" s="84" t="s">
@@ -32438,9 +32477,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="190"/>
-      <c r="B12" s="193"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="195"/>
+      <c r="B12" s="198"/>
       <c r="C12" s="84" t="s">
         <v>251</v>
       </c>
@@ -32448,9 +32487,9 @@
         <v>252</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="191"/>
-      <c r="B13" s="194"/>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="196"/>
+      <c r="B13" s="199"/>
       <c r="C13" s="84" t="s">
         <v>253</v>
       </c>
@@ -32458,7 +32497,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="87" t="s">
         <v>255</v>
       </c>
@@ -32466,11 +32505,11 @@
       <c r="C14" s="87"/>
       <c r="D14" s="88"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="169" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="174" t="s">
         <v>256</v>
       </c>
-      <c r="B15" s="192" t="s">
+      <c r="B15" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C15" s="99" t="s">
@@ -32480,9 +32519,9 @@
         <v>258</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="170"/>
-      <c r="B16" s="194"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="175"/>
+      <c r="B16" s="199"/>
       <c r="C16" s="99" t="s">
         <v>259</v>
       </c>
@@ -32490,7 +32529,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="102" t="s">
         <v>261</v>
       </c>
@@ -32504,7 +32543,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="100" t="s">
         <v>264</v>
       </c>
@@ -32516,11 +32555,11 @@
         <v>265</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="189" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="194" t="s">
         <v>266</v>
       </c>
-      <c r="B19" s="192" t="s">
+      <c r="B19" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C19" s="80" t="s">
@@ -32530,9 +32569,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="190"/>
-      <c r="B20" s="193"/>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="195"/>
+      <c r="B20" s="198"/>
       <c r="C20" s="53" t="s">
         <v>268</v>
       </c>
@@ -32540,9 +32579,9 @@
         <v>269</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="190"/>
-      <c r="B21" s="193"/>
+    <row r="21" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="195"/>
+      <c r="B21" s="198"/>
       <c r="C21" s="99" t="s">
         <v>270</v>
       </c>
@@ -32550,9 +32589,9 @@
         <v>271</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="190"/>
-      <c r="B22" s="193"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="195"/>
+      <c r="B22" s="198"/>
       <c r="C22" s="99" t="s">
         <v>5</v>
       </c>
@@ -32560,9 +32599,9 @@
         <v>272</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="190"/>
-      <c r="B23" s="193"/>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="195"/>
+      <c r="B23" s="198"/>
       <c r="C23" s="84" t="s">
         <v>238</v>
       </c>
@@ -32570,9 +32609,9 @@
         <v>273</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="190"/>
-      <c r="B24" s="193"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="195"/>
+      <c r="B24" s="198"/>
       <c r="C24" s="84" t="s">
         <v>274</v>
       </c>
@@ -32580,9 +32619,9 @@
         <v>275</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="190"/>
-      <c r="B25" s="193"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="195"/>
+      <c r="B25" s="198"/>
       <c r="C25" s="84" t="s">
         <v>276</v>
       </c>
@@ -32590,9 +32629,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="190"/>
-      <c r="B26" s="193"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="195"/>
+      <c r="B26" s="198"/>
       <c r="C26" s="84" t="s">
         <v>238</v>
       </c>
@@ -32600,9 +32639,9 @@
         <v>278</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="190"/>
-      <c r="B27" s="193"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="195"/>
+      <c r="B27" s="198"/>
       <c r="C27" s="99" t="s">
         <v>279</v>
       </c>
@@ -32610,9 +32649,9 @@
         <v>280</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="191"/>
-      <c r="B28" s="194"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="196"/>
+      <c r="B28" s="199"/>
       <c r="C28" s="99">
         <v>1.1000000000000001</v>
       </c>
@@ -32620,11 +32659,11 @@
         <v>242</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="198" t="s">
+    <row r="29" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="203" t="s">
         <v>281</v>
       </c>
-      <c r="B29" s="192" t="s">
+      <c r="B29" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C29" s="84" t="s">
@@ -32634,9 +32673,9 @@
         <v>282</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="199"/>
-      <c r="B30" s="193"/>
+    <row r="30" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="204"/>
+      <c r="B30" s="198"/>
       <c r="C30" s="84" t="s">
         <v>279</v>
       </c>
@@ -32644,9 +32683,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="199"/>
-      <c r="B31" s="193"/>
+    <row r="31" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="204"/>
+      <c r="B31" s="198"/>
       <c r="C31" s="84">
         <v>3.3</v>
       </c>
@@ -32654,9 +32693,9 @@
         <v>284</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="199"/>
-      <c r="B32" s="193"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="204"/>
+      <c r="B32" s="198"/>
       <c r="C32" s="90">
         <v>3</v>
       </c>
@@ -32664,9 +32703,9 @@
         <v>285</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="200"/>
-      <c r="B33" s="194"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="205"/>
+      <c r="B33" s="199"/>
       <c r="C33" s="90">
         <v>3.5</v>
       </c>
@@ -32674,11 +32713,11 @@
         <v>286</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="198" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="203" t="s">
         <v>287</v>
       </c>
-      <c r="B34" s="192" t="s">
+      <c r="B34" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C34" s="90"/>
@@ -32686,28 +32725,28 @@
         <v>288</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="200"/>
-      <c r="B35" s="194"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="205"/>
+      <c r="B35" s="199"/>
       <c r="C35" s="84"/>
       <c r="D35" s="62" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="201" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="206" t="s">
         <v>290</v>
       </c>
-      <c r="B36" s="192" t="s">
+      <c r="B36" s="197" t="s">
         <v>244</v>
       </c>
       <c r="D36" s="62" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="201"/>
-      <c r="B37" s="193"/>
+    <row r="37" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="206"/>
+      <c r="B37" s="198"/>
       <c r="C37" s="106" t="s">
         <v>292</v>
       </c>
@@ -32715,9 +32754,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="201"/>
-      <c r="B38" s="193"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="206"/>
+      <c r="B38" s="198"/>
       <c r="C38" s="53" t="s">
         <v>294</v>
       </c>
@@ -32725,9 +32764,9 @@
         <v>295</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A39" s="201"/>
-      <c r="B39" s="193"/>
+    <row r="39" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A39" s="206"/>
+      <c r="B39" s="198"/>
       <c r="C39" s="56" t="s">
         <v>296</v>
       </c>
@@ -32735,11 +32774,11 @@
         <v>293</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="108" t="s">
         <v>297</v>
       </c>
-      <c r="B40" s="192" t="s">
+      <c r="B40" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C40" s="84"/>
@@ -32747,9 +32786,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="109"/>
-      <c r="B41" s="193"/>
+      <c r="B41" s="198"/>
       <c r="C41" s="84" t="s">
         <v>298</v>
       </c>
@@ -32757,19 +32796,19 @@
         <v>299</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="100"/>
-      <c r="B42" s="194"/>
+      <c r="B42" s="199"/>
       <c r="C42" s="84"/>
       <c r="D42" s="107" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="108" t="s">
         <v>300</v>
       </c>
-      <c r="B43" s="192" t="s">
+      <c r="B43" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C43" s="84"/>
@@ -32777,35 +32816,35 @@
         <v>249</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="100"/>
-      <c r="B44" s="194"/>
+      <c r="B44" s="199"/>
       <c r="C44" s="84"/>
       <c r="D44" s="107" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="189" t="s">
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="194" t="s">
         <v>301</v>
       </c>
-      <c r="B45" s="192" t="s">
+      <c r="B45" s="197" t="s">
         <v>244</v>
       </c>
-      <c r="C45" s="202"/>
+      <c r="C45" s="207"/>
       <c r="D45" s="107" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="191"/>
-      <c r="B46" s="194"/>
-      <c r="C46" s="203"/>
+    <row r="46" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="196"/>
+      <c r="B46" s="199"/>
+      <c r="C46" s="208"/>
       <c r="D46" s="107" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="100" t="s">
         <v>303</v>
       </c>
@@ -32817,7 +32856,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="100" t="s">
         <v>304</v>
       </c>
@@ -32829,7 +32868,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="100" t="s">
         <v>305</v>
       </c>
@@ -32841,7 +32880,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="87" t="s">
         <v>306</v>
       </c>
@@ -32849,11 +32888,11 @@
       <c r="C50" s="87"/>
       <c r="D50" s="88"/>
     </row>
-    <row r="51" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="201" t="s">
+    <row r="51" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A51" s="206" t="s">
         <v>307</v>
       </c>
-      <c r="B51" s="207" t="s">
+      <c r="B51" s="212" t="s">
         <v>244</v>
       </c>
       <c r="C51" s="84" t="s">
@@ -32863,9 +32902,9 @@
         <v>309</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="201"/>
-      <c r="B52" s="207"/>
+    <row r="52" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A52" s="206"/>
+      <c r="B52" s="212"/>
       <c r="C52" s="84" t="s">
         <v>310</v>
       </c>
@@ -32873,9 +32912,9 @@
         <v>311</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="201"/>
-      <c r="B53" s="207"/>
+    <row r="53" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A53" s="206"/>
+      <c r="B53" s="212"/>
       <c r="C53" s="84" t="s">
         <v>308</v>
       </c>
@@ -32883,7 +32922,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="45.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="45.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="87" t="s">
         <v>8</v>
       </c>
@@ -32891,11 +32930,11 @@
       <c r="C54" s="87"/>
       <c r="D54" s="88"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="158" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="163" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="178" t="s">
+      <c r="B55" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C55" s="53"/>
@@ -32903,9 +32942,9 @@
         <v>313</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="158"/>
-      <c r="B56" s="178"/>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="163"/>
+      <c r="B56" s="183"/>
       <c r="C56" s="65" t="s">
         <v>314</v>
       </c>
@@ -32913,9 +32952,9 @@
         <v>315</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="158"/>
-      <c r="B57" s="178"/>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="163"/>
+      <c r="B57" s="183"/>
       <c r="C57" s="65" t="s">
         <v>316</v>
       </c>
@@ -32923,9 +32962,9 @@
         <v>317</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="158"/>
-      <c r="B58" s="178"/>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="163"/>
+      <c r="B58" s="183"/>
       <c r="C58" s="65" t="s">
         <v>316</v>
       </c>
@@ -32933,9 +32972,9 @@
         <v>318</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="158"/>
-      <c r="B59" s="178"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="163"/>
+      <c r="B59" s="183"/>
       <c r="C59" s="65" t="s">
         <v>248</v>
       </c>
@@ -32943,9 +32982,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="158"/>
-      <c r="B60" s="178"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="163"/>
+      <c r="B60" s="183"/>
       <c r="C60" s="70" t="s">
         <v>248</v>
       </c>
@@ -32953,11 +32992,11 @@
         <v>320</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="169" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="174" t="s">
         <v>26</v>
       </c>
-      <c r="B61" s="192" t="s">
+      <c r="B61" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C61" s="65" t="s">
@@ -32967,9 +33006,9 @@
         <v>321</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="210"/>
-      <c r="B62" s="193"/>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="215"/>
+      <c r="B62" s="198"/>
       <c r="C62" s="65" t="s">
         <v>322</v>
       </c>
@@ -32977,9 +33016,9 @@
         <v>323</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="170"/>
-      <c r="B63" s="194"/>
+    <row r="63" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A63" s="175"/>
+      <c r="B63" s="199"/>
       <c r="C63" s="103" t="s">
         <v>324</v>
       </c>
@@ -32987,7 +33026,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="90" t="s">
         <v>326</v>
       </c>
@@ -33001,7 +33040,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="90" t="s">
         <v>327</v>
       </c>
@@ -33015,7 +33054,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="90" t="s">
         <v>328</v>
       </c>
@@ -33027,11 +33066,11 @@
         <v>329</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="158" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="163" t="s">
         <v>330</v>
       </c>
-      <c r="B67" s="178" t="s">
+      <c r="B67" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C67" s="53" t="s">
@@ -33041,25 +33080,25 @@
         <v>332</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="158"/>
-      <c r="B68" s="178"/>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="163"/>
+      <c r="B68" s="183"/>
       <c r="C68" s="53"/>
       <c r="D68" s="71" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="158"/>
-      <c r="B69" s="178"/>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="163"/>
+      <c r="B69" s="183"/>
       <c r="C69" s="53"/>
       <c r="D69" s="53" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="158"/>
-      <c r="B70" s="178"/>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="163"/>
+      <c r="B70" s="183"/>
       <c r="C70" s="65" t="s">
         <v>335</v>
       </c>
@@ -33067,9 +33106,9 @@
         <v>336</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="158"/>
-      <c r="B71" s="178"/>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="163"/>
+      <c r="B71" s="183"/>
       <c r="C71" s="70" t="s">
         <v>337</v>
       </c>
@@ -33077,7 +33116,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="90" t="s">
         <v>339</v>
       </c>
@@ -33089,11 +33128,11 @@
       </c>
       <c r="D72" s="53"/>
     </row>
-    <row r="73" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A73" s="204" t="s">
+    <row r="73" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A73" s="209" t="s">
         <v>121</v>
       </c>
-      <c r="B73" s="192" t="s">
+      <c r="B73" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C73" s="53"/>
@@ -33101,9 +33140,9 @@
         <v>340</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="205"/>
-      <c r="B74" s="193"/>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="210"/>
+      <c r="B74" s="198"/>
       <c r="C74" s="70" t="s">
         <v>341</v>
       </c>
@@ -33111,9 +33150,9 @@
         <v>342</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="205"/>
-      <c r="B75" s="193"/>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="210"/>
+      <c r="B75" s="198"/>
       <c r="C75" s="70" t="s">
         <v>343</v>
       </c>
@@ -33121,9 +33160,9 @@
         <v>344</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="205"/>
-      <c r="B76" s="193"/>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="210"/>
+      <c r="B76" s="198"/>
       <c r="C76" s="91" t="s">
         <v>345</v>
       </c>
@@ -33131,9 +33170,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="205"/>
-      <c r="B77" s="193"/>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="210"/>
+      <c r="B77" s="198"/>
       <c r="C77" s="70" t="s">
         <v>343</v>
       </c>
@@ -33141,9 +33180,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="205"/>
-      <c r="B78" s="193"/>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="210"/>
+      <c r="B78" s="198"/>
       <c r="C78" s="70" t="s">
         <v>348</v>
       </c>
@@ -33151,9 +33190,9 @@
         <v>349</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="205"/>
-      <c r="B79" s="193"/>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="210"/>
+      <c r="B79" s="198"/>
       <c r="C79" s="70" t="s">
         <v>343</v>
       </c>
@@ -33161,9 +33200,9 @@
         <v>350</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="205"/>
-      <c r="B80" s="193"/>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="210"/>
+      <c r="B80" s="198"/>
       <c r="C80" s="70" t="s">
         <v>351</v>
       </c>
@@ -33171,9 +33210,9 @@
         <v>352</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="205"/>
-      <c r="B81" s="193"/>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="210"/>
+      <c r="B81" s="198"/>
       <c r="C81" s="70" t="s">
         <v>353</v>
       </c>
@@ -33181,9 +33220,9 @@
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="205"/>
-      <c r="B82" s="193"/>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="210"/>
+      <c r="B82" s="198"/>
       <c r="C82" s="70" t="s">
         <v>343</v>
       </c>
@@ -33191,9 +33230,9 @@
         <v>355</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="205"/>
-      <c r="B83" s="193"/>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="210"/>
+      <c r="B83" s="198"/>
       <c r="C83" s="70" t="s">
         <v>353</v>
       </c>
@@ -33201,9 +33240,9 @@
         <v>356</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="205"/>
-      <c r="B84" s="193"/>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="210"/>
+      <c r="B84" s="198"/>
       <c r="C84" s="70" t="s">
         <v>343</v>
       </c>
@@ -33211,9 +33250,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="205"/>
-      <c r="B85" s="193"/>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="210"/>
+      <c r="B85" s="198"/>
       <c r="C85" s="70" t="s">
         <v>248</v>
       </c>
@@ -33221,9 +33260,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="205"/>
-      <c r="B86" s="193"/>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="210"/>
+      <c r="B86" s="198"/>
       <c r="C86" s="70" t="s">
         <v>248</v>
       </c>
@@ -33231,9 +33270,9 @@
         <v>358</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="205"/>
-      <c r="B87" s="193"/>
+    <row r="87" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A87" s="210"/>
+      <c r="B87" s="198"/>
       <c r="C87" s="91" t="s">
         <v>359</v>
       </c>
@@ -33241,9 +33280,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="206"/>
-      <c r="B88" s="194"/>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="211"/>
+      <c r="B88" s="199"/>
       <c r="C88" s="70" t="s">
         <v>248</v>
       </c>
@@ -33251,7 +33290,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="90" t="s">
         <v>361</v>
       </c>
@@ -33265,7 +33304,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="90" t="s">
         <v>364</v>
       </c>
@@ -33279,7 +33318,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="90" t="s">
         <v>367</v>
       </c>
@@ -33291,11 +33330,11 @@
       </c>
       <c r="D91" s="53"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="169" t="s">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" s="174" t="s">
         <v>368</v>
       </c>
-      <c r="B92" s="192" t="s">
+      <c r="B92" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C92" s="70" t="s">
@@ -33303,9 +33342,9 @@
       </c>
       <c r="D92" s="53"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="170"/>
-      <c r="B93" s="194"/>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" s="175"/>
+      <c r="B93" s="199"/>
       <c r="C93" s="70" t="s">
         <v>337</v>
       </c>
@@ -33313,7 +33352,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="87" t="s">
         <v>34</v>
       </c>
@@ -33321,11 +33360,11 @@
       <c r="C94" s="87"/>
       <c r="D94" s="87"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="169" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="174" t="s">
         <v>369</v>
       </c>
-      <c r="B95" s="192" t="s">
+      <c r="B95" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C95" s="53"/>
@@ -33333,25 +33372,25 @@
         <v>370</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="210"/>
-      <c r="B96" s="193"/>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="215"/>
+      <c r="B96" s="198"/>
       <c r="C96" s="53"/>
       <c r="D96" s="53" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="210"/>
-      <c r="B97" s="193"/>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="215"/>
+      <c r="B97" s="198"/>
       <c r="C97" s="53"/>
       <c r="D97" s="53" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="210"/>
-      <c r="B98" s="193"/>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="215"/>
+      <c r="B98" s="198"/>
       <c r="C98" s="53" t="s">
         <v>373</v>
       </c>
@@ -33359,9 +33398,9 @@
         <v>374</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="210"/>
-      <c r="B99" s="193"/>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" s="215"/>
+      <c r="B99" s="198"/>
       <c r="C99" s="53" t="s">
         <v>375</v>
       </c>
@@ -33369,9 +33408,9 @@
         <v>376</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="210"/>
-      <c r="B100" s="193"/>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" s="215"/>
+      <c r="B100" s="198"/>
       <c r="C100" s="53" t="s">
         <v>377</v>
       </c>
@@ -33379,9 +33418,9 @@
         <v>378</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101" s="210"/>
-      <c r="B101" s="193"/>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" s="215"/>
+      <c r="B101" s="198"/>
       <c r="C101" s="56" t="s">
         <v>379</v>
       </c>
@@ -33389,9 +33428,9 @@
         <v>349</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="210"/>
-      <c r="B102" s="193"/>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" s="215"/>
+      <c r="B102" s="198"/>
       <c r="C102" s="53" t="s">
         <v>41</v>
       </c>
@@ -33399,9 +33438,9 @@
         <v>380</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="210"/>
-      <c r="B103" s="193"/>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" s="215"/>
+      <c r="B103" s="198"/>
       <c r="C103" s="90" t="s">
         <v>343</v>
       </c>
@@ -33409,9 +33448,9 @@
         <v>355</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="210"/>
-      <c r="B104" s="193"/>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" s="215"/>
+      <c r="B104" s="198"/>
       <c r="C104" s="90" t="s">
         <v>353</v>
       </c>
@@ -33419,9 +33458,9 @@
         <v>381</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="210"/>
-      <c r="B105" s="193"/>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" s="215"/>
+      <c r="B105" s="198"/>
       <c r="C105" s="90" t="s">
         <v>377</v>
       </c>
@@ -33429,9 +33468,9 @@
         <v>382</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="210"/>
-      <c r="B106" s="193"/>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" s="215"/>
+      <c r="B106" s="198"/>
       <c r="C106" s="90" t="s">
         <v>343</v>
       </c>
@@ -33439,9 +33478,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="210"/>
-      <c r="B107" s="193"/>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" s="215"/>
+      <c r="B107" s="198"/>
       <c r="C107" s="90" t="s">
         <v>248</v>
       </c>
@@ -33449,9 +33488,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="210"/>
-      <c r="B108" s="193"/>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" s="215"/>
+      <c r="B108" s="198"/>
       <c r="C108" s="90" t="s">
         <v>248</v>
       </c>
@@ -33459,9 +33498,9 @@
         <v>358</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A109" s="210"/>
-      <c r="B109" s="193"/>
+    <row r="109" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A109" s="215"/>
+      <c r="B109" s="198"/>
       <c r="C109" s="91" t="s">
         <v>359</v>
       </c>
@@ -33469,9 +33508,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="170"/>
-      <c r="B110" s="194"/>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" s="175"/>
+      <c r="B110" s="199"/>
       <c r="C110" s="90" t="s">
         <v>248</v>
       </c>
@@ -33479,11 +33518,11 @@
         <v>320</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="211" t="s">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" s="216" t="s">
         <v>36</v>
       </c>
-      <c r="B111" s="192" t="s">
+      <c r="B111" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C111" s="113" t="s">
@@ -33493,9 +33532,9 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="212"/>
-      <c r="B112" s="193"/>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" s="217"/>
+      <c r="B112" s="198"/>
       <c r="C112" s="53" t="s">
         <v>383</v>
       </c>
@@ -33503,17 +33542,17 @@
         <v>384</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="212"/>
-      <c r="B113" s="193"/>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" s="217"/>
+      <c r="B113" s="198"/>
       <c r="C113" s="53"/>
       <c r="D113" s="53" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A114" s="212"/>
-      <c r="B114" s="193"/>
+    <row r="114" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A114" s="217"/>
+      <c r="B114" s="198"/>
       <c r="C114" s="56" t="s">
         <v>386</v>
       </c>
@@ -33521,9 +33560,9 @@
         <v>387</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="212"/>
-      <c r="B115" s="193"/>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" s="217"/>
+      <c r="B115" s="198"/>
       <c r="C115" s="56" t="s">
         <v>343</v>
       </c>
@@ -33531,9 +33570,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="212"/>
-      <c r="B116" s="193"/>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" s="217"/>
+      <c r="B116" s="198"/>
       <c r="C116" s="56" t="s">
         <v>345</v>
       </c>
@@ -33541,9 +33580,9 @@
         <v>388</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="212"/>
-      <c r="B117" s="193"/>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" s="217"/>
+      <c r="B117" s="198"/>
       <c r="C117" s="56" t="s">
         <v>348</v>
       </c>
@@ -33551,9 +33590,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="212"/>
-      <c r="B118" s="193"/>
+    <row r="118" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A118" s="217"/>
+      <c r="B118" s="198"/>
       <c r="C118" s="56" t="s">
         <v>389</v>
       </c>
@@ -33561,9 +33600,9 @@
         <v>390</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="212"/>
-      <c r="B119" s="193"/>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" s="217"/>
+      <c r="B119" s="198"/>
       <c r="C119" s="90" t="s">
         <v>343</v>
       </c>
@@ -33571,9 +33610,9 @@
         <v>391</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="212"/>
-      <c r="B120" s="193"/>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" s="217"/>
+      <c r="B120" s="198"/>
       <c r="C120" s="90" t="s">
         <v>351</v>
       </c>
@@ -33581,9 +33620,9 @@
         <v>352</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="212"/>
-      <c r="B121" s="193"/>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" s="217"/>
+      <c r="B121" s="198"/>
       <c r="C121" s="90" t="s">
         <v>353</v>
       </c>
@@ -33591,9 +33630,9 @@
         <v>354</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="212"/>
-      <c r="B122" s="193"/>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" s="217"/>
+      <c r="B122" s="198"/>
       <c r="C122" s="90" t="s">
         <v>343</v>
       </c>
@@ -33601,9 +33640,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="212"/>
-      <c r="B123" s="193"/>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" s="217"/>
+      <c r="B123" s="198"/>
       <c r="C123" s="90" t="s">
         <v>353</v>
       </c>
@@ -33611,9 +33650,9 @@
         <v>381</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="212"/>
-      <c r="B124" s="193"/>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" s="217"/>
+      <c r="B124" s="198"/>
       <c r="C124" s="90" t="s">
         <v>377</v>
       </c>
@@ -33621,9 +33660,9 @@
         <v>382</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="212"/>
-      <c r="B125" s="193"/>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" s="217"/>
+      <c r="B125" s="198"/>
       <c r="C125" s="90" t="s">
         <v>343</v>
       </c>
@@ -33631,9 +33670,9 @@
         <v>357</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="212"/>
-      <c r="B126" s="193"/>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" s="217"/>
+      <c r="B126" s="198"/>
       <c r="C126" s="90" t="s">
         <v>248</v>
       </c>
@@ -33641,9 +33680,9 @@
         <v>319</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="212"/>
-      <c r="B127" s="193"/>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" s="217"/>
+      <c r="B127" s="198"/>
       <c r="C127" s="90" t="s">
         <v>248</v>
       </c>
@@ -33651,9 +33690,9 @@
         <v>358</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="212"/>
-      <c r="B128" s="193"/>
+    <row r="128" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A128" s="217"/>
+      <c r="B128" s="198"/>
       <c r="C128" s="91" t="s">
         <v>359</v>
       </c>
@@ -33661,9 +33700,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="213"/>
-      <c r="B129" s="194"/>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" s="218"/>
+      <c r="B129" s="199"/>
       <c r="C129" s="90" t="s">
         <v>248</v>
       </c>
@@ -33671,49 +33710,49 @@
         <v>320</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="169" t="s">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" s="174" t="s">
         <v>205</v>
       </c>
-      <c r="B130" s="192" t="s">
+      <c r="B130" s="197" t="s">
         <v>244</v>
       </c>
-      <c r="C130" s="214" t="s">
+      <c r="C130" s="219" t="s">
         <v>392</v>
       </c>
       <c r="D130" s="80" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="210"/>
-      <c r="B131" s="193"/>
-      <c r="C131" s="215"/>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" s="215"/>
+      <c r="B131" s="198"/>
+      <c r="C131" s="220"/>
       <c r="D131" s="53" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="210"/>
-      <c r="B132" s="193"/>
-      <c r="C132" s="216" t="s">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" s="215"/>
+      <c r="B132" s="198"/>
+      <c r="C132" s="221" t="s">
         <v>395</v>
       </c>
       <c r="D132" s="53" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A133" s="210"/>
-      <c r="B133" s="193"/>
-      <c r="C133" s="216"/>
+    <row r="133" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A133" s="215"/>
+      <c r="B133" s="198"/>
+      <c r="C133" s="221"/>
       <c r="D133" s="56" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="210"/>
-      <c r="B134" s="193"/>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" s="215"/>
+      <c r="B134" s="198"/>
       <c r="C134" s="70" t="s">
         <v>398</v>
       </c>
@@ -33721,9 +33760,9 @@
         <v>399</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="210"/>
-      <c r="B135" s="193"/>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" s="215"/>
+      <c r="B135" s="198"/>
       <c r="C135" s="70">
         <v>2.1</v>
       </c>
@@ -33731,9 +33770,9 @@
         <v>400</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="210"/>
-      <c r="B136" s="193"/>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" s="215"/>
+      <c r="B136" s="198"/>
       <c r="C136" s="70" t="s">
         <v>392</v>
       </c>
@@ -33741,9 +33780,9 @@
         <v>401</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="210"/>
-      <c r="B137" s="193"/>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137" s="215"/>
+      <c r="B137" s="198"/>
       <c r="C137" s="70" t="s">
         <v>392</v>
       </c>
@@ -33751,9 +33790,9 @@
         <v>402</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="210"/>
-      <c r="B138" s="193"/>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" s="215"/>
+      <c r="B138" s="198"/>
       <c r="C138" s="70" t="s">
         <v>392</v>
       </c>
@@ -33761,9 +33800,9 @@
         <v>403</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="210"/>
-      <c r="B139" s="193"/>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" s="215"/>
+      <c r="B139" s="198"/>
       <c r="C139" s="93" t="s">
         <v>404</v>
       </c>
@@ -33771,9 +33810,9 @@
         <v>405</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="210"/>
-      <c r="B140" s="193"/>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" s="215"/>
+      <c r="B140" s="198"/>
       <c r="C140" s="70">
         <v>2.1</v>
       </c>
@@ -33781,9 +33820,9 @@
         <v>406</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="210"/>
-      <c r="B141" s="193"/>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" s="215"/>
+      <c r="B141" s="198"/>
       <c r="C141" s="70" t="s">
         <v>392</v>
       </c>
@@ -33791,9 +33830,9 @@
         <v>338</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="210"/>
-      <c r="B142" s="193"/>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" s="215"/>
+      <c r="B142" s="198"/>
       <c r="C142" s="70" t="s">
         <v>392</v>
       </c>
@@ -33801,9 +33840,9 @@
         <v>407</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="210"/>
-      <c r="B143" s="193"/>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" s="215"/>
+      <c r="B143" s="198"/>
       <c r="C143" s="70">
         <v>2.1</v>
       </c>
@@ -33811,11 +33850,11 @@
         <v>408</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="211" t="s">
+    <row r="144" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="216" t="s">
         <v>409</v>
       </c>
-      <c r="B144" s="192" t="s">
+      <c r="B144" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C144" s="53" t="s">
@@ -33825,9 +33864,9 @@
         <v>411</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A145" s="212"/>
-      <c r="B145" s="193"/>
+    <row r="145" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A145" s="217"/>
+      <c r="B145" s="198"/>
       <c r="C145" s="56" t="s">
         <v>412</v>
       </c>
@@ -33835,9 +33874,9 @@
         <v>413</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="213"/>
-      <c r="B146" s="194"/>
+    <row r="146" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="218"/>
+      <c r="B146" s="199"/>
       <c r="C146" s="53" t="s">
         <v>414</v>
       </c>
@@ -33845,11 +33884,11 @@
         <v>415</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="169" t="s">
+    <row r="147" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="174" t="s">
         <v>416</v>
       </c>
-      <c r="B147" s="192" t="s">
+      <c r="B147" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C147" s="70" t="s">
@@ -33857,9 +33896,9 @@
       </c>
       <c r="D147" s="53"/>
     </row>
-    <row r="148" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="210"/>
-      <c r="B148" s="193"/>
+    <row r="148" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="215"/>
+      <c r="B148" s="198"/>
       <c r="C148" s="70" t="s">
         <v>404</v>
       </c>
@@ -33867,9 +33906,9 @@
         <v>405</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="210"/>
-      <c r="B149" s="193"/>
+    <row r="149" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="215"/>
+      <c r="B149" s="198"/>
       <c r="C149" s="70">
         <v>2.1</v>
       </c>
@@ -33877,9 +33916,9 @@
         <v>406</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="210"/>
-      <c r="B150" s="193"/>
+    <row r="150" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="215"/>
+      <c r="B150" s="198"/>
       <c r="C150" s="70" t="s">
         <v>395</v>
       </c>
@@ -33887,9 +33926,9 @@
         <v>417</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="210"/>
-      <c r="B151" s="193"/>
+    <row r="151" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="215"/>
+      <c r="B151" s="198"/>
       <c r="C151" s="70" t="s">
         <v>392</v>
       </c>
@@ -33897,7 +33936,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" s="87" t="s">
         <v>37</v>
       </c>
@@ -33905,7 +33944,7 @@
       <c r="C152" s="87"/>
       <c r="D152" s="88"/>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" s="90" t="s">
         <v>418</v>
       </c>
@@ -33917,11 +33956,11 @@
       </c>
       <c r="D153" s="53"/>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" s="169" t="s">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A154" s="174" t="s">
         <v>420</v>
       </c>
-      <c r="B154" s="192" t="s">
+      <c r="B154" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C154" s="53"/>
@@ -33929,25 +33968,25 @@
         <v>333</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" s="210"/>
-      <c r="B155" s="193"/>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A155" s="215"/>
+      <c r="B155" s="198"/>
       <c r="C155" s="53"/>
       <c r="D155" s="53" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="210"/>
-      <c r="B156" s="193"/>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156" s="215"/>
+      <c r="B156" s="198"/>
       <c r="C156" s="53"/>
       <c r="D156" s="53" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" s="210"/>
-      <c r="B157" s="193"/>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157" s="215"/>
+      <c r="B157" s="198"/>
       <c r="C157" s="53" t="s">
         <v>422</v>
       </c>
@@ -33955,9 +33994,9 @@
         <v>318</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" s="210"/>
-      <c r="B158" s="193"/>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A158" s="215"/>
+      <c r="B158" s="198"/>
       <c r="C158" s="53" t="s">
         <v>423</v>
       </c>
@@ -33965,9 +34004,9 @@
         <v>424</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" s="210"/>
-      <c r="B159" s="193"/>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A159" s="215"/>
+      <c r="B159" s="198"/>
       <c r="C159" s="53" t="s">
         <v>316</v>
       </c>
@@ -33975,9 +34014,9 @@
         <v>349</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" s="210"/>
-      <c r="B160" s="193"/>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A160" s="215"/>
+      <c r="B160" s="198"/>
       <c r="C160" s="53" t="s">
         <v>248</v>
       </c>
@@ -33985,11 +34024,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="158" t="s">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A161" s="163" t="s">
         <v>426</v>
       </c>
-      <c r="B161" s="178" t="s">
+      <c r="B161" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C161" s="71" t="s">
@@ -33999,9 +34038,9 @@
         <v>428</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="158"/>
-      <c r="B162" s="178"/>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A162" s="163"/>
+      <c r="B162" s="183"/>
       <c r="C162" s="53" t="s">
         <v>429</v>
       </c>
@@ -34009,43 +34048,43 @@
         <v>430</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A163" s="158"/>
-      <c r="B163" s="178"/>
+    <row r="163" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A163" s="163"/>
+      <c r="B163" s="183"/>
       <c r="C163" s="94" t="s">
         <v>431</v>
       </c>
-      <c r="D163" s="192" t="s">
+      <c r="D163" s="197" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A164" s="158"/>
-      <c r="B164" s="178"/>
+    <row r="164" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A164" s="163"/>
+      <c r="B164" s="183"/>
       <c r="C164" s="94" t="s">
         <v>433</v>
       </c>
-      <c r="D164" s="193"/>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="158"/>
-      <c r="B165" s="178"/>
+      <c r="D164" s="198"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A165" s="163"/>
+      <c r="B165" s="183"/>
       <c r="C165" s="94" t="s">
         <v>434</v>
       </c>
-      <c r="D165" s="193"/>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="158"/>
-      <c r="B166" s="178"/>
+      <c r="D165" s="198"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A166" s="163"/>
+      <c r="B166" s="183"/>
       <c r="C166" s="94" t="s">
         <v>435</v>
       </c>
-      <c r="D166" s="193"/>
-    </row>
-    <row r="167" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A167" s="158"/>
-      <c r="B167" s="178"/>
+      <c r="D166" s="198"/>
+    </row>
+    <row r="167" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A167" s="163"/>
+      <c r="B167" s="183"/>
       <c r="C167" s="94" t="s">
         <v>436</v>
       </c>
@@ -34053,7 +34092,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="90" t="s">
         <v>437</v>
       </c>
@@ -34067,11 +34106,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="195" t="s">
+    <row r="169" spans="1:4" ht="30.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="200" t="s">
         <v>43</v>
       </c>
-      <c r="B169" s="192" t="s">
+      <c r="B169" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C169" s="53" t="s">
@@ -34081,9 +34120,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="196"/>
-      <c r="B170" s="193"/>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A170" s="201"/>
+      <c r="B170" s="198"/>
       <c r="C170" s="53" t="s">
         <v>439</v>
       </c>
@@ -34091,9 +34130,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="196"/>
-      <c r="B171" s="193"/>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A171" s="201"/>
+      <c r="B171" s="198"/>
       <c r="C171" s="53" t="s">
         <v>440</v>
       </c>
@@ -34101,9 +34140,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="196"/>
-      <c r="B172" s="193"/>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A172" s="201"/>
+      <c r="B172" s="198"/>
       <c r="C172" s="53" t="s">
         <v>441</v>
       </c>
@@ -34111,9 +34150,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="196"/>
-      <c r="B173" s="193"/>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A173" s="201"/>
+      <c r="B173" s="198"/>
       <c r="C173" s="53" t="s">
         <v>442</v>
       </c>
@@ -34121,9 +34160,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="196"/>
-      <c r="B174" s="193"/>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A174" s="201"/>
+      <c r="B174" s="198"/>
       <c r="C174" s="53" t="s">
         <v>443</v>
       </c>
@@ -34131,9 +34170,9 @@
         <v>444</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="196"/>
-      <c r="B175" s="193"/>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A175" s="201"/>
+      <c r="B175" s="198"/>
       <c r="C175" s="53" t="s">
         <v>445</v>
       </c>
@@ -34141,9 +34180,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="196"/>
-      <c r="B176" s="193"/>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A176" s="201"/>
+      <c r="B176" s="198"/>
       <c r="C176" s="53" t="s">
         <v>446</v>
       </c>
@@ -34151,9 +34190,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="196"/>
-      <c r="B177" s="193"/>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A177" s="201"/>
+      <c r="B177" s="198"/>
       <c r="C177" s="53" t="s">
         <v>447</v>
       </c>
@@ -34161,9 +34200,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A178" s="196"/>
-      <c r="B178" s="193"/>
+    <row r="178" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A178" s="201"/>
+      <c r="B178" s="198"/>
       <c r="C178" s="95" t="s">
         <v>448</v>
       </c>
@@ -34171,9 +34210,9 @@
         <v>449</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A179" s="196"/>
-      <c r="B179" s="193"/>
+    <row r="179" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A179" s="201"/>
+      <c r="B179" s="198"/>
       <c r="C179" s="56" t="s">
         <v>450</v>
       </c>
@@ -34181,9 +34220,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="196"/>
-      <c r="B180" s="193"/>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A180" s="201"/>
+      <c r="B180" s="198"/>
       <c r="C180" s="53" t="s">
         <v>451</v>
       </c>
@@ -34191,9 +34230,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="196"/>
-      <c r="B181" s="193"/>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A181" s="201"/>
+      <c r="B181" s="198"/>
       <c r="C181" s="53" t="s">
         <v>452</v>
       </c>
@@ -34201,9 +34240,9 @@
         <v>453</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" s="196"/>
-      <c r="B182" s="193"/>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A182" s="201"/>
+      <c r="B182" s="198"/>
       <c r="C182" s="53" t="s">
         <v>454</v>
       </c>
@@ -34211,9 +34250,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="196"/>
-      <c r="B183" s="193"/>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A183" s="201"/>
+      <c r="B183" s="198"/>
       <c r="C183" s="53" t="s">
         <v>438</v>
       </c>
@@ -34221,9 +34260,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="196"/>
-      <c r="B184" s="193"/>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A184" s="201"/>
+      <c r="B184" s="198"/>
       <c r="C184" s="53" t="s">
         <v>455</v>
       </c>
@@ -34231,9 +34270,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="196"/>
-      <c r="B185" s="193"/>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A185" s="201"/>
+      <c r="B185" s="198"/>
       <c r="C185" s="53" t="s">
         <v>443</v>
       </c>
@@ -34241,9 +34280,9 @@
         <v>456</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="196"/>
-      <c r="B186" s="193"/>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A186" s="201"/>
+      <c r="B186" s="198"/>
       <c r="C186" s="53" t="s">
         <v>457</v>
       </c>
@@ -34251,17 +34290,17 @@
         <v>249</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A187" s="196"/>
-      <c r="B187" s="193"/>
+    <row r="187" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A187" s="201"/>
+      <c r="B187" s="198"/>
       <c r="C187" s="53"/>
       <c r="D187" s="81" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="196"/>
-      <c r="B188" s="193"/>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A188" s="201"/>
+      <c r="B188" s="198"/>
       <c r="C188" s="53" t="s">
         <v>459</v>
       </c>
@@ -34269,9 +34308,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="196"/>
-      <c r="B189" s="193"/>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A189" s="201"/>
+      <c r="B189" s="198"/>
       <c r="C189" s="53" t="s">
         <v>438</v>
       </c>
@@ -34279,9 +34318,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="196"/>
-      <c r="B190" s="193"/>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A190" s="201"/>
+      <c r="B190" s="198"/>
       <c r="C190" s="53" t="s">
         <v>460</v>
       </c>
@@ -34289,9 +34328,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="196"/>
-      <c r="B191" s="193"/>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A191" s="201"/>
+      <c r="B191" s="198"/>
       <c r="C191" s="53" t="s">
         <v>461</v>
       </c>
@@ -34299,9 +34338,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="196"/>
-      <c r="B192" s="193"/>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A192" s="201"/>
+      <c r="B192" s="198"/>
       <c r="C192" s="53" t="s">
         <v>462</v>
       </c>
@@ -34309,9 +34348,9 @@
         <v>463</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A193" s="196"/>
-      <c r="B193" s="193"/>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A193" s="201"/>
+      <c r="B193" s="198"/>
       <c r="C193" s="53" t="s">
         <v>464</v>
       </c>
@@ -34319,9 +34358,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A194" s="196"/>
-      <c r="B194" s="193"/>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A194" s="201"/>
+      <c r="B194" s="198"/>
       <c r="C194" s="53" t="s">
         <v>465</v>
       </c>
@@ -34329,9 +34368,9 @@
         <v>466</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="196"/>
-      <c r="B195" s="193"/>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A195" s="201"/>
+      <c r="B195" s="198"/>
       <c r="C195" s="53" t="s">
         <v>467</v>
       </c>
@@ -34339,9 +34378,9 @@
         <v>468</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A196" s="196"/>
-      <c r="B196" s="193"/>
+    <row r="196" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A196" s="201"/>
+      <c r="B196" s="198"/>
       <c r="C196" s="85" t="s">
         <v>469</v>
       </c>
@@ -34349,9 +34388,9 @@
         <v>470</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="196"/>
-      <c r="B197" s="193"/>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A197" s="201"/>
+      <c r="B197" s="198"/>
       <c r="C197" s="53" t="s">
         <v>471</v>
       </c>
@@ -34359,9 +34398,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" s="196"/>
-      <c r="B198" s="193"/>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A198" s="201"/>
+      <c r="B198" s="198"/>
       <c r="C198" s="53" t="s">
         <v>472</v>
       </c>
@@ -34369,9 +34408,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" s="196"/>
-      <c r="B199" s="193"/>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A199" s="201"/>
+      <c r="B199" s="198"/>
       <c r="C199" s="53" t="s">
         <v>473</v>
       </c>
@@ -34379,9 +34418,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A200" s="196"/>
-      <c r="B200" s="193"/>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A200" s="201"/>
+      <c r="B200" s="198"/>
       <c r="C200" s="53" t="s">
         <v>474</v>
       </c>
@@ -34389,9 +34428,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" s="196"/>
-      <c r="B201" s="193"/>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A201" s="201"/>
+      <c r="B201" s="198"/>
       <c r="C201" s="53" t="s">
         <v>475</v>
       </c>
@@ -34399,9 +34438,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A202" s="196"/>
-      <c r="B202" s="193"/>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A202" s="201"/>
+      <c r="B202" s="198"/>
       <c r="C202" s="53" t="s">
         <v>473</v>
       </c>
@@ -34409,9 +34448,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A203" s="196"/>
-      <c r="B203" s="193"/>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A203" s="201"/>
+      <c r="B203" s="198"/>
       <c r="C203" s="92" t="s">
         <v>476</v>
       </c>
@@ -34419,9 +34458,9 @@
         <v>477</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A204" s="196"/>
-      <c r="B204" s="193"/>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A204" s="201"/>
+      <c r="B204" s="198"/>
       <c r="C204" s="53" t="s">
         <v>478</v>
       </c>
@@ -34429,9 +34468,9 @@
         <v>479</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A205" s="196"/>
-      <c r="B205" s="193"/>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A205" s="201"/>
+      <c r="B205" s="198"/>
       <c r="C205" s="53" t="s">
         <v>480</v>
       </c>
@@ -34439,9 +34478,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A206" s="196"/>
-      <c r="B206" s="193"/>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A206" s="201"/>
+      <c r="B206" s="198"/>
       <c r="C206" s="53" t="s">
         <v>482</v>
       </c>
@@ -34449,9 +34488,9 @@
         <v>483</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A207" s="196"/>
-      <c r="B207" s="193"/>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A207" s="201"/>
+      <c r="B207" s="198"/>
       <c r="C207" s="53" t="s">
         <v>484</v>
       </c>
@@ -34459,9 +34498,9 @@
         <v>483</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A208" s="196"/>
-      <c r="B208" s="193"/>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A208" s="201"/>
+      <c r="B208" s="198"/>
       <c r="C208" s="53" t="s">
         <v>485</v>
       </c>
@@ -34469,9 +34508,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A209" s="196"/>
-      <c r="B209" s="193"/>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A209" s="201"/>
+      <c r="B209" s="198"/>
       <c r="C209" s="53" t="s">
         <v>486</v>
       </c>
@@ -34479,9 +34518,9 @@
         <v>346</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A210" s="196"/>
-      <c r="B210" s="193"/>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A210" s="201"/>
+      <c r="B210" s="198"/>
       <c r="C210" s="53" t="s">
         <v>487</v>
       </c>
@@ -34489,9 +34528,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A211" s="196"/>
-      <c r="B211" s="193"/>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A211" s="201"/>
+      <c r="B211" s="198"/>
       <c r="C211" s="53" t="s">
         <v>488</v>
       </c>
@@ -34499,9 +34538,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A212" s="196"/>
-      <c r="B212" s="193"/>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A212" s="201"/>
+      <c r="B212" s="198"/>
       <c r="C212" s="53" t="s">
         <v>489</v>
       </c>
@@ -34509,9 +34548,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A213" s="196"/>
-      <c r="B213" s="193"/>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A213" s="201"/>
+      <c r="B213" s="198"/>
       <c r="C213" s="53" t="s">
         <v>490</v>
       </c>
@@ -34519,9 +34558,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A214" s="196"/>
-      <c r="B214" s="193"/>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A214" s="201"/>
+      <c r="B214" s="198"/>
       <c r="C214" s="53" t="s">
         <v>491</v>
       </c>
@@ -34529,9 +34568,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A215" s="196"/>
-      <c r="B215" s="193"/>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A215" s="201"/>
+      <c r="B215" s="198"/>
       <c r="C215" s="53" t="s">
         <v>492</v>
       </c>
@@ -34539,9 +34578,9 @@
         <v>493</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A216" s="196"/>
-      <c r="B216" s="193"/>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A216" s="201"/>
+      <c r="B216" s="198"/>
       <c r="C216" s="53" t="s">
         <v>494</v>
       </c>
@@ -34549,9 +34588,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A217" s="196"/>
-      <c r="B217" s="193"/>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A217" s="201"/>
+      <c r="B217" s="198"/>
       <c r="C217" s="53" t="s">
         <v>490</v>
       </c>
@@ -34559,9 +34598,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A218" s="196"/>
-      <c r="B218" s="193"/>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A218" s="201"/>
+      <c r="B218" s="198"/>
       <c r="C218" s="53" t="s">
         <v>495</v>
       </c>
@@ -34569,9 +34608,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A219" s="196"/>
-      <c r="B219" s="193"/>
+    <row r="219" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A219" s="201"/>
+      <c r="B219" s="198"/>
       <c r="C219" s="56" t="s">
         <v>496</v>
       </c>
@@ -34579,9 +34618,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A220" s="197"/>
-      <c r="B220" s="194"/>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A220" s="202"/>
+      <c r="B220" s="199"/>
       <c r="C220" s="56" t="s">
         <v>465</v>
       </c>
@@ -34589,11 +34628,11 @@
         <v>466</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A221" s="195" t="s">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A221" s="200" t="s">
         <v>497</v>
       </c>
-      <c r="B221" s="192" t="s">
+      <c r="B221" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C221" s="53" t="s">
@@ -34603,9 +34642,9 @@
         <v>498</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A222" s="196"/>
-      <c r="B222" s="193"/>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A222" s="201"/>
+      <c r="B222" s="198"/>
       <c r="C222" s="92" t="s">
         <v>499</v>
       </c>
@@ -34613,9 +34652,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A223" s="197"/>
-      <c r="B223" s="194"/>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A223" s="202"/>
+      <c r="B223" s="199"/>
       <c r="C223" s="53" t="s">
         <v>500</v>
       </c>
@@ -34623,7 +34662,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" s="90" t="s">
         <v>501</v>
       </c>
@@ -34637,7 +34676,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="90" t="s">
         <v>502</v>
       </c>
@@ -34651,7 +34690,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" s="87" t="s">
         <v>44</v>
       </c>
@@ -34659,11 +34698,11 @@
       <c r="C226" s="87"/>
       <c r="D226" s="88"/>
     </row>
-    <row r="227" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="169" t="s">
+    <row r="227" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A227" s="174" t="s">
         <v>156</v>
       </c>
-      <c r="B227" s="192" t="s">
+      <c r="B227" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C227" s="53"/>
@@ -34671,9 +34710,9 @@
         <v>333</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A228" s="210"/>
-      <c r="B228" s="193"/>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A228" s="215"/>
+      <c r="B228" s="198"/>
       <c r="C228" s="65" t="s">
         <v>503</v>
       </c>
@@ -34681,9 +34720,9 @@
         <v>504</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A229" s="210"/>
-      <c r="B229" s="193"/>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A229" s="215"/>
+      <c r="B229" s="198"/>
       <c r="C229" s="65">
         <v>10.1</v>
       </c>
@@ -34691,9 +34730,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A230" s="210"/>
-      <c r="B230" s="193"/>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A230" s="215"/>
+      <c r="B230" s="198"/>
       <c r="C230" s="65">
         <v>10.199999999999999</v>
       </c>
@@ -34701,9 +34740,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A231" s="210"/>
-      <c r="B231" s="193"/>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A231" s="215"/>
+      <c r="B231" s="198"/>
       <c r="C231" s="82" t="s">
         <v>506</v>
       </c>
@@ -34711,9 +34750,9 @@
         <v>507</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A232" s="210"/>
-      <c r="B232" s="193"/>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A232" s="215"/>
+      <c r="B232" s="198"/>
       <c r="C232" s="82" t="s">
         <v>508</v>
       </c>
@@ -34721,9 +34760,9 @@
         <v>509</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A233" s="210"/>
-      <c r="B233" s="193"/>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A233" s="215"/>
+      <c r="B233" s="198"/>
       <c r="C233" s="82" t="s">
         <v>166</v>
       </c>
@@ -34731,9 +34770,9 @@
         <v>510</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A234" s="210"/>
-      <c r="B234" s="193"/>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A234" s="215"/>
+      <c r="B234" s="198"/>
       <c r="C234" s="82" t="s">
         <v>511</v>
       </c>
@@ -34741,9 +34780,9 @@
         <v>512</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A235" s="210"/>
-      <c r="B235" s="193"/>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A235" s="215"/>
+      <c r="B235" s="198"/>
       <c r="C235" s="82" t="s">
         <v>60</v>
       </c>
@@ -34751,9 +34790,9 @@
         <v>513</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A236" s="210"/>
-      <c r="B236" s="193"/>
+    <row r="236" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A236" s="215"/>
+      <c r="B236" s="198"/>
       <c r="C236" s="82" t="s">
         <v>514</v>
       </c>
@@ -34761,9 +34800,9 @@
         <v>515</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A237" s="170"/>
-      <c r="B237" s="194"/>
+    <row r="237" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A237" s="175"/>
+      <c r="B237" s="199"/>
       <c r="C237" s="82" t="s">
         <v>514</v>
       </c>
@@ -34771,11 +34810,11 @@
         <v>516</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A238" s="169" t="s">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A238" s="174" t="s">
         <v>517</v>
       </c>
-      <c r="B238" s="192" t="s">
+      <c r="B238" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C238" s="82"/>
@@ -34783,9 +34822,9 @@
         <v>333</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A239" s="210"/>
-      <c r="B239" s="193"/>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A239" s="215"/>
+      <c r="B239" s="198"/>
       <c r="C239" s="62" t="s">
         <v>518</v>
       </c>
@@ -34793,7 +34832,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="61" t="s">
         <v>520</v>
       </c>
@@ -34807,7 +34846,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" s="98" t="s">
         <v>72</v>
       </c>
@@ -34815,11 +34854,11 @@
       <c r="C241" s="98"/>
       <c r="D241" s="98"/>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A242" s="169" t="s">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A242" s="174" t="s">
         <v>74</v>
       </c>
-      <c r="B242" s="192" t="s">
+      <c r="B242" s="197" t="s">
         <v>522</v>
       </c>
       <c r="C242" s="99" t="s">
@@ -34829,9 +34868,9 @@
         <v>523</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A243" s="210"/>
-      <c r="B243" s="193"/>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A243" s="215"/>
+      <c r="B243" s="198"/>
       <c r="C243" s="99" t="s">
         <v>257</v>
       </c>
@@ -34839,19 +34878,19 @@
         <v>524</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="170"/>
-      <c r="B244" s="194"/>
+    <row r="244" spans="1:4" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A244" s="175"/>
+      <c r="B244" s="199"/>
       <c r="C244" s="53"/>
       <c r="D244" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A245" s="208" t="s">
+    <row r="245" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A245" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="B245" s="192" t="s">
+      <c r="B245" s="197" t="s">
         <v>522</v>
       </c>
       <c r="C245" s="56" t="s">
@@ -34861,19 +34900,19 @@
         <v>144</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A246" s="209"/>
-      <c r="B246" s="194"/>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A246" s="214"/>
+      <c r="B246" s="199"/>
       <c r="C246" s="56"/>
       <c r="D246" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A247" s="208" t="s">
+    <row r="247" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A247" s="213" t="s">
         <v>527</v>
       </c>
-      <c r="B247" s="192" t="s">
+      <c r="B247" s="197" t="s">
         <v>522</v>
       </c>
       <c r="C247" s="56"/>
@@ -34881,19 +34920,19 @@
         <v>528</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A248" s="209"/>
-      <c r="B248" s="194"/>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A248" s="214"/>
+      <c r="B248" s="199"/>
       <c r="C248" s="53"/>
       <c r="D248" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A249" s="208" t="s">
+    <row r="249" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A249" s="213" t="s">
         <v>76</v>
       </c>
-      <c r="B249" s="192" t="s">
+      <c r="B249" s="197" t="s">
         <v>522</v>
       </c>
       <c r="C249" s="56" t="s">
@@ -34903,15 +34942,15 @@
         <v>529</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A250" s="209"/>
-      <c r="B250" s="194"/>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A250" s="214"/>
+      <c r="B250" s="199"/>
       <c r="C250" s="53"/>
       <c r="D250" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" s="98" t="s">
         <v>530</v>
       </c>
@@ -34919,7 +34958,7 @@
       <c r="C251" s="98"/>
       <c r="D251" s="98"/>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" s="53"/>
       <c r="B252" s="65" t="s">
         <v>244</v>
@@ -34931,7 +34970,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" s="98" t="s">
         <v>531</v>
       </c>
@@ -34939,7 +34978,7 @@
       <c r="C253" s="98"/>
       <c r="D253" s="98"/>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" s="53"/>
       <c r="B254" s="65" t="s">
         <v>244</v>
@@ -34951,7 +34990,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" s="53"/>
       <c r="B255" s="65"/>
       <c r="C255" s="53" t="s">
@@ -34961,13 +35000,13 @@
         <v>533</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B256" s="115"/>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B257" s="115"/>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" s="62" t="s">
         <v>13</v>
       </c>
@@ -34979,7 +35018,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" s="62" t="s">
         <v>369</v>
       </c>
@@ -34991,7 +35030,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" s="62" t="s">
         <v>36</v>
       </c>
@@ -35003,7 +35042,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" s="62" t="s">
         <v>535</v>
       </c>
@@ -35015,7 +35054,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" s="62" t="s">
         <v>536</v>
       </c>
@@ -35027,7 +35066,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" s="62" t="s">
         <v>537</v>
       </c>
@@ -35039,7 +35078,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" s="62" t="s">
         <v>538</v>
       </c>
@@ -35053,7 +35092,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" s="62" t="s">
         <v>369</v>
       </c>
@@ -35067,7 +35106,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" s="62" t="s">
         <v>36</v>
       </c>
@@ -35081,7 +35120,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" s="62" t="s">
         <v>542</v>
       </c>
@@ -35095,7 +35134,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" s="53" t="s">
         <v>36</v>
       </c>
@@ -35109,7 +35148,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" s="90" t="s">
         <v>535</v>
       </c>
@@ -35123,7 +35162,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" s="90" t="s">
         <v>703</v>
       </c>
@@ -35137,7 +35176,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" s="90" t="s">
         <v>705</v>
       </c>
@@ -35152,7 +35191,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" s="90" t="s">
         <v>707</v>
       </c>
@@ -35167,7 +35206,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" s="90" t="s">
         <v>287</v>
       </c>
@@ -35182,7 +35221,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" s="90" t="s">
         <v>714</v>
       </c>
@@ -35197,7 +35236,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" s="90" t="s">
         <v>715</v>
       </c>
@@ -35212,12 +35251,12 @@
         <v>713</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A276" s="56" t="s">
         <v>721</v>
       </c>
       <c r="B276" s="138" t="str">
-        <f t="shared" ref="B276:B277" si="0">$B$270</f>
+        <f t="shared" ref="B276:B279" si="0">$B$270</f>
         <v>PIT Next Version</v>
       </c>
       <c r="C276" s="90" t="s">
@@ -35227,7 +35266,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" s="53" t="s">
         <v>722</v>
       </c>
@@ -35240,6 +35279,78 @@
       </c>
       <c r="D277" s="90" t="s">
         <v>719</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A278" s="144" t="s">
+        <v>723</v>
+      </c>
+      <c r="B278" s="142" t="str">
+        <f t="shared" si="0"/>
+        <v>PIT Next Version</v>
+      </c>
+      <c r="C278" t="s">
+        <v>724</v>
+      </c>
+      <c r="D278" s="144" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A279" s="56" t="s">
+        <v>721</v>
+      </c>
+      <c r="B279" s="141" t="str">
+        <f t="shared" si="0"/>
+        <v>PIT Next Version</v>
+      </c>
+      <c r="C279" s="222" t="s">
+        <v>727</v>
+      </c>
+      <c r="D279" s="62" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A280" s="62" t="s">
+        <v>538</v>
+      </c>
+      <c r="B280" s="143" t="s">
+        <v>244</v>
+      </c>
+      <c r="C280" s="53" t="s">
+        <v>729</v>
+      </c>
+      <c r="D280" s="53" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A281" s="62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B281" s="143" t="s">
+        <v>244</v>
+      </c>
+      <c r="C281" s="222" t="s">
+        <v>727</v>
+      </c>
+      <c r="D281" s="53" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A282" s="90" t="s">
+        <v>535</v>
+      </c>
+      <c r="B282" s="141" t="s">
+        <v>244</v>
+      </c>
+      <c r="C282" s="222" t="s">
+        <v>727</v>
+      </c>
+      <c r="D282" s="62" t="s">
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -35319,15 +35430,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DBC65A-63D2-46B3-B8B5-A94A70B9EDFE}">
   <dimension ref="A1:D155"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="52.7109375" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="3" width="85.42578125" customWidth="1"/>
-    <col min="4" max="4" width="128.42578125" customWidth="1"/>
+    <col min="1" max="1" width="52.7265625" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" customWidth="1"/>
+    <col min="3" max="3" width="85.453125" customWidth="1"/>
+    <col min="4" max="4" width="128.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -35341,11 +35452,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="192" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="197" t="s">
         <v>369</v>
       </c>
-      <c r="B2" s="192" t="s">
+      <c r="B2" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C2" s="53" t="s">
@@ -35355,9 +35466,9 @@
         <v>546</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="193"/>
-      <c r="B3" s="193"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="198"/>
+      <c r="B3" s="198"/>
       <c r="C3" s="53" t="s">
         <v>547</v>
       </c>
@@ -35365,9 +35476,9 @@
         <v>548</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="193"/>
-      <c r="B4" s="193"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="198"/>
+      <c r="B4" s="198"/>
       <c r="C4" s="53" t="s">
         <v>549</v>
       </c>
@@ -35375,9 +35486,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="193"/>
-      <c r="B5" s="193"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="198"/>
+      <c r="B5" s="198"/>
       <c r="C5" s="53" t="s">
         <v>551</v>
       </c>
@@ -35385,9 +35496,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="193"/>
-      <c r="B6" s="193"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="198"/>
+      <c r="B6" s="198"/>
       <c r="C6" s="53" t="s">
         <v>552</v>
       </c>
@@ -35395,9 +35506,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="193"/>
-      <c r="B7" s="193"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="198"/>
+      <c r="B7" s="198"/>
       <c r="C7" s="53" t="s">
         <v>553</v>
       </c>
@@ -35405,9 +35516,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="193"/>
-      <c r="B8" s="193"/>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="198"/>
+      <c r="B8" s="198"/>
       <c r="C8" s="53" t="s">
         <v>554</v>
       </c>
@@ -35415,9 +35526,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="193"/>
-      <c r="B9" s="193"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="198"/>
+      <c r="B9" s="198"/>
       <c r="C9" s="53" t="s">
         <v>555</v>
       </c>
@@ -35425,9 +35536,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="193"/>
-      <c r="B10" s="193"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="198"/>
+      <c r="B10" s="198"/>
       <c r="C10" s="53" t="s">
         <v>556</v>
       </c>
@@ -35435,9 +35546,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="193"/>
-      <c r="B11" s="193"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="198"/>
+      <c r="B11" s="198"/>
       <c r="C11" s="53" t="s">
         <v>557</v>
       </c>
@@ -35445,9 +35556,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="193"/>
-      <c r="B12" s="193"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="198"/>
+      <c r="B12" s="198"/>
       <c r="C12" s="53" t="s">
         <v>558</v>
       </c>
@@ -35455,9 +35566,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="193"/>
-      <c r="B13" s="193"/>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="198"/>
+      <c r="B13" s="198"/>
       <c r="C13" s="53" t="s">
         <v>559</v>
       </c>
@@ -35465,9 +35576,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="193"/>
-      <c r="B14" s="193"/>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="198"/>
+      <c r="B14" s="198"/>
       <c r="C14" s="53" t="s">
         <v>560</v>
       </c>
@@ -35475,9 +35586,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="193"/>
-      <c r="B15" s="193"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="198"/>
+      <c r="B15" s="198"/>
       <c r="C15" s="53" t="s">
         <v>561</v>
       </c>
@@ -35485,9 +35596,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="193"/>
-      <c r="B16" s="193"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="198"/>
+      <c r="B16" s="198"/>
       <c r="C16" s="53" t="s">
         <v>562</v>
       </c>
@@ -35495,9 +35606,9 @@
         <v>563</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="193"/>
-      <c r="B17" s="193"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="198"/>
+      <c r="B17" s="198"/>
       <c r="C17" s="53" t="s">
         <v>564</v>
       </c>
@@ -35505,9 +35616,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="193"/>
-      <c r="B18" s="193"/>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="198"/>
+      <c r="B18" s="198"/>
       <c r="C18" s="56" t="s">
         <v>565</v>
       </c>
@@ -35515,9 +35626,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="193"/>
-      <c r="B19" s="193"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="198"/>
+      <c r="B19" s="198"/>
       <c r="C19" s="53" t="s">
         <v>566</v>
       </c>
@@ -35525,9 +35636,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="194"/>
-      <c r="B20" s="194"/>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="199"/>
+      <c r="B20" s="199"/>
       <c r="C20" s="56" t="s">
         <v>567</v>
       </c>
@@ -35535,11 +35646,11 @@
         <v>550</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="159" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="164" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="178" t="s">
+      <c r="B21" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C21" s="53" t="s">
@@ -35549,9 +35660,9 @@
         <v>546</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="159"/>
-      <c r="B22" s="178"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="164"/>
+      <c r="B22" s="183"/>
       <c r="C22" s="53" t="s">
         <v>547</v>
       </c>
@@ -35559,9 +35670,9 @@
         <v>548</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="159"/>
-      <c r="B23" s="178"/>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="164"/>
+      <c r="B23" s="183"/>
       <c r="C23" s="53" t="s">
         <v>549</v>
       </c>
@@ -35569,9 +35680,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="159"/>
-      <c r="B24" s="178"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="164"/>
+      <c r="B24" s="183"/>
       <c r="C24" s="53" t="s">
         <v>551</v>
       </c>
@@ -35579,9 +35690,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="159"/>
-      <c r="B25" s="178"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="164"/>
+      <c r="B25" s="183"/>
       <c r="C25" s="53" t="s">
         <v>552</v>
       </c>
@@ -35589,9 +35700,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="159"/>
-      <c r="B26" s="178"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="164"/>
+      <c r="B26" s="183"/>
       <c r="C26" s="53" t="s">
         <v>553</v>
       </c>
@@ -35599,9 +35710,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="159"/>
-      <c r="B27" s="178"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="164"/>
+      <c r="B27" s="183"/>
       <c r="C27" s="53" t="s">
         <v>554</v>
       </c>
@@ -35609,9 +35720,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="159"/>
-      <c r="B28" s="178"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="164"/>
+      <c r="B28" s="183"/>
       <c r="C28" s="53" t="s">
         <v>555</v>
       </c>
@@ -35619,9 +35730,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="159"/>
-      <c r="B29" s="178"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="164"/>
+      <c r="B29" s="183"/>
       <c r="C29" s="53" t="s">
         <v>556</v>
       </c>
@@ -35629,9 +35740,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="159"/>
-      <c r="B30" s="178"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="164"/>
+      <c r="B30" s="183"/>
       <c r="C30" s="53" t="s">
         <v>557</v>
       </c>
@@ -35639,9 +35750,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="159"/>
-      <c r="B31" s="178"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="164"/>
+      <c r="B31" s="183"/>
       <c r="C31" s="53" t="s">
         <v>558</v>
       </c>
@@ -35649,9 +35760,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="159"/>
-      <c r="B32" s="178"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="164"/>
+      <c r="B32" s="183"/>
       <c r="C32" s="53" t="s">
         <v>559</v>
       </c>
@@ -35659,9 +35770,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="159"/>
-      <c r="B33" s="178"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="164"/>
+      <c r="B33" s="183"/>
       <c r="C33" s="53" t="s">
         <v>560</v>
       </c>
@@ -35669,9 +35780,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="159"/>
-      <c r="B34" s="178"/>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="164"/>
+      <c r="B34" s="183"/>
       <c r="C34" s="53" t="s">
         <v>561</v>
       </c>
@@ -35679,9 +35790,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="159"/>
-      <c r="B35" s="178"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="164"/>
+      <c r="B35" s="183"/>
       <c r="C35" s="53" t="s">
         <v>562</v>
       </c>
@@ -35689,9 +35800,9 @@
         <v>563</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="159"/>
-      <c r="B36" s="178"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="164"/>
+      <c r="B36" s="183"/>
       <c r="C36" s="53" t="s">
         <v>564</v>
       </c>
@@ -35699,9 +35810,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="159"/>
-      <c r="B37" s="178"/>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="164"/>
+      <c r="B37" s="183"/>
       <c r="C37" s="56" t="s">
         <v>565</v>
       </c>
@@ -35709,9 +35820,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="159"/>
-      <c r="B38" s="178"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="164"/>
+      <c r="B38" s="183"/>
       <c r="C38" s="53" t="s">
         <v>566</v>
       </c>
@@ -35719,9 +35830,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="159"/>
-      <c r="B39" s="178"/>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="164"/>
+      <c r="B39" s="183"/>
       <c r="C39" s="56" t="s">
         <v>567</v>
       </c>
@@ -35729,11 +35840,11 @@
         <v>550</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="192" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="197" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="192" t="s">
+      <c r="B40" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C40" s="90" t="s">
@@ -35743,9 +35854,9 @@
         <v>569</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="193"/>
-      <c r="B41" s="193"/>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="198"/>
+      <c r="B41" s="198"/>
       <c r="C41" s="53" t="s">
         <v>570</v>
       </c>
@@ -35753,9 +35864,9 @@
         <v>571</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="193"/>
-      <c r="B42" s="193"/>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="198"/>
+      <c r="B42" s="198"/>
       <c r="C42" s="53" t="s">
         <v>572</v>
       </c>
@@ -35763,7 +35874,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="90" t="s">
         <v>574</v>
       </c>
@@ -35775,11 +35886,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="192" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="197" t="s">
         <v>330</v>
       </c>
-      <c r="B44" s="192" t="s">
+      <c r="B44" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C44" s="90" t="s">
@@ -35789,9 +35900,9 @@
         <v>569</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="193"/>
-      <c r="B45" s="193"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="198"/>
+      <c r="B45" s="198"/>
       <c r="C45" s="90" t="s">
         <v>575</v>
       </c>
@@ -35799,9 +35910,9 @@
         <v>571</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="194"/>
-      <c r="B46" s="194"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="199"/>
+      <c r="B46" s="199"/>
       <c r="C46" s="90" t="s">
         <v>576</v>
       </c>
@@ -35809,7 +35920,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="62" t="s">
         <v>577</v>
       </c>
@@ -35821,7 +35932,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="62" t="s">
         <v>579</v>
       </c>
@@ -35833,7 +35944,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="62" t="s">
         <v>328</v>
       </c>
@@ -35845,7 +35956,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="62" t="s">
         <v>581</v>
       </c>
@@ -35857,7 +35968,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="62" t="s">
         <v>582</v>
       </c>
@@ -35869,7 +35980,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="62" t="s">
         <v>583</v>
       </c>
@@ -35881,7 +35992,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="62" t="s">
         <v>535</v>
       </c>
@@ -35893,7 +36004,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="62" t="s">
         <v>583</v>
       </c>
@@ -35907,7 +36018,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="62" t="s">
         <v>583</v>
       </c>
@@ -35921,7 +36032,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="62" t="s">
         <v>589</v>
       </c>
@@ -35933,7 +36044,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="62" t="s">
         <v>369</v>
       </c>
@@ -35947,7 +36058,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="62" t="s">
         <v>36</v>
       </c>
@@ -35961,7 +36072,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="62" t="s">
         <v>593</v>
       </c>
@@ -35973,7 +36084,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="62" t="s">
         <v>583</v>
       </c>
@@ -35985,7 +36096,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="90" t="s">
         <v>574</v>
       </c>
@@ -35997,7 +36108,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="62" t="s">
         <v>596</v>
       </c>
@@ -36009,7 +36120,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="62" t="s">
         <v>205</v>
       </c>
@@ -36021,7 +36132,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="62" t="s">
         <v>330</v>
       </c>
@@ -36033,7 +36144,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="62" t="s">
         <v>577</v>
       </c>
@@ -36045,11 +36156,11 @@
         <v>598</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="178" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="183" t="s">
         <v>579</v>
       </c>
-      <c r="B66" s="178" t="s">
+      <c r="B66" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C66" s="53" t="s">
@@ -36059,9 +36170,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="178"/>
-      <c r="B67" s="178"/>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="183"/>
+      <c r="B67" s="183"/>
       <c r="C67" s="53" t="s">
         <v>601</v>
       </c>
@@ -36069,9 +36180,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="178"/>
-      <c r="B68" s="178"/>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="183"/>
+      <c r="B68" s="183"/>
       <c r="C68" s="53" t="s">
         <v>602</v>
       </c>
@@ -36079,9 +36190,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="178"/>
-      <c r="B69" s="178"/>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="183"/>
+      <c r="B69" s="183"/>
       <c r="C69" s="53" t="s">
         <v>603</v>
       </c>
@@ -36089,9 +36200,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="178"/>
-      <c r="B70" s="178"/>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="183"/>
+      <c r="B70" s="183"/>
       <c r="C70" s="53" t="s">
         <v>604</v>
       </c>
@@ -36099,7 +36210,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="62" t="s">
         <v>328</v>
       </c>
@@ -36111,7 +36222,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="62" t="s">
         <v>582</v>
       </c>
@@ -36123,11 +36234,11 @@
         <v>606</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="178" t="s">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="183" t="s">
         <v>369</v>
       </c>
-      <c r="B73" s="178" t="s">
+      <c r="B73" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C73" s="53"/>
@@ -36135,9 +36246,9 @@
         <v>597</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="178"/>
-      <c r="B74" s="178"/>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="183"/>
+      <c r="B74" s="183"/>
       <c r="C74" s="53" t="s">
         <v>599</v>
       </c>
@@ -36145,9 +36256,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="178"/>
-      <c r="B75" s="178"/>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="183"/>
+      <c r="B75" s="183"/>
       <c r="C75" s="53" t="s">
         <v>601</v>
       </c>
@@ -36155,9 +36266,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="178"/>
-      <c r="B76" s="178"/>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="183"/>
+      <c r="B76" s="183"/>
       <c r="C76" s="53" t="s">
         <v>602</v>
       </c>
@@ -36165,9 +36276,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="178"/>
-      <c r="B77" s="178"/>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="183"/>
+      <c r="B77" s="183"/>
       <c r="C77" s="53" t="s">
         <v>603</v>
       </c>
@@ -36175,9 +36286,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="178"/>
-      <c r="B78" s="178"/>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="183"/>
+      <c r="B78" s="183"/>
       <c r="C78" s="53" t="s">
         <v>604</v>
       </c>
@@ -36185,9 +36296,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="178"/>
-      <c r="B79" s="178"/>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="183"/>
+      <c r="B79" s="183"/>
       <c r="C79" s="53" t="s">
         <v>607</v>
       </c>
@@ -36195,11 +36306,11 @@
         <v>550</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="178" t="s">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="183" t="s">
         <v>36</v>
       </c>
-      <c r="B80" s="178" t="s">
+      <c r="B80" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C80" s="53"/>
@@ -36207,9 +36318,9 @@
         <v>597</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="178"/>
-      <c r="B81" s="178"/>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="183"/>
+      <c r="B81" s="183"/>
       <c r="C81" s="53" t="s">
         <v>599</v>
       </c>
@@ -36217,9 +36328,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="178"/>
-      <c r="B82" s="178"/>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="183"/>
+      <c r="B82" s="183"/>
       <c r="C82" s="53" t="s">
         <v>601</v>
       </c>
@@ -36227,9 +36338,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="178"/>
-      <c r="B83" s="178"/>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="183"/>
+      <c r="B83" s="183"/>
       <c r="C83" s="53" t="s">
         <v>602</v>
       </c>
@@ -36237,9 +36348,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="178"/>
-      <c r="B84" s="178"/>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="183"/>
+      <c r="B84" s="183"/>
       <c r="C84" s="53" t="s">
         <v>603</v>
       </c>
@@ -36247,9 +36358,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="178"/>
-      <c r="B85" s="178"/>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="183"/>
+      <c r="B85" s="183"/>
       <c r="C85" s="53" t="s">
         <v>604</v>
       </c>
@@ -36257,9 +36368,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="178"/>
-      <c r="B86" s="178"/>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="183"/>
+      <c r="B86" s="183"/>
       <c r="C86" s="53" t="s">
         <v>607</v>
       </c>
@@ -36267,7 +36378,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="62" t="s">
         <v>535</v>
       </c>
@@ -36279,7 +36390,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="62" t="s">
         <v>583</v>
       </c>
@@ -36293,7 +36404,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="62" t="s">
         <v>610</v>
       </c>
@@ -36305,7 +36416,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="62" t="s">
         <v>611</v>
       </c>
@@ -36317,7 +36428,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="62" t="s">
         <v>613</v>
       </c>
@@ -36329,7 +36440,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="62" t="s">
         <v>615</v>
       </c>
@@ -36341,7 +36452,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="62" t="s">
         <v>617</v>
       </c>
@@ -36353,7 +36464,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="62" t="s">
         <v>619</v>
       </c>
@@ -36365,11 +36476,11 @@
         <v>620</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="192" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="197" t="s">
         <v>610</v>
       </c>
-      <c r="B95" s="192" t="s">
+      <c r="B95" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C95" s="53" t="s">
@@ -36379,9 +36490,9 @@
         <v>622</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="193"/>
-      <c r="B96" s="193"/>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="198"/>
+      <c r="B96" s="198"/>
       <c r="C96" s="53" t="s">
         <v>623</v>
       </c>
@@ -36389,9 +36500,9 @@
         <v>624</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="193"/>
-      <c r="B97" s="193"/>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="198"/>
+      <c r="B97" s="198"/>
       <c r="C97" s="53" t="s">
         <v>625</v>
       </c>
@@ -36399,9 +36510,9 @@
         <v>626</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="194"/>
-      <c r="B98" s="194"/>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="199"/>
+      <c r="B98" s="199"/>
       <c r="C98" s="53" t="s">
         <v>627</v>
       </c>
@@ -36409,7 +36520,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A99" s="65" t="s">
         <v>369</v>
       </c>
@@ -36423,7 +36534,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A100" s="65" t="s">
         <v>36</v>
       </c>
@@ -36437,7 +36548,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" s="53" t="s">
         <v>631</v>
       </c>
@@ -36451,11 +36562,11 @@
         <v>633</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="192" t="s">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" s="197" t="s">
         <v>369</v>
       </c>
-      <c r="B102" s="192" t="s">
+      <c r="B102" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C102" s="53" t="s">
@@ -36465,9 +36576,9 @@
         <v>635</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="193"/>
-      <c r="B103" s="193"/>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" s="198"/>
+      <c r="B103" s="198"/>
       <c r="C103" s="116" t="s">
         <v>557</v>
       </c>
@@ -36475,9 +36586,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="193"/>
-      <c r="B104" s="193"/>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" s="198"/>
+      <c r="B104" s="198"/>
       <c r="C104" s="53" t="s">
         <v>565</v>
       </c>
@@ -36485,9 +36596,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="194"/>
-      <c r="B105" s="194"/>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" s="199"/>
+      <c r="B105" s="199"/>
       <c r="C105" s="53" t="s">
         <v>564</v>
       </c>
@@ -36495,11 +36606,11 @@
         <v>637</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="192" t="s">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" s="197" t="s">
         <v>36</v>
       </c>
-      <c r="B106" s="192" t="s">
+      <c r="B106" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C106" s="53" t="s">
@@ -36509,9 +36620,9 @@
         <v>635</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="193"/>
-      <c r="B107" s="193"/>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" s="198"/>
+      <c r="B107" s="198"/>
       <c r="C107" s="116" t="s">
         <v>557</v>
       </c>
@@ -36519,9 +36630,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="193"/>
-      <c r="B108" s="193"/>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" s="198"/>
+      <c r="B108" s="198"/>
       <c r="C108" s="53" t="s">
         <v>565</v>
       </c>
@@ -36529,9 +36640,9 @@
         <v>636</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="194"/>
-      <c r="B109" s="194"/>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" s="199"/>
+      <c r="B109" s="199"/>
       <c r="C109" s="53" t="s">
         <v>564</v>
       </c>
@@ -36539,7 +36650,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="53" t="s">
         <v>535</v>
       </c>
@@ -36551,7 +36662,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="53" t="s">
         <v>328</v>
       </c>
@@ -36563,7 +36674,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" s="53" t="s">
         <v>579</v>
       </c>
@@ -36575,7 +36686,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" s="53" t="s">
         <v>535</v>
       </c>
@@ -36589,7 +36700,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="53" t="s">
         <v>579</v>
       </c>
@@ -36603,7 +36714,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" s="62" t="s">
         <v>639</v>
       </c>
@@ -36617,7 +36728,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" s="62" t="s">
         <v>369</v>
       </c>
@@ -36629,7 +36740,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" s="53" t="s">
         <v>36</v>
       </c>
@@ -36641,7 +36752,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" s="53" t="s">
         <v>643</v>
       </c>
@@ -36653,7 +36764,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" s="53" t="s">
         <v>619</v>
       </c>
@@ -36665,7 +36776,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" s="53" t="s">
         <v>646</v>
       </c>
@@ -36677,7 +36788,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="53" t="s">
         <v>535</v>
       </c>
@@ -36691,7 +36802,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" s="53" t="s">
         <v>582</v>
       </c>
@@ -36705,7 +36816,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="53" t="s">
         <v>579</v>
       </c>
@@ -36719,7 +36830,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="53" t="s">
         <v>36</v>
       </c>
@@ -36733,11 +36844,11 @@
         <v>512</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="178" t="s">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" s="183" t="s">
         <v>583</v>
       </c>
-      <c r="B125" s="178" t="s">
+      <c r="B125" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C125" s="89" t="s">
@@ -36747,9 +36858,9 @@
         <v>652</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="178"/>
-      <c r="B126" s="178"/>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" s="183"/>
+      <c r="B126" s="183"/>
       <c r="C126" s="53" t="s">
         <v>653</v>
       </c>
@@ -36757,9 +36868,9 @@
         <v>654</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="178"/>
-      <c r="B127" s="178"/>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" s="183"/>
+      <c r="B127" s="183"/>
       <c r="C127" s="53" t="s">
         <v>655</v>
       </c>
@@ -36767,9 +36878,9 @@
         <v>656</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="178"/>
-      <c r="B128" s="178"/>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" s="183"/>
+      <c r="B128" s="183"/>
       <c r="C128" s="53" t="s">
         <v>657</v>
       </c>
@@ -36777,9 +36888,9 @@
         <v>658</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="178"/>
-      <c r="B129" s="178"/>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" s="183"/>
+      <c r="B129" s="183"/>
       <c r="C129" s="53" t="s">
         <v>659</v>
       </c>
@@ -36787,7 +36898,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" s="53" t="s">
         <v>631</v>
       </c>
@@ -36801,7 +36912,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" s="121" t="s">
         <v>667</v>
       </c>
@@ -36815,8 +36926,8 @@
         <v>669</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="169" t="s">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" s="174" t="s">
         <v>663</v>
       </c>
       <c r="B132" s="117" t="s">
@@ -36829,8 +36940,8 @@
         <v>664</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="170"/>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" s="175"/>
       <c r="B133" s="118" t="s">
         <v>244</v>
       </c>
@@ -36841,7 +36952,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" s="53" t="s">
         <v>583</v>
       </c>
@@ -36855,7 +36966,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" s="121" t="s">
         <v>631</v>
       </c>
@@ -36869,7 +36980,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="136" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A136" s="53" t="s">
         <v>674</v>
       </c>
@@ -36883,7 +36994,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="137" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A137" s="53" t="s">
         <v>674</v>
       </c>
@@ -36897,11 +37008,11 @@
         <v>677</v>
       </c>
     </row>
-    <row r="138" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="178" t="s">
+    <row r="138" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="183" t="s">
         <v>574</v>
       </c>
-      <c r="B138" s="178" t="s">
+      <c r="B138" s="183" t="s">
         <v>244</v>
       </c>
       <c r="C138" s="53" t="s">
@@ -36911,9 +37022,9 @@
         <v>685</v>
       </c>
     </row>
-    <row r="139" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="178"/>
-      <c r="B139" s="178"/>
+    <row r="139" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="183"/>
+      <c r="B139" s="183"/>
       <c r="C139" s="53" t="s">
         <v>684</v>
       </c>
@@ -36921,7 +37032,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="140" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" s="125" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A140" s="62" t="s">
         <v>593</v>
       </c>
@@ -36935,11 +37046,11 @@
         <v>680</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="169" t="s">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" s="174" t="s">
         <v>681</v>
       </c>
-      <c r="B141" s="192" t="s">
+      <c r="B141" s="197" t="s">
         <v>244</v>
       </c>
       <c r="C141" s="53" t="s">
@@ -36949,9 +37060,9 @@
         <v>683</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="170"/>
-      <c r="B142" s="194"/>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" s="175"/>
+      <c r="B142" s="199"/>
       <c r="C142" s="53" t="s">
         <v>686</v>
       </c>
@@ -36959,7 +37070,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" s="53" t="s">
         <v>579</v>
       </c>
@@ -36973,7 +37084,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" s="53" t="s">
         <v>328</v>
       </c>
@@ -36987,7 +37098,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A145" s="53" t="s">
         <v>535</v>
       </c>
@@ -37001,7 +37112,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A146" s="53" t="s">
         <v>36</v>
       </c>
@@ -37015,7 +37126,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A147" s="53" t="s">
         <v>369</v>
       </c>
@@ -37029,7 +37140,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" s="62" t="s">
         <v>639</v>
       </c>
@@ -37043,7 +37154,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" s="53" t="s">
         <v>696</v>
       </c>
@@ -37057,7 +37168,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" s="90" t="s">
         <v>681</v>
       </c>
@@ -37071,7 +37182,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" s="90" t="s">
         <v>681</v>
       </c>
@@ -37085,7 +37196,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" s="90" t="s">
         <v>681</v>
       </c>
@@ -37099,7 +37210,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" s="90" t="s">
         <v>681</v>
       </c>
@@ -37113,8 +37224,8 @@
         <v>717</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A154" s="217" t="s">
+    <row r="154" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A154" s="140" t="s">
         <v>718</v>
       </c>
       <c r="B154" s="138" t="s">
@@ -37127,7 +37238,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" s="56" t="s">
         <v>720</v>
       </c>
